--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="2244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="2245">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697328567505</t>
+    <t xml:space="preserve">2.23697376251221</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22277069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23223900794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21685290336609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20146584510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23460602760315</t>
+    <t xml:space="preserve">2.27958297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22277045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21685242652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20146608352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23460650444031</t>
   </si>
   <si>
     <t xml:space="preserve">2.21211814880371</t>
@@ -71,64 +71,64 @@
     <t xml:space="preserve">2.17187643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13281798362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0925760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16004061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20620012283325</t>
+    <t xml:space="preserve">2.13281869888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767359733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09257578849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16004037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20620036125183</t>
   </si>
   <si>
     <t xml:space="preserve">2.19436454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22513699531555</t>
+    <t xml:space="preserve">2.22513771057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.25236010551453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17305970191956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987246513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395372390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081377983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702105522156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07008790969849</t>
+    <t xml:space="preserve">2.17306017875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987198829651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395420074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081354141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849381446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07008814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.06772089004517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0866584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090908050537</t>
+    <t xml:space="preserve">2.08665823936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090860366821</t>
   </si>
   <si>
     <t xml:space="preserve">2.09375977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16477489471436</t>
+    <t xml:space="preserve">2.16477465629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.15057158470154</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">2.15649008750916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14228677749634</t>
+    <t xml:space="preserve">2.14228653907776</t>
   </si>
   <si>
     <t xml:space="preserve">2.15293908119202</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.19199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21330165863037</t>
+    <t xml:space="preserve">2.21330189704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.19791507720947</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">2.17542719841003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24170804023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25354385375977</t>
+    <t xml:space="preserve">2.24170780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25354337692261</t>
   </si>
   <si>
     <t xml:space="preserve">2.31508994102478</t>
@@ -179,55 +179,55 @@
     <t xml:space="preserve">2.30207061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30562138557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31745719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088663101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390595436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059762001038</t>
+    <t xml:space="preserve">2.30562114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3174569606781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982445716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3115394115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35059714317322</t>
   </si>
   <si>
     <t xml:space="preserve">2.36716747283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.306804895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496884346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2736644744873</t>
+    <t xml:space="preserve">2.30680513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2949686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27366471290588</t>
   </si>
   <si>
     <t xml:space="preserve">2.20738387107849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16595840454102</t>
+    <t xml:space="preserve">2.16595816612244</t>
   </si>
   <si>
     <t xml:space="preserve">2.22632122039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23579025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21921968460083</t>
+    <t xml:space="preserve">2.23579001426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21921992301941</t>
   </si>
   <si>
     <t xml:space="preserve">2.26182866096497</t>
@@ -239,79 +239,79 @@
     <t xml:space="preserve">2.32337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29615306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39912462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231209754944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3411283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32929253578186</t>
+    <t xml:space="preserve">2.29615259170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576991558075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39912390708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112858772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929277420044</t>
   </si>
   <si>
     <t xml:space="preserve">2.30917191505432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34941411018372</t>
+    <t xml:space="preserve">2.34941434860229</t>
   </si>
   <si>
     <t xml:space="preserve">2.37071871757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37663578987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33757853507996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35296511650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3316605091095</t>
+    <t xml:space="preserve">2.37663626670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33166003227234</t>
   </si>
   <si>
     <t xml:space="preserve">2.36124968528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33994507789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385866165161</t>
+    <t xml:space="preserve">2.33994555473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385842323303</t>
   </si>
   <si>
     <t xml:space="preserve">2.41096043586731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42989754676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42516303062439</t>
+    <t xml:space="preserve">2.42989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42516279220581</t>
   </si>
   <si>
     <t xml:space="preserve">2.43699908256531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38965559005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794087409973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37782001495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463158607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44173336029053</t>
+    <t xml:space="preserve">2.38965606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794111251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37781977653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463182449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44173359870911</t>
   </si>
   <si>
     <t xml:space="preserve">2.43936657905579</t>
@@ -326,40 +326,40 @@
     <t xml:space="preserve">2.27839875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37900376319885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43817019462585</t>
+    <t xml:space="preserve">2.37900328636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43817043304443</t>
   </si>
   <si>
     <t xml:space="preserve">2.44433403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4073543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652150154114</t>
+    <t xml:space="preserve">2.40735459327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652102470398</t>
   </si>
   <si>
     <t xml:space="preserve">2.21875953674316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21013140678406</t>
+    <t xml:space="preserve">2.21013116836548</t>
   </si>
   <si>
     <t xml:space="preserve">2.30627775192261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40365624427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049715042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45419478416443</t>
+    <t xml:space="preserve">2.40365648269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296216011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45419502258301</t>
   </si>
   <si>
     <t xml:space="preserve">2.39256262779236</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">2.37653803825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42214632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43940305709839</t>
+    <t xml:space="preserve">2.42214584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43940281867981</t>
   </si>
   <si>
     <t xml:space="preserve">2.45912551879883</t>
@@ -380,121 +380,121 @@
     <t xml:space="preserve">2.46035814285278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46282291412354</t>
+    <t xml:space="preserve">2.46282362937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.4467990398407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48007988929749</t>
+    <t xml:space="preserve">2.48008060455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254537582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47638249397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47268462181091</t>
+    <t xml:space="preserve">2.4763822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47268438339233</t>
   </si>
   <si>
     <t xml:space="preserve">2.53801465034485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52568793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240708351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4813129901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49117374420166</t>
+    <t xml:space="preserve">2.52568769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240660667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48131346702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49117422103882</t>
   </si>
   <si>
     <t xml:space="preserve">2.52322292327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51089668273926</t>
+    <t xml:space="preserve">2.51089644432068</t>
   </si>
   <si>
     <t xml:space="preserve">2.50350046157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49857044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53308439254761</t>
+    <t xml:space="preserve">2.49856948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53308391571045</t>
   </si>
   <si>
     <t xml:space="preserve">2.52938604354858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47021889686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42461133003235</t>
+    <t xml:space="preserve">2.470219373703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42461156845093</t>
   </si>
   <si>
     <t xml:space="preserve">2.42707681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39749336242676</t>
+    <t xml:space="preserve">2.3974928855896</t>
   </si>
   <si>
     <t xml:space="preserve">2.40242409706116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42830967903137</t>
+    <t xml:space="preserve">2.42830944061279</t>
   </si>
   <si>
     <t xml:space="preserve">2.42954182624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4357054233551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45172929763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41351771354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4320068359375</t>
+    <t xml:space="preserve">2.43570494651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41351723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43200731277466</t>
   </si>
   <si>
     <t xml:space="preserve">2.48747611045837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48994207382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541063308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53061890602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49610471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44556593894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105246543884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41474986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39133048057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41968059539795</t>
+    <t xml:space="preserve">2.48994159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761511802673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541039466858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49610447883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4455668926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3913300037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41968083381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.40981936454773</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">2.4480311870575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41721558570862</t>
+    <t xml:space="preserve">2.41721510887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.42091369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44926428794861</t>
+    <t xml:space="preserve">2.44926404953003</t>
   </si>
   <si>
     <t xml:space="preserve">2.41228532791138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3728404045105</t>
+    <t xml:space="preserve">2.37283992767334</t>
   </si>
   <si>
     <t xml:space="preserve">2.35928130149841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32476711273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051368713379</t>
+    <t xml:space="preserve">2.32476735115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
     <t xml:space="preserve">2.33832621574402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31983637809753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36421203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35435056686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43693780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858697891235</t>
+    <t xml:space="preserve">2.31983613967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36421179771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35435032844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43693804740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858745574951</t>
   </si>
   <si>
     <t xml:space="preserve">2.4307746887207</t>
@@ -557,43 +557,43 @@
     <t xml:space="preserve">2.36297917366028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35311770439148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36667680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38393378257751</t>
+    <t xml:space="preserve">2.35311818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36667728424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38393402099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.32723259925842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24711036682129</t>
+    <t xml:space="preserve">2.24711060523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.243412733078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369074821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080847740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2828574180603</t>
+    <t xml:space="preserve">2.22369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28285717964172</t>
   </si>
   <si>
     <t xml:space="preserve">2.22862076759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24834322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860423088074</t>
+    <t xml:space="preserve">2.24834299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860399246216</t>
   </si>
   <si>
     <t xml:space="preserve">2.3075098991394</t>
@@ -605,115 +605,115 @@
     <t xml:space="preserve">2.30257940292358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33586120605469</t>
+    <t xml:space="preserve">2.33586072921753</t>
   </si>
   <si>
     <t xml:space="preserve">2.35065221786499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33339548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336216926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47884750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49980235099792</t>
+    <t xml:space="preserve">2.33339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51952457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336169242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47884774208069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49980282783508</t>
   </si>
   <si>
     <t xml:space="preserve">2.53924703598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56513261795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54910898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266760826111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58115673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60211229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883120536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252860069275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622671127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896973609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54048037528992</t>
+    <t xml:space="preserve">2.56513285636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58115696907043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60211253166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883072853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622694969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896925926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048013687134</t>
   </si>
   <si>
     <t xml:space="preserve">2.54664325714111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56636571884155</t>
+    <t xml:space="preserve">2.56636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.55403923988342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55650448799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55157375335693</t>
+    <t xml:space="preserve">2.55650424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55157351493835</t>
   </si>
   <si>
     <t xml:space="preserve">2.57299423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56795406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52763342857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50873279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47849130630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4255702495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4343900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43565011024475</t>
+    <t xml:space="preserve">2.56795382499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52763295173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50873231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42557001113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43439078330994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43565082550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.44825077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4671516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41926980018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54401350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5503134727478</t>
+    <t xml:space="preserve">2.46715116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41927027702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069075584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5440137386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55031371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023313522339</t>
@@ -722,154 +722,154 @@
     <t xml:space="preserve">2.53267312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49361181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53141331672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5452733039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52133250236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5263729095459</t>
+    <t xml:space="preserve">2.49361205101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53141307830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54527354240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52133297920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52637314796448</t>
   </si>
   <si>
     <t xml:space="preserve">2.50369215011597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52007293701172</t>
+    <t xml:space="preserve">2.52007269859314</t>
   </si>
   <si>
     <t xml:space="preserve">2.55787396430969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55283355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57803463935852</t>
+    <t xml:space="preserve">2.55283331871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57803416252136</t>
   </si>
   <si>
     <t xml:space="preserve">2.59945511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6032350063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6082751750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62717580795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851618766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63347625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473582267761</t>
+    <t xml:space="preserve">2.60323524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62717652320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347554206848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473629951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961579322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67757725715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237641334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63977646827698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6586766242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033835411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71537852287292</t>
+    <t xml:space="preserve">2.67757773399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65237665176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63977670669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65867638587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71033787727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151829719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">2.7342791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74183940887451</t>
+    <t xml:space="preserve">2.74183964729309</t>
   </si>
   <si>
     <t xml:space="preserve">2.75191950798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78090047836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964043617249</t>
+    <t xml:space="preserve">2.78090023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964067459106</t>
   </si>
   <si>
     <t xml:space="preserve">2.77460026741028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76199984550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77208018302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309873580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75947999954224</t>
+    <t xml:space="preserve">2.76199960708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77208042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75947976112366</t>
   </si>
   <si>
     <t xml:space="preserve">2.75821971893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72671866416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67253732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907855033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80484104156494</t>
+    <t xml:space="preserve">2.72671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67253756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907831192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8048415184021</t>
   </si>
   <si>
     <t xml:space="preserve">2.79098057746887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77081990242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939870834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78720021247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650277137756</t>
+    <t xml:space="preserve">2.77711939811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77081966400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939942359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78720045089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7935004234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650229454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.88422322273254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87792301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658263206482</t>
+    <t xml:space="preserve">2.87792277336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86658310890198</t>
   </si>
   <si>
     <t xml:space="preserve">2.8791835308075</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">2.87414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87666368484497</t>
+    <t xml:space="preserve">2.87666296958923</t>
   </si>
   <si>
     <t xml:space="preserve">2.88044333457947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94974565505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91572451591492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9220244884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998595237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518703460693</t>
+    <t xml:space="preserve">2.94974541664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92202425003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998666763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526665687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00518679618835</t>
   </si>
   <si>
     <t xml:space="preserve">3.02912759780884</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">2.96108531951904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762678146362</t>
+    <t xml:space="preserve">2.97872591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762654304504</t>
   </si>
   <si>
     <t xml:space="preserve">3.01274681091309</t>
@@ -926,196 +926,196 @@
     <t xml:space="preserve">2.96990561485291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01148724555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11355018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180811882019</t>
+    <t xml:space="preserve">3.01148700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156710624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11354994773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582854270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180835723877</t>
   </si>
   <si>
     <t xml:space="preserve">3.05558800697327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05810880661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440901756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968972206116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10724973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204960823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10346961021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1185896396637</t>
+    <t xml:space="preserve">3.05810832977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440877914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10724949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204984664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749003410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10347032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11858987808228</t>
   </si>
   <si>
     <t xml:space="preserve">3.02408766746521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04928755760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98754596710205</t>
+    <t xml:space="preserve">3.04928827285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98754668235779</t>
   </si>
   <si>
     <t xml:space="preserve">2.95730519294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99888706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9547860622406</t>
+    <t xml:space="preserve">2.99888682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478534698486</t>
   </si>
   <si>
     <t xml:space="preserve">2.97368550300598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02282762527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778769493103</t>
+    <t xml:space="preserve">3.02282667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778745651245</t>
   </si>
   <si>
     <t xml:space="preserve">3.06944847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1324508190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13119029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10095024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489056587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12867045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09338974952698</t>
+    <t xml:space="preserve">3.13245058059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13119006156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10095000267029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12489080429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12867069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0933895111084</t>
   </si>
   <si>
     <t xml:space="preserve">3.11906051635742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.079270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777710914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595632553101</t>
+    <t xml:space="preserve">3.07926940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953881263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595680236816</t>
   </si>
   <si>
     <t xml:space="preserve">3.13703036308289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13189625740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040324211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864225387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735789299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532845497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19222402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1601345539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22816395759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383543968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23458170890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987886428833</t>
+    <t xml:space="preserve">3.13189673423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864153862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735813140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222378730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16013479232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2506263256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025223731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987910270691</t>
   </si>
   <si>
     <t xml:space="preserve">3.26346158981323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29875922203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271436691284</t>
+    <t xml:space="preserve">3.29876017570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950692176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271389007568</t>
   </si>
   <si>
     <t xml:space="preserve">3.30196833610535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3308482170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122230529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614680290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405780792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159472465515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517721176147</t>
+    <t xml:space="preserve">3.33084893226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122182846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3661470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159567832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629685401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517768859863</t>
   </si>
   <si>
     <t xml:space="preserve">3.28592395782471</t>
@@ -1124,31 +1124,31 @@
     <t xml:space="preserve">3.28913283348083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27308869361877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24099946022034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18708944320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23778986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704407691956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31480407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764005661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30838656425476</t>
+    <t xml:space="preserve">3.2730884552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099898338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18708968162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25704312324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31480383872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801247596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32763981819153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3083860874176</t>
   </si>
   <si>
     <t xml:space="preserve">3.32443046569824</t>
@@ -1157,103 +1157,103 @@
     <t xml:space="preserve">3.35010194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39502763748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39181852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428017616272</t>
+    <t xml:space="preserve">3.39502716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4142804145813</t>
   </si>
   <si>
     <t xml:space="preserve">3.41748857498169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45599627494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44316029548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920538902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995237350464</t>
+    <t xml:space="preserve">3.45599579811096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44316053390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957876205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920515060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46241426467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4399516582489</t>
   </si>
   <si>
     <t xml:space="preserve">3.42390751838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38540029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256479263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37898278236389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689331054688</t>
+    <t xml:space="preserve">3.38539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256455421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898182868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39823579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689354896545</t>
   </si>
   <si>
     <t xml:space="preserve">3.35331130027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40786266326904</t>
+    <t xml:space="preserve">3.40786290168762</t>
   </si>
   <si>
     <t xml:space="preserve">3.43674230575562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46883201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51375651359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092148780823</t>
+    <t xml:space="preserve">3.46883225440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51375603675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092077255249</t>
   </si>
   <si>
     <t xml:space="preserve">3.44636940956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51054739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584574699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56189036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166751861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5041298866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107106208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234170913696</t>
+    <t xml:space="preserve">3.51054787635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189060211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53621864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166704177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50413012504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293816566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234147071838</t>
   </si>
   <si>
     <t xml:space="preserve">3.42711615562439</t>
@@ -1262,37 +1262,37 @@
     <t xml:space="preserve">3.40144491195679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44611477851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975115776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047884941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382533073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31717109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34466218948364</t>
+    <t xml:space="preserve">3.44611382484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4297513961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3773889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31717133522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3446626663208</t>
   </si>
   <si>
     <t xml:space="preserve">3.31586241722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25302672386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146663665771</t>
+    <t xml:space="preserve">3.25302743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310019493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146687507629</t>
   </si>
   <si>
     <t xml:space="preserve">3.19019246101379</t>
@@ -1304,223 +1304,223 @@
     <t xml:space="preserve">3.03310465812683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06844902038574</t>
+    <t xml:space="preserve">3.06844973564148</t>
   </si>
   <si>
     <t xml:space="preserve">3.0461950302124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12866640090942</t>
+    <t xml:space="preserve">3.12866592407227</t>
   </si>
   <si>
     <t xml:space="preserve">3.13652014732361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18102860450745</t>
+    <t xml:space="preserve">3.18102884292603</t>
   </si>
   <si>
     <t xml:space="preserve">3.127357006073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12212085723877</t>
+    <t xml:space="preserve">3.12212109565735</t>
   </si>
   <si>
     <t xml:space="preserve">3.07630348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16466498374939</t>
+    <t xml:space="preserve">3.16466546058655</t>
   </si>
   <si>
     <t xml:space="preserve">3.15877485275269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16597485542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801194190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07695841789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09528493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12670278549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16793751716614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16531991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1633563041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18757367134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17448306083679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684550285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13913893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.175137758255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259363174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979291915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25629997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320936203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30539011955261</t>
+    <t xml:space="preserve">3.16597437858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801098823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11688446998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04815864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0769579410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09528517723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12670230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1679379940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1653196811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16335606575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17448353767395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673681259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150137901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13913869857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17513823509216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259291648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979363441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630021095276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320888519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844598770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538940429688</t>
   </si>
   <si>
     <t xml:space="preserve">3.30277180671692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32764434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324434280396</t>
+    <t xml:space="preserve">3.32764410972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240748405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">3.34597086906433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34728002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095138549805</t>
+    <t xml:space="preserve">3.34727931022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095186233521</t>
   </si>
   <si>
     <t xml:space="preserve">3.39833331108093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38393354415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487909317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39309740066528</t>
+    <t xml:space="preserve">3.38393330574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487933158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3930971622467</t>
   </si>
   <si>
     <t xml:space="preserve">3.44284248352051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4362964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44807863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520444869995</t>
+    <t xml:space="preserve">3.43629670143127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.448077917099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520421028137</t>
   </si>
   <si>
     <t xml:space="preserve">3.48211359977722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52531337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662134170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891429901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31848120689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34335327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3629891872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23797297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2059006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655560493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19542837142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19215512275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10772085189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08415770530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033868789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07826709747314</t>
+    <t xml:space="preserve">3.52531290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5266227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891501426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3210985660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3184802532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34335255622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36298894882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2379732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153588294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590090751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655608177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19542813301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1921558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10772109031677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08415818214417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888705253601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033892631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826685905457</t>
   </si>
   <si>
     <t xml:space="preserve">3.098557472229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13324785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564949989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386756896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692319869995</t>
+    <t xml:space="preserve">3.13324809074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564878463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386804580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692296028137</t>
   </si>
   <si>
     <t xml:space="preserve">3.11557579040527</t>
@@ -1529,130 +1529,130 @@
     <t xml:space="preserve">3.12932085990906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18953824043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888282775879</t>
+    <t xml:space="preserve">3.189537525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888330459595</t>
   </si>
   <si>
     <t xml:space="preserve">3.16401076316833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1620466709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746545791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10641145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808493614197</t>
+    <t xml:space="preserve">3.16204762458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481240272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10641193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06452202796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808517456055</t>
   </si>
   <si>
     <t xml:space="preserve">3.12342953681946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10313963890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510230064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15550136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710185050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1973922252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1489565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17252039909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1941192150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917391777039</t>
+    <t xml:space="preserve">3.10313940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11361193656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1555016040802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739294052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186498641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364667892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17252016067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411969184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917367935181</t>
   </si>
   <si>
     <t xml:space="preserve">3.21113729476929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17952418327332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530943870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13647556304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212438583374</t>
+    <t xml:space="preserve">3.179523229599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530896186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647484779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656519889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17212462425232</t>
   </si>
   <si>
     <t xml:space="preserve">3.16338014602661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20844697952271</t>
+    <t xml:space="preserve">3.20844721794128</t>
   </si>
   <si>
     <t xml:space="preserve">3.08401036262512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02347326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432511329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468317985535</t>
+    <t xml:space="preserve">3.02347302436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499769210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468294143677</t>
   </si>
   <si>
     <t xml:space="preserve">3.08333706855774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06921243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00598502159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99051451683044</t>
+    <t xml:space="preserve">3.0692126750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00598478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99051427841187</t>
   </si>
   <si>
     <t xml:space="preserve">3.01203894615173</t>
@@ -1661,67 +1661,67 @@
     <t xml:space="preserve">2.98042511940002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97638964653015</t>
+    <t xml:space="preserve">2.97638916969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.96629977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99791288375854</t>
+    <t xml:space="preserve">2.99791383743286</t>
   </si>
   <si>
     <t xml:space="preserve">2.98513340950012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95082974433899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96293663978577</t>
+    <t xml:space="preserve">2.95082950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96293640136719</t>
   </si>
   <si>
     <t xml:space="preserve">2.95150184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94006752967834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836430549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540508270264</t>
+    <t xml:space="preserve">2.92997765541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94006705284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836359024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540555953979</t>
   </si>
   <si>
     <t xml:space="preserve">2.85397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94477558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091818809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584930419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894400596619</t>
+    <t xml:space="preserve">2.8862566947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88558411598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94477534294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091866493225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719470024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584858894348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894424438477</t>
   </si>
   <si>
     <t xml:space="preserve">3.06652140617371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05979561805725</t>
+    <t xml:space="preserve">3.05979537963867</t>
   </si>
   <si>
     <t xml:space="preserve">3.03625345230103</t>
@@ -1730,40 +1730,40 @@
     <t xml:space="preserve">3.05912256240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11629676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0739209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09342694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10149812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064699172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96764516830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9474663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562671661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04096150398254</t>
+    <t xml:space="preserve">3.11629629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07392120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09342670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10149836540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064675331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96764540672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94746613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562695503235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04096221923828</t>
   </si>
   <si>
     <t xml:space="preserve">2.99993181228638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97504353523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9441032409668</t>
+    <t xml:space="preserve">2.9750440120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94410276412964</t>
   </si>
   <si>
     <t xml:space="preserve">2.94343018531799</t>
@@ -1772,37 +1772,37 @@
     <t xml:space="preserve">2.92325162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88423919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99589514732361</t>
+    <t xml:space="preserve">2.88423895835876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99589562416077</t>
   </si>
   <si>
     <t xml:space="preserve">2.96898984909058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93468642234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975277900696</t>
+    <t xml:space="preserve">2.93468594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9797523021698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98446083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9669725894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612121582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95957374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91517996788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94544839859009</t>
+    <t xml:space="preserve">2.96697235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95957350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91517972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94544816017151</t>
   </si>
   <si>
     <t xml:space="preserve">2.96428203582764</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">2.9716808795929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00665736198425</t>
+    <t xml:space="preserve">3.00665783882141</t>
   </si>
   <si>
     <t xml:space="preserve">3.01540184020996</t>
@@ -1826,31 +1826,31 @@
     <t xml:space="preserve">3.02683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06853985786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13378477096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13243913650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16472554206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19835758209229</t>
+    <t xml:space="preserve">3.06853938102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.133784532547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13243961334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16472578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19835686683655</t>
   </si>
   <si>
     <t xml:space="preserve">3.20441126823425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2151734828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037531852722</t>
+    <t xml:space="preserve">3.21517300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037460327148</t>
   </si>
   <si>
     <t xml:space="preserve">3.22189950942993</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">3.23804259300232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22728037834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24880433082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1929759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19364857673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189612865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333406448364</t>
+    <t xml:space="preserve">3.22727942466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24880409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19297647476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19364905357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333430290222</t>
   </si>
   <si>
     <t xml:space="preserve">3.3167405128479</t>
@@ -1883,121 +1883,121 @@
     <t xml:space="preserve">3.37660431861877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37525868415833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3725688457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122321128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655728340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270060539246</t>
+    <t xml:space="preserve">3.37525916099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256813049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655752182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270036697388</t>
   </si>
   <si>
     <t xml:space="preserve">3.4882607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39543795585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39274716377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965246200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099809646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808266639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673703193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153519630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4734628200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53130912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440335273743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51112961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458262443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032179832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57861185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5869026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5675585269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62144494056702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61591792106628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6380250453949</t>
+    <t xml:space="preserve">3.39543771743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39274764060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965270042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099785804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46673679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47346258163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5313093662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440359115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978493690491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032227516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275675773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5786120891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58690190315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6214451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61591815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63802528381348</t>
   </si>
   <si>
     <t xml:space="preserve">3.57170343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58137559890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545092582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472543716431</t>
+    <t xml:space="preserve">3.58137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545140266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472519874573</t>
   </si>
   <si>
     <t xml:space="preserve">3.55097794532776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5910472869873</t>
+    <t xml:space="preserve">3.59104752540588</t>
   </si>
   <si>
     <t xml:space="preserve">3.6034824848175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60071921348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61730003356934</t>
+    <t xml:space="preserve">3.60071969032288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61730027198792</t>
   </si>
   <si>
     <t xml:space="preserve">3.62282681465149</t>
@@ -2015,76 +2015,76 @@
     <t xml:space="preserve">3.64631581306458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66980457305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66151452064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118716239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66427779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085789680481</t>
+    <t xml:space="preserve">3.6698043346405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66151404380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533135414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118692398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66427850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085765838623</t>
   </si>
   <si>
     <t xml:space="preserve">3.7292172908783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80106639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205109596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79830265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79001212120056</t>
+    <t xml:space="preserve">3.80106616020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863024711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205061912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79830288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79001307487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.79139423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77895855903625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350135803223</t>
+    <t xml:space="preserve">3.77895903587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350040435791</t>
   </si>
   <si>
     <t xml:space="preserve">3.83008193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85495233535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9392364025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752717018127</t>
+    <t xml:space="preserve">3.85495281219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225840568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752764701843</t>
   </si>
   <si>
     <t xml:space="preserve">3.92818260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94061779975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90883898735046</t>
+    <t xml:space="preserve">3.94061851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90883946418762</t>
   </si>
   <si>
     <t xml:space="preserve">3.91091156005859</t>
@@ -2093,178 +2093,178 @@
     <t xml:space="preserve">3.94338154792786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93440055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93370914459229</t>
+    <t xml:space="preserve">3.93440008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93370962142944</t>
   </si>
   <si>
     <t xml:space="preserve">3.92127442359924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91022109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847683906555</t>
+    <t xml:space="preserve">3.91022086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847636222839</t>
   </si>
   <si>
     <t xml:space="preserve">3.8756787776947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379487991333</t>
+    <t xml:space="preserve">3.85564303398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379535675049</t>
   </si>
   <si>
     <t xml:space="preserve">3.81419253349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81695628166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281113624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593703269958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83629941940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571309089661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531567573547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182596206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85218977928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83491849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452108383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8514986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080742835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186170578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88880491256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93094682693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068857192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99934124946594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8390634059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8480441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844157218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581722259521</t>
+    <t xml:space="preserve">3.81695556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281065940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8024480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593679428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840678215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83629965782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182620048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015175819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8521900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491778373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80451965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85149884223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080790519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186075210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88880443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93094611167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690485954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068761825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99934029579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906388282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84804463386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407343864441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581793785095</t>
   </si>
   <si>
     <t xml:space="preserve">4.01108551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0698070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02628421783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911659240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13889360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1934700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20037746429443</t>
+    <t xml:space="preserve">4.06980752944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02628374099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911706924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13889265060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19347095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20037841796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.30884218215942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2625560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27637195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3053879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30055284500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20314168930054</t>
+    <t xml:space="preserve">4.26255559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27637243270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30538845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30055141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397226333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20314264297485</t>
   </si>
   <si>
     <t xml:space="preserve">4.24182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2321572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32473182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42697811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539213180542</t>
+    <t xml:space="preserve">4.23215818405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32473230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42697763442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45392179489136</t>
   </si>
   <si>
     <t xml:space="preserve">4.42145109176636</t>
@@ -2273,79 +2273,79 @@
     <t xml:space="preserve">4.4283595085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42766952514648</t>
+    <t xml:space="preserve">4.42766857147217</t>
   </si>
   <si>
     <t xml:space="preserve">4.43941307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49744510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45668411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48500871658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53129625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34407520294189</t>
+    <t xml:space="preserve">4.49744462966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45668506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48500967025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49951696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5312967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34407567977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.4323992729187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43310594558716</t>
+    <t xml:space="preserve">4.43310546875</t>
   </si>
   <si>
     <t xml:space="preserve">4.47267436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41402816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38788318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41332101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35891389846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38011074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40908050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940502166748</t>
+    <t xml:space="preserve">4.41402769088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38788414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41332006454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35891437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38011169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40908145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940454483032</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33418321609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842325210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493835449219</t>
+    <t xml:space="preserve">4.33418273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842372894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493883132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.28472280502319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29461479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2458610534668</t>
+    <t xml:space="preserve">4.29461526870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24586057662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.44087791442871</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">4.40625524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46419429779053</t>
+    <t xml:space="preserve">4.46419525146484</t>
   </si>
   <si>
     <t xml:space="preserve">4.44017124176025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39707040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59208679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59349918365479</t>
+    <t xml:space="preserve">4.39706945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59208726882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59349966049194</t>
   </si>
   <si>
     <t xml:space="preserve">4.68606233596802</t>
@@ -2378,28 +2378,28 @@
     <t xml:space="preserve">4.65921258926392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71997737884521</t>
+    <t xml:space="preserve">4.71997833251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.72068548202515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7609601020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70937967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758369445801</t>
+    <t xml:space="preserve">4.76095962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70937871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758321762085</t>
   </si>
   <si>
     <t xml:space="preserve">4.62458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58572721481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181121826172</t>
+    <t xml:space="preserve">4.58572816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181169509888</t>
   </si>
   <si>
     <t xml:space="preserve">4.67263698577881</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">4.657799243927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58007478713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480546951294</t>
+    <t xml:space="preserve">4.58007431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480499267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">4.67405080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64649438858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71361875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215789794922</t>
+    <t xml:space="preserve">4.64649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71361970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215837478638</t>
   </si>
   <si>
     <t xml:space="preserve">4.7553071975708</t>
@@ -2435,64 +2435,64 @@
     <t xml:space="preserve">4.82737922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79487705230713</t>
+    <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
     <t xml:space="preserve">4.84080410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81678009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6910080909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77226543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8365650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78498363494873</t>
+    <t xml:space="preserve">4.81678104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69100904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77226591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83656406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78498411178589</t>
   </si>
   <si>
     <t xml:space="preserve">4.81536722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78145122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78992986679077</t>
+    <t xml:space="preserve">4.78145170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78993082046509</t>
   </si>
   <si>
     <t xml:space="preserve">4.83161878585815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80830097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78357172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82455348968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7659068107605</t>
+    <t xml:space="preserve">4.80830144882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78357076644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82455253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590633392334</t>
   </si>
   <si>
     <t xml:space="preserve">4.84221744537354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86129570007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8499903678894</t>
+    <t xml:space="preserve">4.86129522323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84998941421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.85564279556274</t>
@@ -2504,40 +2504,40 @@
     <t xml:space="preserve">4.90368986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89733123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92347526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249254226685</t>
+    <t xml:space="preserve">4.89733076095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92347478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.882493019104</t>
   </si>
   <si>
     <t xml:space="preserve">4.87471961975098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77085208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84716367721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93407297134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8577618598938</t>
+    <t xml:space="preserve">4.77085161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.851402759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84716320037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93407249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662408828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85776281356812</t>
   </si>
   <si>
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401294708252</t>
+    <t xml:space="preserve">4.87401342391968</t>
   </si>
   <si>
     <t xml:space="preserve">4.82596588134766</t>
@@ -2546,85 +2546,85 @@
     <t xml:space="preserve">4.80759429931641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78710460662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83303117752075</t>
+    <t xml:space="preserve">4.78710412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83303260803223</t>
   </si>
   <si>
     <t xml:space="preserve">4.85493564605713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84433746337891</t>
+    <t xml:space="preserve">4.84433650970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.66698503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71785974502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036191940308</t>
+    <t xml:space="preserve">4.71785926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.75601387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83727216720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89309167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9531512260437</t>
+    <t xml:space="preserve">4.83727121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89309120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95315170288086</t>
   </si>
   <si>
     <t xml:space="preserve">4.93336629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94679164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09164142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04359340667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99695873260498</t>
+    <t xml:space="preserve">4.94679260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09164190292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973648071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0435938835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99695920944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.09588050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09517478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10577297210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10859966278076</t>
+    <t xml:space="preserve">5.09517431259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10577344894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10859870910645</t>
   </si>
   <si>
     <t xml:space="preserve">5.13686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16159343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24072980880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22871875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24355697631836</t>
+    <t xml:space="preserve">5.16159296035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22871828079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355602264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.3778076171875</t>
@@ -2633,31 +2633,31 @@
     <t xml:space="preserve">5.45835828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50453615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4908275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44464921951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49804306030273</t>
+    <t xml:space="preserve">5.50453662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49082612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44464874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49804210662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.64162588119507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83571767807007</t>
+    <t xml:space="preserve">5.53700494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83571720123291</t>
   </si>
   <si>
     <t xml:space="preserve">5.66760158538818</t>
@@ -2666,64 +2666,64 @@
     <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7722225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82272958755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602115631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89993286132812</t>
+    <t xml:space="preserve">5.77222347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82272911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89993238449097</t>
   </si>
   <si>
     <t xml:space="preserve">5.91652822494507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91147756576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86746406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9215784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97208595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05650472640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917615890503</t>
+    <t xml:space="preserve">5.91147708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8674635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92157936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97208642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05650520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917663574219</t>
   </si>
   <si>
     <t xml:space="preserve">6.18060731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08464431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09258127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152456283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51247262954712</t>
+    <t xml:space="preserve">6.08464479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09258079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386854171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975419998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71161460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5124716758728</t>
   </si>
   <si>
     <t xml:space="preserve">5.62286615371704</t>
@@ -2732,31 +2732,31 @@
     <t xml:space="preserve">5.94538879394531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87684440612793</t>
+    <t xml:space="preserve">5.87684488296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.69357585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12717723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712244033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70436096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77070450782776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426502227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830202102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12713956832886</t>
+    <t xml:space="preserve">5.1271767616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77070426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830225944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1271390914917</t>
   </si>
   <si>
     <t xml:space="preserve">4.2497992515564</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">4.24907779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30896472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55356216430664</t>
+    <t xml:space="preserve">4.30896425247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5535626411438</t>
   </si>
   <si>
     <t xml:space="preserve">4.54562568664551</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">4.53047370910645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44100475311279</t>
+    <t xml:space="preserve">4.44100427627563</t>
   </si>
   <si>
     <t xml:space="preserve">4.60767650604248</t>
@@ -2789,76 +2789,76 @@
     <t xml:space="preserve">4.57376527786255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37823057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37895202636719</t>
+    <t xml:space="preserve">4.37823152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378877639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37895154953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.43018102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59974050521851</t>
+    <t xml:space="preserve">4.59974002838135</t>
   </si>
   <si>
     <t xml:space="preserve">4.53480291366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65601921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6516900062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47852325439453</t>
+    <t xml:space="preserve">4.65601968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65169048309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47852373123169</t>
   </si>
   <si>
     <t xml:space="preserve">4.50882768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47996616363525</t>
+    <t xml:space="preserve">4.47996711730957</t>
   </si>
   <si>
     <t xml:space="preserve">4.46770095825195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3327751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3183445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27577447891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25701427459717</t>
+    <t xml:space="preserve">4.33277463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31834363937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2757740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25701475143433</t>
   </si>
   <si>
     <t xml:space="preserve">4.37967443466187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43739652633667</t>
+    <t xml:space="preserve">4.43739604949951</t>
   </si>
   <si>
     <t xml:space="preserve">4.52397966384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49944734573364</t>
+    <t xml:space="preserve">4.4994478225708</t>
   </si>
   <si>
     <t xml:space="preserve">4.33421802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39266109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37750911712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46481370925903</t>
+    <t xml:space="preserve">4.39266157150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37750959396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46481418609619</t>
   </si>
   <si>
     <t xml:space="preserve">4.473473072052</t>
@@ -2873,37 +2873,37 @@
     <t xml:space="preserve">4.24546957015991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15672206878662</t>
+    <t xml:space="preserve">4.15672302246094</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35586309432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5109920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56727123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62499284744263</t>
+    <t xml:space="preserve">4.35586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51099157333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56727170944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62499380111694</t>
   </si>
   <si>
     <t xml:space="preserve">4.69714641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926425933838</t>
+    <t xml:space="preserve">4.70147514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926378250122</t>
   </si>
   <si>
     <t xml:space="preserve">5.04925203323364</t>
@@ -2912,52 +2912,52 @@
     <t xml:space="preserve">5.1870641708374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41434574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40063524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46773767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46701622009277</t>
+    <t xml:space="preserve">5.41434478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40063619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46773672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46701669692993</t>
   </si>
   <si>
     <t xml:space="preserve">5.44176244735718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42011737823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28663444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29962205886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4590802192688</t>
+    <t xml:space="preserve">5.42011690139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28663492202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29962158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">5.41506624221802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39197731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361158370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63585329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906799316406</t>
+    <t xml:space="preserve">5.39197826385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63585376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906847000122</t>
   </si>
   <si>
     <t xml:space="preserve">5.51175117492676</t>
@@ -2966,94 +2966,94 @@
     <t xml:space="preserve">5.57308101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5398907661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55720806121826</t>
+    <t xml:space="preserve">5.53989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55720710754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.73398160934448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68131017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71017169952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75418376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83427429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86024856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89416074752808</t>
+    <t xml:space="preserve">5.68130970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71017217636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75418424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83427476882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86024951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232431411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89416170120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.95476961135864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08031558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12669610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1325855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98828983306885</t>
+    <t xml:space="preserve">6.08031463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12669515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13258504867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246212005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98828840255737</t>
   </si>
   <si>
     <t xml:space="preserve">5.84841012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83147811889648</t>
+    <t xml:space="preserve">5.83147859573364</t>
   </si>
   <si>
     <t xml:space="preserve">5.81601762771606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87123250961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69601631164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69012641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79319524765015</t>
+    <t xml:space="preserve">5.8712329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69012689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7931957244873</t>
   </si>
   <si>
     <t xml:space="preserve">5.76669216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69086313247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75344038009644</t>
+    <t xml:space="preserve">5.69086217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75343990325928</t>
   </si>
   <si>
     <t xml:space="preserve">5.79024982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86313533782959</t>
+    <t xml:space="preserve">5.86313438415527</t>
   </si>
   <si>
     <t xml:space="preserve">5.97062063217163</t>
@@ -3062,34 +3062,34 @@
     <t xml:space="preserve">5.89552783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8049750328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74828672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70926809310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69159936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79098701477051</t>
+    <t xml:space="preserve">5.80497455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74828720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70926856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69159889221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79098749160767</t>
   </si>
   <si>
     <t xml:space="preserve">5.74534177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74092531204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460422515869</t>
+    <t xml:space="preserve">5.74092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460374832153</t>
   </si>
   <si>
     <t xml:space="preserve">5.58705806732178</t>
@@ -3098,61 +3098,61 @@
     <t xml:space="preserve">5.52448081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63049411773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043241500854</t>
+    <t xml:space="preserve">5.63049364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043193817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.45674991607666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59000301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165891647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63270282745361</t>
+    <t xml:space="preserve">5.59000253677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165748596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63270330429077</t>
   </si>
   <si>
     <t xml:space="preserve">5.5981011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63932847976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56644439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57675123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319129943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263980865479</t>
+    <t xml:space="preserve">5.63932800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5664439201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57675075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319082260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263933181763</t>
   </si>
   <si>
     <t xml:space="preserve">5.3441104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3897557258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40006160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48325347900391</t>
+    <t xml:space="preserve">5.38975524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208784103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582941055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40006256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48325252532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.52153587341309</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">5.49797677993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4434986114502</t>
+    <t xml:space="preserve">5.44349813461304</t>
   </si>
   <si>
     <t xml:space="preserve">5.42141199111938</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">5.59221124649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55613708496094</t>
+    <t xml:space="preserve">5.5561375617981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5392050743103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65920639038086</t>
+    <t xml:space="preserve">5.6592059135437</t>
   </si>
   <si>
     <t xml:space="preserve">5.67761135101318</t>
@@ -3194,88 +3194,88 @@
     <t xml:space="preserve">5.49871349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58190393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53257894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57233333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4442343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662292480469</t>
+    <t xml:space="preserve">5.58190441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472547531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57233381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44423389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.116623878479</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705232620239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03122329711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312648773193</t>
+    <t xml:space="preserve">5.03122282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312601089478</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42435741424561</t>
+    <t xml:space="preserve">5.42435598373413</t>
   </si>
   <si>
     <t xml:space="preserve">5.6032543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92718410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92423915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04571390151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853448867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90436267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95516014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97209358215332</t>
+    <t xml:space="preserve">5.92718458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92423963546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04571342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90436220169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95515966415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97209310531616</t>
   </si>
   <si>
     <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01037502288818</t>
+    <t xml:space="preserve">6.01037549972534</t>
   </si>
   <si>
     <t xml:space="preserve">6.06117391586304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19737148284912</t>
+    <t xml:space="preserve">6.19737243652344</t>
   </si>
   <si>
     <t xml:space="preserve">6.24816989898682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23565435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25921249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.162034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522315979004</t>
+    <t xml:space="preserve">6.2356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25921297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16203308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522268295288</t>
   </si>
   <si>
     <t xml:space="preserve">6.09724712371826</t>
@@ -3287,28 +3287,28 @@
     <t xml:space="preserve">6.04129695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02289152145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00743055343628</t>
+    <t xml:space="preserve">6.0228910446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00743103027344</t>
   </si>
   <si>
     <t xml:space="preserve">5.97798204421997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04424142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92276668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00890350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01700162887573</t>
+    <t xml:space="preserve">6.04424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92571115493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.922767162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00890302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01700210571289</t>
   </si>
   <si>
     <t xml:space="preserve">5.94190883636475</t>
@@ -3317,31 +3317,31 @@
     <t xml:space="preserve">6.08914947509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14362859725952</t>
+    <t xml:space="preserve">6.14362907409668</t>
   </si>
   <si>
     <t xml:space="preserve">6.09283065795898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22608327865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18043947219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57357311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166896820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019876480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081111907959</t>
+    <t xml:space="preserve">6.22608375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18043994903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57357168197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166944503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081016540527</t>
   </si>
   <si>
     <t xml:space="preserve">6.57062721252441</t>
@@ -3353,40 +3353,40 @@
     <t xml:space="preserve">6.52203798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44768524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43942308425903</t>
+    <t xml:space="preserve">6.4476842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43942356109619</t>
   </si>
   <si>
     <t xml:space="preserve">6.44242763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3530535697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26743507385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.259925365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30874252319336</t>
+    <t xml:space="preserve">6.35305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25992488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30874156951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.18932676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30949354171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15177536010742</t>
+    <t xml:space="preserve">6.30949306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15177488327026</t>
   </si>
   <si>
     <t xml:space="preserve">6.17430591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15853404998779</t>
+    <t xml:space="preserve">6.15853357315063</t>
   </si>
   <si>
     <t xml:space="preserve">6.42290067672729</t>
@@ -3395,115 +3395,115 @@
     <t xml:space="preserve">6.42590475082397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3440408706665</t>
+    <t xml:space="preserve">6.34404134750366</t>
   </si>
   <si>
     <t xml:space="preserve">6.38384675979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22162199020386</t>
+    <t xml:space="preserve">6.22162246704102</t>
   </si>
   <si>
     <t xml:space="preserve">6.24715709686279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35530757904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35981369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23589134216309</t>
+    <t xml:space="preserve">6.35530710220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35981416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23589181900024</t>
   </si>
   <si>
     <t xml:space="preserve">6.15552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06615591049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88815975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89116382598877</t>
+    <t xml:space="preserve">6.0661563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105310440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94824361801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88816022872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89116334915161</t>
   </si>
   <si>
     <t xml:space="preserve">5.9685206413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85962009429932</t>
+    <t xml:space="preserve">5.85962057113647</t>
   </si>
   <si>
     <t xml:space="preserve">5.72743654251099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89041328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91294384002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1697998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316524505615</t>
+    <t xml:space="preserve">5.8904128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91294431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16979932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316572189331</t>
   </si>
   <si>
     <t xml:space="preserve">6.19984197616577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14426469802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18707370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12999486923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05639314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2381443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166368484497</t>
+    <t xml:space="preserve">6.14426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18707418441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12999439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23814535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166320800781</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34028720855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33352661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37858915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502912521362</t>
+    <t xml:space="preserve">6.34028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33352708816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37858867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502864837646</t>
   </si>
   <si>
     <t xml:space="preserve">6.42440223693848</t>
@@ -3515,70 +3515,70 @@
     <t xml:space="preserve">6.49725341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392967224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39060544967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44468116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326251983643</t>
+    <t xml:space="preserve">6.45444440841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44393014907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47472238540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39060640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44468021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326299667358</t>
   </si>
   <si>
     <t xml:space="preserve">6.50551462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42515468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37408304214478</t>
+    <t xml:space="preserve">6.4251537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
     <t xml:space="preserve">6.54757356643677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56034088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48899364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217746734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27569723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16304111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22537660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20960474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00231790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07742166519165</t>
+    <t xml:space="preserve">6.5603404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48899269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27569675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16304063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22537612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20960426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.214111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00231838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07742214202881</t>
   </si>
   <si>
     <t xml:space="preserve">6.16153907775879</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">6.12623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10445976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98279142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06390380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13374948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11872959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05038404464722</t>
+    <t xml:space="preserve">6.10445928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98279094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06390285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13375043869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11872911453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05038499832153</t>
   </si>
   <si>
     <t xml:space="preserve">5.99405670166016</t>
@@ -3620,46 +3620,46 @@
     <t xml:space="preserve">5.9272141456604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95650434494019</t>
+    <t xml:space="preserve">5.95650482177734</t>
   </si>
   <si>
     <t xml:space="preserve">6.01057910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01733875274658</t>
+    <t xml:space="preserve">6.01733922958374</t>
   </si>
   <si>
     <t xml:space="preserve">6.01808881759644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9790358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0248498916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08493185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06840944290161</t>
+    <t xml:space="preserve">5.97903537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02484941482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08493280410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06840896606445</t>
   </si>
   <si>
     <t xml:space="preserve">6.16829824447632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0676589012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04888248443604</t>
+    <t xml:space="preserve">6.06765794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04888200759888</t>
   </si>
   <si>
     <t xml:space="preserve">6.09845066070557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98654556274414</t>
+    <t xml:space="preserve">6.08943891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9865460395813</t>
   </si>
   <si>
     <t xml:space="preserve">6.03386163711548</t>
@@ -3677,40 +3677,40 @@
     <t xml:space="preserve">5.88215112686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89491844177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8964204788208</t>
+    <t xml:space="preserve">5.89491939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89642143249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.93772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401453018188</t>
+    <t xml:space="preserve">5.96401500701904</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.951247215271</t>
+    <t xml:space="preserve">5.95124673843384</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489110946655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05188608169556</t>
+    <t xml:space="preserve">6.05188655853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.02635145187378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95725536346436</t>
+    <t xml:space="preserve">5.9572548866272</t>
   </si>
   <si>
     <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84443855285645</t>
+    <t xml:space="preserve">5.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">5.8513560295105</t>
@@ -3719,16 +3719,16 @@
     <t xml:space="preserve">6.00277042388916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1157546043396</t>
+    <t xml:space="preserve">6.11575508117676</t>
   </si>
   <si>
     <t xml:space="preserve">6.18723487854004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11959791183472</t>
+    <t xml:space="preserve">6.21106147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1195969581604</t>
   </si>
   <si>
     <t xml:space="preserve">6.19107818603516</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">6.16033411026001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97971200942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94819974899292</t>
+    <t xml:space="preserve">5.97971248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94820022583008</t>
   </si>
   <si>
     <t xml:space="preserve">5.91361284255981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92052984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819139480591</t>
+    <t xml:space="preserve">5.92053031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819187164307</t>
   </si>
   <si>
     <t xml:space="preserve">5.96357154846191</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">6.02044820785522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02890253067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03120946884155</t>
+    <t xml:space="preserve">6.02890300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
     <t xml:space="preserve">5.97740602493286</t>
@@ -3785,52 +3785,52 @@
     <t xml:space="preserve">6.149573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01968002319336</t>
+    <t xml:space="preserve">6.0196795463562</t>
   </si>
   <si>
     <t xml:space="preserve">5.96510887145996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9013147354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90208339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95511627197266</t>
+    <t xml:space="preserve">5.90131521224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90208387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95511722564697</t>
   </si>
   <si>
     <t xml:space="preserve">5.93129062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99815845489502</t>
+    <t xml:space="preserve">5.99815893173218</t>
   </si>
   <si>
     <t xml:space="preserve">5.93513345718384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92975378036499</t>
+    <t xml:space="preserve">5.92975330352783</t>
   </si>
   <si>
     <t xml:space="preserve">5.83367824554443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77833938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756237030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76373624801636</t>
+    <t xml:space="preserve">5.77833890914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756189346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66842889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76373529434204</t>
   </si>
   <si>
     <t xml:space="preserve">5.71454572677612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3994197845459</t>
+    <t xml:space="preserve">5.39941883087158</t>
   </si>
   <si>
     <t xml:space="preserve">5.38097286224365</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">5.34869146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2572283744812</t>
+    <t xml:space="preserve">5.25722789764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.30257606506348</t>
@@ -3848,163 +3848,163 @@
     <t xml:space="preserve">5.33408784866333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4409236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39403915405273</t>
+    <t xml:space="preserve">5.44092321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39403867721558</t>
   </si>
   <si>
     <t xml:space="preserve">5.33946800231934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25492238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22110366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11196279525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17883014678955</t>
+    <t xml:space="preserve">5.25492191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22110414505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11196231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17191362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30565023422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31794786453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18651628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958257675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24954175949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30795621871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44246053695679</t>
+    <t xml:space="preserve">5.3056492805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31794738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18651723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958353042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24954223632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30795574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44246101379395</t>
   </si>
   <si>
     <t xml:space="preserve">5.54160976409912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51317167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5462212562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772611618042</t>
+    <t xml:space="preserve">5.5131721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54622173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772659301758</t>
   </si>
   <si>
     <t xml:space="preserve">5.56159353256226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5992546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55775022506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57696580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57389068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60617256164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5300817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45245265960693</t>
+    <t xml:space="preserve">5.59925556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5577507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57696533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57389163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60617303848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53008079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45245122909546</t>
   </si>
   <si>
     <t xml:space="preserve">5.5031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45629549026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49549436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44707250595093</t>
+    <t xml:space="preserve">5.45629596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49549388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44707202911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.4324688911438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41248559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34177303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34331130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30872440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41479110717773</t>
+    <t xml:space="preserve">5.41248512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34177398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34331083297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30872392654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41479158401489</t>
   </si>
   <si>
     <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23878145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21802997589111</t>
+    <t xml:space="preserve">5.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2180290222168</t>
   </si>
   <si>
     <t xml:space="preserve">5.15500402450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19189739227295</t>
+    <t xml:space="preserve">5.19189691543579</t>
   </si>
   <si>
     <t xml:space="preserve">5.06507778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01588726043701</t>
+    <t xml:space="preserve">5.01588773727417</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039300918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15116167068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14193820953369</t>
+    <t xml:space="preserve">5.23493814468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1511607170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14193773269653</t>
   </si>
   <si>
     <t xml:space="preserve">5.07583808898926</t>
@@ -4013,16 +4013,16 @@
     <t xml:space="preserve">5.0927472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14731740951538</t>
+    <t xml:space="preserve">5.1473183631897</t>
   </si>
   <si>
     <t xml:space="preserve">5.10965633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18497943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1134991645813</t>
+    <t xml:space="preserve">5.18497896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11349964141846</t>
   </si>
   <si>
     <t xml:space="preserve">5.25338459014893</t>
@@ -4037,85 +4037,85 @@
     <t xml:space="preserve">5.32486486434937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40787363052368</t>
+    <t xml:space="preserve">5.40787267684937</t>
   </si>
   <si>
     <t xml:space="preserve">5.38789033889771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4155592918396</t>
+    <t xml:space="preserve">5.41555976867676</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34100484848022</t>
+    <t xml:space="preserve">5.47243547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34100580215454</t>
   </si>
   <si>
     <t xml:space="preserve">5.31026124954224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32640218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32717037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35022830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23186445236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27490568161011</t>
+    <t xml:space="preserve">5.32640171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32717132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35022878646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2318639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27490615844727</t>
   </si>
   <si>
     <t xml:space="preserve">5.38250970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30718612670898</t>
+    <t xml:space="preserve">5.30718755722046</t>
   </si>
   <si>
     <t xml:space="preserve">5.26766920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26845979690552</t>
+    <t xml:space="preserve">5.26845932006836</t>
   </si>
   <si>
     <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41546487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33643007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35935020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41704511642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41309356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35776901245117</t>
+    <t xml:space="preserve">5.41546440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33642959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35934972763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41309404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35776948928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.24712038040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08272838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00369358062744</t>
+    <t xml:space="preserve">5.08272886276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908483505249</t>
@@ -4124,25 +4124,25 @@
     <t xml:space="preserve">5.08351850509644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05348587036133</t>
+    <t xml:space="preserve">5.05348491668701</t>
   </si>
   <si>
     <t xml:space="preserve">4.99499988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08114767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14516544342041</t>
+    <t xml:space="preserve">5.08114719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14516639709473</t>
   </si>
   <si>
     <t xml:space="preserve">5.12303590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08588933944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97603178024292</t>
+    <t xml:space="preserve">5.08588981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9760308265686</t>
   </si>
   <si>
     <t xml:space="preserve">5.01396799087524</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">4.99025726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89383459091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17598867416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2155065536499</t>
+    <t xml:space="preserve">4.89383506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17598915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21550607681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.87960863113403</t>
@@ -4166,25 +4166,25 @@
     <t xml:space="preserve">4.87644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70652294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48127365112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
+    <t xml:space="preserve">4.7065224647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48127317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.52237176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77291250228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53580713272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52711391448975</t>
+    <t xml:space="preserve">4.7729115486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53580760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52711343765259</t>
   </si>
   <si>
     <t xml:space="preserve">4.59903526306152</t>
@@ -4193,58 +4193,58 @@
     <t xml:space="preserve">4.604567527771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60298681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52079010009766</t>
+    <t xml:space="preserve">4.60298633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52079057693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.55240488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60219669342041</t>
+    <t xml:space="preserve">4.60219717025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.51209735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294561386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81875228881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82428455352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.829026222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92544937133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90648078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87486600875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98709583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566516876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8187518119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79583120346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82428407669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82902669906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92544841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90648126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87486696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98709630966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96891832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.89857721328735</t>
@@ -4253,37 +4253,37 @@
     <t xml:space="preserve">4.90173864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88514137268066</t>
+    <t xml:space="preserve">4.88514184951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.87249565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75236320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82349443435669</t>
+    <t xml:space="preserve">4.75236225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82349395751953</t>
   </si>
   <si>
     <t xml:space="preserve">4.81559038162231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79978322982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91596412658691</t>
+    <t xml:space="preserve">4.7997841835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91596508026123</t>
   </si>
   <si>
     <t xml:space="preserve">4.91438388824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87881803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93888425827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89541530609131</t>
+    <t xml:space="preserve">4.87881898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93888521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89541578292847</t>
   </si>
   <si>
     <t xml:space="preserve">4.78555727005005</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">4.74841117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64171409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7262806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61405181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69229555130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73181295394897</t>
+    <t xml:space="preserve">4.64171361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61721277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6140513420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69229650497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73181390762329</t>
   </si>
   <si>
     <t xml:space="preserve">4.74999189376831</t>
@@ -4319,10 +4319,10 @@
     <t xml:space="preserve">4.69150590896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83930063247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84720420837402</t>
+    <t xml:space="preserve">4.83930110931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84720516204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.84641408920288</t>
@@ -4331,52 +4331,52 @@
     <t xml:space="preserve">4.88751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88909244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87012481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77686357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68202114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70573282241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66700506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76500749588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73260354995728</t>
+    <t xml:space="preserve">4.88909196853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87012434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77686309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6820216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7057318687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66700553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76500844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73260450363159</t>
   </si>
   <si>
     <t xml:space="preserve">4.62037467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52790403366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3318977355957</t>
+    <t xml:space="preserve">4.52790451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33189821243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.25839519500732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21492624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39117383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26787996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30107450485229</t>
+    <t xml:space="preserve">4.21492576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39117431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26787948608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30107402801514</t>
   </si>
   <si>
     <t xml:space="preserve">4.33822059631348</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">4.31925201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22915172576904</t>
+    <t xml:space="preserve">4.2291522026062</t>
   </si>
   <si>
     <t xml:space="preserve">4.2852668762207</t>
@@ -4394,19 +4394,19 @@
     <t xml:space="preserve">4.35718822479248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27499198913574</t>
+    <t xml:space="preserve">4.2749924659729</t>
   </si>
   <si>
     <t xml:space="preserve">4.32794523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1256160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911909103394</t>
+    <t xml:space="preserve">4.26946020126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12561702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911956787109</t>
   </si>
   <si>
     <t xml:space="preserve">4.173828125</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09084129333496</t>
+    <t xml:space="preserve">4.09084177017212</t>
   </si>
   <si>
     <t xml:space="preserve">4.15960168838501</t>
@@ -4427,16 +4427,16 @@
     <t xml:space="preserve">4.14300441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0924220085144</t>
+    <t xml:space="preserve">4.09242248535156</t>
   </si>
   <si>
     <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8213324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95173954963684</t>
+    <t xml:space="preserve">3.82133293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.951740026474</t>
   </si>
   <si>
     <t xml:space="preserve">4.0330753326416</t>
@@ -4445,46 +4445,46 @@
     <t xml:space="preserve">4.08606576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95831203460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90080285072327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88108539581299</t>
+    <t xml:space="preserve">3.95831227302551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90080332756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88108611106873</t>
   </si>
   <si>
     <t xml:space="preserve">3.90244626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89053297042847</t>
+    <t xml:space="preserve">3.89053320884705</t>
   </si>
   <si>
     <t xml:space="preserve">3.88683652877808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9381844997406</t>
+    <t xml:space="preserve">3.93818378448486</t>
   </si>
   <si>
     <t xml:space="preserve">4.06922435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9961040019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0051417350769</t>
+    <t xml:space="preserve">3.99610447883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00514221191406</t>
   </si>
   <si>
     <t xml:space="preserve">4.03636169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06758165359497</t>
+    <t xml:space="preserve">4.06758213043213</t>
   </si>
   <si>
     <t xml:space="preserve">4.13412809371948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11440992355347</t>
+    <t xml:space="preserve">4.11441040039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
@@ -4493,55 +4493,55 @@
     <t xml:space="preserve">4.10783815383911</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13659238815308</t>
+    <t xml:space="preserve">4.13659286499023</t>
   </si>
   <si>
     <t xml:space="preserve">4.19163799285889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753004074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18342208862305</t>
+    <t xml:space="preserve">4.18753051757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18342256546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.11030197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05443572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05854368209839</t>
+    <t xml:space="preserve">4.05443620681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05854415893555</t>
   </si>
   <si>
     <t xml:space="preserve">4.06265211105347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06347322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97022581100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94639992713928</t>
+    <t xml:space="preserve">4.06347370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97022533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94640040397644</t>
   </si>
   <si>
     <t xml:space="preserve">3.95461559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.857670545578</t>
+    <t xml:space="preserve">3.85767030715942</t>
   </si>
   <si>
     <t xml:space="preserve">3.81412720680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90614318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86136722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84288239479065</t>
+    <t xml:space="preserve">3.90614295005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86136746406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84288215637207</t>
   </si>
   <si>
     <t xml:space="preserve">3.90162467956543</t>
@@ -4550,43 +4550,43 @@
     <t xml:space="preserve">3.94845390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98871064186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10085487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06593751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04211282730103</t>
+    <t xml:space="preserve">3.98871040344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10085439682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06593799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04211235046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.02321624755859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0417013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073881149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679829597473</t>
+    <t xml:space="preserve">4.04170179367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679758071899</t>
   </si>
   <si>
     <t xml:space="preserve">3.98419213294983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97186875343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81536030769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73607850074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53438401222229</t>
+    <t xml:space="preserve">3.97186851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81535959243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607897758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53438353538513</t>
   </si>
   <si>
     <t xml:space="preserve">3.54835057258606</t>
@@ -4598,25 +4598,25 @@
     <t xml:space="preserve">3.47030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57956981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66706705093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55040383338928</t>
+    <t xml:space="preserve">3.57956957817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66706681251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55040407180786</t>
   </si>
   <si>
     <t xml:space="preserve">3.42593669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38609075546265</t>
+    <t xml:space="preserve">3.38609099388123</t>
   </si>
   <si>
     <t xml:space="preserve">3.44154667854309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34870958328247</t>
+    <t xml:space="preserve">3.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">3.28873491287231</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">3.34542322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37910771369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46290707588196</t>
+    <t xml:space="preserve">3.37910747528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46290731430054</t>
   </si>
   <si>
     <t xml:space="preserve">3.49823474884033</t>
@@ -4646,55 +4646,55 @@
     <t xml:space="preserve">3.52740049362183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5976448059082</t>
+    <t xml:space="preserve">3.59764432907104</t>
   </si>
   <si>
     <t xml:space="preserve">3.60257434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71512818336487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67405033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7126636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72950577735901</t>
+    <t xml:space="preserve">3.71512842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405104637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71266388893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72950601577759</t>
   </si>
   <si>
     <t xml:space="preserve">3.77304935455322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7578501701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037939071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95913362503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11605358123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14727306365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274188995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1982102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22203588485718</t>
+    <t xml:space="preserve">3.75784993171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452557563782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217662811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913434028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11605405807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14727354049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19821071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22203540802002</t>
   </si>
   <si>
     <t xml:space="preserve">4.23682451248169</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">4.17767095565796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15959739685059</t>
+    <t xml:space="preserve">4.15959692001343</t>
   </si>
   <si>
     <t xml:space="preserve">4.2335376739502</t>
@@ -4715,13 +4715,13 @@
     <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19492340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2179274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31323003768921</t>
+    <t xml:space="preserve">4.19492387771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21792793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31322956085205</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
@@ -4733,13 +4733,13 @@
     <t xml:space="preserve">4.27708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29186868667603</t>
+    <t xml:space="preserve">4.29186964035034</t>
   </si>
   <si>
     <t xml:space="preserve">4.2507905960083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29022598266602</t>
+    <t xml:space="preserve">4.29022693634033</t>
   </si>
   <si>
     <t xml:space="preserve">4.27050828933716</t>
@@ -4748,10 +4748,10 @@
     <t xml:space="preserve">4.31158685684204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31487321853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1530237197876</t>
+    <t xml:space="preserve">4.31487274169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15302324295044</t>
   </si>
   <si>
     <t xml:space="preserve">4.14891672134399</t>
@@ -4769,13 +4769,13 @@
     <t xml:space="preserve">4.16863346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1908164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17191982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14809370040894</t>
+    <t xml:space="preserve">4.19081592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17192029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14809465408325</t>
   </si>
   <si>
     <t xml:space="preserve">4.13248491287231</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">4.24832582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35430860519409</t>
+    <t xml:space="preserve">4.35430812835693</t>
   </si>
   <si>
     <t xml:space="preserve">4.50794124603271</t>
@@ -4793,19 +4793,19 @@
     <t xml:space="preserve">4.50054693222046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6016001701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59995746612549</t>
+    <t xml:space="preserve">4.60159969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59995603561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.54819822311401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62542581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68868589401245</t>
+    <t xml:space="preserve">4.62542533874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68868637084961</t>
   </si>
   <si>
     <t xml:space="preserve">4.70593929290771</t>
@@ -4817,19 +4817,19 @@
     <t xml:space="preserve">4.73222970962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73551511764526</t>
+    <t xml:space="preserve">4.73551559448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.64760780334473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64185667037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65548515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68103551864624</t>
+    <t xml:space="preserve">4.6418571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65548467636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6810359954834</t>
   </si>
   <si>
     <t xml:space="preserve">4.66570472717285</t>
@@ -4841,25 +4841,25 @@
     <t xml:space="preserve">4.67166709899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62737798690796</t>
+    <t xml:space="preserve">4.6273775100708</t>
   </si>
   <si>
     <t xml:space="preserve">4.59160566329956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110269546509</t>
+    <t xml:space="preserve">4.49110317230225</t>
   </si>
   <si>
     <t xml:space="preserve">4.58394002914429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5669059753418</t>
+    <t xml:space="preserve">4.56690549850464</t>
   </si>
   <si>
     <t xml:space="preserve">4.58138513565063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5643515586853</t>
+    <t xml:space="preserve">4.56435060501099</t>
   </si>
   <si>
     <t xml:space="preserve">4.55327844619751</t>
@@ -4868,13 +4868,13 @@
     <t xml:space="preserve">4.54816818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60864019393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58223676681519</t>
+    <t xml:space="preserve">4.60863971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60182619094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58223724365234</t>
   </si>
   <si>
     <t xml:space="preserve">4.5881986618042</t>
@@ -4886,10 +4886,10 @@
     <t xml:space="preserve">4.55924034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55668592453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52687501907349</t>
+    <t xml:space="preserve">4.55668497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687549591064</t>
   </si>
   <si>
     <t xml:space="preserve">4.46214485168457</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">4.48003149032593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45788669586182</t>
+    <t xml:space="preserve">4.45788621902466</t>
   </si>
   <si>
     <t xml:space="preserve">4.51920986175537</t>
@@ -4916,13 +4916,13 @@
     <t xml:space="preserve">4.5149507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54305744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50984144210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5311336517334</t>
+    <t xml:space="preserve">4.54305839538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.509840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53113412857056</t>
   </si>
   <si>
     <t xml:space="preserve">4.53028202056885</t>
@@ -4931,10 +4931,10 @@
     <t xml:space="preserve">4.53624391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45192432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56860971450806</t>
+    <t xml:space="preserve">4.4519248008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56860876083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.46810674667358</t>
@@ -4946,19 +4946,19 @@
     <t xml:space="preserve">4.50302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58905076980591</t>
+    <t xml:space="preserve">4.58905029296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.66740846633911</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68784999847412</t>
+    <t xml:space="preserve">4.68784952163696</t>
   </si>
   <si>
     <t xml:space="preserve">4.69040489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59245729446411</t>
+    <t xml:space="preserve">4.59245777130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.65378093719482</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">4.69125652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77813196182251</t>
+    <t xml:space="preserve">4.77813148498535</t>
   </si>
   <si>
     <t xml:space="preserve">4.79261112213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77131795883179</t>
+    <t xml:space="preserve">4.77131843566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.75683879852295</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">4.82242107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98169231414795</t>
+    <t xml:space="preserve">4.98169183731079</t>
   </si>
   <si>
     <t xml:space="preserve">5.02853631973267</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">4.90503740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94762372970581</t>
+    <t xml:space="preserve">4.94762325286865</t>
   </si>
   <si>
     <t xml:space="preserve">4.97402667999268</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">5.05153322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1341495513916</t>
+    <t xml:space="preserve">5.13414859771729</t>
   </si>
   <si>
     <t xml:space="preserve">5.15799760818481</t>
@@ -5021,31 +5021,31 @@
     <t xml:space="preserve">5.18695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2508339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979326248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19376945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19462108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18440008163452</t>
+    <t xml:space="preserve">5.25083446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19376993179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19462060928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18440055847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.2482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21165561676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20569324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18951082229614</t>
+    <t xml:space="preserve">5.2116551399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20569372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1895112991333</t>
   </si>
   <si>
     <t xml:space="preserve">5.14777660369873</t>
@@ -5060,28 +5060,28 @@
     <t xml:space="preserve">5.12733554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09156370162964</t>
+    <t xml:space="preserve">5.09156322479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.02598142623901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1179666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14351749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13670492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08049154281616</t>
+    <t xml:space="preserve">5.11796617507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14351797103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13670444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080491065979</t>
   </si>
   <si>
     <t xml:space="preserve">5.00809574127197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07112216949463</t>
+    <t xml:space="preserve">5.07112169265747</t>
   </si>
   <si>
     <t xml:space="preserve">5.07367706298828</t>
@@ -5096,7 +5096,7 @@
     <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14948034286499</t>
+    <t xml:space="preserve">5.14947986602783</t>
   </si>
   <si>
     <t xml:space="preserve">5.10774612426758</t>
@@ -5105,13 +5105,13 @@
     <t xml:space="preserve">5.15288686752319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1733283996582</t>
+    <t xml:space="preserve">5.17332792282104</t>
   </si>
   <si>
     <t xml:space="preserve">5.17247676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20484209060669</t>
+    <t xml:space="preserve">5.20484161376953</t>
   </si>
   <si>
     <t xml:space="preserve">5.16992139816284</t>
@@ -5120,22 +5120,22 @@
     <t xml:space="preserve">5.20228672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19632387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884971618652</t>
+    <t xml:space="preserve">5.19632434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884923934937</t>
   </si>
   <si>
     <t xml:space="preserve">5.17843866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22698640823364</t>
+    <t xml:space="preserve">5.2269868850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.23635530471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25339031219482</t>
+    <t xml:space="preserve">5.25338983535767</t>
   </si>
   <si>
     <t xml:space="preserve">5.31471300125122</t>
@@ -5147,46 +5147,46 @@
     <t xml:space="preserve">5.28916168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14266633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19291830062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17503213882446</t>
+    <t xml:space="preserve">5.14266681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1929178237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1750316619873</t>
   </si>
   <si>
     <t xml:space="preserve">5.2125072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30619621276855</t>
+    <t xml:space="preserve">5.3061957359314</t>
   </si>
   <si>
     <t xml:space="preserve">5.39136791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31300973892212</t>
+    <t xml:space="preserve">5.31300926208496</t>
   </si>
   <si>
     <t xml:space="preserve">5.34622716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34452390670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36070585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39647817611694</t>
+    <t xml:space="preserve">5.34452342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3607063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39647722244263</t>
   </si>
   <si>
     <t xml:space="preserve">5.44836759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45012664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47035455703735</t>
+    <t xml:space="preserve">5.45012617111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47035360336304</t>
   </si>
   <si>
     <t xml:space="preserve">5.55038642883301</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">5.5160870552063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4615592956543</t>
+    <t xml:space="preserve">5.46155977249146</t>
   </si>
   <si>
     <t xml:space="preserve">5.34370946884155</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">5.22673892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21706485748291</t>
+    <t xml:space="preserve">5.21706438064575</t>
   </si>
   <si>
     <t xml:space="preserve">5.20914888381958</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">5.36129951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32436037063599</t>
+    <t xml:space="preserve">5.32436084747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.23553371429443</t>
@@ -5231,10 +5231,10 @@
     <t xml:space="preserve">5.17484903335571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21002817153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2671947479248</t>
+    <t xml:space="preserve">5.21002864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26719427108765</t>
   </si>
   <si>
     <t xml:space="preserve">5.33227634429932</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">5.34195041656494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37273216247559</t>
+    <t xml:space="preserve">5.37273263931274</t>
   </si>
   <si>
     <t xml:space="preserve">5.39120149612427</t>
@@ -5258,16 +5258,16 @@
     <t xml:space="preserve">5.41406774520874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40791130065918</t>
+    <t xml:space="preserve">5.4079122543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.39383983612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36745595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46068000793457</t>
+    <t xml:space="preserve">5.36745548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46068048477173</t>
   </si>
   <si>
     <t xml:space="preserve">5.44484949111938</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">5.45188522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38768339157104</t>
+    <t xml:space="preserve">5.38768291473389</t>
   </si>
   <si>
     <t xml:space="preserve">5.56006097793579</t>
@@ -5291,13 +5291,13 @@
     <t xml:space="preserve">5.4747519493103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35338354110718</t>
+    <t xml:space="preserve">5.35338401794434</t>
   </si>
   <si>
     <t xml:space="preserve">5.31644535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25488233566284</t>
+    <t xml:space="preserve">5.25488185882568</t>
   </si>
   <si>
     <t xml:space="preserve">5.23113584518433</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">5.14582681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09042024612427</t>
+    <t xml:space="preserve">5.09041976928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856317520142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97872591018677</t>
+    <t xml:space="preserve">4.97872638702393</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
@@ -5321,19 +5321,19 @@
     <t xml:space="preserve">4.88726043701172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88462114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92859601974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02269983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08426332473755</t>
+    <t xml:space="preserve">4.88462257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92595720291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92859554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02270030975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">5.06051731109619</t>
@@ -5342,22 +5342,22 @@
     <t xml:space="preserve">5.03325366973877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05172300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04996347427368</t>
+    <t xml:space="preserve">5.05172252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04996395111084</t>
   </si>
   <si>
     <t xml:space="preserve">5.01390504837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99719476699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9664134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00511026382446</t>
+    <t xml:space="preserve">4.99719524383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96641302108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00511074066162</t>
   </si>
   <si>
     <t xml:space="preserve">5.07722759246826</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">5.05875873565674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0825047492981</t>
+    <t xml:space="preserve">5.08250379562378</t>
   </si>
   <si>
     <t xml:space="preserve">5.06139707565308</t>
@@ -5381,7 +5381,7 @@
     <t xml:space="preserve">5.30589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37713003158569</t>
+    <t xml:space="preserve">5.37712955474854</t>
   </si>
   <si>
     <t xml:space="preserve">5.4175853729248</t>
@@ -5399,7 +5399,7 @@
     <t xml:space="preserve">5.39032173156738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43869304656982</t>
+    <t xml:space="preserve">5.43869352340698</t>
   </si>
   <si>
     <t xml:space="preserve">5.49585962295532</t>
@@ -5408,16 +5408,16 @@
     <t xml:space="preserve">5.54247140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63305759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70781326293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64273166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6207447052002</t>
+    <t xml:space="preserve">5.63305807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70781373977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62074518203735</t>
   </si>
   <si>
     <t xml:space="preserve">5.61282968521118</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">5.64097309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65680360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66559886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65768337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70429563522339</t>
+    <t xml:space="preserve">5.65680408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66559791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6576828956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70429515838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.72276496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74738931655884</t>
+    <t xml:space="preserve">5.747389793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.760582447052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75882339477539</t>
+    <t xml:space="preserve">5.75882291793823</t>
   </si>
   <si>
     <t xml:space="preserve">5.75354623794556</t>
@@ -5459,10 +5459,10 @@
     <t xml:space="preserve">5.73155927658081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81510972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91185235977173</t>
+    <t xml:space="preserve">5.815110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91185283660889</t>
   </si>
   <si>
     <t xml:space="preserve">5.86611938476562</t>
@@ -5471,13 +5471,13 @@
     <t xml:space="preserve">5.85996294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89250421524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86436033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86963701248169</t>
+    <t xml:space="preserve">5.89250373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86436080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86963748931885</t>
   </si>
   <si>
     <t xml:space="preserve">5.90921401977539</t>
@@ -5489,22 +5489,22 @@
     <t xml:space="preserve">5.90041971206665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91888856887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361141204834</t>
+    <t xml:space="preserve">5.91888809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91361093521118</t>
   </si>
   <si>
     <t xml:space="preserve">5.88458871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89162397384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92504501342773</t>
+    <t xml:space="preserve">5.89162445068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92504453659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.86787843704224</t>
@@ -5531,31 +5531,31 @@
     <t xml:space="preserve">5.80092000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75638818740845</t>
+    <t xml:space="preserve">5.75638866424561</t>
   </si>
   <si>
     <t xml:space="preserve">5.74002981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72185373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69913291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68550157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76275014877319</t>
+    <t xml:space="preserve">5.72185325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69913339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551090240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68550109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76274967193604</t>
   </si>
   <si>
     <t xml:space="preserve">5.63824319839478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61824941635132</t>
+    <t xml:space="preserve">5.61824989318848</t>
   </si>
   <si>
     <t xml:space="preserve">5.56826496124268</t>
@@ -5564,10 +5564,10 @@
     <t xml:space="preserve">5.52191591262817</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48011064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41013240814209</t>
+    <t xml:space="preserve">5.48011112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41013288497925</t>
   </si>
   <si>
     <t xml:space="preserve">5.33833694458008</t>
@@ -5582,10 +5582,10 @@
     <t xml:space="preserve">5.37468910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38468551635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32652235031128</t>
+    <t xml:space="preserve">5.38468599319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32652282714844</t>
   </si>
   <si>
     <t xml:space="preserve">5.36469221115112</t>
@@ -5603,22 +5603,22 @@
     <t xml:space="preserve">5.34015417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39831781387329</t>
+    <t xml:space="preserve">5.39831829071045</t>
   </si>
   <si>
     <t xml:space="preserve">5.31925201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35469579696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48738145828247</t>
+    <t xml:space="preserve">5.35469532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48738098144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.54463577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5791711807251</t>
+    <t xml:space="preserve">5.57917070388794</t>
   </si>
   <si>
     <t xml:space="preserve">5.57099151611328</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">5.5700831413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57190084457397</t>
+    <t xml:space="preserve">5.57190036773682</t>
   </si>
   <si>
     <t xml:space="preserve">5.5200982093811</t>
@@ -5645,13 +5645,13 @@
     <t xml:space="preserve">5.54645395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51646327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52645969390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51373672485352</t>
+    <t xml:space="preserve">5.51646280288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52646017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51373624801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.52918672561646</t>
@@ -5660,16 +5660,16 @@
     <t xml:space="preserve">5.60552644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56099510192871</t>
+    <t xml:space="preserve">5.56099462509155</t>
   </si>
   <si>
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49465131759644</t>
+    <t xml:space="preserve">5.44375801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49465179443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.36832761764526</t>
@@ -5681,34 +5681,34 @@
     <t xml:space="preserve">5.29380464553833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1792950630188</t>
+    <t xml:space="preserve">5.17929553985596</t>
   </si>
   <si>
     <t xml:space="preserve">5.18656539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3374285697937</t>
+    <t xml:space="preserve">5.33742761611938</t>
   </si>
   <si>
     <t xml:space="preserve">5.31470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26563215255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25836181640625</t>
+    <t xml:space="preserve">5.26563262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25836133956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.33651924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41195011138916</t>
+    <t xml:space="preserve">5.411949634552</t>
   </si>
   <si>
     <t xml:space="preserve">5.49737787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190347671509</t>
+    <t xml:space="preserve">5.56190299987793</t>
   </si>
   <si>
     <t xml:space="preserve">5.53282117843628</t>
@@ -5726,22 +5726,22 @@
     <t xml:space="preserve">5.67277812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68004846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74820899963379</t>
+    <t xml:space="preserve">5.68004894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74820852279663</t>
   </si>
   <si>
     <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8581748008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91452121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13899612426758</t>
+    <t xml:space="preserve">5.85817432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91452074050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13899660110474</t>
   </si>
   <si>
     <t xml:space="preserve">6.13626956939697</t>
@@ -5750,7 +5750,7 @@
     <t xml:space="preserve">6.10173559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21806287765503</t>
+    <t xml:space="preserve">6.21806240081787</t>
   </si>
   <si>
     <t xml:space="preserve">6.19715976715088</t>
@@ -5762,13 +5762,13 @@
     <t xml:space="preserve">6.14444923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12082052230835</t>
+    <t xml:space="preserve">6.12082004547119</t>
   </si>
   <si>
     <t xml:space="preserve">6.06538248062134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00358390808105</t>
+    <t xml:space="preserve">6.00358438491821</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814371109009</t>
@@ -5780,16 +5780,16 @@
     <t xml:space="preserve">6.05265951156616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97086715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01630735397339</t>
+    <t xml:space="preserve">5.97086668014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01630687713623</t>
   </si>
   <si>
     <t xml:space="preserve">6.04902458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13445234298706</t>
+    <t xml:space="preserve">6.1344518661499</t>
   </si>
   <si>
     <t xml:space="preserve">6.12172937393188</t>
@@ -5801,13 +5801,13 @@
     <t xml:space="preserve">6.17807483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09810018539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06992673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904897689819</t>
+    <t xml:space="preserve">6.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904945373535</t>
   </si>
   <si>
     <t xml:space="preserve">6.03539180755615</t>
@@ -5816,7 +5816,7 @@
     <t xml:space="preserve">5.95632600784302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75911474227905</t>
+    <t xml:space="preserve">5.75911426544189</t>
   </si>
   <si>
     <t xml:space="preserve">5.74275588989258</t>
@@ -5846,28 +5846,28 @@
     <t xml:space="preserve">5.90452432632446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9017972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00449323654175</t>
+    <t xml:space="preserve">5.90179777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00449275970459</t>
   </si>
   <si>
     <t xml:space="preserve">5.98449897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02812147140503</t>
+    <t xml:space="preserve">6.02812194824219</t>
   </si>
   <si>
     <t xml:space="preserve">6.04266262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09446477890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11809396743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16989612579346</t>
+    <t xml:space="preserve">6.09446430206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11809349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1698956489563</t>
   </si>
   <si>
     <t xml:space="preserve">6.25714159011841</t>
@@ -5879,31 +5879,31 @@
     <t xml:space="preserve">6.1262731552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15081071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13081693649292</t>
+    <t xml:space="preserve">6.15081119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13081741333008</t>
   </si>
   <si>
     <t xml:space="preserve">6.16179513931274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25191259384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2613000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24252510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22375059127808</t>
+    <t xml:space="preserve">6.18150854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468996047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25191211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26129961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24252557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22375106811523</t>
   </si>
   <si>
     <t xml:space="preserve">6.18995666503906</t>
@@ -5921,40 +5921,40 @@
     <t xml:space="preserve">5.91209363937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03600549697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03412818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01629209518433</t>
+    <t xml:space="preserve">6.03600597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03412866592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01629257202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.04351568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10641050338745</t>
+    <t xml:space="preserve">6.10641002655029</t>
   </si>
   <si>
     <t xml:space="preserve">6.09139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16742753982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18714094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17587566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20216035842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30260419845581</t>
+    <t xml:space="preserve">6.16742706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17587614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19840526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2021598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30260372161865</t>
   </si>
   <si>
     <t xml:space="preserve">6.29791021347046</t>
@@ -5966,10 +5966,10 @@
     <t xml:space="preserve">6.41149616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42651605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44341278076172</t>
+    <t xml:space="preserve">6.42651557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44341230392456</t>
   </si>
   <si>
     <t xml:space="preserve">6.46594190597534</t>
@@ -5978,13 +5978,13 @@
     <t xml:space="preserve">6.47063589096069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46030950546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56638526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6189546585083</t>
+    <t xml:space="preserve">6.4603099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5663857460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61895418167114</t>
   </si>
   <si>
     <t xml:space="preserve">6.62177038192749</t>
@@ -6023,10 +6023,10 @@
     <t xml:space="preserve">6.71752071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7710280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535633087158</t>
+    <t xml:space="preserve">6.77102756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535680770874</t>
   </si>
   <si>
     <t xml:space="preserve">6.7785382270813</t>
@@ -6038,7 +6038,7 @@
     <t xml:space="preserve">6.55605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52883672714233</t>
+    <t xml:space="preserve">6.52883625030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147557258606</t>
@@ -6050,7 +6050,7 @@
     <t xml:space="preserve">6.57201766967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55418252944946</t>
+    <t xml:space="preserve">6.5541820526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.63303518295288</t>
@@ -6059,7 +6059,7 @@
     <t xml:space="preserve">6.73629522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76727342605591</t>
+    <t xml:space="preserve">6.76727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.83861589431763</t>
@@ -6071,22 +6071,22 @@
     <t xml:space="preserve">6.88273620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88743019104004</t>
+    <t xml:space="preserve">6.88742971420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.73066282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73723363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75976371765137</t>
+    <t xml:space="preserve">6.73723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75976324081421</t>
   </si>
   <si>
     <t xml:space="preserve">6.74756002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76633453369141</t>
+    <t xml:space="preserve">6.76633405685425</t>
   </si>
   <si>
     <t xml:space="preserve">6.70062351226807</t>
@@ -6101,7 +6101,7 @@
     <t xml:space="preserve">6.58234405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60017967224121</t>
+    <t xml:space="preserve">6.60018014907837</t>
   </si>
   <si>
     <t xml:space="preserve">6.56920194625854</t>
@@ -6119,10 +6119,10 @@
     <t xml:space="preserve">6.34109163284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37206935882568</t>
+    <t xml:space="preserve">6.21436309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37206983566284</t>
   </si>
   <si>
     <t xml:space="preserve">6.28852272033691</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">6.32888841629028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072641372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32607221603394</t>
+    <t xml:space="preserve">6.30072593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32607173919678</t>
   </si>
   <si>
     <t xml:space="preserve">6.3551721572876</t>
@@ -6176,7 +6176,7 @@
     <t xml:space="preserve">6.48565530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58891487121582</t>
+    <t xml:space="preserve">6.58891534805298</t>
   </si>
   <si>
     <t xml:space="preserve">6.49222612380981</t>
@@ -6197,7 +6197,7 @@
     <t xml:space="preserve">6.4640645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59454727172852</t>
+    <t xml:space="preserve">6.59454774856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.58328247070312</t>
@@ -6209,22 +6209,22 @@
     <t xml:space="preserve">6.5654468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5588755607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60205698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46312570571899</t>
+    <t xml:space="preserve">6.55887603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60205745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46312618255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.49692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6170768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66870641708374</t>
+    <t xml:space="preserve">6.61707639694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6687068939209</t>
   </si>
   <si>
     <t xml:space="preserve">6.572350025177</t>
@@ -6744,6 +6744,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.32600021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34899997711182</t>
   </si>
 </sst>
 </file>
@@ -71718,7 +71721,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6497685185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>22070422</v>
@@ -71739,6 +71742,32 @@
         <v>2243</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494444444</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>14838732</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>8.36699962615967</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>8.29699993133545</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>8.33899974822998</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>8.34899997711182</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2244</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="2246">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22277045249939</t>
+    <t xml:space="preserve">2.27958202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22277021408081</t>
   </si>
   <si>
     <t xml:space="preserve">2.23223924636841</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">2.21448564529419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21685242652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20146608352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23460650444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21211814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17187643051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281869888306</t>
+    <t xml:space="preserve">2.21685290336609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20146584510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23460626602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21211838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1718761920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13281846046448</t>
   </si>
   <si>
     <t xml:space="preserve">2.15767359733582</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.09257578849792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16004037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20620036125183</t>
+    <t xml:space="preserve">2.16004061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20620012283325</t>
   </si>
   <si>
     <t xml:space="preserve">2.19436454772949</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">2.25236010551453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17306017875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987198829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849381446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07008814811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06772089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08665823936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090860366821</t>
+    <t xml:space="preserve">2.17305970191956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395372390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081401824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702105522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849429130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07008790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06772065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08665871620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090884208679</t>
   </si>
   <si>
     <t xml:space="preserve">2.09375977516174</t>
@@ -131,70 +131,70 @@
     <t xml:space="preserve">2.16477465629578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057158470154</t>
+    <t xml:space="preserve">2.15057134628296</t>
   </si>
   <si>
     <t xml:space="preserve">2.15649008750916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14228653907776</t>
+    <t xml:space="preserve">2.14228630065918</t>
   </si>
   <si>
     <t xml:space="preserve">2.15293908119202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09494352340698</t>
+    <t xml:space="preserve">2.0949432849884</t>
   </si>
   <si>
     <t xml:space="preserve">2.18016147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19199705123901</t>
+    <t xml:space="preserve">2.19199681282043</t>
   </si>
   <si>
     <t xml:space="preserve">2.21330189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19791507720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714215278625</t>
+    <t xml:space="preserve">2.19791483879089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16714191436768</t>
   </si>
   <si>
     <t xml:space="preserve">2.17542719841003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24170780181885</t>
+    <t xml:space="preserve">2.24170732498169</t>
   </si>
   <si>
     <t xml:space="preserve">2.25354337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31508994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30798840522766</t>
+    <t xml:space="preserve">2.31509017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30798864364624</t>
   </si>
   <si>
     <t xml:space="preserve">2.30207061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30562114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3174569606781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3115394115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088710784912</t>
+    <t xml:space="preserve">2.30562162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982493400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31153917312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088663101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.31390619277954</t>
@@ -203,37 +203,37 @@
     <t xml:space="preserve">2.35059714317322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36716747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680513381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2949686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27366471290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595816612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22632122039795</t>
+    <t xml:space="preserve">2.36716771125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.306804895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2736644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595864295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22632145881653</t>
   </si>
   <si>
     <t xml:space="preserve">2.23579001426697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21921992301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26182866096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129745483398</t>
+    <t xml:space="preserve">2.21921968460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26182889938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129721641541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337522506714</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39912390708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112858772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32929277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30917191505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941434860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071871757507</t>
+    <t xml:space="preserve">2.39912438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3423125743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112882614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3091721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941363334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071847915649</t>
   </si>
   <si>
     <t xml:space="preserve">2.37663626670837</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">2.33757781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35296440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33166003227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36124968528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33994555473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385842323303</t>
+    <t xml:space="preserve">2.3529646396637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3316605091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36124992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33994507789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385866165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.41096043586731</t>
@@ -293,37 +293,37 @@
     <t xml:space="preserve">2.42989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42516279220581</t>
+    <t xml:space="preserve">2.42516350746155</t>
   </si>
   <si>
     <t xml:space="preserve">2.43699908256531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38965606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37781977653503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463182449341</t>
+    <t xml:space="preserve">2.38965582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794087409973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37782025337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463206291199</t>
   </si>
   <si>
     <t xml:space="preserve">2.44173359870911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43936657905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651540756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27839875221252</t>
+    <t xml:space="preserve">2.43936634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651564598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31864094734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2783989906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.37900328636169</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.43817043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44433403015137</t>
+    <t xml:space="preserve">2.44433355331421</t>
   </si>
   <si>
     <t xml:space="preserve">2.40735459327698</t>
@@ -341,79 +341,79 @@
     <t xml:space="preserve">2.46652102470398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21875953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013116836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627775192261</t>
+    <t xml:space="preserve">2.21875977516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2101309299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627751350403</t>
   </si>
   <si>
     <t xml:space="preserve">2.40365648269653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45296216011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049667358398</t>
+    <t xml:space="preserve">2.45296168327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049715042114</t>
   </si>
   <si>
     <t xml:space="preserve">2.45419502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39256262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37653803825378</t>
+    <t xml:space="preserve">2.39256286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37653851509094</t>
   </si>
   <si>
     <t xml:space="preserve">2.42214584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43940281867981</t>
+    <t xml:space="preserve">2.43940305709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.45912551879883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46035814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282362937927</t>
+    <t xml:space="preserve">2.46035838127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282315254211</t>
   </si>
   <si>
     <t xml:space="preserve">2.4467990398407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4763822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47268438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53801465034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52568769454956</t>
+    <t xml:space="preserve">2.48008036613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47638273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47268462181091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53801441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568817138672</t>
   </si>
   <si>
     <t xml:space="preserve">2.49240660667419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48131346702576</t>
+    <t xml:space="preserve">2.48131275177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.49117422103882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322292327881</t>
+    <t xml:space="preserve">2.52322268486023</t>
   </si>
   <si>
     <t xml:space="preserve">2.51089644432068</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">2.50350046157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49856948852539</t>
+    <t xml:space="preserve">2.49857044219971</t>
   </si>
   <si>
     <t xml:space="preserve">2.53308391571045</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">2.52938604354858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.470219373703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42461156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3974928855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40242409706116</t>
+    <t xml:space="preserve">2.47021913528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42461133003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39749336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40242385864258</t>
   </si>
   <si>
     <t xml:space="preserve">2.42830944061279</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">2.45172953605652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41351723670959</t>
+    <t xml:space="preserve">2.41351795196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.43200731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48747611045837</t>
+    <t xml:space="preserve">2.48747634887695</t>
   </si>
   <si>
     <t xml:space="preserve">2.48994159698486</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">2.53061866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49610447883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4455668926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105222702026</t>
+    <t xml:space="preserve">2.49610543251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44556617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105198860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.41475009918213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3913300037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41968083381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40981936454773</t>
+    <t xml:space="preserve">2.39132976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41968035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40981984138489</t>
   </si>
   <si>
     <t xml:space="preserve">2.4480311870575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41721510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42091369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926404953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41228532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37283992767334</t>
+    <t xml:space="preserve">2.41721558570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42091345787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926428794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37284064292908</t>
   </si>
   <si>
     <t xml:space="preserve">2.35928130149841</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">2.32476735115051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36051392555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33832621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31983613967896</t>
+    <t xml:space="preserve">2.36051344871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33832597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31983661651611</t>
   </si>
   <si>
     <t xml:space="preserve">2.36421179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35435032844543</t>
+    <t xml:space="preserve">2.35435080528259</t>
   </si>
   <si>
     <t xml:space="preserve">2.43693804740906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40858745574951</t>
+    <t xml:space="preserve">2.40858674049377</t>
   </si>
   <si>
     <t xml:space="preserve">2.4307746887207</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">2.41598272323608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37037491798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36297917366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35311818122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36667728424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32723259925842</t>
+    <t xml:space="preserve">2.37037467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36297941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35311794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3666775226593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38393425941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32723236083984</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711060523987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.243412733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24957609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28285717964172</t>
+    <t xml:space="preserve">2.24341297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22369027137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957585334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28285694122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.22862076759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24834299087524</t>
+    <t xml:space="preserve">2.24834322929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.31860399246216</t>
@@ -599,34 +599,34 @@
     <t xml:space="preserve">2.3075098991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29764914512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30257940292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586072921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33339595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336169242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47884774208069</t>
+    <t xml:space="preserve">2.29764890670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30257964134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3333957195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47884726524353</t>
   </si>
   <si>
     <t xml:space="preserve">2.49980282783508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53924703598022</t>
+    <t xml:space="preserve">2.5392472743988</t>
   </si>
   <si>
     <t xml:space="preserve">2.56513285636902</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">2.54910850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56266784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58115696907043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60211253166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883072853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622694969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896925926208</t>
+    <t xml:space="preserve">2.56266713142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58115744590759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60211229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252860069275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622671127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896949768066</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048013687134</t>
@@ -665,61 +665,61 @@
     <t xml:space="preserve">2.56636524200439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55403923988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650424957275</t>
+    <t xml:space="preserve">2.55403876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5565037727356</t>
   </si>
   <si>
     <t xml:space="preserve">2.55157351493835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57299423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56795382499695</t>
+    <t xml:space="preserve">2.57299470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56795406341553</t>
   </si>
   <si>
     <t xml:space="preserve">2.52763295173645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50873231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47849178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42557001113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43439078330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43565082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825077056885</t>
+    <t xml:space="preserve">2.50873255729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47849130630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42556953430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43564987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825100898743</t>
   </si>
   <si>
     <t xml:space="preserve">2.46715116500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41927027702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069075584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5440137386322</t>
+    <t xml:space="preserve">2.41927003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54401326179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.55031371116638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54023313522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53267312049866</t>
+    <t xml:space="preserve">2.54023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53267335891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.49361205101013</t>
@@ -734,91 +734,91 @@
     <t xml:space="preserve">2.52133297920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52637314796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50369215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787396430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283331871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57803416252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59945511817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60323524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62717652320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63347554206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473629951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961579322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63977670669556</t>
+    <t xml:space="preserve">2.5263729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50369238853455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5200731754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283403396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57803440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59945559501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6032350063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6082751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62717604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851618766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961531639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6523768901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63977646827698</t>
   </si>
   <si>
     <t xml:space="preserve">2.65867638587952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71033787727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151829719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7342791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74183964729309</t>
+    <t xml:space="preserve">2.71033835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71537828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73427939414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74183940887451</t>
   </si>
   <si>
     <t xml:space="preserve">2.75191950798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78090023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77460026741028</t>
+    <t xml:space="preserve">2.78090071678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964043617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7746000289917</t>
   </si>
   <si>
     <t xml:space="preserve">2.76199960708618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208042144775</t>
+    <t xml:space="preserve">2.77208018302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.74309897422791</t>
@@ -833,73 +833,73 @@
     <t xml:space="preserve">2.72671890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67253756523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907831192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8048415184021</t>
+    <t xml:space="preserve">2.67253708839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907807350159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80484127998352</t>
   </si>
   <si>
     <t xml:space="preserve">2.79098057746887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77711939811707</t>
+    <t xml:space="preserve">2.77712035179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.77081966400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74939942359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78720045089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7935004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650229454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422322273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792277336121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658310890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8791835308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87666296958923</t>
+    <t xml:space="preserve">2.74939966201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78720021247864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650277137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88422346115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86658263206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87918329238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87414336204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87666320800781</t>
   </si>
   <si>
     <t xml:space="preserve">2.88044333457947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94974541664124</t>
+    <t xml:space="preserve">2.94974493980408</t>
   </si>
   <si>
     <t xml:space="preserve">2.91572403907776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92202425003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998666763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526665687561</t>
+    <t xml:space="preserve">2.9220244884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100522041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998595237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526713371277</t>
   </si>
   <si>
     <t xml:space="preserve">2.98628568649292</t>
@@ -911,145 +911,145 @@
     <t xml:space="preserve">3.02912759780884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96108531951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762654304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990561485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156710624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11354994773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582854270935</t>
+    <t xml:space="preserve">2.96108555793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148724555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11355018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582925796509</t>
   </si>
   <si>
     <t xml:space="preserve">3.05180835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05558800697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810832977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440877914429</t>
+    <t xml:space="preserve">3.05558848381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810856819153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440854072571</t>
   </si>
   <si>
     <t xml:space="preserve">3.09968948364258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10724949836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749003410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10347032546997</t>
+    <t xml:space="preserve">3.10724997520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204889297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749051094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10346937179565</t>
   </si>
   <si>
     <t xml:space="preserve">3.11858987808228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02408766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04928827285767</t>
+    <t xml:space="preserve">3.02408742904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04928851127625</t>
   </si>
   <si>
     <t xml:space="preserve">2.98754668235779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95730519294739</t>
+    <t xml:space="preserve">2.95730543136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.99888682365417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98880648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97368550300598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778745651245</t>
+    <t xml:space="preserve">2.98880624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478510856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02282738685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778697967529</t>
   </si>
   <si>
     <t xml:space="preserve">3.06944847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13245058059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13119006156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10095000267029</t>
+    <t xml:space="preserve">3.13245129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13119053840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094952583313</t>
   </si>
   <si>
     <t xml:space="preserve">3.12489080429077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12867069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0933895111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07926940917969</t>
+    <t xml:space="preserve">3.12867045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09338879585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.119060754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07927012443542</t>
   </si>
   <si>
     <t xml:space="preserve">3.11777687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13831353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953881263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703036308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13189673423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040348052979</t>
+    <t xml:space="preserve">3.13831377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953809738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595608711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13703060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13189649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040324211121</t>
   </si>
   <si>
     <t xml:space="preserve">3.19864153862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19735813140869</t>
+    <t xml:space="preserve">3.19735765457153</t>
   </si>
   <si>
     <t xml:space="preserve">3.21532821655273</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">3.19222378730774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16013479232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22816324234009</t>
+    <t xml:space="preserve">3.1601345539093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816395759583</t>
   </si>
   <si>
     <t xml:space="preserve">3.2506263256073</t>
@@ -1070,64 +1070,64 @@
     <t xml:space="preserve">3.25383496284485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025223731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987910270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26346158981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29876017570496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950692176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271389007568</t>
+    <t xml:space="preserve">3.23458075523376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607424736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987957954407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26346182823181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29875922203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950668334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.30196833610535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33084893226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122182846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3661470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159567832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629685401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517768859863</t>
+    <t xml:space="preserve">3.33084845542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122230529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614680290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405780792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159448623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629733085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517721176147</t>
   </si>
   <si>
     <t xml:space="preserve">3.28592395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28913283348083</t>
+    <t xml:space="preserve">3.28913187980652</t>
   </si>
   <si>
     <t xml:space="preserve">3.2730884552002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24099898338318</t>
+    <t xml:space="preserve">3.24099946022034</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708968162537</t>
@@ -1139,43 +1139,43 @@
     <t xml:space="preserve">3.25704312324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31480383872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801247596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32763981819153</t>
+    <t xml:space="preserve">3.3148033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801295280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764005661011</t>
   </si>
   <si>
     <t xml:space="preserve">3.3083860874176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32443046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35010194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39502716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39181780815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4142804145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45599579811096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44316053390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957876205444</t>
+    <t xml:space="preserve">3.32443022727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.350102186203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39502739906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181804656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41428065299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748881340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599627494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44316077232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957828521729</t>
   </si>
   <si>
     <t xml:space="preserve">3.45920515060425</t>
@@ -1184,103 +1184,103 @@
     <t xml:space="preserve">3.46241426467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4399516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42390751838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38539981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256455421448</t>
+    <t xml:space="preserve">3.43995141983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42390704154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38540029525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3725643157959</t>
   </si>
   <si>
     <t xml:space="preserve">3.37898182868958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39823579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689354896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674230575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883225440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51375603675842</t>
+    <t xml:space="preserve">3.39823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3468930721283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331082344055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786194801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883130073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.513756275177</t>
   </si>
   <si>
     <t xml:space="preserve">3.50092077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44636940956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054787635803</t>
+    <t xml:space="preserve">3.44636964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054739952087</t>
   </si>
   <si>
     <t xml:space="preserve">3.54584527015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56189060211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114337921143</t>
+    <t xml:space="preserve">3.56189012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114385604858</t>
   </si>
   <si>
     <t xml:space="preserve">3.53621864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48166704177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50413012504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293816566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234147071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711615562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40144491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44611382484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4297513961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3773889541626</t>
+    <t xml:space="preserve">3.48166680335999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50412964820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107058525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711591720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40144467353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44611406326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047884941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738800048828</t>
   </si>
   <si>
     <t xml:space="preserve">3.35382509231567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31717133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3446626663208</t>
+    <t xml:space="preserve">3.31717157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34466218948364</t>
   </si>
   <si>
     <t xml:space="preserve">3.31586241722107</t>
@@ -1289,67 +1289,67 @@
     <t xml:space="preserve">3.25302743911743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21310019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146687507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019246101379</t>
+    <t xml:space="preserve">3.21310091018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146639823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019198417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.09070348739624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03310465812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06844973564148</t>
+    <t xml:space="preserve">3.03310441970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06844925880432</t>
   </si>
   <si>
     <t xml:space="preserve">3.0461950302124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12866592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652014732361</t>
+    <t xml:space="preserve">3.12866640090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652038574219</t>
   </si>
   <si>
     <t xml:space="preserve">3.18102884292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.127357006073</t>
+    <t xml:space="preserve">3.12735724449158</t>
   </si>
   <si>
     <t xml:space="preserve">3.12212109565735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07630348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466546058655</t>
+    <t xml:space="preserve">3.07630324363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466522216797</t>
   </si>
   <si>
     <t xml:space="preserve">3.15877485275269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16597437858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801098823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688446998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0769579410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09528517723083</t>
+    <t xml:space="preserve">3.16597461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801146507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1168839931488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0481584072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07695817947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09528493881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.12670230865479</t>
@@ -1358,85 +1358,85 @@
     <t xml:space="preserve">3.1679379940033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1653196811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16335606575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18757438659668</t>
+    <t xml:space="preserve">3.16531944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1633563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18757367134094</t>
   </si>
   <si>
     <t xml:space="preserve">3.17448353767395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19673681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150137901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13913869857788</t>
+    <t xml:space="preserve">3.19673705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684645652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1391384601593</t>
   </si>
   <si>
     <t xml:space="preserve">3.17513823509216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13259291648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979363441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630021095276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320888519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844598770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277180671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764410972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240748405457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3132438659668</t>
+    <t xml:space="preserve">3.13259315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979315757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630044937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844527244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538964271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30277132987976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764363288879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324410438538</t>
   </si>
   <si>
     <t xml:space="preserve">3.34597086906433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34727931022644</t>
+    <t xml:space="preserve">3.3472797870636</t>
   </si>
   <si>
     <t xml:space="preserve">3.40095186233521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39833331108093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393330574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487933158875</t>
+    <t xml:space="preserve">3.39833307266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393425941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487885475159</t>
   </si>
   <si>
     <t xml:space="preserve">3.3930971622467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44284248352051</t>
+    <t xml:space="preserve">3.44284176826477</t>
   </si>
   <si>
     <t xml:space="preserve">3.43629670143127</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">3.448077917099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49520421028137</t>
+    <t xml:space="preserve">3.49520444869995</t>
   </si>
   <si>
     <t xml:space="preserve">3.48211359977722</t>
@@ -1454,220 +1454,220 @@
     <t xml:space="preserve">3.52531290054321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5266227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891501426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3210985660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3184802532196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34335255622864</t>
+    <t xml:space="preserve">3.5266215801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31848096847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34335279464722</t>
   </si>
   <si>
     <t xml:space="preserve">3.36298894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2379732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153588294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20590090751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655608177185</t>
+    <t xml:space="preserve">3.23797369003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590138435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655584335327</t>
   </si>
   <si>
     <t xml:space="preserve">3.19542813301086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1921558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037414550781</t>
+    <t xml:space="preserve">3.19215536117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037462234497</t>
   </si>
   <si>
     <t xml:space="preserve">3.10772109031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08415818214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888705253601</t>
+    <t xml:space="preserve">3.08415722846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888657569885</t>
   </si>
   <si>
     <t xml:space="preserve">3.11033892631531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07826685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.098557472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324809074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564878463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386804580688</t>
+    <t xml:space="preserve">3.0782675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855818748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13324761390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564854621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386756896973</t>
   </si>
   <si>
     <t xml:space="preserve">3.00692296028137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11557579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12932085990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888330459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401076316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204762458801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481240272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10641193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452202796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808517456055</t>
+    <t xml:space="preserve">3.11557555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12932109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888354301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401028633118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746521949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10641169548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0645215511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808469772339</t>
   </si>
   <si>
     <t xml:space="preserve">3.12342953681946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10313940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11361193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510277748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1555016040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739294052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186498641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364667892456</t>
+    <t xml:space="preserve">3.10313963890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11361145973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15550184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1973922252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1718647480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895701408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364644050598</t>
   </si>
   <si>
     <t xml:space="preserve">3.17252016067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19411969184875</t>
+    <t xml:space="preserve">3.19411873817444</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048283576965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20917367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113729476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.179523229599</t>
+    <t xml:space="preserve">3.20917391777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113634109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952346801758</t>
   </si>
   <si>
     <t xml:space="preserve">3.15530896186829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13647484779358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212462425232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338014602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844721794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08401036262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347302436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499769210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468294143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08333706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0692126750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00598478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99051427841187</t>
+    <t xml:space="preserve">3.13647556304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17212438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338086128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844674110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08401012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432511329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.044997215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468270301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0833375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06921172142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00598526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99051403999329</t>
   </si>
   <si>
     <t xml:space="preserve">3.01203894615173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98042511940002</t>
+    <t xml:space="preserve">2.9804253578186</t>
   </si>
   <si>
     <t xml:space="preserve">2.97638916969299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96629977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791383743286</t>
+    <t xml:space="preserve">2.96630001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99791312217712</t>
   </si>
   <si>
     <t xml:space="preserve">2.98513340950012</t>
@@ -1676,61 +1676,61 @@
     <t xml:space="preserve">2.95082950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96293640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150184631348</t>
+    <t xml:space="preserve">2.96293663978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150136947632</t>
   </si>
   <si>
     <t xml:space="preserve">2.92997765541077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94006705284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836359024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540555953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8862566947937</t>
+    <t xml:space="preserve">2.94006752967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836454391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540532112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85397100448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88625717163086</t>
   </si>
   <si>
     <t xml:space="preserve">2.88558411598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94477534294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091866493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719470024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584858894348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06652140617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05979537963867</t>
+    <t xml:space="preserve">2.94477605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584882736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894376754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06652212142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05979514122009</t>
   </si>
   <si>
     <t xml:space="preserve">3.03625345230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05912256240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629629135132</t>
+    <t xml:space="preserve">3.05912303924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629605293274</t>
   </si>
   <si>
     <t xml:space="preserve">3.07392120361328</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">3.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10149836540222</t>
+    <t xml:space="preserve">3.1014986038208</t>
   </si>
   <si>
     <t xml:space="preserve">3.08064675331116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96764540672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94746613502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562695503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04096221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99993181228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9750440120697</t>
+    <t xml:space="preserve">2.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9474663734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562743186951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04096126556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99993133544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97504425048828</t>
   </si>
   <si>
     <t xml:space="preserve">2.94410276412964</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">2.92325162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88423895835876</t>
+    <t xml:space="preserve">2.88423871994019</t>
   </si>
   <si>
     <t xml:space="preserve">2.99589562416077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96898984909058</t>
+    <t xml:space="preserve">2.96899056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.93468594551086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9797523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446083068848</t>
+    <t xml:space="preserve">2.97975206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98446035385132</t>
   </si>
   <si>
     <t xml:space="preserve">2.96697235107422</t>
@@ -1796,73 +1796,73 @@
     <t xml:space="preserve">2.94612073898315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95957350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94544816017151</t>
+    <t xml:space="preserve">2.95957374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91518020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94544839859009</t>
   </si>
   <si>
     <t xml:space="preserve">2.96428203582764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9716808795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00665783882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01540184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99455046653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06853938102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.133784532547</t>
+    <t xml:space="preserve">2.97168111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00665736198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01540160179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228009223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99455094337463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683687210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06853985786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378500938416</t>
   </si>
   <si>
     <t xml:space="preserve">3.13243961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16472578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19835686683655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20441126823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21517300605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22189950942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23804259300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22727942466736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24880409240723</t>
+    <t xml:space="preserve">3.1647253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19835734367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20441102981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2151734828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037484169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22189903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22728037834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24880456924438</t>
   </si>
   <si>
     <t xml:space="preserve">3.19297647476196</t>
@@ -1871,49 +1871,49 @@
     <t xml:space="preserve">3.19364905357361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333430290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3167405128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37660431861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37525916099548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256813049316</t>
+    <t xml:space="preserve">3.18961310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333406448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31674003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3766040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37525939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256836891174</t>
   </si>
   <si>
     <t xml:space="preserve">3.37122344970703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44655752182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4882607460022</t>
+    <t xml:space="preserve">3.44655776023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270108222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48826122283936</t>
   </si>
   <si>
     <t xml:space="preserve">3.39543771743774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39274764060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965270042419</t>
+    <t xml:space="preserve">3.39274740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965293884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.42099785804749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46808195114136</t>
+    <t xml:space="preserve">3.46808266639709</t>
   </si>
   <si>
     <t xml:space="preserve">3.46673679351807</t>
@@ -1925,94 +1925,94 @@
     <t xml:space="preserve">3.47346258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5313093662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440359115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51113033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978493690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032227516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275675773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446718215942</t>
+    <t xml:space="preserve">3.53130912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767756462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440454483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51112985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978589057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.524582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275723457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.574467420578</t>
   </si>
   <si>
     <t xml:space="preserve">3.54683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5786120891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690190315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56755828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6214451789856</t>
+    <t xml:space="preserve">3.57861185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58690237998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755781173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62144494056702</t>
   </si>
   <si>
     <t xml:space="preserve">3.61591815948486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63802528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57170343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137583732605</t>
+    <t xml:space="preserve">3.63802576065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57170414924622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137559890747</t>
   </si>
   <si>
     <t xml:space="preserve">3.54545140266418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52472519874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097794532776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59104752540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6034824848175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071969032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61730027198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282681465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61039113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61453604698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64631581306458</t>
+    <t xml:space="preserve">3.52472543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097842216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5910472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60348320007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6007194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61039137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61453676223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6242082118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64631533622742</t>
   </si>
   <si>
     <t xml:space="preserve">3.6698043346405</t>
@@ -2024,214 +2024,214 @@
     <t xml:space="preserve">3.67533135414124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67118692398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66427850723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7292172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80106616020203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863024711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205061912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79830288887024</t>
+    <t xml:space="preserve">3.67118620872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66427779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085861206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921776771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80106687545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205038070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7983033657074</t>
   </si>
   <si>
     <t xml:space="preserve">3.79001307487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79139423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895903587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83008193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225840568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258600234985</t>
+    <t xml:space="preserve">3.79139447212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895879745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350183486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258719444275</t>
   </si>
   <si>
     <t xml:space="preserve">3.93923711776733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94752764701843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92818260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94061851501465</t>
+    <t xml:space="preserve">3.94752717018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92818355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94061899185181</t>
   </si>
   <si>
     <t xml:space="preserve">3.90883946418762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338154792786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93440008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93370962142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92127442359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91022086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847636222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8756787776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564303398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379535675049</t>
+    <t xml:space="preserve">3.91091203689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338250160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.934401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9337100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92127418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847707748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564351081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379559516907</t>
   </si>
   <si>
     <t xml:space="preserve">3.81419253349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81695556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281065940857</t>
+    <t xml:space="preserve">3.81695604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281137466431</t>
   </si>
   <si>
     <t xml:space="preserve">3.8024480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82593679428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83629965782166</t>
+    <t xml:space="preserve">3.82593727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840749740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83629941940308</t>
   </si>
   <si>
     <t xml:space="preserve">3.89571285247803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85288023948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182620048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83491778373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80451965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85149884223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080790519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186075210571</t>
+    <t xml:space="preserve">3.85288071632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531567573547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85219049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8514986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">3.88880443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93094611167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690485954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068761825562</t>
+    <t xml:space="preserve">3.93094682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068833351135</t>
   </si>
   <si>
     <t xml:space="preserve">3.92403745651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99934029579163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906388282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84804463386536</t>
+    <t xml:space="preserve">3.99934053421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906245231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84804511070251</t>
   </si>
   <si>
     <t xml:space="preserve">3.87844133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94407343864441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581793785095</t>
+    <t xml:space="preserve">3.94407296180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581746101379</t>
   </si>
   <si>
     <t xml:space="preserve">4.01108551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06980752944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02628374099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010200500488</t>
+    <t xml:space="preserve">4.06980848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010105133057</t>
   </si>
   <si>
     <t xml:space="preserve">4.06911706924438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13889265060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19347095489502</t>
+    <t xml:space="preserve">4.13889312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1934700012207</t>
   </si>
   <si>
     <t xml:space="preserve">4.20037841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30884218215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26255559921265</t>
+    <t xml:space="preserve">4.30884265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26255512237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.27637243270874</t>
@@ -2240,25 +2240,25 @@
     <t xml:space="preserve">4.30538845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692468643188</t>
+    <t xml:space="preserve">4.3005518913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692420959473</t>
   </si>
   <si>
     <t xml:space="preserve">4.20314264297485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24182987213135</t>
+    <t xml:space="preserve">4.24182939529419</t>
   </si>
   <si>
     <t xml:space="preserve">4.23215818405151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32473230361938</t>
+    <t xml:space="preserve">4.32473278045654</t>
   </si>
   <si>
     <t xml:space="preserve">4.42697763442993</t>
@@ -2267,37 +2267,37 @@
     <t xml:space="preserve">4.45392179489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42145109176636</t>
+    <t xml:space="preserve">4.42145156860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.4283595085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42766857147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43941307067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49744462966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45668506622314</t>
+    <t xml:space="preserve">4.42766904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45668458938599</t>
   </si>
   <si>
     <t xml:space="preserve">4.48500967025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49951696395874</t>
+    <t xml:space="preserve">4.49951791763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.5312967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34407567977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4323992729187</t>
+    <t xml:space="preserve">4.34407615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43239879608154</t>
   </si>
   <si>
     <t xml:space="preserve">4.43310546875</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">4.47267436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41402769088745</t>
+    <t xml:space="preserve">4.41402816772461</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41332006454468</t>
+    <t xml:space="preserve">4.41332149505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.35891437530518</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">4.40908145904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37940454483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33418273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842372894287</t>
+    <t xml:space="preserve">4.37940502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711839675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33418321609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842277526855</t>
   </si>
   <si>
     <t xml:space="preserve">4.26493883132935</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">4.28472280502319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29461526870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24586057662964</t>
+    <t xml:space="preserve">4.29461479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24586153030396</t>
   </si>
   <si>
     <t xml:space="preserve">4.44087791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49316501617432</t>
+    <t xml:space="preserve">4.49316549301147</t>
   </si>
   <si>
     <t xml:space="preserve">4.40625524520874</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">4.46419525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44017124176025</t>
+    <t xml:space="preserve">4.44017171859741</t>
   </si>
   <si>
     <t xml:space="preserve">4.39706945419312</t>
@@ -2375,58 +2375,58 @@
     <t xml:space="preserve">4.68606233596802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65921258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72068548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76095962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70937871932983</t>
+    <t xml:space="preserve">4.6592116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71997785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72068500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76096057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70938014984131</t>
   </si>
   <si>
     <t xml:space="preserve">4.67758321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58572816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181169509888</t>
+    <t xml:space="preserve">4.62458944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58572721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181121826172</t>
   </si>
   <si>
     <t xml:space="preserve">4.67263698577881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.657799243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58007431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69878101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67405080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71361970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215837478638</t>
+    <t xml:space="preserve">4.65779876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58007526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69878149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67405033111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64649391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71361875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215789794922</t>
   </si>
   <si>
     <t xml:space="preserve">4.7553071975708</t>
@@ -2438,139 +2438,139 @@
     <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81678104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69100904464722</t>
+    <t xml:space="preserve">4.84080457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81678056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6910080909729</t>
   </si>
   <si>
     <t xml:space="preserve">4.77226591110229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83656406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78498411178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81536722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78145170211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78993082046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83161878585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80830144882202</t>
+    <t xml:space="preserve">4.8365650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78498458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81536769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78993034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.831618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80830097198486</t>
   </si>
   <si>
     <t xml:space="preserve">4.78357076644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82455253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76590633392334</t>
+    <t xml:space="preserve">4.8245530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590585708618</t>
   </si>
   <si>
     <t xml:space="preserve">4.84221744537354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86129522323608</t>
+    <t xml:space="preserve">4.86129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.84998941421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85564279556274</t>
+    <t xml:space="preserve">4.8556432723999</t>
   </si>
   <si>
     <t xml:space="preserve">4.87754678726196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90368986129761</t>
+    <t xml:space="preserve">4.90369033813477</t>
   </si>
   <si>
     <t xml:space="preserve">4.89733076095581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92347478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.882493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87471961975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.851402759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84716320037842</t>
+    <t xml:space="preserve">4.92347383499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87472009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85140323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84716367721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.93407249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89662408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85776281356812</t>
+    <t xml:space="preserve">4.89662456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8577618598938</t>
   </si>
   <si>
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401342391968</t>
+    <t xml:space="preserve">4.87401390075684</t>
   </si>
   <si>
     <t xml:space="preserve">4.82596588134766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80759429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78710412979126</t>
+    <t xml:space="preserve">4.80759477615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7871036529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.76943969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83303260803223</t>
+    <t xml:space="preserve">4.83303165435791</t>
   </si>
   <si>
     <t xml:space="preserve">4.85493564605713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84433650970459</t>
+    <t xml:space="preserve">4.84433698654175</t>
   </si>
   <si>
     <t xml:space="preserve">4.66698503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71785926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75601387023926</t>
+    <t xml:space="preserve">4.71785831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75601482391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.83727121353149</t>
@@ -2585,151 +2585,151 @@
     <t xml:space="preserve">4.93336629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94679260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09164190292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973648071289</t>
+    <t xml:space="preserve">4.94679164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09164142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973743438721</t>
   </si>
   <si>
     <t xml:space="preserve">5.0435938835144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09588050842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09517431259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10577344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10859870910645</t>
+    <t xml:space="preserve">4.9969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09588146209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09517383575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10577249526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1085991859436</t>
   </si>
   <si>
     <t xml:space="preserve">5.13686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16159296035767</t>
+    <t xml:space="preserve">5.16159343719482</t>
   </si>
   <si>
     <t xml:space="preserve">5.24073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22871828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24355602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45835828781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50453662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49082612991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44464874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49804210662842</t>
+    <t xml:space="preserve">5.22871780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2435564994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37780809402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45835876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50453567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4908275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44464921951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49804306030273</t>
   </si>
   <si>
     <t xml:space="preserve">5.64162588119507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53700494766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83571720123291</t>
+    <t xml:space="preserve">5.5370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83571767807007</t>
   </si>
   <si>
     <t xml:space="preserve">5.66760158538818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74769067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77222347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82272911071777</t>
+    <t xml:space="preserve">5.74769020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77222299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82272958755493</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602163314819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89993238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91652822494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91147708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8674635887146</t>
+    <t xml:space="preserve">5.89993333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91652870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91147756576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86746501922607</t>
   </si>
   <si>
     <t xml:space="preserve">5.92157936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97208642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05650520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18060731887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08464479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09258079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386854171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975419998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71161460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5124716758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62286615371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538879394531</t>
+    <t xml:space="preserve">5.97208595275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05650472640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917615890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18060636520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08464431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51247262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62286567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538974761963</t>
   </si>
   <si>
     <t xml:space="preserve">5.87684488296509</t>
@@ -2738,22 +2738,22 @@
     <t xml:space="preserve">5.69357585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1271767616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70436191558838</t>
+    <t xml:space="preserve">5.12717723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70436096191406</t>
   </si>
   <si>
     <t xml:space="preserve">3.77070426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05426549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830225944519</t>
+    <t xml:space="preserve">4.05426454544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830202102661</t>
   </si>
   <si>
     <t xml:space="preserve">4.1271390914917</t>
@@ -2762,13 +2762,13 @@
     <t xml:space="preserve">4.2497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20650768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24907779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30896425247192</t>
+    <t xml:space="preserve">4.20650720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24907732009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30896472930908</t>
   </si>
   <si>
     <t xml:space="preserve">4.5535626411438</t>
@@ -2777,22 +2777,22 @@
     <t xml:space="preserve">4.54562568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53047370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44100427627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60767650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57376527786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37823152542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378877639771</t>
+    <t xml:space="preserve">4.53047323226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60767698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57376480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37823057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378829956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.37895154953003</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">4.43018102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59974002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480291366577</t>
+    <t xml:space="preserve">4.59974098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480243682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.65601968765259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65169048309326</t>
+    <t xml:space="preserve">4.6516900062561</t>
   </si>
   <si>
     <t xml:space="preserve">4.47852373123169</t>
@@ -2819,34 +2819,34 @@
     <t xml:space="preserve">4.50882768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47996711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46770095825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33277463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31834363937378</t>
+    <t xml:space="preserve">4.47996664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46770000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33277559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3183445930481</t>
   </si>
   <si>
     <t xml:space="preserve">4.2757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25701475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37967443466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43739604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52397966384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4994478225708</t>
+    <t xml:space="preserve">4.25701427459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37967395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43739652633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52397871017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49944686889648</t>
   </si>
   <si>
     <t xml:space="preserve">4.33421802520752</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">4.39266157150269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37750959396362</t>
+    <t xml:space="preserve">4.37750864028931</t>
   </si>
   <si>
     <t xml:space="preserve">4.46481418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.473473072052</t>
+    <t xml:space="preserve">4.47347259521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.38688898086548</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">4.3508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24546957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672302246094</t>
+    <t xml:space="preserve">4.24547052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672206878662</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">4.35586357116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51099157333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56727170944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62499380111694</t>
+    <t xml:space="preserve">4.5109920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56727123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62499332427979</t>
   </si>
   <si>
     <t xml:space="preserve">4.69714641571045</t>
@@ -2897,58 +2897,58 @@
     <t xml:space="preserve">4.70147514343262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90061712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926378250122</t>
+    <t xml:space="preserve">4.75198173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926330566406</t>
   </si>
   <si>
     <t xml:space="preserve">5.04925203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1870641708374</t>
+    <t xml:space="preserve">5.18706321716309</t>
   </si>
   <si>
     <t xml:space="preserve">5.41434478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40063619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46773672103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46701669692993</t>
+    <t xml:space="preserve">5.40063571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46773815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46701717376709</t>
   </si>
   <si>
     <t xml:space="preserve">5.44176244735718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42011690139771</t>
+    <t xml:space="preserve">5.42011737823486</t>
   </si>
   <si>
     <t xml:space="preserve">5.28663492202759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29962158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188774108887</t>
+    <t xml:space="preserve">5.29962110519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188821792603</t>
   </si>
   <si>
     <t xml:space="preserve">5.45907974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41506624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361206054688</t>
+    <t xml:space="preserve">5.41506576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361110687256</t>
   </si>
   <si>
     <t xml:space="preserve">5.63585376739502</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">5.50092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52906847000122</t>
+    <t xml:space="preserve">5.52906799316406</t>
   </si>
   <si>
     <t xml:space="preserve">5.51175117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57308101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53989028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55720710754395</t>
+    <t xml:space="preserve">5.57308149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5398907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55720806121826</t>
   </si>
   <si>
     <t xml:space="preserve">5.73398160934448</t>
@@ -2978,49 +2978,49 @@
     <t xml:space="preserve">5.68130970001221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71017217636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75418424606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83427476882935</t>
+    <t xml:space="preserve">5.71017169952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75418472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8342752456665</t>
   </si>
   <si>
     <t xml:space="preserve">5.72604513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86024951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232431411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89416170120239</t>
+    <t xml:space="preserve">5.86024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89416027069092</t>
   </si>
   <si>
     <t xml:space="preserve">5.95476961135864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08031463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12669515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13258504867554</t>
+    <t xml:space="preserve">6.08031511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12669563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13258600234985</t>
   </si>
   <si>
     <t xml:space="preserve">6.03246212005615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98828840255737</t>
+    <t xml:space="preserve">5.98828935623169</t>
   </si>
   <si>
     <t xml:space="preserve">5.84841012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83147859573364</t>
+    <t xml:space="preserve">5.83147811889648</t>
   </si>
   <si>
     <t xml:space="preserve">5.81601762771606</t>
@@ -3029,31 +3029,31 @@
     <t xml:space="preserve">5.8712329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69601583480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69012689590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7931957244873</t>
+    <t xml:space="preserve">5.69601631164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69012641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">5.76669216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69086217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79024982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313438415527</t>
+    <t xml:space="preserve">5.69086313247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75344085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79025030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313486099243</t>
   </si>
   <si>
     <t xml:space="preserve">5.97062063217163</t>
@@ -3065,43 +3065,43 @@
     <t xml:space="preserve">5.80497455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74828720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70926856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69159889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79098749160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74534177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58705806732178</t>
+    <t xml:space="preserve">5.74828672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356199264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70926809310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69159936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79098653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74534130096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58705902099609</t>
   </si>
   <si>
     <t xml:space="preserve">5.52448081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043193817139</t>
+    <t xml:space="preserve">5.63049411773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043241500854</t>
   </si>
   <si>
     <t xml:space="preserve">5.45674991607666</t>
@@ -3110,76 +3110,76 @@
     <t xml:space="preserve">5.59000253677368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50165748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63270330429077</t>
+    <t xml:space="preserve">5.50165796279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63270235061646</t>
   </si>
   <si>
     <t xml:space="preserve">5.5981011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63932800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5664439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650562286377</t>
+    <t xml:space="preserve">5.639328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56644439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650514602661</t>
   </si>
   <si>
     <t xml:space="preserve">5.57675075531006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43319082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263933181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3441104888916</t>
+    <t xml:space="preserve">5.43319129943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34411001205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.38975524902344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49208784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40006256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48325252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52153587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4611668586731</t>
+    <t xml:space="preserve">5.49208736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40006160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48325347900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52153539657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46116733551025</t>
   </si>
   <si>
     <t xml:space="preserve">5.49797677993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44349813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42141199111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59221124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5561375617981</t>
+    <t xml:space="preserve">5.44349765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42141151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59221172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55613708496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.5392050743103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6592059135437</t>
+    <t xml:space="preserve">5.65920639038086</t>
   </si>
   <si>
     <t xml:space="preserve">5.67761135101318</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">5.49429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54141283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49871349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58190441131592</t>
+    <t xml:space="preserve">5.5414137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58190393447876</t>
   </si>
   <si>
     <t xml:space="preserve">5.53257846832275</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">5.48472547531128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57233381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44423389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.116623878479</t>
+    <t xml:space="preserve">5.57233285903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4442343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662292480469</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705232620239</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">5.03122282028198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312601089478</t>
+    <t xml:space="preserve">5.14312648773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318998336792</t>
@@ -3230,52 +3230,52 @@
     <t xml:space="preserve">5.6032543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92423963546753</t>
+    <t xml:space="preserve">5.92718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92424011230469</t>
   </si>
   <si>
     <t xml:space="preserve">6.04571342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94853401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90436220169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95515966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97209310531616</t>
+    <t xml:space="preserve">5.94853496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90436267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95516061782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97209358215332</t>
   </si>
   <si>
     <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01037549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24816989898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25921297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522268295288</t>
+    <t xml:space="preserve">6.01037502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19737195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24817085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23565435409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25921249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16203355789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522411346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.09724712371826</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">6.04350423812866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04129695892334</t>
+    <t xml:space="preserve">6.04129648208618</t>
   </si>
   <si>
     <t xml:space="preserve">6.0228910446167</t>
@@ -3293,55 +3293,55 @@
     <t xml:space="preserve">6.00743103027344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97798204421997</t>
+    <t xml:space="preserve">5.97798252105713</t>
   </si>
   <si>
     <t xml:space="preserve">6.04424095153809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92571115493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.922767162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00890302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01700210571289</t>
+    <t xml:space="preserve">5.92571210861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92276668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00890350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01700115203857</t>
   </si>
   <si>
     <t xml:space="preserve">5.94190883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08914947509766</t>
+    <t xml:space="preserve">6.0891489982605</t>
   </si>
   <si>
     <t xml:space="preserve">6.14362907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09283065795898</t>
+    <t xml:space="preserve">6.09283018112183</t>
   </si>
   <si>
     <t xml:space="preserve">6.22608375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18043994903564</t>
+    <t xml:space="preserve">6.18043899536133</t>
   </si>
   <si>
     <t xml:space="preserve">6.57357168197632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166944503784</t>
+    <t xml:space="preserve">6.46166896820068</t>
   </si>
   <si>
     <t xml:space="preserve">6.58019781112671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58756017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081016540527</t>
+    <t xml:space="preserve">6.58755970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081064224243</t>
   </si>
   <si>
     <t xml:space="preserve">6.57062721252441</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">6.50289726257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52203798294067</t>
+    <t xml:space="preserve">6.52203845977783</t>
   </si>
   <si>
     <t xml:space="preserve">6.4476842880249</t>
@@ -3362,46 +3362,46 @@
     <t xml:space="preserve">6.44242763519287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26743602752686</t>
+    <t xml:space="preserve">6.3530535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2674355506897</t>
   </si>
   <si>
     <t xml:space="preserve">6.25992488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30874156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932676315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30949306488037</t>
+    <t xml:space="preserve">6.30874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30949354171753</t>
   </si>
   <si>
     <t xml:space="preserve">6.15177488327026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17430591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15853357315063</t>
+    <t xml:space="preserve">6.17430639266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15853452682495</t>
   </si>
   <si>
     <t xml:space="preserve">6.42290067672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42590475082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34404134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38384675979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22162246704102</t>
+    <t xml:space="preserve">6.42590427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3440408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3838472366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2216215133667</t>
   </si>
   <si>
     <t xml:space="preserve">6.24715709686279</t>
@@ -3410,136 +3410,136 @@
     <t xml:space="preserve">6.35530710220337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756015777588</t>
+    <t xml:space="preserve">6.35981369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35755968093872</t>
   </si>
   <si>
     <t xml:space="preserve">6.23589181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15552997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0661563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94824361801147</t>
+    <t xml:space="preserve">6.15553045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06615543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105262756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94824314117432</t>
   </si>
   <si>
     <t xml:space="preserve">5.88816022872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9685206413269</t>
+    <t xml:space="preserve">5.89116382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96852159500122</t>
   </si>
   <si>
     <t xml:space="preserve">5.85962057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72743654251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8904128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91294431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16979932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316572189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19984197616577</t>
+    <t xml:space="preserve">5.72743701934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89041233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9129433631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16980028152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19984149932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.14426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18707418441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12999439239502</t>
+    <t xml:space="preserve">6.18707370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12999486923218</t>
   </si>
   <si>
     <t xml:space="preserve">6.05639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23814535140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166320800781</t>
+    <t xml:space="preserve">6.23814392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166368484497</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34028625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902145385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33352708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37858867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44843578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49725341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444440841675</t>
+    <t xml:space="preserve">6.34028673171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33352613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37858963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502817153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44843769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49725389480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">6.44393014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47472238540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39060640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44468021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50551462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4251537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37408351898193</t>
+    <t xml:space="preserve">6.47472333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39060544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44468116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50551509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42515468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">6.54757356643677</t>
@@ -3548,16 +3548,16 @@
     <t xml:space="preserve">6.5603404045105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885467529297</t>
+    <t xml:space="preserve">6.48899221420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885419845581</t>
   </si>
   <si>
     <t xml:space="preserve">6.27569675445557</t>
@@ -3572,22 +3572,22 @@
     <t xml:space="preserve">6.20960426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.214111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00231838226318</t>
+    <t xml:space="preserve">6.21411180496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00231790542603</t>
   </si>
   <si>
     <t xml:space="preserve">6.07742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16153907775879</t>
+    <t xml:space="preserve">6.16153812408447</t>
   </si>
   <si>
     <t xml:space="preserve">6.12623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10445928573608</t>
+    <t xml:space="preserve">6.10445976257324</t>
   </si>
   <si>
     <t xml:space="preserve">5.98279094696045</t>
@@ -3596,22 +3596,22 @@
     <t xml:space="preserve">6.06390285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14952182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13375043869019</t>
+    <t xml:space="preserve">6.1495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">6.11872911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11572504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05038499832153</t>
+    <t xml:space="preserve">6.11572408676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05038404464722</t>
   </si>
   <si>
     <t xml:space="preserve">5.99405670166016</t>
@@ -3620,52 +3620,52 @@
     <t xml:space="preserve">5.9272141456604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95650482177734</t>
+    <t xml:space="preserve">5.9565052986145</t>
   </si>
   <si>
     <t xml:space="preserve">6.01057910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01733922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01808881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97903537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02484941482544</t>
+    <t xml:space="preserve">6.01733875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01808977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9790358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02484893798828</t>
   </si>
   <si>
     <t xml:space="preserve">6.08493280410767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06840896606445</t>
+    <t xml:space="preserve">6.06840991973877</t>
   </si>
   <si>
     <t xml:space="preserve">6.16829824447632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06765794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04888200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09845066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08943891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9865460395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03386163711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01508569717407</t>
+    <t xml:space="preserve">6.06765842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04888248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09845113754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08943843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03386211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01508522033691</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879909515381</t>
@@ -3674,28 +3674,28 @@
     <t xml:space="preserve">6.03686571121216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88215112686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89491939544678</t>
+    <t xml:space="preserve">5.88215065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89491987228394</t>
   </si>
   <si>
     <t xml:space="preserve">5.89642143249512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93772888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96401500701904</t>
+    <t xml:space="preserve">5.93772840499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96401405334473</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95124673843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05489110946655</t>
+    <t xml:space="preserve">5.951247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05489063262939</t>
   </si>
   <si>
     <t xml:space="preserve">6.05188655853271</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">6.02635145187378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9572548866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01583671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8444390296936</t>
+    <t xml:space="preserve">5.95725536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01583623886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">5.8513560295105</t>
@@ -3719,19 +3719,19 @@
     <t xml:space="preserve">6.00277042388916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11575508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18723487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21106147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1195969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19107818603516</t>
+    <t xml:space="preserve">6.1157546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1872353553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21106195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11959791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19107866287231</t>
   </si>
   <si>
     <t xml:space="preserve">6.16033411026001</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">5.97971248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94820022583008</t>
+    <t xml:space="preserve">5.94819974899292</t>
   </si>
   <si>
     <t xml:space="preserve">5.91361284255981</t>
@@ -3749,46 +3749,46 @@
     <t xml:space="preserve">5.92053031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95819187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96357154846191</t>
+    <t xml:space="preserve">5.95819139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96357202529907</t>
   </si>
   <si>
     <t xml:space="preserve">5.99354696273804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98586130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02044820785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02890300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348991394043</t>
+    <t xml:space="preserve">5.98586082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02044868469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02890253067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06349039077759</t>
   </si>
   <si>
     <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97740602493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735780715942</t>
+    <t xml:space="preserve">5.97740650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735828399658</t>
   </si>
   <si>
     <t xml:space="preserve">6.08885383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0196795463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96510887145996</t>
+    <t xml:space="preserve">6.14957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01967906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96510934829712</t>
   </si>
   <si>
     <t xml:space="preserve">5.90131521224976</t>
@@ -3797,16 +3797,16 @@
     <t xml:space="preserve">5.90208387374878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95511722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93129062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99815893173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93513345718384</t>
+    <t xml:space="preserve">5.95511674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93129110336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99815845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.935133934021</t>
   </si>
   <si>
     <t xml:space="preserve">5.92975330352783</t>
@@ -3815,31 +3815,31 @@
     <t xml:space="preserve">5.83367824554443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77833890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756189346313</t>
+    <t xml:space="preserve">5.77833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756237030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.66842889785767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76373529434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71454572677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39941883087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38097286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34869146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25722789764404</t>
+    <t xml:space="preserve">5.7637357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71454477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39941930770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38097238540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3486909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25722742080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.30257606506348</t>
@@ -3848,25 +3848,25 @@
     <t xml:space="preserve">5.33408784866333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44092321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39403867721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33946800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25492191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22110414505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11196231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17191362380981</t>
+    <t xml:space="preserve">5.44092273712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39403915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33946847915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25492143630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22110366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11196279525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17191314697266</t>
   </si>
   <si>
     <t xml:space="preserve">5.17883062362671</t>
@@ -3875,25 +3875,25 @@
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3056492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31794738769531</t>
+    <t xml:space="preserve">5.30564975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31794786453247</t>
   </si>
   <si>
     <t xml:space="preserve">5.18651723861694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24954223632812</t>
+    <t xml:space="preserve">5.19958257675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24954175949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.30795574188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44246101379395</t>
+    <t xml:space="preserve">5.44246006011963</t>
   </si>
   <si>
     <t xml:space="preserve">5.54160976409912</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">5.5131721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47781658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165105819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54622173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772659301758</t>
+    <t xml:space="preserve">5.47781610488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54622220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772611618042</t>
   </si>
   <si>
     <t xml:space="preserve">5.56159353256226</t>
@@ -3923,64 +3923,64 @@
     <t xml:space="preserve">5.59925556182861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5577507019043</t>
+    <t xml:space="preserve">5.55775022506714</t>
   </si>
   <si>
     <t xml:space="preserve">5.57696533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389163970947</t>
+    <t xml:space="preserve">5.57389116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.60617303848267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53008079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45245122909546</t>
+    <t xml:space="preserve">5.53008127212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45245218276978</t>
   </si>
   <si>
     <t xml:space="preserve">5.5031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45629596710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49549388885498</t>
+    <t xml:space="preserve">5.45629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49549436569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.44707202911377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4324688911438</t>
+    <t xml:space="preserve">5.43246841430664</t>
   </si>
   <si>
     <t xml:space="preserve">5.41248512268066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34177398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34331083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30872392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41479158401489</t>
+    <t xml:space="preserve">5.34177350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34331035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30872440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41479110717773</t>
   </si>
   <si>
     <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2387809753418</t>
+    <t xml:space="preserve">5.23878192901611</t>
   </si>
   <si>
     <t xml:space="preserve">5.2180290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15500402450562</t>
+    <t xml:space="preserve">5.15500354766846</t>
   </si>
   <si>
     <t xml:space="preserve">5.19189691543579</t>
@@ -3992,10 +3992,10 @@
     <t xml:space="preserve">5.01588773727417</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23493814468384</t>
+    <t xml:space="preserve">5.16730213165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039253234863</t>
@@ -4007,97 +4007,97 @@
     <t xml:space="preserve">5.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07583808898926</t>
+    <t xml:space="preserve">5.07583856582642</t>
   </si>
   <si>
     <t xml:space="preserve">5.0927472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1473183631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10965633392334</t>
+    <t xml:space="preserve">5.14731788635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1096568107605</t>
   </si>
   <si>
     <t xml:space="preserve">5.18497896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11349964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25338459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28489780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31564140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32486486434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40787267684937</t>
+    <t xml:space="preserve">5.11350011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25338506698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2848973274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3156418800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32486534118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40787363052368</t>
   </si>
   <si>
     <t xml:space="preserve">5.38789033889771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555976867676</t>
+    <t xml:space="preserve">5.4155592918396</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47243547439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34100580215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32640171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32717132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35022878646851</t>
+    <t xml:space="preserve">5.47243642807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34100532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32640218734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32717084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35022830963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.2318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27490615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38250970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30718755722046</t>
+    <t xml:space="preserve">5.27490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38250923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30718660354614</t>
   </si>
   <si>
     <t xml:space="preserve">5.26766920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26845932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3071870803833</t>
+    <t xml:space="preserve">5.26846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30718612670898</t>
   </si>
   <si>
     <t xml:space="preserve">5.41546440124512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33642959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35934972763062</t>
+    <t xml:space="preserve">5.33642911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35935020446777</t>
   </si>
   <si>
     <t xml:space="preserve">5.41704559326172</t>
@@ -4106,58 +4106,58 @@
     <t xml:space="preserve">5.41309404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35776948928833</t>
+    <t xml:space="preserve">5.35776901245117</t>
   </si>
   <si>
     <t xml:space="preserve">5.24712038040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08272886276245</t>
+    <t xml:space="preserve">5.08272838592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11908483505249</t>
+    <t xml:space="preserve">5.11908388137817</t>
   </si>
   <si>
     <t xml:space="preserve">5.08351850509644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05348491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99499988555908</t>
+    <t xml:space="preserve">5.05348539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99499893188477</t>
   </si>
   <si>
     <t xml:space="preserve">5.08114719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14516639709473</t>
+    <t xml:space="preserve">5.14516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">5.12303590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08588981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9760308265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01396799087524</t>
+    <t xml:space="preserve">5.08588933944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97603178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01396751403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.99025726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89383506774902</t>
+    <t xml:space="preserve">4.89383459091187</t>
   </si>
   <si>
     <t xml:space="preserve">5.17598915100098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21550607681274</t>
+    <t xml:space="preserve">5.2155065536499</t>
   </si>
   <si>
     <t xml:space="preserve">4.87960863113403</t>
@@ -4169,13 +4169,13 @@
     <t xml:space="preserve">4.7065224647522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52237176895142</t>
+    <t xml:space="preserve">4.48127365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512538909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5223708152771</t>
   </si>
   <si>
     <t xml:space="preserve">4.7729115486145</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">4.53580760955811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52711343765259</t>
+    <t xml:space="preserve">4.52711391448975</t>
   </si>
   <si>
     <t xml:space="preserve">4.59903526306152</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">4.604567527771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60298633575439</t>
+    <t xml:space="preserve">4.60298681259155</t>
   </si>
   <si>
     <t xml:space="preserve">4.52079057693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55240488052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60219717025757</t>
+    <t xml:space="preserve">4.55240440368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60219621658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.51209735870361</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">4.56030797958374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64566516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8187518119812</t>
+    <t xml:space="preserve">4.64566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294561386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81875228881836</t>
   </si>
   <si>
     <t xml:space="preserve">4.79583120346069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82428407669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82902669906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90648126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87486696243286</t>
+    <t xml:space="preserve">4.82428455352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.829026222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92544889450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90648031234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87486743927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.98709630966187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96891832351685</t>
+    <t xml:space="preserve">4.968918800354</t>
   </si>
   <si>
     <t xml:space="preserve">4.93809509277344</t>
@@ -4253,52 +4253,52 @@
     <t xml:space="preserve">4.90173864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88514184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87249565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75236225128174</t>
+    <t xml:space="preserve">4.88514089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87249517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7523627281189</t>
   </si>
   <si>
     <t xml:space="preserve">4.82349395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81559038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7997841835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91596508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91438388824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87881898880005</t>
+    <t xml:space="preserve">4.81559085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79978275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91596412658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91438436508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87881803512573</t>
   </si>
   <si>
     <t xml:space="preserve">4.93888521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89541578292847</t>
+    <t xml:space="preserve">4.89541482925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.78555727005005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74841117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64171361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72628116607666</t>
+    <t xml:space="preserve">4.74841165542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64171409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628164291382</t>
   </si>
   <si>
     <t xml:space="preserve">4.6140513420105</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">4.73181390762329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74999189376831</t>
+    <t xml:space="preserve">4.74999237060547</t>
   </si>
   <si>
     <t xml:space="preserve">4.69308662414551</t>
@@ -4319,25 +4319,25 @@
     <t xml:space="preserve">4.69150590896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83930110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84720516204834</t>
+    <t xml:space="preserve">4.83930063247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84720468521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.84641408920288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88909196853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87012434005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77686309814453</t>
+    <t xml:space="preserve">4.88751268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88909244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87012386322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77686357498169</t>
   </si>
   <si>
     <t xml:space="preserve">4.6820216178894</t>
@@ -4349,28 +4349,28 @@
     <t xml:space="preserve">4.66700553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76500844955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73260450363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62037467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52790451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33189821243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25839519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39117431640625</t>
+    <t xml:space="preserve">4.76500797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73260402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62037515640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52790403366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33189725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25839471817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39117383956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26787948608398</t>
@@ -4397,22 +4397,22 @@
     <t xml:space="preserve">4.2749924659729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32794523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26946020126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12561702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259708404541</t>
+    <t xml:space="preserve">4.32794618606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12561655044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17382764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259660720825</t>
   </si>
   <si>
     <t xml:space="preserve">4.09084177017212</t>
@@ -4421,55 +4421,55 @@
     <t xml:space="preserve">4.15960168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15090799331665</t>
+    <t xml:space="preserve">4.15090751647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.14300441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09242248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05211448669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82133293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.951740026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0330753326416</t>
+    <t xml:space="preserve">4.0924220085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05211400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82133221626282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95174050331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03307485580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.08606576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95831227302551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90080332756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88108611106873</t>
+    <t xml:space="preserve">3.95831298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90080261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88108468055725</t>
   </si>
   <si>
     <t xml:space="preserve">3.90244626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89053320884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818378448486</t>
+    <t xml:space="preserve">3.89053297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683676719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9381844997406</t>
   </si>
   <si>
     <t xml:space="preserve">4.06922435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99610447883606</t>
+    <t xml:space="preserve">3.99610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.00514221191406</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">4.03636169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06758213043213</t>
+    <t xml:space="preserve">4.06758117675781</t>
   </si>
   <si>
     <t xml:space="preserve">4.13412809371948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11441040039062</t>
+    <t xml:space="preserve">4.11441087722778</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">4.19163799285889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753051757812</t>
+    <t xml:space="preserve">4.18753004074097</t>
   </si>
   <si>
     <t xml:space="preserve">4.18342256546021</t>
@@ -4511,28 +4511,28 @@
     <t xml:space="preserve">4.05443620681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05854415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06265211105347</t>
+    <t xml:space="preserve">4.05854368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06265163421631</t>
   </si>
   <si>
     <t xml:space="preserve">4.06347370147705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97022533416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94640040397644</t>
+    <t xml:space="preserve">3.97022557258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94640064239502</t>
   </si>
   <si>
     <t xml:space="preserve">3.95461559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85767030715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81412720680237</t>
+    <t xml:space="preserve">3.857670545578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81412744522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.90614295005798</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">3.86136746406555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84288215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94845390319824</t>
+    <t xml:space="preserve">3.84288239479065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90162444114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94845414161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.98871040344238</t>
@@ -4562,40 +4562,40 @@
     <t xml:space="preserve">4.04211235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02321624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04170179367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419213294983</t>
+    <t xml:space="preserve">4.02321672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04170227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073881149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679781913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419141769409</t>
   </si>
   <si>
     <t xml:space="preserve">3.97186851501465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81535959243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73607897758484</t>
+    <t xml:space="preserve">3.8153600692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607850074768</t>
   </si>
   <si>
     <t xml:space="preserve">3.53438353538513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54835057258606</t>
+    <t xml:space="preserve">3.5483500957489</t>
   </si>
   <si>
     <t xml:space="preserve">3.49001932144165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47030162811279</t>
+    <t xml:space="preserve">3.47030138969421</t>
   </si>
   <si>
     <t xml:space="preserve">3.57956957817078</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">3.66706681251526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55040407180786</t>
+    <t xml:space="preserve">3.55040431022644</t>
   </si>
   <si>
     <t xml:space="preserve">3.42593669891357</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">3.44154667854309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34870982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28873491287231</t>
+    <t xml:space="preserve">3.34870958328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28873467445374</t>
   </si>
   <si>
     <t xml:space="preserve">3.34542322158813</t>
@@ -4637,73 +4637,73 @@
     <t xml:space="preserve">3.51918506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48426818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44606494903564</t>
+    <t xml:space="preserve">3.48426866531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44606518745422</t>
   </si>
   <si>
     <t xml:space="preserve">3.52740049362183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59764432907104</t>
+    <t xml:space="preserve">3.5976448059082</t>
   </si>
   <si>
     <t xml:space="preserve">3.60257434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71512842178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67405104637146</t>
+    <t xml:space="preserve">3.71512866020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">3.71266388893127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72950601577759</t>
+    <t xml:space="preserve">3.72950577735901</t>
   </si>
   <si>
     <t xml:space="preserve">3.77304935455322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75784993171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452557563782</t>
+    <t xml:space="preserve">3.7578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8445258140564</t>
   </si>
   <si>
     <t xml:space="preserve">3.89217662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95913434028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11605405807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14727354049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274141311646</t>
+    <t xml:space="preserve">3.93037962913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11605453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14727306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274188995361</t>
   </si>
   <si>
     <t xml:space="preserve">4.19821071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23682451248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17767095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15959692001343</t>
+    <t xml:space="preserve">4.22203588485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23682403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17767143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15959739685059</t>
   </si>
   <si>
     <t xml:space="preserve">4.2335376739502</t>
@@ -4721,37 +4721,37 @@
     <t xml:space="preserve">4.21792793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31322956085205</t>
+    <t xml:space="preserve">4.31323003768921</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33623361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27708053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29186964035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2507905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29022693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27050828933716</t>
+    <t xml:space="preserve">4.33623313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27708101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29186916351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25079107284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29022598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2705078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.31158685684204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31487274169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15302324295044</t>
+    <t xml:space="preserve">4.31487321853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15302419662476</t>
   </si>
   <si>
     <t xml:space="preserve">4.14891672134399</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">4.21464157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16863346099854</t>
+    <t xml:space="preserve">4.16863441467285</t>
   </si>
   <si>
     <t xml:space="preserve">4.19081592559814</t>
@@ -4775,61 +4775,61 @@
     <t xml:space="preserve">4.17192029953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14809465408325</t>
+    <t xml:space="preserve">4.14809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">4.13248491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24832582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35430812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50794124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50054693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60159969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59995603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54819822311401</t>
+    <t xml:space="preserve">4.24832630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35430860519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50794172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50054740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6016001701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59995698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.62542533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68868637084961</t>
+    <t xml:space="preserve">4.68868589401245</t>
   </si>
   <si>
     <t xml:space="preserve">4.70593929290771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7716646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73222970962524</t>
+    <t xml:space="preserve">4.77166509628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73222875595093</t>
   </si>
   <si>
     <t xml:space="preserve">4.73551559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64760780334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6418571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65548467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6810359954834</t>
+    <t xml:space="preserve">4.64760732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64185667037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65548419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68103551864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.66570472717285</t>
@@ -4838,25 +4838,25 @@
     <t xml:space="preserve">4.66996335983276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67166709899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6273775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59160566329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58394002914429</t>
+    <t xml:space="preserve">4.67166662216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62737798690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5916051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58394050598145</t>
   </si>
   <si>
     <t xml:space="preserve">4.56690549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58138513565063</t>
+    <t xml:space="preserve">4.58138561248779</t>
   </si>
   <si>
     <t xml:space="preserve">4.56435060501099</t>
@@ -4865,22 +4865,22 @@
     <t xml:space="preserve">4.55327844619751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54816818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60863971710205</t>
+    <t xml:space="preserve">4.54816770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60864019393921</t>
   </si>
   <si>
     <t xml:space="preserve">4.60182619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58223724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5881986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57712650299072</t>
+    <t xml:space="preserve">4.58223676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58819913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57712697982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.55924034118652</t>
@@ -4889,13 +4889,13 @@
     <t xml:space="preserve">4.55668497085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52687549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48003149032593</t>
+    <t xml:space="preserve">4.52687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46214437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48003101348877</t>
   </si>
   <si>
     <t xml:space="preserve">4.45788621902466</t>
@@ -4904,34 +4904,34 @@
     <t xml:space="preserve">4.51920986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52857875823975</t>
+    <t xml:space="preserve">4.52857828140259</t>
   </si>
   <si>
     <t xml:space="preserve">4.42892742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48428916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5149507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54305839538574</t>
+    <t xml:space="preserve">4.48428869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51495170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54305791854858</t>
   </si>
   <si>
     <t xml:space="preserve">4.509840965271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53113412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53624391555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4519248008728</t>
+    <t xml:space="preserve">4.5311336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53028154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53624439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45192432403564</t>
   </si>
   <si>
     <t xml:space="preserve">4.56860876083374</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">4.51069259643555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50302696228027</t>
+    <t xml:space="preserve">4.50302743911743</t>
   </si>
   <si>
     <t xml:space="preserve">4.58905029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66740846633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68784952163696</t>
+    <t xml:space="preserve">4.66740798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68784999847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.69040489196777</t>
@@ -4976,31 +4976,31 @@
     <t xml:space="preserve">4.77131843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75683879852295</t>
+    <t xml:space="preserve">4.75683832168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.82242107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98169183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02853631973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10348749160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90333414077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86159992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8718204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90503740310669</t>
+    <t xml:space="preserve">4.98169231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02853584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10348701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90333318710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86160039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87181997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90503692626953</t>
   </si>
   <si>
     <t xml:space="preserve">4.94762325286865</t>
@@ -5012,49 +5012,49 @@
     <t xml:space="preserve">5.05153322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13414859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15799760818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25083446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19376993179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19462060928345</t>
+    <t xml:space="preserve">5.13414907455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15799808502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25083494186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19376945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19462156295776</t>
   </si>
   <si>
     <t xml:space="preserve">5.18440055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2482795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2116551399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20569372177124</t>
+    <t xml:space="preserve">5.24827909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21165561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">5.1895112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14777660369873</t>
+    <t xml:space="preserve">5.14777708053589</t>
   </si>
   <si>
     <t xml:space="preserve">5.15970087051392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12563180923462</t>
+    <t xml:space="preserve">5.12563228607178</t>
   </si>
   <si>
     <t xml:space="preserve">5.12733554840088</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">5.02598142623901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11796617507935</t>
+    <t xml:space="preserve">5.1179666519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.14351797103882</t>
@@ -5075,40 +5075,40 @@
     <t xml:space="preserve">5.13670444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.080491065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00809574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07112169265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07367706298828</t>
+    <t xml:space="preserve">5.08049154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00809526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07112216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07367658615112</t>
   </si>
   <si>
     <t xml:space="preserve">5.12052202224731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98935747146606</t>
+    <t xml:space="preserve">4.98935794830322</t>
   </si>
   <si>
     <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14947986602783</t>
+    <t xml:space="preserve">5.14948034286499</t>
   </si>
   <si>
     <t xml:space="preserve">5.10774612426758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15288686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17332792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17247676849365</t>
+    <t xml:space="preserve">5.15288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17247581481934</t>
   </si>
   <si>
     <t xml:space="preserve">5.20484161376953</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">5.20228672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19632434844971</t>
+    <t xml:space="preserve">5.19632482528687</t>
   </si>
   <si>
     <t xml:space="preserve">5.15884923934937</t>
@@ -5132,22 +5132,22 @@
     <t xml:space="preserve">5.2269868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23635530471802</t>
+    <t xml:space="preserve">5.23635482788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.25338983535767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31471300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14266681671143</t>
+    <t xml:space="preserve">5.31471347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3990330696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28916215896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14266586303711</t>
   </si>
   <si>
     <t xml:space="preserve">5.1929178237915</t>
@@ -5156,16 +5156,16 @@
     <t xml:space="preserve">5.1750316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2125072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3061957359314</t>
+    <t xml:space="preserve">5.21250677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30619621276855</t>
   </si>
   <si>
     <t xml:space="preserve">5.39136791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31300926208496</t>
+    <t xml:space="preserve">5.31300973892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.34622716903687</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">5.34452342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3607063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39647722244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44836759567261</t>
+    <t xml:space="preserve">5.36070585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39647817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44836711883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.45012617111206</t>
@@ -5204,13 +5204,13 @@
     <t xml:space="preserve">5.34370946884155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28214597702026</t>
+    <t xml:space="preserve">5.28214645385742</t>
   </si>
   <si>
     <t xml:space="preserve">5.22673892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21706438064575</t>
+    <t xml:space="preserve">5.21706485748291</t>
   </si>
   <si>
     <t xml:space="preserve">5.20914888381958</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">5.28302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36129951477051</t>
+    <t xml:space="preserve">5.36129903793335</t>
   </si>
   <si>
     <t xml:space="preserve">5.32436084747314</t>
@@ -5228,10 +5228,10 @@
     <t xml:space="preserve">5.23553371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17484903335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21002864837646</t>
+    <t xml:space="preserve">5.17484998703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21002912521362</t>
   </si>
   <si>
     <t xml:space="preserve">5.26719427108765</t>
@@ -5246,19 +5246,19 @@
     <t xml:space="preserve">5.37273263931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39120149612427</t>
+    <t xml:space="preserve">5.39120197296143</t>
   </si>
   <si>
     <t xml:space="preserve">5.45892095565796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43957233428955</t>
+    <t xml:space="preserve">5.43957281112671</t>
   </si>
   <si>
     <t xml:space="preserve">5.41406774520874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4079122543335</t>
+    <t xml:space="preserve">5.40791130065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.39383983612061</t>
@@ -5270,76 +5270,76 @@
     <t xml:space="preserve">5.46068048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44484949111938</t>
+    <t xml:space="preserve">5.44484901428223</t>
   </si>
   <si>
     <t xml:space="preserve">5.45188522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38768291473389</t>
+    <t xml:space="preserve">5.38768339157104</t>
   </si>
   <si>
     <t xml:space="preserve">5.56006097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52752017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48442602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4747519493103</t>
+    <t xml:space="preserve">5.52752065658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48442554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47475147247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.35338401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31644535064697</t>
+    <t xml:space="preserve">5.31644582748413</t>
   </si>
   <si>
     <t xml:space="preserve">5.25488185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23113584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14582681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09041976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11856317520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97872638702393</t>
+    <t xml:space="preserve">5.23113632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14582633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09041929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11856269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97872591018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88726043701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88462257385254</t>
+    <t xml:space="preserve">4.88725996017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88462162017822</t>
   </si>
   <si>
     <t xml:space="preserve">4.92595720291138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92859554290771</t>
+    <t xml:space="preserve">4.92859506607056</t>
   </si>
   <si>
     <t xml:space="preserve">5.02270030975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08426380157471</t>
+    <t xml:space="preserve">5.08426332473755</t>
   </si>
   <si>
     <t xml:space="preserve">5.06051731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03325366973877</t>
+    <t xml:space="preserve">5.03325319290161</t>
   </si>
   <si>
     <t xml:space="preserve">5.05172252655029</t>
@@ -5351,22 +5351,22 @@
     <t xml:space="preserve">5.01390504837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96641302108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00511074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07722759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05875873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08250379562378</t>
+    <t xml:space="preserve">4.99719476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9664134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00511026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0772271156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05875825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08250427246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.06139707565308</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">5.17660903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26631546020508</t>
+    <t xml:space="preserve">5.26631498336792</t>
   </si>
   <si>
     <t xml:space="preserve">5.30589199066162</t>
@@ -5390,16 +5390,16 @@
     <t xml:space="preserve">5.40527296066284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38152742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3542628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39032173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43869352340698</t>
+    <t xml:space="preserve">5.38152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39032220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43869304656982</t>
   </si>
   <si>
     <t xml:space="preserve">5.49585962295532</t>
@@ -5417,7 +5417,7 @@
     <t xml:space="preserve">5.6427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62074518203735</t>
+    <t xml:space="preserve">5.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">5.61282968521118</t>
@@ -5426,19 +5426,19 @@
     <t xml:space="preserve">5.64097309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65680408477783</t>
+    <t xml:space="preserve">5.65680360794067</t>
   </si>
   <si>
     <t xml:space="preserve">5.66559791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6576828956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70429515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72276496887207</t>
+    <t xml:space="preserve">5.65768337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70429563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72276449203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.747389793396</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">5.75882291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75354623794556</t>
+    <t xml:space="preserve">5.7535457611084</t>
   </si>
   <si>
     <t xml:space="preserve">5.77465391159058</t>
@@ -5462,40 +5462,40 @@
     <t xml:space="preserve">5.815110206604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91185283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86611938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85996294021606</t>
+    <t xml:space="preserve">5.91185235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86611986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85996341705322</t>
   </si>
   <si>
     <t xml:space="preserve">5.89250373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86436080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86963748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90921401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.910973072052</t>
+    <t xml:space="preserve">5.86436033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86963701248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90921354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91097259521484</t>
   </si>
   <si>
     <t xml:space="preserve">5.90041971206665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91888809204102</t>
+    <t xml:space="preserve">5.91888856887817</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361093521118</t>
+    <t xml:space="preserve">5.91361141204834</t>
   </si>
   <si>
     <t xml:space="preserve">5.88458871841431</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">5.93647766113281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83621740341187</t>
+    <t xml:space="preserve">5.83621692657471</t>
   </si>
   <si>
     <t xml:space="preserve">5.8239049911499</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">5.80092000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75638866424561</t>
+    <t xml:space="preserve">5.75638818740845</t>
   </si>
   <si>
     <t xml:space="preserve">5.74002981185913</t>
@@ -5540,34 +5540,34 @@
     <t xml:space="preserve">5.72185325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69913339614868</t>
+    <t xml:space="preserve">5.69913291931152</t>
   </si>
   <si>
     <t xml:space="preserve">5.65551090240479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68550109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76274967193604</t>
+    <t xml:space="preserve">5.68550157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76275014877319</t>
   </si>
   <si>
     <t xml:space="preserve">5.63824319839478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61824989318848</t>
+    <t xml:space="preserve">5.61824941635132</t>
   </si>
   <si>
     <t xml:space="preserve">5.56826496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52191591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48011112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41013288497925</t>
+    <t xml:space="preserve">5.52191638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48011064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41013240814209</t>
   </si>
   <si>
     <t xml:space="preserve">5.33833694458008</t>
@@ -5585,7 +5585,7 @@
     <t xml:space="preserve">5.38468599319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32652282714844</t>
+    <t xml:space="preserve">5.32652235031128</t>
   </si>
   <si>
     <t xml:space="preserve">5.36469221115112</t>
@@ -5618,13 +5618,13 @@
     <t xml:space="preserve">5.54463577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57917070388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57099151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59462070465088</t>
+    <t xml:space="preserve">5.5791711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57099199295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59462022781372</t>
   </si>
   <si>
     <t xml:space="preserve">5.5900764465332</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">5.64278745651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5700831413269</t>
+    <t xml:space="preserve">5.57008266448975</t>
   </si>
   <si>
     <t xml:space="preserve">5.57190036773682</t>
@@ -5645,10 +5645,10 @@
     <t xml:space="preserve">5.54645395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51646280288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52646017074585</t>
+    <t xml:space="preserve">5.51646327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52645969390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.51373624801636</t>
@@ -5657,7 +5657,7 @@
     <t xml:space="preserve">5.52918672561646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60552644729614</t>
+    <t xml:space="preserve">5.60552597045898</t>
   </si>
   <si>
     <t xml:space="preserve">5.56099462509155</t>
@@ -5666,10 +5666,10 @@
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49465179443359</t>
+    <t xml:space="preserve">5.44375848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49465131759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.36832761764526</t>
@@ -5684,34 +5684,34 @@
     <t xml:space="preserve">5.17929553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18656539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33742761611938</t>
+    <t xml:space="preserve">5.18656587600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33742809295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.31470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26563262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25836133956909</t>
+    <t xml:space="preserve">5.26563215255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25836181640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.33651924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.411949634552</t>
+    <t xml:space="preserve">5.41195011138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.49737787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53282117843628</t>
+    <t xml:space="preserve">5.56190347671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53282165527344</t>
   </si>
   <si>
     <t xml:space="preserve">5.50737476348877</t>
@@ -5729,13 +5729,13 @@
     <t xml:space="preserve">5.68004894256592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74820852279663</t>
+    <t xml:space="preserve">5.74820899963379</t>
   </si>
   <si>
     <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85817432403564</t>
+    <t xml:space="preserve">5.8581748008728</t>
   </si>
   <si>
     <t xml:space="preserve">5.91452074050903</t>
@@ -5750,25 +5750,25 @@
     <t xml:space="preserve">6.10173559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21806240081787</t>
+    <t xml:space="preserve">6.21806287765503</t>
   </si>
   <si>
     <t xml:space="preserve">6.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17989301681519</t>
+    <t xml:space="preserve">6.17989253997803</t>
   </si>
   <si>
     <t xml:space="preserve">6.14444923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12082004547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06538248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00358438491821</t>
+    <t xml:space="preserve">6.12082052230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00358390808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814371109009</t>
@@ -5780,13 +5780,13 @@
     <t xml:space="preserve">6.05265951156616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97086668014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01630687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04902458190918</t>
+    <t xml:space="preserve">5.97086715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01630735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04902410507202</t>
   </si>
   <si>
     <t xml:space="preserve">6.1344518661499</t>
@@ -5801,10 +5801,10 @@
     <t xml:space="preserve">6.17807483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09809970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06992721557617</t>
+    <t xml:space="preserve">6.09810018539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06992673873901</t>
   </si>
   <si>
     <t xml:space="preserve">5.96904945373535</t>
@@ -5816,7 +5816,7 @@
     <t xml:space="preserve">5.95632600784302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75911426544189</t>
+    <t xml:space="preserve">5.75911474227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.74275588989258</t>
@@ -5840,70 +5840,70 @@
     <t xml:space="preserve">5.97813749313354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95087337493896</t>
+    <t xml:space="preserve">5.95087289810181</t>
   </si>
   <si>
     <t xml:space="preserve">5.90452432632446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90179777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00449275970459</t>
+    <t xml:space="preserve">5.9017972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00449323654175</t>
   </si>
   <si>
     <t xml:space="preserve">5.98449897766113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02812194824219</t>
+    <t xml:space="preserve">6.02812147140503</t>
   </si>
   <si>
     <t xml:space="preserve">6.04266262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09446430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11809349060059</t>
+    <t xml:space="preserve">6.09446477890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11809396743774</t>
   </si>
   <si>
     <t xml:space="preserve">6.1698956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25714159011841</t>
+    <t xml:space="preserve">6.25714111328125</t>
   </si>
   <si>
     <t xml:space="preserve">6.17171335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1262731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15081119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13081741333008</t>
+    <t xml:space="preserve">6.12627363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15081071853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13081693649292</t>
   </si>
   <si>
     <t xml:space="preserve">6.16179513931274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18150854110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468996047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25191211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26129961013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24252557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22375106811523</t>
+    <t xml:space="preserve">6.18150806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25191259384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2613000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24252510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22375059127808</t>
   </si>
   <si>
     <t xml:space="preserve">6.18995666503906</t>
@@ -5921,40 +5921,40 @@
     <t xml:space="preserve">5.91209363937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03600597381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03412866592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01629257202148</t>
+    <t xml:space="preserve">6.03600549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03412818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01629209518433</t>
   </si>
   <si>
     <t xml:space="preserve">6.04351568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10641002655029</t>
+    <t xml:space="preserve">6.10641050338745</t>
   </si>
   <si>
     <t xml:space="preserve">6.09139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16742706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18714046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17587614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19840526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2021598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30260372161865</t>
+    <t xml:space="preserve">6.16742753982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18714094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17587566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20216035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30260419845581</t>
   </si>
   <si>
     <t xml:space="preserve">6.29791021347046</t>
@@ -5966,10 +5966,10 @@
     <t xml:space="preserve">6.41149616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42651557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44341230392456</t>
+    <t xml:space="preserve">6.42651605606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44341278076172</t>
   </si>
   <si>
     <t xml:space="preserve">6.46594190597534</t>
@@ -5978,13 +5978,13 @@
     <t xml:space="preserve">6.47063589096069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5663857460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61895418167114</t>
+    <t xml:space="preserve">6.46030950546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56638526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6189546585083</t>
   </si>
   <si>
     <t xml:space="preserve">6.62177038192749</t>
@@ -6023,10 +6023,10 @@
     <t xml:space="preserve">6.71752071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77102756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535680770874</t>
+    <t xml:space="preserve">6.7710280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535633087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.7785382270813</t>
@@ -6038,7 +6038,7 @@
     <t xml:space="preserve">6.55605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52883625030518</t>
+    <t xml:space="preserve">6.52883672714233</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147557258606</t>
@@ -6050,7 +6050,7 @@
     <t xml:space="preserve">6.57201766967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5541820526123</t>
+    <t xml:space="preserve">6.55418252944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.63303518295288</t>
@@ -6059,7 +6059,7 @@
     <t xml:space="preserve">6.73629522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76727294921875</t>
+    <t xml:space="preserve">6.76727342605591</t>
   </si>
   <si>
     <t xml:space="preserve">6.83861589431763</t>
@@ -6071,22 +6071,22 @@
     <t xml:space="preserve">6.88273620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88742971420288</t>
+    <t xml:space="preserve">6.88743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">6.73066282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73723411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75976324081421</t>
+    <t xml:space="preserve">6.73723363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75976371765137</t>
   </si>
   <si>
     <t xml:space="preserve">6.74756002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76633405685425</t>
+    <t xml:space="preserve">6.76633453369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.70062351226807</t>
@@ -6101,7 +6101,7 @@
     <t xml:space="preserve">6.58234405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60018014907837</t>
+    <t xml:space="preserve">6.60017967224121</t>
   </si>
   <si>
     <t xml:space="preserve">6.56920194625854</t>
@@ -6119,10 +6119,10 @@
     <t xml:space="preserve">6.34109163284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21436309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37206983566284</t>
+    <t xml:space="preserve">6.21436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.28852272033691</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">6.32888841629028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32607173919678</t>
+    <t xml:space="preserve">6.30072641372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32607221603394</t>
   </si>
   <si>
     <t xml:space="preserve">6.3551721572876</t>
@@ -6176,7 +6176,7 @@
     <t xml:space="preserve">6.48565530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58891534805298</t>
+    <t xml:space="preserve">6.58891487121582</t>
   </si>
   <si>
     <t xml:space="preserve">6.49222612380981</t>
@@ -6197,7 +6197,7 @@
     <t xml:space="preserve">6.4640645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59454774856567</t>
+    <t xml:space="preserve">6.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.58328247070312</t>
@@ -6209,22 +6209,22 @@
     <t xml:space="preserve">6.5654468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55887603759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60205745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46312618255615</t>
+    <t xml:space="preserve">6.5588755607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60205698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46312570571899</t>
   </si>
   <si>
     <t xml:space="preserve">6.49692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61707639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6687068939209</t>
+    <t xml:space="preserve">6.6170768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66870641708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.572350025177</t>
@@ -6747,6 +6747,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.34899997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44600009918213</t>
   </si>
 </sst>
 </file>
@@ -71747,7 +71750,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494444444</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>14838732</v>
@@ -71768,6 +71771,32 @@
         <v>2244</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6512962963</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>23406144</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>8.47999954223633</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>8.33500003814697</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>8.35499954223633</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>8.44600009918213</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2245</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="2249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="2250">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697352409363</t>
+    <t xml:space="preserve">2.23697376251221</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958250045776</t>
+    <t xml:space="preserve">2.27958273887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.22277021408081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23223948478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21685290336609</t>
+    <t xml:space="preserve">2.23223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21685242652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.20146608352661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23460626602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21211791038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17187643051147</t>
+    <t xml:space="preserve">2.23460650444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21211767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1718761920929</t>
   </si>
   <si>
     <t xml:space="preserve">2.13281798362732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15767335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09257626533508</t>
+    <t xml:space="preserve">2.15767312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0925760269165</t>
   </si>
   <si>
     <t xml:space="preserve">2.16004085540771</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">2.19436454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22513747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305970191956</t>
+    <t xml:space="preserve">2.22513723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25235986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17305994033813</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987174987793</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">2.22395396232605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19081330299377</t>
+    <t xml:space="preserve">2.19081354141235</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702105522156</t>
@@ -113,64 +113,64 @@
     <t xml:space="preserve">2.09849429130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06772089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08665823936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090931892395</t>
+    <t xml:space="preserve">2.07008743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06772065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0866584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090884208679</t>
   </si>
   <si>
     <t xml:space="preserve">2.09375977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16477465629578</t>
+    <t xml:space="preserve">2.16477537155151</t>
   </si>
   <si>
     <t xml:space="preserve">2.1505720615387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15648984909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228653907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15293884277344</t>
+    <t xml:space="preserve">2.156489610672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1529393196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.09494352340698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18016171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19199752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791507720947</t>
+    <t xml:space="preserve">2.18016123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19199728965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330189704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791483879089</t>
   </si>
   <si>
     <t xml:space="preserve">2.16714215278625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17542767524719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24170827865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31508946418762</t>
+    <t xml:space="preserve">2.17542719841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24170780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25354361534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31509017944336</t>
   </si>
   <si>
     <t xml:space="preserve">2.30798864364624</t>
@@ -179,55 +179,55 @@
     <t xml:space="preserve">2.30207061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30562162399292</t>
+    <t xml:space="preserve">2.30562114715576</t>
   </si>
   <si>
     <t xml:space="preserve">2.32574224472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31745672225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982493400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153917312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088686943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390619277954</t>
+    <t xml:space="preserve">2.31745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3115394115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3008873462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390643119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.3505973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36716818809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496884346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2736644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22632098197937</t>
+    <t xml:space="preserve">2.36716771125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30680441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27366471290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595816612244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22632169723511</t>
   </si>
   <si>
     <t xml:space="preserve">2.23579001426697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21922016143799</t>
+    <t xml:space="preserve">2.21921968460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.26182842254639</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">2.32337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29615259170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35769867897034</t>
+    <t xml:space="preserve">2.2961528301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35769891738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.39912438392639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231305122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112858772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3292932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30917239189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941411018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071824073792</t>
+    <t xml:space="preserve">2.3423125743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112906455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30917191505432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941387176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071847915649</t>
   </si>
   <si>
     <t xml:space="preserve">2.37663626670837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33757781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3529646396637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3316605091095</t>
+    <t xml:space="preserve">2.33757829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33166027069092</t>
   </si>
   <si>
     <t xml:space="preserve">2.36125016212463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3399453163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385842323303</t>
+    <t xml:space="preserve">2.33994555473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385866165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.41096043586731</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">2.42516350746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43699932098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38965606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794135093689</t>
+    <t xml:space="preserve">2.43699860572815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38965582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794111251831</t>
   </si>
   <si>
     <t xml:space="preserve">2.37782001495361</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">2.43463206291199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44173336029053</t>
+    <t xml:space="preserve">2.44173312187195</t>
   </si>
   <si>
     <t xml:space="preserve">2.43936634063721</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">2.35651540756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27839851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37900352478027</t>
+    <t xml:space="preserve">2.31864094734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2783989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37900328636169</t>
   </si>
   <si>
     <t xml:space="preserve">2.43817043304443</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.44433403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4073543548584</t>
+    <t xml:space="preserve">2.40735411643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.46652126312256</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.45296216011047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45049691200256</t>
+    <t xml:space="preserve">2.45049715042114</t>
   </si>
   <si>
     <t xml:space="preserve">2.45419502258301</t>
@@ -365,43 +365,43 @@
     <t xml:space="preserve">2.39256262779236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37653779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4221465587616</t>
+    <t xml:space="preserve">2.37653803825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42214608192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.43940305709839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45912575721741</t>
+    <t xml:space="preserve">2.45912551879883</t>
   </si>
   <si>
     <t xml:space="preserve">2.46035814285278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46282362937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467990398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47638273239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47268414497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53801488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5256884098053</t>
+    <t xml:space="preserve">2.46282315254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44679880142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48008036613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4825451374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47638249397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47268438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53801441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568864822388</t>
   </si>
   <si>
     <t xml:space="preserve">2.49240684509277</t>
@@ -410,28 +410,28 @@
     <t xml:space="preserve">2.4813129901886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49117374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52322316169739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51089668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350046157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49856996536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53308415412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52938604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47021889686584</t>
+    <t xml:space="preserve">2.49117422103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52322292327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51089692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50349998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49857020378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53308391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52938628196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47021961212158</t>
   </si>
   <si>
     <t xml:space="preserve">2.42461156845093</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">2.39749312400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40242338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42830967903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42954158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43570518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4517297744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41351699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43200755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48747587203979</t>
+    <t xml:space="preserve">2.40242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42830920219421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42954182624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43570494651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41351747512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43200707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48747611045837</t>
   </si>
   <si>
     <t xml:space="preserve">2.48994159698486</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">2.47761487960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53061842918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49610471725464</t>
+    <t xml:space="preserve">2.54541063308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53061819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49610447883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.44556593894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41105198860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475033760071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3913300037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41968083381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40981984138489</t>
+    <t xml:space="preserve">2.41105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39133024215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41968131065369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40981912612915</t>
   </si>
   <si>
     <t xml:space="preserve">2.44803142547607</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">2.42091345787048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44926428794861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41228532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37283968925476</t>
+    <t xml:space="preserve">2.44926452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4122850894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37284016609192</t>
   </si>
   <si>
     <t xml:space="preserve">2.35928130149841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32476782798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051321029663</t>
+    <t xml:space="preserve">2.32476735115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051368713379</t>
   </si>
   <si>
     <t xml:space="preserve">2.33832621574402</t>
@@ -536,37 +536,37 @@
     <t xml:space="preserve">2.36421179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35435080528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43693828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858721733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43077421188354</t>
+    <t xml:space="preserve">2.35435056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43693804740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43077445030212</t>
   </si>
   <si>
     <t xml:space="preserve">2.41598320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37037515640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3629789352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35311818122864</t>
+    <t xml:space="preserve">2.37037491798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36297941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35311770439148</t>
   </si>
   <si>
     <t xml:space="preserve">2.3666775226593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32723236083984</t>
+    <t xml:space="preserve">2.38393425941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32723259925842</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711060523987</t>
@@ -575,25 +575,25 @@
     <t xml:space="preserve">2.243412733078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369050979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24957633018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080847740173</t>
+    <t xml:space="preserve">2.22369027137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080895423889</t>
   </si>
   <si>
     <t xml:space="preserve">2.28285717964172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22862076759338</t>
+    <t xml:space="preserve">2.2286205291748</t>
   </si>
   <si>
     <t xml:space="preserve">2.24834322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31860399246216</t>
+    <t xml:space="preserve">2.31860423088074</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751037597656</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">2.29764890670776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30257940292358</t>
+    <t xml:space="preserve">2.30258011817932</t>
   </si>
   <si>
     <t xml:space="preserve">2.33586072921753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35065269470215</t>
+    <t xml:space="preserve">2.35065245628357</t>
   </si>
   <si>
     <t xml:space="preserve">2.33339524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51952433586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336193084717</t>
+    <t xml:space="preserve">2.51952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336169242859</t>
   </si>
   <si>
     <t xml:space="preserve">2.47884798049927</t>
@@ -629,52 +629,52 @@
     <t xml:space="preserve">2.53924703598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56513261795044</t>
+    <t xml:space="preserve">2.56513285636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.54910850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56266760826111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58115720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60211205482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252860069275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896973609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664301872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56636524200439</t>
+    <t xml:space="preserve">2.56266713142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60211181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622671127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896925926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047989845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56636571884155</t>
   </si>
   <si>
     <t xml:space="preserve">2.55403876304626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55650401115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55157399177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57299399375916</t>
+    <t xml:space="preserve">2.55650424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55157327651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57299423217773</t>
   </si>
   <si>
     <t xml:space="preserve">2.56795430183411</t>
@@ -683,49 +683,49 @@
     <t xml:space="preserve">2.52763271331787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50873255729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47849178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42556953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43565034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825100898743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715068817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41927027702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5440137386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55031371116638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023337364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53267288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49361205101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53141355514526</t>
+    <t xml:space="preserve">2.50873208045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47849130630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42557001113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4343900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43565011024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825053215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715140342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.419269323349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069027900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54401350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5503134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5326726436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49361181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53141283988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.54527354240417</t>
@@ -734,58 +734,58 @@
     <t xml:space="preserve">2.52133274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52637267112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50369238853455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787396430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283403396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57803463935852</t>
+    <t xml:space="preserve">2.52637338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50369262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787348747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283379554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57803416252136</t>
   </si>
   <si>
     <t xml:space="preserve">2.59945511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6032350063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60827565193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6271755695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851618766785</t>
+    <t xml:space="preserve">2.60323524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60827469825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62717580795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851571083069</t>
   </si>
   <si>
     <t xml:space="preserve">2.63347578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63473629951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961579322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237665176392</t>
+    <t xml:space="preserve">2.63473606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757678031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65237641334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.6397762298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65867638587952</t>
+    <t xml:space="preserve">2.65867614746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.71033811569214</t>
@@ -794,40 +794,40 @@
     <t xml:space="preserve">2.70151829719543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73427844047546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74183940887451</t>
+    <t xml:space="preserve">2.71537828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7342791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74183988571167</t>
   </si>
   <si>
     <t xml:space="preserve">2.75191974639893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78090071678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77459979057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76199960708618</t>
+    <t xml:space="preserve">2.7809009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77460026741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7619993686676</t>
   </si>
   <si>
     <t xml:space="preserve">2.77208042144775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74309945106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75947952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75821971893311</t>
+    <t xml:space="preserve">2.74309921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75947976112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75822019577026</t>
   </si>
   <si>
     <t xml:space="preserve">2.72671890258789</t>
@@ -836,94 +836,94 @@
     <t xml:space="preserve">2.67253732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907831192017</t>
+    <t xml:space="preserve">2.70907807350159</t>
   </si>
   <si>
     <t xml:space="preserve">2.80484104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79098081588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7771201133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77081990242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939870834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78720021247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350090026855</t>
+    <t xml:space="preserve">2.79098033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77712035179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77082014083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939894676208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78719997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7935004234314</t>
   </si>
   <si>
     <t xml:space="preserve">2.85650253295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88422322273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792253494263</t>
+    <t xml:space="preserve">2.88422346115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792325019836</t>
   </si>
   <si>
     <t xml:space="preserve">2.86658310890198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87918329238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87666368484497</t>
+    <t xml:space="preserve">2.87918376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87414312362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87666296958923</t>
   </si>
   <si>
     <t xml:space="preserve">2.88044309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94974541664124</t>
+    <t xml:space="preserve">2.94974493980408</t>
   </si>
   <si>
     <t xml:space="preserve">2.91572427749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9220244884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998595237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628664016724</t>
+    <t xml:space="preserve">2.92202401161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998571395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526665687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628640174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.0051863193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02912664413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9610857963562</t>
+    <t xml:space="preserve">3.0291268825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96108555793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.97872591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99762725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274728775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990561485291</t>
+    <t xml:space="preserve">2.9976270198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990609169006</t>
   </si>
   <si>
     <t xml:space="preserve">3.01148724555969</t>
@@ -932,46 +932,46 @@
     <t xml:space="preserve">3.02156686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11354947090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180788040161</t>
+    <t xml:space="preserve">3.11354970932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180764198303</t>
   </si>
   <si>
     <t xml:space="preserve">3.05558824539185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05810880661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440854072571</t>
+    <t xml:space="preserve">3.05810809135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440782546997</t>
   </si>
   <si>
     <t xml:space="preserve">3.09968972206116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10724973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749051094055</t>
+    <t xml:space="preserve">3.10724925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204865455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749003410339</t>
   </si>
   <si>
     <t xml:space="preserve">3.10346961021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11859011650085</t>
+    <t xml:space="preserve">3.11859035491943</t>
   </si>
   <si>
     <t xml:space="preserve">3.02408766746521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04928851127625</t>
+    <t xml:space="preserve">3.04928803443909</t>
   </si>
   <si>
     <t xml:space="preserve">2.98754668235779</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">2.95730543136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99888682365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97368550300598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06944918632507</t>
+    <t xml:space="preserve">2.9988865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9888060092926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478510856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06944942474365</t>
   </si>
   <si>
     <t xml:space="preserve">3.13245105743408</t>
@@ -1007,379 +1007,379 @@
     <t xml:space="preserve">3.13119029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10094952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489056587219</t>
+    <t xml:space="preserve">3.10094928741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12489008903503</t>
   </si>
   <si>
     <t xml:space="preserve">3.12867069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0933895111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906099319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.079270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777710914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953833580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595656394958</t>
+    <t xml:space="preserve">3.09338974952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906027793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07927012443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1177773475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831400871277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953881263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595632553101</t>
   </si>
   <si>
     <t xml:space="preserve">3.13703036308289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13189554214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040371894836</t>
+    <t xml:space="preserve">3.13189578056335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040300369263</t>
   </si>
   <si>
     <t xml:space="preserve">3.19864153862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19735813140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19222354888916</t>
+    <t xml:space="preserve">3.19735789299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.215327501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.192223072052</t>
   </si>
   <si>
     <t xml:space="preserve">3.1601345539093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22816371917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062584877014</t>
+    <t xml:space="preserve">3.22816395759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062561035156</t>
   </si>
   <si>
     <t xml:space="preserve">3.25383520126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607448577881</t>
+    <t xml:space="preserve">3.23458123207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607400894165</t>
   </si>
   <si>
     <t xml:space="preserve">3.26025223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26987934112549</t>
+    <t xml:space="preserve">3.26987886428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.26346135139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2987596988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271436691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30196857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33084917068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122182846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614680290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405780792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28592300415039</t>
+    <t xml:space="preserve">3.29875874519348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271532058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3019688129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33084893226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122230529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614632606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405756950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629685401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517721176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28592395782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.28913259506226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2730884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24099969863892</t>
+    <t xml:space="preserve">3.27308797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099898338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708968162537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23779010772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704336166382</t>
+    <t xml:space="preserve">3.23779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25704407691956</t>
   </si>
   <si>
     <t xml:space="preserve">3.31480431556702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31801295280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32763957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30838632583618</t>
+    <t xml:space="preserve">3.31801271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32763934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30838680267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.32443046569824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35010123252869</t>
+    <t xml:space="preserve">3.350102186203</t>
   </si>
   <si>
     <t xml:space="preserve">3.39502668380737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3918182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428017616272</t>
+    <t xml:space="preserve">3.39181780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4142804145813</t>
   </si>
   <si>
     <t xml:space="preserve">3.41748857498169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4559965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44316029548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957852363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920515060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46241402626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42390751838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38540005683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37898254394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39823603630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689354896545</t>
+    <t xml:space="preserve">3.45599603652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44316005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920538902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4624137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4399516582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42390704154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38540053367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898230552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3982355594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689331054688</t>
   </si>
   <si>
     <t xml:space="preserve">3.35331034660339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40786218643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674254417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883201599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51375579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092077255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44637012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584574699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5618896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114337921143</t>
+    <t xml:space="preserve">3.40786194801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883177757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51375675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092053413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44636940956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054787635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114409446716</t>
   </si>
   <si>
     <t xml:space="preserve">3.53621888160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48166704177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50412964820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107130050659</t>
+    <t xml:space="preserve">3.48166728019714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50413036346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107177734375</t>
   </si>
   <si>
     <t xml:space="preserve">3.36293768882751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234194755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711663246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40144515037537</t>
+    <t xml:space="preserve">3.29234170913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711567878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40144443511963</t>
   </si>
   <si>
     <t xml:space="preserve">3.4461145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42975091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382556915283</t>
+    <t xml:space="preserve">3.42975115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047884941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738847732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382509231567</t>
   </si>
   <si>
     <t xml:space="preserve">3.31717109680176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34466195106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31586241722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302720069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146639823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070372581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310418128967</t>
+    <t xml:space="preserve">3.34466218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31586194038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310067176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146592140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019174575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070324897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310465812683</t>
   </si>
   <si>
     <t xml:space="preserve">3.06844925880432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04619526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12866592407227</t>
+    <t xml:space="preserve">3.04619479179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12866616249084</t>
   </si>
   <si>
     <t xml:space="preserve">3.13652014732361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1810290813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.127357006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630372047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466546058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15877437591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16597437858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801122665405</t>
+    <t xml:space="preserve">3.18102812767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735724449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15877509117126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16597414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801170349121</t>
   </si>
   <si>
     <t xml:space="preserve">3.11688446998596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04815888404846</t>
+    <t xml:space="preserve">3.04815864562988</t>
   </si>
   <si>
     <t xml:space="preserve">3.07695817947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09528541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12670278549194</t>
+    <t xml:space="preserve">3.09528493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12670254707336</t>
   </si>
   <si>
     <t xml:space="preserve">3.1679379940033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16532039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16335606575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18757438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17448282241821</t>
+    <t xml:space="preserve">3.16532015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1633563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18757390975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17448306083679</t>
   </si>
   <si>
     <t xml:space="preserve">3.19673705101013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22684621810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150137901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1391384601593</t>
+    <t xml:space="preserve">3.22684597969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150066375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13913798332214</t>
   </si>
   <si>
     <t xml:space="preserve">3.175137758255</t>
@@ -1388,76 +1388,76 @@
     <t xml:space="preserve">3.13259267807007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13979268074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2562997341156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320912361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844455718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30539035797119</t>
+    <t xml:space="preserve">3.13979291915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320936203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844527244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538988113403</t>
   </si>
   <si>
     <t xml:space="preserve">3.30277180671692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32764458656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240796089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3472797870636</t>
+    <t xml:space="preserve">3.32764363288879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240748405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324458122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597086906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34727931022644</t>
   </si>
   <si>
     <t xml:space="preserve">3.40095138549805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39833283424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487909317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3930971622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44284200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4362964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44807863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520492553711</t>
+    <t xml:space="preserve">3.39833307266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39309740066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44284296035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43629693984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44807815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520421028137</t>
   </si>
   <si>
     <t xml:space="preserve">3.48211359977722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52531361579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662205696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891429901123</t>
+    <t xml:space="preserve">3.52531337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52662134170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891453742981</t>
   </si>
   <si>
     <t xml:space="preserve">3.3210985660553</t>
@@ -1466,79 +1466,79 @@
     <t xml:space="preserve">3.31848096847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34335207939148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36298871040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23797345161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153635978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20590043067932</t>
+    <t xml:space="preserve">3.34335255622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36298894882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23797369003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590090751648</t>
   </si>
   <si>
     <t xml:space="preserve">3.20655608177185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19542837142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19215536117554</t>
+    <t xml:space="preserve">3.19542813301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19215559959412</t>
   </si>
   <si>
     <t xml:space="preserve">3.18037462234497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10772156715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08415818214417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07826685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855794906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324809074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564854621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386756896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11557531356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12932109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401124000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204714775085</t>
+    <t xml:space="preserve">3.10772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08415770530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888681411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033940315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.098557472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1332483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564926147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386733055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692296028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11557507514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12932062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401052474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204738616943</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746545791626</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">3.08481240272522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10641121864319</t>
+    <t xml:space="preserve">3.1064121723175</t>
   </si>
   <si>
     <t xml:space="preserve">3.06452202796936</t>
@@ -1556,91 +1556,91 @@
     <t xml:space="preserve">3.08808493614197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12343001365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1031391620636</t>
+    <t xml:space="preserve">3.12342977523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10313963890076</t>
   </si>
   <si>
     <t xml:space="preserve">3.11361193656921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10510277748108</t>
+    <t xml:space="preserve">3.10510230064392</t>
   </si>
   <si>
     <t xml:space="preserve">3.15550184249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437437057495</t>
+    <t xml:space="preserve">3.14437460899353</t>
   </si>
   <si>
     <t xml:space="preserve">3.17710161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19739174842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186546325684</t>
+    <t xml:space="preserve">3.19739246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186594009399</t>
   </si>
   <si>
     <t xml:space="preserve">3.1489565372467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18364667892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251944541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19411849975586</t>
+    <t xml:space="preserve">3.1836462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17252016067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411897659302</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20917344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113729476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17952370643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530920028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.136474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212510108948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338014602661</t>
+    <t xml:space="preserve">3.20917367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113705635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952394485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647508621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17212462425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338038444519</t>
   </si>
   <si>
     <t xml:space="preserve">3.20844626426697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08400964736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432511329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468270301819</t>
+    <t xml:space="preserve">3.08400988578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347373962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432463645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499793052673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468294143677</t>
   </si>
   <si>
     <t xml:space="preserve">3.0833375453949</t>
@@ -1655,121 +1655,121 @@
     <t xml:space="preserve">2.99051475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01203894615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98042464256287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96630001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791312217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95082950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96293663978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9515016078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94006776809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88625645637512</t>
+    <t xml:space="preserve">3.01203846931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98042511940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96629977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99791359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98513340950012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95082974433899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96293711662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150232315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9299783706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94006705284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836382865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540484428406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8539707660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88625693321228</t>
   </si>
   <si>
     <t xml:space="preserve">2.88558411598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94477558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091818809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719470024109</t>
+    <t xml:space="preserve">2.94477605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091890335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">3.06584906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03894400596619</t>
+    <t xml:space="preserve">3.03894424438477</t>
   </si>
   <si>
     <t xml:space="preserve">3.06652164459229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05979561805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0362536907196</t>
+    <t xml:space="preserve">3.05979514122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03625345230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.05912280082703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11629605293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07392072677612</t>
+    <t xml:space="preserve">3.11629629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07392120361328</t>
   </si>
   <si>
     <t xml:space="preserve">3.09342694282532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10149836540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064675331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96764469146729</t>
+    <t xml:space="preserve">3.10149812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9676456451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9474663734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562647819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04096174240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99993085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97504377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94410276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94343018531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92325139045715</t>
+    <t xml:space="preserve">2.96562743186951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0409619808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99993109703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9750440120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94410252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94343042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92325186729431</t>
   </si>
   <si>
     <t xml:space="preserve">2.88423895835876</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">2.96899080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93468642234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975301742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9844605922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96697235107422</t>
+    <t xml:space="preserve">2.93468618392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97975206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96697211265564</t>
   </si>
   <si>
     <t xml:space="preserve">2.94612073898315</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">2.95957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91517996788025</t>
+    <t xml:space="preserve">2.91517972946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.94544839859009</t>
@@ -1814,85 +1814,85 @@
     <t xml:space="preserve">3.00665760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01540184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280068397522</t>
+    <t xml:space="preserve">3.01540160179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02280044555664</t>
   </si>
   <si>
     <t xml:space="preserve">2.9945502281189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02683615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06853914260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275412559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13378429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13244032859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16472625732422</t>
+    <t xml:space="preserve">3.02683663368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06853938102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378500938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13243961334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16472578048706</t>
   </si>
   <si>
     <t xml:space="preserve">3.19835710525513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20441126823425</t>
+    <t xml:space="preserve">3.20441102981567</t>
   </si>
   <si>
     <t xml:space="preserve">3.21517300605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20037508010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22189974784851</t>
+    <t xml:space="preserve">3.2003755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22189950942993</t>
   </si>
   <si>
     <t xml:space="preserve">3.23804259300232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2272801399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24880480766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19297695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19364905357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189612865448</t>
+    <t xml:space="preserve">3.22728037834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24880433082581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19364953041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961310386658</t>
   </si>
   <si>
     <t xml:space="preserve">3.23333406448364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31674027442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3766040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37525939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256813049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655823707581</t>
+    <t xml:space="preserve">3.31674075126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37660431861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3752589225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256836891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655752182007</t>
   </si>
   <si>
     <t xml:space="preserve">3.46270108222961</t>
@@ -1901,322 +1901,322 @@
     <t xml:space="preserve">3.4882607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39543867111206</t>
+    <t xml:space="preserve">3.39543747901917</t>
   </si>
   <si>
     <t xml:space="preserve">3.39274740219116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41965270042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099761962891</t>
+    <t xml:space="preserve">3.41965222358704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099785804749</t>
   </si>
   <si>
     <t xml:space="preserve">3.46808195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46673703193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47346353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5313093662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767804145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5044047832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51112985610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978589057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032155990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275723457336</t>
+    <t xml:space="preserve">3.46673655509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47346305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53130984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440430641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978541374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458310127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032203674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275699615479</t>
   </si>
   <si>
     <t xml:space="preserve">3.57446694374084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5786120891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690214157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5675585269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61591815948486</t>
+    <t xml:space="preserve">3.5468327999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57861185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58690166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6214451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6159188747406</t>
   </si>
   <si>
     <t xml:space="preserve">3.63802552223206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5717031955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545140266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097794532776</t>
+    <t xml:space="preserve">3.57170343399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137559890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545116424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472567558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5509774684906</t>
   </si>
   <si>
     <t xml:space="preserve">3.59104776382446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60348320007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61729955673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282633781433</t>
+    <t xml:space="preserve">3.6034824848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071921348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729979515076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282657623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.61039113998413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61453604698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64631485939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66980409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66151428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533087730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118668556213</t>
+    <t xml:space="preserve">3.61453580856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420868873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.646315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66980385780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6615138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533135414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118620872498</t>
   </si>
   <si>
     <t xml:space="preserve">3.66427779197693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68085765838623</t>
+    <t xml:space="preserve">3.68085837364197</t>
   </si>
   <si>
     <t xml:space="preserve">3.72921776771545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80106663703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77204990386963</t>
+    <t xml:space="preserve">3.80106592178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205038070679</t>
   </si>
   <si>
     <t xml:space="preserve">3.79830288887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79001259803772</t>
+    <t xml:space="preserve">3.7900128364563</t>
   </si>
   <si>
     <t xml:space="preserve">3.79139423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77895927429199</t>
+    <t xml:space="preserve">3.77895879745483</t>
   </si>
   <si>
     <t xml:space="preserve">3.81350111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83008241653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495233535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.892258644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258719444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923687934875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752764701843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92818331718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90883946418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091132164001</t>
+    <t xml:space="preserve">3.83008193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225935935974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752669334412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92818284034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94061875343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9088397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091179847717</t>
   </si>
   <si>
     <t xml:space="preserve">3.94338202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93440127372742</t>
+    <t xml:space="preserve">3.9344003200531</t>
   </si>
   <si>
     <t xml:space="preserve">3.9337100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9212749004364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91021990776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8756787776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379583358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419253349304</t>
+    <t xml:space="preserve">3.92127370834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022086143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847588539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87567853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564279556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419205665588</t>
   </si>
   <si>
     <t xml:space="preserve">3.81695604324341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81281089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244755744934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840678215027</t>
+    <t xml:space="preserve">3.81281042098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8024480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593703269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840749740601</t>
   </si>
   <si>
     <t xml:space="preserve">3.83630013465881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89571309089661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288047790527</t>
+    <t xml:space="preserve">3.89571261405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288023948669</t>
   </si>
   <si>
     <t xml:space="preserve">3.86531519889832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84182643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015128135681</t>
+    <t xml:space="preserve">3.84182667732239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015151977539</t>
   </si>
   <si>
     <t xml:space="preserve">3.85218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83491826057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452013015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8514986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186170578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8888041973114</t>
+    <t xml:space="preserve">3.8349175453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80451965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85149812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080742835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88880443572998</t>
   </si>
   <si>
     <t xml:space="preserve">3.93094635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98690485954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068785667419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99934101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906316757202</t>
+    <t xml:space="preserve">3.98690462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99934148788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906388282776</t>
   </si>
   <si>
     <t xml:space="preserve">3.84804463386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87844181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581674575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108503341675</t>
+    <t xml:space="preserve">3.87844109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581746101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108551025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.06980752944946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02628421783447</t>
+    <t xml:space="preserve">4.02628469467163</t>
   </si>
   <si>
     <t xml:space="preserve">4.04010057449341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06911659240723</t>
+    <t xml:space="preserve">4.06911706924438</t>
   </si>
   <si>
     <t xml:space="preserve">4.13889312744141</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">4.1934700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20037841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30884265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2763729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30538749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20314168930054</t>
+    <t xml:space="preserve">4.20037794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30884313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26255559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27637195587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3053879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3005518913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397226333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2031421661377</t>
   </si>
   <si>
     <t xml:space="preserve">4.24182987213135</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">4.23215770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32473230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42697858810425</t>
+    <t xml:space="preserve">4.32473278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42697763442993</t>
   </si>
   <si>
     <t xml:space="preserve">4.45392179489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42145156860352</t>
+    <t xml:space="preserve">4.42145109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.4283595085144</t>
@@ -2279,103 +2279,103 @@
     <t xml:space="preserve">4.43941307067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49744558334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45668458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48500967025757</t>
+    <t xml:space="preserve">4.49744462966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45668506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.49951791763306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5312967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34407567977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4323992729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43310499191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47267389297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41402816772461</t>
+    <t xml:space="preserve">4.53129625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34407663345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43239831924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47267436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41402769088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41332149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35891437530518</t>
+    <t xml:space="preserve">4.41332054138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35891485214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.38011169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
+    <t xml:space="preserve">4.40908193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711839675903</t>
   </si>
   <si>
     <t xml:space="preserve">4.33418416976929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3384222984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28472280502319</t>
+    <t xml:space="preserve">4.33842325210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28472375869751</t>
   </si>
   <si>
     <t xml:space="preserve">4.29461526870728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24586153030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44087839126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49316549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40625476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44017028808594</t>
+    <t xml:space="preserve">4.24585962295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44087743759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49316501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40625524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44017171859741</t>
   </si>
   <si>
     <t xml:space="preserve">4.39706993103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59208726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5935001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68606185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65921211242676</t>
+    <t xml:space="preserve">4.59208679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59349966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68606233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6592116355896</t>
   </si>
   <si>
     <t xml:space="preserve">4.71997833251953</t>
@@ -2384,46 +2384,46 @@
     <t xml:space="preserve">4.72068500518799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76096057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70937919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58572673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181074142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263698577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65779876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58007526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69878101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67404985427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71361970901489</t>
+    <t xml:space="preserve">4.7609601020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70938014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62458944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58572816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263746261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.657799243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58007431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69878005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67404937744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64649391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71361923217773</t>
   </si>
   <si>
     <t xml:space="preserve">4.78215837478638</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">4.7553071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82737827301025</t>
+    <t xml:space="preserve">4.82738018035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84080457687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81678056716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220636367798</t>
+    <t xml:space="preserve">4.84080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81678104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220588684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.6910080909729</t>
@@ -2453,31 +2453,31 @@
     <t xml:space="preserve">4.77226638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83656406402588</t>
+    <t xml:space="preserve">4.83656454086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.78498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81536722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7814507484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78992986679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83161783218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80830097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78357124328613</t>
+    <t xml:space="preserve">4.81536769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78145170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78992938995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.831618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78357076644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.8245530128479</t>
@@ -2486,19 +2486,19 @@
     <t xml:space="preserve">4.76590585708618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84221744537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86129570007324</t>
+    <t xml:space="preserve">4.84221792221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.84998941421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85564279556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87754678726196</t>
+    <t xml:space="preserve">4.85564231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8775463104248</t>
   </si>
   <si>
     <t xml:space="preserve">4.90369033813477</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">4.92347383499146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.882493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87472057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140371322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84716367721558</t>
+    <t xml:space="preserve">4.88249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87472009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085256576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.851402759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84716415405273</t>
   </si>
   <si>
     <t xml:space="preserve">4.93407297134399</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">4.8966236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8577618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84857559204102</t>
+    <t xml:space="preserve">4.85776281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.87401342391968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82596588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78710508346558</t>
+    <t xml:space="preserve">4.82596635818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759477615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78710412979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.76943969726562</t>
@@ -2555,58 +2555,58 @@
     <t xml:space="preserve">4.83303213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85493612289429</t>
+    <t xml:space="preserve">4.85493564605713</t>
   </si>
   <si>
     <t xml:space="preserve">4.84433746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66698408126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.717857837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036191940308</t>
+    <t xml:space="preserve">4.66698503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71785879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.75601434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83727169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89309167861938</t>
+    <t xml:space="preserve">4.83727216720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89309215545654</t>
   </si>
   <si>
     <t xml:space="preserve">4.95315170288086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93336629867554</t>
+    <t xml:space="preserve">4.9333667755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.94679164886475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09164094924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0435938835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09588098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09517478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10577392578125</t>
+    <t xml:space="preserve">5.09164142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973695755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04359340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09588050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09517431259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10577344894409</t>
   </si>
   <si>
     <t xml:space="preserve">5.10859966278076</t>
@@ -2615,64 +2615,64 @@
     <t xml:space="preserve">5.13686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16159391403198</t>
+    <t xml:space="preserve">5.16159296035767</t>
   </si>
   <si>
     <t xml:space="preserve">5.24073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22871875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24355745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37780857086182</t>
+    <t xml:space="preserve">5.22871828079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3778076171875</t>
   </si>
   <si>
     <t xml:space="preserve">5.45835781097412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50453615188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49082660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44464921951294</t>
+    <t xml:space="preserve">5.50453567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49082708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44464826583862</t>
   </si>
   <si>
     <t xml:space="preserve">5.49804162979126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64162635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53700494766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83571815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66760110855103</t>
+    <t xml:space="preserve">5.64162588119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83571767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66760158538818</t>
   </si>
   <si>
     <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7722225189209</t>
+    <t xml:space="preserve">5.77222299575806</t>
   </si>
   <si>
     <t xml:space="preserve">5.82272958755493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602210998535</t>
+    <t xml:space="preserve">5.86602163314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.89993381500244</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">5.91652822494507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9114785194397</t>
+    <t xml:space="preserve">5.91147708892822</t>
   </si>
   <si>
     <t xml:space="preserve">5.86746454238892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92157888412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97208690643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05650472640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917615890503</t>
+    <t xml:space="preserve">5.9215784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97208642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05650520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917663574219</t>
   </si>
   <si>
     <t xml:space="preserve">6.18060779571533</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">6.08464431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09258127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386854171753</t>
+    <t xml:space="preserve">6.0925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386806488037</t>
   </si>
   <si>
     <t xml:space="preserve">5.63152456283569</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">5.73975419998169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71161556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629524230957</t>
+    <t xml:space="preserve">5.71161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629476547241</t>
   </si>
   <si>
     <t xml:space="preserve">5.51247262954712</t>
@@ -2729,106 +2729,106 @@
     <t xml:space="preserve">5.6228666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94538879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87684488296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6935772895813</t>
+    <t xml:space="preserve">5.94538974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87684440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69357633590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.1271767616272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83712291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70436143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77070426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830202102661</t>
+    <t xml:space="preserve">4.83712244033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77070379257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426502227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830178260803</t>
   </si>
   <si>
     <t xml:space="preserve">4.1271390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24979829788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20650625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24907827377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30896472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5535626411438</t>
+    <t xml:space="preserve">4.2497992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20650720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24907732009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30896425247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55356168746948</t>
   </si>
   <si>
     <t xml:space="preserve">4.54562568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53047370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44100284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60767698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57376575469971</t>
+    <t xml:space="preserve">4.53047275543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44100522994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6076774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57376527786255</t>
   </si>
   <si>
     <t xml:space="preserve">4.37823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43378877639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37895250320435</t>
+    <t xml:space="preserve">4.43378829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37895202636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.43018054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59974050521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480291366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65601873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65169095993042</t>
+    <t xml:space="preserve">4.59973955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65601968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6516900062561</t>
   </si>
   <si>
     <t xml:space="preserve">4.47852325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50882816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47996664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46770000457764</t>
+    <t xml:space="preserve">4.50882720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47996616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46770048141479</t>
   </si>
   <si>
     <t xml:space="preserve">4.33277463912964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3183445930481</t>
+    <t xml:space="preserve">4.31834411621094</t>
   </si>
   <si>
     <t xml:space="preserve">4.27577447891235</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">4.25701427459717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37967443466187</t>
+    <t xml:space="preserve">4.37967395782471</t>
   </si>
   <si>
     <t xml:space="preserve">4.43739652633667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52397966384888</t>
+    <t xml:space="preserve">4.52398014068604</t>
   </si>
   <si>
     <t xml:space="preserve">4.4994478225708</t>
@@ -2852,64 +2852,64 @@
     <t xml:space="preserve">4.3342170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39266157150269</t>
+    <t xml:space="preserve">4.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">4.37750959396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46481466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47347211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081338882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24546957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672206878662</t>
+    <t xml:space="preserve">4.46481418609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47347259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688898086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35081243515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672254562378</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35586404800415</t>
+    <t xml:space="preserve">4.35586357116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.51099157333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56727123260498</t>
+    <t xml:space="preserve">4.56727170944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.62499332427979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69714593887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147514343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0492525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1870641708374</t>
+    <t xml:space="preserve">4.69714641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147466659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04925203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706369400024</t>
   </si>
   <si>
     <t xml:space="preserve">5.41434526443481</t>
@@ -2918,100 +2918,100 @@
     <t xml:space="preserve">5.40063619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46773862838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46701622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011785507202</t>
+    <t xml:space="preserve">5.46773815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46701717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176340103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011690139771</t>
   </si>
   <si>
     <t xml:space="preserve">5.28663444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29962158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188774108887</t>
+    <t xml:space="preserve">5.29962205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188726425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.45907974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41506624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197778701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361110687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63585329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50092792510986</t>
+    <t xml:space="preserve">5.41506671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361158370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63585424423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50092887878418</t>
   </si>
   <si>
     <t xml:space="preserve">5.52906799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51175117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57308149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53989124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5572075843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73398113250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68131113052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71017169952393</t>
+    <t xml:space="preserve">5.51175165176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57308101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5398907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55720710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7339825630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68131065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71017074584961</t>
   </si>
   <si>
     <t xml:space="preserve">5.75418424606323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83427476882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86024856567383</t>
+    <t xml:space="preserve">5.8342752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604465484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86024904251099</t>
   </si>
   <si>
     <t xml:space="preserve">5.78232431411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89416170120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9547700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08031558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12669563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13258504867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246164321899</t>
+    <t xml:space="preserve">5.89416027069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95476913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08031511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12669467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13258600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246259689331</t>
   </si>
   <si>
     <t xml:space="preserve">5.98828983306885</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">5.84841060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83147859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8712329864502</t>
+    <t xml:space="preserve">5.83147811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601858139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123250961304</t>
   </si>
   <si>
     <t xml:space="preserve">5.69601631164551</t>
@@ -3038,115 +3038,115 @@
     <t xml:space="preserve">5.78362512588501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79319524765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76669216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69086217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79024982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313581466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97061967849731</t>
+    <t xml:space="preserve">5.7931957244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7666916847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69086265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75344038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062110900879</t>
   </si>
   <si>
     <t xml:space="preserve">5.89552783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8049750328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74828672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70926856994629</t>
+    <t xml:space="preserve">5.80497407913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74828720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70926761627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.69159889221191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79098701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74534177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58705854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52447986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63049411773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4567494392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59000253677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63270235061646</t>
+    <t xml:space="preserve">5.79098653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74534273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58705759048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52448129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63049364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043146133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45674991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165796279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63270282745361</t>
   </si>
   <si>
     <t xml:space="preserve">5.59810066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63932752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5664439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57675170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319129943848</t>
+    <t xml:space="preserve">5.63932847976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56644439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57675123214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319082260132</t>
   </si>
   <si>
     <t xml:space="preserve">5.46263933181763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3441104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975477218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582988739014</t>
+    <t xml:space="preserve">5.34411001205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3897557258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582893371582</t>
   </si>
   <si>
     <t xml:space="preserve">5.400062084198</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">5.48325347900391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52153539657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4611668586731</t>
+    <t xml:space="preserve">5.52153587341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46116781234741</t>
   </si>
   <si>
     <t xml:space="preserve">5.49797677993774</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">5.44349813461304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42141199111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59221172332764</t>
+    <t xml:space="preserve">5.42141246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59221076965332</t>
   </si>
   <si>
     <t xml:space="preserve">5.55613708496094</t>
@@ -3179,55 +3179,55 @@
     <t xml:space="preserve">5.53920459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6592059135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67761087417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5414137840271</t>
+    <t xml:space="preserve">5.65920495986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67761135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54141330718994</t>
   </si>
   <si>
     <t xml:space="preserve">5.49871301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58190441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53257846832275</t>
+    <t xml:space="preserve">5.58190393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257894515991</t>
   </si>
   <si>
     <t xml:space="preserve">5.48472547531128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57233428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44423389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662244796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10705184936523</t>
+    <t xml:space="preserve">5.57233381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4442343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10705232620239</t>
   </si>
   <si>
     <t xml:space="preserve">5.03122329711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312648773193</t>
+    <t xml:space="preserve">5.14312601089478</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42435646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60325479507446</t>
+    <t xml:space="preserve">5.42435598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6032543182373</t>
   </si>
   <si>
     <t xml:space="preserve">5.92718458175659</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">5.94853448867798</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90436220169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95516014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97209358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97945499420166</t>
+    <t xml:space="preserve">5.90436267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95515966415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.972092628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97945547103882</t>
   </si>
   <si>
     <t xml:space="preserve">6.0103759765625</t>
@@ -3266,28 +3266,28 @@
     <t xml:space="preserve">6.24817037582397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23565435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25921249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09724712371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04350519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04129600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02289152145386</t>
+    <t xml:space="preserve">6.23565483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25921297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.162034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1252236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09724760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04129648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0228910446167</t>
   </si>
   <si>
     <t xml:space="preserve">6.00743103027344</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">6.04424047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92571210861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.922767162323</t>
+    <t xml:space="preserve">5.92571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92276763916016</t>
   </si>
   <si>
     <t xml:space="preserve">6.00890302658081</t>
@@ -3320,82 +3320,82 @@
     <t xml:space="preserve">6.14362955093384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09283113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18043947219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57357263565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57062768936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5028977394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52203845977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44768524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44242811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2674355506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25992488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30874252319336</t>
+    <t xml:space="preserve">6.09283065795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22608327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18043851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57357215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57062721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50289630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52203798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44768476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43942356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44242763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35305309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26743507385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30874156951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.18932723999023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30949354171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15177488327026</t>
+    <t xml:space="preserve">6.30949306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15177536010742</t>
   </si>
   <si>
     <t xml:space="preserve">6.17430639266968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15853404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42290067672729</t>
+    <t xml:space="preserve">6.15853452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42290115356445</t>
   </si>
   <si>
     <t xml:space="preserve">6.42590427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3440408706665</t>
+    <t xml:space="preserve">6.34404039382935</t>
   </si>
   <si>
     <t xml:space="preserve">6.38384628295898</t>
@@ -3404,22 +3404,22 @@
     <t xml:space="preserve">6.22162199020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24715757369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35530662536621</t>
+    <t xml:space="preserve">6.24715662002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35530710220337</t>
   </si>
   <si>
     <t xml:space="preserve">6.35981321334839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3575611114502</t>
+    <t xml:space="preserve">6.35756015777588</t>
   </si>
   <si>
     <t xml:space="preserve">6.23589181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15552997589111</t>
+    <t xml:space="preserve">6.15553045272827</t>
   </si>
   <si>
     <t xml:space="preserve">6.06615686416626</t>
@@ -3428,37 +3428,37 @@
     <t xml:space="preserve">5.99105215072632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94824361801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88815975189209</t>
+    <t xml:space="preserve">5.94824314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88816022872925</t>
   </si>
   <si>
     <t xml:space="preserve">5.89116382598877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9685206413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85961961746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7274374961853</t>
+    <t xml:space="preserve">5.96852111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85962057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72743654251099</t>
   </si>
   <si>
     <t xml:space="preserve">5.8904128074646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9129433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141399383545</t>
+    <t xml:space="preserve">5.91294479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141304016113</t>
   </si>
   <si>
     <t xml:space="preserve">6.08568286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1697998046875</t>
+    <t xml:space="preserve">6.16980075836182</t>
   </si>
   <si>
     <t xml:space="preserve">6.25316572189331</t>
@@ -3470,67 +3470,67 @@
     <t xml:space="preserve">6.14426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18707418441772</t>
+    <t xml:space="preserve">6.18707466125488</t>
   </si>
   <si>
     <t xml:space="preserve">6.12999439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05639314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2381443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826948165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34028625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902002334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910341262817</t>
+    <t xml:space="preserve">6.05639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23814487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826852798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34028577804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910388946533</t>
   </si>
   <si>
     <t xml:space="preserve">6.33352661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37858915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502912521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44843626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49725389480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444440841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44393014907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47472333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39060640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44468116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326251983643</t>
+    <t xml:space="preserve">6.37858963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49725341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444345474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44393062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47472286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39060497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4446816444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326156616211</t>
   </si>
   <si>
     <t xml:space="preserve">6.50551462173462</t>
@@ -3542,37 +3542,37 @@
     <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54757499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56034088134766</t>
+    <t xml:space="preserve">6.54757404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034183502197</t>
   </si>
   <si>
     <t xml:space="preserve">6.4889931678772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34479284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27569723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16304063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22537660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20960378646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.214111328125</t>
+    <t xml:space="preserve">6.34479236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27569627761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16304111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22537708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20960474014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21411180496216</t>
   </si>
   <si>
     <t xml:space="preserve">6.00231790542603</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">6.12623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10445976257324</t>
+    <t xml:space="preserve">6.1044602394104</t>
   </si>
   <si>
     <t xml:space="preserve">5.98279094696045</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">6.06390285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14952182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774181365967</t>
+    <t xml:space="preserve">6.1495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774276733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.13374948501587</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">6.11572456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05038452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.994056224823</t>
+    <t xml:space="preserve">6.05038404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99405574798584</t>
   </si>
   <si>
     <t xml:space="preserve">5.92721366882324</t>
@@ -3623,85 +3623,85 @@
     <t xml:space="preserve">5.95650482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01057910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01733922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01808881759644</t>
+    <t xml:space="preserve">6.01058006286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01733875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01808977127075</t>
   </si>
   <si>
     <t xml:space="preserve">5.9790358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02484941482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08493280410767</t>
+    <t xml:space="preserve">6.02484893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08493232727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.06840944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0676589012146</t>
+    <t xml:space="preserve">6.16829776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06765794754028</t>
   </si>
   <si>
     <t xml:space="preserve">6.04888248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09845066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08943891525269</t>
+    <t xml:space="preserve">6.09845018386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08943843841553</t>
   </si>
   <si>
     <t xml:space="preserve">5.98654651641846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03386163711548</t>
+    <t xml:space="preserve">6.03386211395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.01508569717407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98879861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88215065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89491891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89642143249512</t>
+    <t xml:space="preserve">5.98879909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03686571121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88215208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89491939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89642095565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.93772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401453018188</t>
+    <t xml:space="preserve">5.9640154838562</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.951247215271</t>
+    <t xml:space="preserve">5.95124673843384</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489110946655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05188655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02635192871094</t>
+    <t xml:space="preserve">6.05188608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02635097503662</t>
   </si>
   <si>
     <t xml:space="preserve">5.95725536346436</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84443855285645</t>
+    <t xml:space="preserve">5.84443950653076</t>
   </si>
   <si>
     <t xml:space="preserve">5.8513560295105</t>
@@ -3725,16 +3725,16 @@
     <t xml:space="preserve">6.18723487854004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21106100082397</t>
+    <t xml:space="preserve">6.21106147766113</t>
   </si>
   <si>
     <t xml:space="preserve">6.11959791183472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19107723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16033363342285</t>
+    <t xml:space="preserve">6.191077709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16033411026001</t>
   </si>
   <si>
     <t xml:space="preserve">5.97971248626709</t>
@@ -3743,79 +3743,79 @@
     <t xml:space="preserve">5.94819974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819139480591</t>
+    <t xml:space="preserve">5.91361284255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92053079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819091796875</t>
   </si>
   <si>
     <t xml:space="preserve">5.96357202529907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99354696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98586130142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02044820785522</t>
+    <t xml:space="preserve">5.9935474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98586177825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02044868469238</t>
   </si>
   <si>
     <t xml:space="preserve">6.02890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06348991394043</t>
+    <t xml:space="preserve">6.06348943710327</t>
   </si>
   <si>
     <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97740697860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735780715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08885335922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14957332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01967906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96510934829712</t>
+    <t xml:space="preserve">5.97740650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08885383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14957284927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0196795463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96510887145996</t>
   </si>
   <si>
     <t xml:space="preserve">5.90131521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90208435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95511770248413</t>
+    <t xml:space="preserve">5.90208339691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95511722564697</t>
   </si>
   <si>
     <t xml:space="preserve">5.93129062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99815893173218</t>
+    <t xml:space="preserve">5.99815845489502</t>
   </si>
   <si>
     <t xml:space="preserve">5.93513345718384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92975330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77833890914917</t>
+    <t xml:space="preserve">5.92975282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367776870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77833843231201</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756237030029</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">5.66842937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7637357711792</t>
+    <t xml:space="preserve">5.76373624801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.71454524993896</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">5.34869146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2572283744812</t>
+    <t xml:space="preserve">5.25722789764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.30257558822632</t>
@@ -3848,22 +3848,22 @@
     <t xml:space="preserve">5.33408832550049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44092321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39403820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33946895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25492191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22110366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11196231842041</t>
+    <t xml:space="preserve">5.4409236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39403915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33946800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25492238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22110414505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11196279525757</t>
   </si>
   <si>
     <t xml:space="preserve">5.17191314697266</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17114496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30565023422241</t>
+    <t xml:space="preserve">5.17114448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3056492805481</t>
   </si>
   <si>
     <t xml:space="preserve">5.31794738769531</t>
@@ -3893,22 +3893,22 @@
     <t xml:space="preserve">5.30795574188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44246101379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54160928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51317167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165058135986</t>
+    <t xml:space="preserve">5.44246053695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54161071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51317262649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781610488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165105819702</t>
   </si>
   <si>
     <t xml:space="preserve">5.54622173309326</t>
@@ -3923,139 +3923,139 @@
     <t xml:space="preserve">5.59925556182861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55774974822998</t>
+    <t xml:space="preserve">5.5577507019043</t>
   </si>
   <si>
     <t xml:space="preserve">5.57696580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389211654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60617303848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53008127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45245218276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50318050384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45629501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49549436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44707250595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4324688911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41248559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34177398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34331083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30872392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41479063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49472570419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2387809753418</t>
+    <t xml:space="preserve">5.57389116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60617256164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53008079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45245265960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45629453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49549341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44707202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41248464584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34177350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34331226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30872440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41479158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49472618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23878145217896</t>
   </si>
   <si>
     <t xml:space="preserve">5.21802949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15500402450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19189691543579</t>
+    <t xml:space="preserve">5.15500450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19189786911011</t>
   </si>
   <si>
     <t xml:space="preserve">5.06507778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01588726043701</t>
+    <t xml:space="preserve">5.01588773727417</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23493814468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039300918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1511607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14193725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0758376121521</t>
+    <t xml:space="preserve">5.234938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039205551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15116119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14193868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07583808898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.0927472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14731788635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10965585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18497896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11349964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25338506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28489780426025</t>
+    <t xml:space="preserve">5.1473183631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18497943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1134991645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25338459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2848973274231</t>
   </si>
   <si>
     <t xml:space="preserve">5.31564140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32486486434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38789033889771</t>
+    <t xml:space="preserve">5.32486438751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40787315368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38788986206055</t>
   </si>
   <si>
     <t xml:space="preserve">5.41555976867676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51240348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34100484848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026077270508</t>
+    <t xml:space="preserve">5.51240301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47243547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34100532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026124954224</t>
   </si>
   <si>
     <t xml:space="preserve">5.32640171051025</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">5.32717084884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32025241851807</t>
+    <t xml:space="preserve">5.32025289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.35022830963135</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">5.23186445236206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27490520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38250923156738</t>
+    <t xml:space="preserve">5.27490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38250970840454</t>
   </si>
   <si>
     <t xml:space="preserve">5.3071870803833</t>
@@ -4085,28 +4085,28 @@
     <t xml:space="preserve">5.26766967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26845979690552</t>
+    <t xml:space="preserve">5.26846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">5.41546487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33643007278442</t>
+    <t xml:space="preserve">5.33642959594727</t>
   </si>
   <si>
     <t xml:space="preserve">5.35935020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41704511642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41309356689453</t>
+    <t xml:space="preserve">5.41704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41309404373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.35776948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24712038040161</t>
+    <t xml:space="preserve">5.24712085723877</t>
   </si>
   <si>
     <t xml:space="preserve">5.08272838592529</t>
@@ -4118,40 +4118,40 @@
     <t xml:space="preserve">5.11908483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08351898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05348587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99499988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08114767074585</t>
+    <t xml:space="preserve">5.08351850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05348539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99499940872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08114719390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.14516592025757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12303590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08588933944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97603130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01396799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99025821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89383459091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17598867416382</t>
+    <t xml:space="preserve">5.1230354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08589029312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9760308265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01396751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99025774002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89383506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17598915100098</t>
   </si>
   <si>
     <t xml:space="preserve">5.2155065536499</t>
@@ -4166,10 +4166,10 @@
     <t xml:space="preserve">4.7065224647522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
+    <t xml:space="preserve">4.48127365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.52237129211426</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">4.55240488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60219669342041</t>
+    <t xml:space="preserve">4.60219717025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.51209688186646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566516876221</t>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566612243652</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294513702393</t>
@@ -4220,31 +4220,31 @@
     <t xml:space="preserve">4.79583168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82428407669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82902669906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92544841766357</t>
+    <t xml:space="preserve">4.82428503036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.829026222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92544889450073</t>
   </si>
   <si>
     <t xml:space="preserve">4.90648078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87486743927002</t>
+    <t xml:space="preserve">4.87486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.98709583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8985767364502</t>
+    <t xml:space="preserve">4.96891832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89857721328735</t>
   </si>
   <si>
     <t xml:space="preserve">4.90173864364624</t>
@@ -4253,22 +4253,22 @@
     <t xml:space="preserve">4.88514137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87249565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75236225128174</t>
+    <t xml:space="preserve">4.87249517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7523627281189</t>
   </si>
   <si>
     <t xml:space="preserve">4.82349395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81559038162231</t>
+    <t xml:space="preserve">4.81559085845947</t>
   </si>
   <si>
     <t xml:space="preserve">4.79978370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91596412658691</t>
+    <t xml:space="preserve">4.91596460342407</t>
   </si>
   <si>
     <t xml:space="preserve">4.91438388824463</t>
@@ -4277,37 +4277,37 @@
     <t xml:space="preserve">4.87881755828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93888521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89541625976562</t>
+    <t xml:space="preserve">4.93888473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89541530609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.78555727005005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74841070175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64171457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72628116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6140513420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69229555130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73181390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74999189376831</t>
+    <t xml:space="preserve">4.74841117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64171409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61405181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69229602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73181343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74999141693115</t>
   </si>
   <si>
     <t xml:space="preserve">4.69308662414551</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">4.83930110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84720420837402</t>
+    <t xml:space="preserve">4.84720468521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.84641456604004</t>
@@ -4328,16 +4328,16 @@
     <t xml:space="preserve">4.88751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88909339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87012434005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77686309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68202209472656</t>
+    <t xml:space="preserve">4.88909244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87012481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77686357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68202114105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.70573234558105</t>
@@ -4346,40 +4346,40 @@
     <t xml:space="preserve">4.66700506210327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76500844955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73260354995728</t>
+    <t xml:space="preserve">4.76500797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73260402679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.62037467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52790355682373</t>
+    <t xml:space="preserve">4.52790403366089</t>
   </si>
   <si>
     <t xml:space="preserve">4.3318977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25839519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39117336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26787948608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30107355117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33821964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31925249099731</t>
+    <t xml:space="preserve">4.25839471817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39117431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26787900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30107402801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33822011947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31925201416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.2291522026062</t>
@@ -4391,25 +4391,25 @@
     <t xml:space="preserve">4.35718870162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27499198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32794570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26946020126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1256160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911909103394</t>
+    <t xml:space="preserve">4.2749924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32794523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12561702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911956787109</t>
   </si>
   <si>
     <t xml:space="preserve">4.173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01259756088257</t>
+    <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">4.09084129333496</t>
@@ -4418,10 +4418,10 @@
     <t xml:space="preserve">4.15960168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15090799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14300441741943</t>
+    <t xml:space="preserve">4.15090751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14300489425659</t>
   </si>
   <si>
     <t xml:space="preserve">4.09242248535156</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8213324546814</t>
+    <t xml:space="preserve">3.82133221626282</t>
   </si>
   <si>
     <t xml:space="preserve">3.95173978805542</t>
@@ -4439,31 +4439,31 @@
     <t xml:space="preserve">4.0330753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606576919556</t>
+    <t xml:space="preserve">4.08606624603271</t>
   </si>
   <si>
     <t xml:space="preserve">3.95831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90080332756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88108563423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90244603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89053320884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06922435760498</t>
+    <t xml:space="preserve">3.90080261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88108468055725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90244626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89053297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683581352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9381844997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06922483444214</t>
   </si>
   <si>
     <t xml:space="preserve">3.99610471725464</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">4.13412857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11440944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09756803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10783815383911</t>
+    <t xml:space="preserve">4.11441040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09756851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">4.13659286499023</t>
@@ -4499,16 +4499,16 @@
     <t xml:space="preserve">4.18753004074097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18342256546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11030197143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05443572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05854368209839</t>
+    <t xml:space="preserve">4.18342208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11030292510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05443668365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05854463577271</t>
   </si>
   <si>
     <t xml:space="preserve">4.06265163421631</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">4.06347370147705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97022485733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94639992713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9546160697937</t>
+    <t xml:space="preserve">3.9702250957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94640040397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95461511611938</t>
   </si>
   <si>
     <t xml:space="preserve">3.857670545578</t>
@@ -4532,28 +4532,28 @@
     <t xml:space="preserve">3.81412744522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90614318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86136794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84288215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94845390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98871064186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10085439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06593751907349</t>
+    <t xml:space="preserve">3.90614295005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86136746406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84288191795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90162444114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94845414161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98871040344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10085487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0659384727478</t>
   </si>
   <si>
     <t xml:space="preserve">4.04211235046387</t>
@@ -4565,34 +4565,34 @@
     <t xml:space="preserve">4.04170179367065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05073881149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679829597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419213294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97186851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81535935401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73607921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53438353538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54835033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49001908302307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47030162811279</t>
+    <t xml:space="preserve">4.05073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679781913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97186803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81535959243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53438401222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54835057258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49001932144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47030138969421</t>
   </si>
   <si>
     <t xml:space="preserve">3.57956957817078</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">3.66706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55040407180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42593693733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38609075546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44154691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34870982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28873515129089</t>
+    <t xml:space="preserve">3.55040431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42593717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38609099388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44154667854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34870958328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28873467445374</t>
   </si>
   <si>
     <t xml:space="preserve">3.34542298316956</t>
@@ -4631,19 +4631,19 @@
     <t xml:space="preserve">3.49823474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51918530464172</t>
+    <t xml:space="preserve">3.51918458938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.48426818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44606494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52740001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764456748962</t>
+    <t xml:space="preserve">3.44606518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52740049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976448059082</t>
   </si>
   <si>
     <t xml:space="preserve">3.60257411003113</t>
@@ -4655,25 +4655,25 @@
     <t xml:space="preserve">3.6740505695343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7126636505127</t>
+    <t xml:space="preserve">3.71266388893127</t>
   </si>
   <si>
     <t xml:space="preserve">3.72950577735901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7730495929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452509880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217638969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037939071655</t>
+    <t xml:space="preserve">3.77304911613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217662811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037915229797</t>
   </si>
   <si>
     <t xml:space="preserve">3.95913410186768</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">4.14727306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17274236679077</t>
+    <t xml:space="preserve">4.17274188995361</t>
   </si>
   <si>
     <t xml:space="preserve">4.1982102394104</t>
@@ -4697,43 +4697,43 @@
     <t xml:space="preserve">4.23682451248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17767095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15959692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23353815078735</t>
+    <t xml:space="preserve">4.17767143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15959739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23353719711304</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16534757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19492435455322</t>
+    <t xml:space="preserve">4.16534852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19492483139038</t>
   </si>
   <si>
     <t xml:space="preserve">4.21792793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31322908401489</t>
+    <t xml:space="preserve">4.31323003768921</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33623361587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27708005905151</t>
+    <t xml:space="preserve">4.3362340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27708101272583</t>
   </si>
   <si>
     <t xml:space="preserve">4.29186916351318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2507905960083</t>
+    <t xml:space="preserve">4.25079107284546</t>
   </si>
   <si>
     <t xml:space="preserve">4.29022598266602</t>
@@ -4742,22 +4742,22 @@
     <t xml:space="preserve">4.27050828933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3115873336792</t>
+    <t xml:space="preserve">4.31158685684204</t>
   </si>
   <si>
     <t xml:space="preserve">4.31487274169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1530237197876</t>
+    <t xml:space="preserve">4.15302419662476</t>
   </si>
   <si>
     <t xml:space="preserve">4.14891672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14563083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14645195007324</t>
+    <t xml:space="preserve">4.14563035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14645147323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.21464157104492</t>
@@ -4766,13 +4766,13 @@
     <t xml:space="preserve">4.16863393783569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1908164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17192029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14809417724609</t>
+    <t xml:space="preserve">4.19081544876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17192077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">4.13248491287231</t>
@@ -4784,49 +4784,49 @@
     <t xml:space="preserve">4.35430860519409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50794219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50054693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60159969329834</t>
+    <t xml:space="preserve">4.50794124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50054788589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6016001701355</t>
   </si>
   <si>
     <t xml:space="preserve">4.59995651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54819822311401</t>
+    <t xml:space="preserve">4.5481972694397</t>
   </si>
   <si>
     <t xml:space="preserve">4.62542581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68868541717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70593929290771</t>
+    <t xml:space="preserve">4.68868589401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70593976974487</t>
   </si>
   <si>
     <t xml:space="preserve">4.7716646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73222923278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73551607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64760828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6418571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65548467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6810359954834</t>
+    <t xml:space="preserve">4.73222970962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73551511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64760780334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64185619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65548419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68103551864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.66570520401001</t>
@@ -4835,19 +4835,19 @@
     <t xml:space="preserve">4.66996335983276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67166709899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6273775100708</t>
+    <t xml:space="preserve">4.67166662216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62737798690796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59160566329956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58393955230713</t>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58394050598145</t>
   </si>
   <si>
     <t xml:space="preserve">4.5669059753418</t>
@@ -4862,13 +4862,13 @@
     <t xml:space="preserve">4.55327844619751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54816865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60863971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60182619094849</t>
+    <t xml:space="preserve">4.54816818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60864019393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60182666778564</t>
   </si>
   <si>
     <t xml:space="preserve">4.58223676681519</t>
@@ -4883,73 +4883,73 @@
     <t xml:space="preserve">4.55924034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55668544769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52687549591064</t>
+    <t xml:space="preserve">4.55668497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687501907349</t>
   </si>
   <si>
     <t xml:space="preserve">4.46214437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48003149032593</t>
+    <t xml:space="preserve">4.48003053665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.45788621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51920938491821</t>
+    <t xml:space="preserve">4.51921033859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.52857828140259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48428964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5149507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54305839538574</t>
+    <t xml:space="preserve">4.42892742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48428916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51495170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54305791854858</t>
   </si>
   <si>
     <t xml:space="preserve">4.509840965271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53113412857056</t>
+    <t xml:space="preserve">4.5311336517334</t>
   </si>
   <si>
     <t xml:space="preserve">4.53028154373169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53624391555786</t>
+    <t xml:space="preserve">4.53624439239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.45192432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56860971450806</t>
+    <t xml:space="preserve">4.5686092376709</t>
   </si>
   <si>
     <t xml:space="preserve">4.46810674667358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51069211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58905029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66740894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68784952163696</t>
+    <t xml:space="preserve">4.51069259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50302743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58905076980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66740846633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68784999847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.69040489196777</t>
@@ -4958,10 +4958,10 @@
     <t xml:space="preserve">4.59245777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65378093719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69125604629517</t>
+    <t xml:space="preserve">4.65378046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69125652313232</t>
   </si>
   <si>
     <t xml:space="preserve">4.77813148498535</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">4.77131843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75683832168579</t>
+    <t xml:space="preserve">4.75683879852295</t>
   </si>
   <si>
     <t xml:space="preserve">4.82242107391357</t>
@@ -4982,16 +4982,16 @@
     <t xml:space="preserve">4.98169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02853584289551</t>
+    <t xml:space="preserve">5.02853631973267</t>
   </si>
   <si>
     <t xml:space="preserve">5.10348749160767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90333414077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86160039901733</t>
+    <t xml:space="preserve">4.90333366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86159992218018</t>
   </si>
   <si>
     <t xml:space="preserve">4.87181997299194</t>
@@ -5000,46 +5000,46 @@
     <t xml:space="preserve">4.90503740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94762325286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97402715682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05153322219849</t>
+    <t xml:space="preserve">4.94762277603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97402667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05153274536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.13414907455444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15799713134766</t>
+    <t xml:space="preserve">5.15799760818481</t>
   </si>
   <si>
     <t xml:space="preserve">5.18695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2508339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979278564453</t>
+    <t xml:space="preserve">5.25083446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979230880737</t>
   </si>
   <si>
     <t xml:space="preserve">5.19376945495605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19462108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18440103530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2482795715332</t>
+    <t xml:space="preserve">5.19462156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18440008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24827909469604</t>
   </si>
   <si>
     <t xml:space="preserve">5.21165561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20569324493408</t>
+    <t xml:space="preserve">5.20569372177124</t>
   </si>
   <si>
     <t xml:space="preserve">5.18951082229614</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">5.14777660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15970134735107</t>
+    <t xml:space="preserve">5.15970039367676</t>
   </si>
   <si>
     <t xml:space="preserve">5.12563228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12733554840088</t>
+    <t xml:space="preserve">5.12733602523804</t>
   </si>
   <si>
     <t xml:space="preserve">5.09156322479248</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">5.02598142623901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1179666519165</t>
+    <t xml:space="preserve">5.11796712875366</t>
   </si>
   <si>
     <t xml:space="preserve">5.14351844787598</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">5.13670444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08049154281616</t>
+    <t xml:space="preserve">5.080491065979</t>
   </si>
   <si>
     <t xml:space="preserve">5.00809526443481</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">5.07112264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07367706298828</t>
+    <t xml:space="preserve">5.07367658615112</t>
   </si>
   <si>
     <t xml:space="preserve">5.12052202224731</t>
@@ -5093,25 +5093,25 @@
     <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14948034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10774612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17332792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17247676849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20484209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16992139816284</t>
+    <t xml:space="preserve">5.14947986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10774660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15288686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17247629165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20484161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.169921875</t>
   </si>
   <si>
     <t xml:space="preserve">5.20228672027588</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">5.19632482528687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884971618652</t>
+    <t xml:space="preserve">5.15884923934937</t>
   </si>
   <si>
     <t xml:space="preserve">5.17843866348267</t>
@@ -5129,25 +5129,25 @@
     <t xml:space="preserve">5.22698640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25339031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31471252441406</t>
+    <t xml:space="preserve">5.23635530471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25338935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31471347808838</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28916120529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14266633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19291830062866</t>
+    <t xml:space="preserve">5.28916168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14266586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1929178237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.17503213882446</t>
@@ -5156,16 +5156,16 @@
     <t xml:space="preserve">5.2125072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30619621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39136791229248</t>
+    <t xml:space="preserve">5.30619668960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39136743545532</t>
   </si>
   <si>
     <t xml:space="preserve">5.31301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34622716903687</t>
+    <t xml:space="preserve">5.34622669219971</t>
   </si>
   <si>
     <t xml:space="preserve">5.34452342987061</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">5.39647817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44836759567261</t>
+    <t xml:space="preserve">5.44836711883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.45012617111206</t>
@@ -5186,16 +5186,16 @@
     <t xml:space="preserve">5.4703540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55038642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51872587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5160870552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46155977249146</t>
+    <t xml:space="preserve">5.55038690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51872539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51608657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4615592956543</t>
   </si>
   <si>
     <t xml:space="preserve">5.34370994567871</t>
@@ -5204,16 +5204,16 @@
     <t xml:space="preserve">5.28214597702026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22673892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21706438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20914888381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28302526473999</t>
+    <t xml:space="preserve">5.22673845291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21706485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20914936065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28302574157715</t>
   </si>
   <si>
     <t xml:space="preserve">5.36129903793335</t>
@@ -5225,37 +5225,37 @@
     <t xml:space="preserve">5.23553371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17484998703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21002817153931</t>
+    <t xml:space="preserve">5.17484951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21002864837646</t>
   </si>
   <si>
     <t xml:space="preserve">5.2671947479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33227682113647</t>
+    <t xml:space="preserve">5.33227634429932</t>
   </si>
   <si>
     <t xml:space="preserve">5.34195041656494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37273263931274</t>
+    <t xml:space="preserve">5.37273216247559</t>
   </si>
   <si>
     <t xml:space="preserve">5.39120149612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4589204788208</t>
+    <t xml:space="preserve">5.45892095565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.43957281112671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41406774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40791177749634</t>
+    <t xml:space="preserve">5.41406726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40791130065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.39383983612061</t>
@@ -5267,16 +5267,16 @@
     <t xml:space="preserve">5.46068000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45188474655151</t>
+    <t xml:space="preserve">5.44484949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45188522338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.38768339157104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56006145477295</t>
+    <t xml:space="preserve">5.56006097793579</t>
   </si>
   <si>
     <t xml:space="preserve">5.52752017974854</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">5.35338354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31644582748413</t>
+    <t xml:space="preserve">5.31644535064697</t>
   </si>
   <si>
     <t xml:space="preserve">5.25488185882568</t>
@@ -5300,10 +5300,10 @@
     <t xml:space="preserve">5.23113632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14582633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09041929244995</t>
+    <t xml:space="preserve">5.14582681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09042024612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856269836426</t>
@@ -5315,10 +5315,10 @@
     <t xml:space="preserve">4.85208129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88726091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88462162017822</t>
+    <t xml:space="preserve">4.88726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88462114334106</t>
   </si>
   <si>
     <t xml:space="preserve">4.92595720291138</t>
@@ -5330,28 +5330,28 @@
     <t xml:space="preserve">5.02270030975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08426380157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06051826477051</t>
+    <t xml:space="preserve">5.08426332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06051778793335</t>
   </si>
   <si>
     <t xml:space="preserve">5.03325366973877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05172300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01390504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96641254425049</t>
+    <t xml:space="preserve">5.05172252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04996347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01390552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99719476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9664134979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.00511026382446</t>
@@ -5360,16 +5360,16 @@
     <t xml:space="preserve">5.07722759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05875873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0825047492981</t>
+    <t xml:space="preserve">5.05875825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08250427246094</t>
   </si>
   <si>
     <t xml:space="preserve">5.06139707565308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17660903930664</t>
+    <t xml:space="preserve">5.17660856246948</t>
   </si>
   <si>
     <t xml:space="preserve">5.26631546020508</t>
@@ -5378,25 +5378,25 @@
     <t xml:space="preserve">5.30589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37713003158569</t>
+    <t xml:space="preserve">5.37712955474854</t>
   </si>
   <si>
     <t xml:space="preserve">5.4175853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40527248382568</t>
+    <t xml:space="preserve">5.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">5.38152694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3542628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39032173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43869304656982</t>
+    <t xml:space="preserve">5.35426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39032220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43869256973267</t>
   </si>
   <si>
     <t xml:space="preserve">5.49585962295532</t>
@@ -5405,7 +5405,7 @@
     <t xml:space="preserve">5.54247140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63305807113647</t>
+    <t xml:space="preserve">5.63305759429932</t>
   </si>
   <si>
     <t xml:space="preserve">5.70781326293945</t>
@@ -5417,13 +5417,13 @@
     <t xml:space="preserve">5.6207447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61282968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64097356796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65680408477783</t>
+    <t xml:space="preserve">5.61283016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65680360794067</t>
   </si>
   <si>
     <t xml:space="preserve">5.66559839248657</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">5.65768337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70429515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72276449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.747389793396</t>
+    <t xml:space="preserve">5.70429563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72276496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74738931655884</t>
   </si>
   <si>
     <t xml:space="preserve">5.760582447052</t>
@@ -5450,19 +5450,19 @@
     <t xml:space="preserve">5.7535457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77465343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73155975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81510925292969</t>
+    <t xml:space="preserve">5.77465391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73155927658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81510972976685</t>
   </si>
   <si>
     <t xml:space="preserve">5.91185235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86611938476562</t>
+    <t xml:space="preserve">5.86611986160278</t>
   </si>
   <si>
     <t xml:space="preserve">5.85996341705322</t>
@@ -5474,10 +5474,10 @@
     <t xml:space="preserve">5.86436080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86963701248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90921401977539</t>
+    <t xml:space="preserve">5.86963748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90921354293823</t>
   </si>
   <si>
     <t xml:space="preserve">5.910973072052</t>
@@ -5486,19 +5486,19 @@
     <t xml:space="preserve">5.90041923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91888809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361093521118</t>
+    <t xml:space="preserve">5.91888856887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91361141204834</t>
   </si>
   <si>
     <t xml:space="preserve">5.88458871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89162397384644</t>
+    <t xml:space="preserve">5.89162445068359</t>
   </si>
   <si>
     <t xml:space="preserve">5.92504453659058</t>
@@ -5507,43 +5507,43 @@
     <t xml:space="preserve">5.86787843704224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97165727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98660755157471</t>
+    <t xml:space="preserve">5.97165679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98660802841187</t>
   </si>
   <si>
     <t xml:space="preserve">5.93647718429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83621740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82390451431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8590841293335</t>
+    <t xml:space="preserve">5.83621692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8239049911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85908365249634</t>
   </si>
   <si>
     <t xml:space="preserve">5.80092000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75638866424561</t>
+    <t xml:space="preserve">5.75638818740845</t>
   </si>
   <si>
     <t xml:space="preserve">5.74002981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72185373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69913339614868</t>
+    <t xml:space="preserve">5.72185325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69913291931152</t>
   </si>
   <si>
     <t xml:space="preserve">5.65551090240479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68550109863281</t>
+    <t xml:space="preserve">5.68550157546997</t>
   </si>
   <si>
     <t xml:space="preserve">5.76275014877319</t>
@@ -5561,22 +5561,22 @@
     <t xml:space="preserve">5.52191638946533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48011112213135</t>
+    <t xml:space="preserve">5.48011064529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.41013240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33833646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37741565704346</t>
+    <t xml:space="preserve">5.33833694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.34651613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37468957901001</t>
+    <t xml:space="preserve">5.37468910217285</t>
   </si>
   <si>
     <t xml:space="preserve">5.38468599319458</t>
@@ -5588,10 +5588,10 @@
     <t xml:space="preserve">5.36469221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41376781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39195680618286</t>
+    <t xml:space="preserve">5.41376733779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3919563293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.41467666625977</t>
@@ -5606,22 +5606,22 @@
     <t xml:space="preserve">5.31925201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35469579696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48738145828247</t>
+    <t xml:space="preserve">5.35469532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48738098144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.54463577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57917070388794</t>
+    <t xml:space="preserve">5.5791711807251</t>
   </si>
   <si>
     <t xml:space="preserve">5.57099199295044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59462070465088</t>
+    <t xml:space="preserve">5.59462022781372</t>
   </si>
   <si>
     <t xml:space="preserve">5.5900764465332</t>
@@ -5645,7 +5645,7 @@
     <t xml:space="preserve">5.51646327972412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52646017074585</t>
+    <t xml:space="preserve">5.52645969390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.51373624801636</t>
@@ -5654,7 +5654,7 @@
     <t xml:space="preserve">5.52918672561646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6055269241333</t>
+    <t xml:space="preserve">5.60552597045898</t>
   </si>
   <si>
     <t xml:space="preserve">5.56099462509155</t>
@@ -5666,22 +5666,22 @@
     <t xml:space="preserve">5.44375848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49465179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36105680465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29380512237549</t>
+    <t xml:space="preserve">5.49465131759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36832761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36105728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29380464553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.17929553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18656539916992</t>
+    <t xml:space="preserve">5.18656587600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.33742809295654</t>
@@ -5693,7 +5693,7 @@
     <t xml:space="preserve">5.26563215255737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25836133956909</t>
+    <t xml:space="preserve">5.25836181640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.33651924133301</t>
@@ -5705,10 +5705,10 @@
     <t xml:space="preserve">5.49737787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53282117843628</t>
+    <t xml:space="preserve">5.56190347671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53282165527344</t>
   </si>
   <si>
     <t xml:space="preserve">5.50737476348877</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">5.67277812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68004846572876</t>
+    <t xml:space="preserve">5.68004894256592</t>
   </si>
   <si>
     <t xml:space="preserve">5.74820899963379</t>
@@ -5738,22 +5738,22 @@
     <t xml:space="preserve">5.91452074050903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13899612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13627004623413</t>
+    <t xml:space="preserve">6.13899660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13626956939697</t>
   </si>
   <si>
     <t xml:space="preserve">6.10173559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21806240081787</t>
+    <t xml:space="preserve">6.21806287765503</t>
   </si>
   <si>
     <t xml:space="preserve">6.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17989301681519</t>
+    <t xml:space="preserve">6.17989253997803</t>
   </si>
   <si>
     <t xml:space="preserve">6.14444923400879</t>
@@ -5762,10 +5762,10 @@
     <t xml:space="preserve">6.12082052230835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06538248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00358438491821</t>
+    <t xml:space="preserve">6.0653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00358390808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814371109009</t>
@@ -5774,16 +5774,16 @@
     <t xml:space="preserve">6.0535683631897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05265998840332</t>
+    <t xml:space="preserve">6.05265951156616</t>
   </si>
   <si>
     <t xml:space="preserve">5.97086715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01630687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04902458190918</t>
+    <t xml:space="preserve">6.01630735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04902410507202</t>
   </si>
   <si>
     <t xml:space="preserve">6.1344518661499</t>
@@ -5792,28 +5792,28 @@
     <t xml:space="preserve">6.12172937393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19170713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17807531356812</t>
+    <t xml:space="preserve">6.19170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17807483673096</t>
   </si>
   <si>
     <t xml:space="preserve">6.09810018539429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06992721557617</t>
+    <t xml:space="preserve">6.06992673873901</t>
   </si>
   <si>
     <t xml:space="preserve">5.96904945373535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03539228439331</t>
+    <t xml:space="preserve">6.03539180755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.95632600784302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75911426544189</t>
+    <t xml:space="preserve">5.75911474227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.74275588989258</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">5.87907743453979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9454197883606</t>
+    <t xml:space="preserve">5.94542026519775</t>
   </si>
   <si>
     <t xml:space="preserve">5.97813749313354</t>
@@ -5843,31 +5843,31 @@
     <t xml:space="preserve">5.90452432632446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90179777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00449275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98449850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02812194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04266309738159</t>
+    <t xml:space="preserve">5.9017972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00449323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98449897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02812147140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04266262054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.09446477890015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11809349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16989612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25714159011841</t>
+    <t xml:space="preserve">6.11809396743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1698956489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25714111328125</t>
   </si>
   <si>
     <t xml:space="preserve">6.17171335220337</t>
@@ -5876,31 +5876,31 @@
     <t xml:space="preserve">6.12627363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15081119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13081741333008</t>
+    <t xml:space="preserve">6.15081071853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13081693649292</t>
   </si>
   <si>
     <t xml:space="preserve">6.16179513931274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18150854110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468996047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25191211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26129961013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24252557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22375106811523</t>
+    <t xml:space="preserve">6.18150806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25191259384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2613000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24252510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22375059127808</t>
   </si>
   <si>
     <t xml:space="preserve">6.18995666503906</t>
@@ -5918,40 +5918,40 @@
     <t xml:space="preserve">5.91209363937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03600597381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03412866592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01629257202148</t>
+    <t xml:space="preserve">6.03600549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03412818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01629209518433</t>
   </si>
   <si>
     <t xml:space="preserve">6.04351568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10641002655029</t>
+    <t xml:space="preserve">6.10641050338745</t>
   </si>
   <si>
     <t xml:space="preserve">6.09139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16742706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18714046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17587614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19840526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2021598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30260372161865</t>
+    <t xml:space="preserve">6.16742753982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18714094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17587566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20216035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30260419845581</t>
   </si>
   <si>
     <t xml:space="preserve">6.29791021347046</t>
@@ -5963,10 +5963,10 @@
     <t xml:space="preserve">6.41149616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42651557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44341230392456</t>
+    <t xml:space="preserve">6.42651605606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44341278076172</t>
   </si>
   <si>
     <t xml:space="preserve">6.46594190597534</t>
@@ -5975,13 +5975,13 @@
     <t xml:space="preserve">6.47063589096069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5663857460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61895418167114</t>
+    <t xml:space="preserve">6.46030950546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56638526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6189546585083</t>
   </si>
   <si>
     <t xml:space="preserve">6.62177038192749</t>
@@ -6020,10 +6020,10 @@
     <t xml:space="preserve">6.71752071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77102756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535680770874</t>
+    <t xml:space="preserve">6.7710280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535633087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.7785382270813</t>
@@ -6035,7 +6035,7 @@
     <t xml:space="preserve">6.55605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52883625030518</t>
+    <t xml:space="preserve">6.52883672714233</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147557258606</t>
@@ -6047,7 +6047,7 @@
     <t xml:space="preserve">6.57201766967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5541820526123</t>
+    <t xml:space="preserve">6.55418252944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.63303518295288</t>
@@ -6056,7 +6056,7 @@
     <t xml:space="preserve">6.73629522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76727294921875</t>
+    <t xml:space="preserve">6.76727342605591</t>
   </si>
   <si>
     <t xml:space="preserve">6.83861589431763</t>
@@ -6068,22 +6068,22 @@
     <t xml:space="preserve">6.88273620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88742971420288</t>
+    <t xml:space="preserve">6.88743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">6.73066282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73723411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75976324081421</t>
+    <t xml:space="preserve">6.73723363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75976371765137</t>
   </si>
   <si>
     <t xml:space="preserve">6.74756002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76633405685425</t>
+    <t xml:space="preserve">6.76633453369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.70062351226807</t>
@@ -6098,7 +6098,7 @@
     <t xml:space="preserve">6.58234405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60018014907837</t>
+    <t xml:space="preserve">6.60017967224121</t>
   </si>
   <si>
     <t xml:space="preserve">6.56920194625854</t>
@@ -6116,10 +6116,10 @@
     <t xml:space="preserve">6.34109163284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21436309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37206983566284</t>
+    <t xml:space="preserve">6.21436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.28852272033691</t>
@@ -6137,10 +6137,10 @@
     <t xml:space="preserve">6.32888841629028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32607173919678</t>
+    <t xml:space="preserve">6.30072641372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32607221603394</t>
   </si>
   <si>
     <t xml:space="preserve">6.3551721572876</t>
@@ -6173,7 +6173,7 @@
     <t xml:space="preserve">6.48565530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58891534805298</t>
+    <t xml:space="preserve">6.58891487121582</t>
   </si>
   <si>
     <t xml:space="preserve">6.49222612380981</t>
@@ -6194,7 +6194,7 @@
     <t xml:space="preserve">6.4640645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59454774856567</t>
+    <t xml:space="preserve">6.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.58328247070312</t>
@@ -6206,22 +6206,22 @@
     <t xml:space="preserve">6.5654468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55887603759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60205745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46312618255615</t>
+    <t xml:space="preserve">6.5588755607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60205698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46312570571899</t>
   </si>
   <si>
     <t xml:space="preserve">6.49692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61707639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6687068939209</t>
+    <t xml:space="preserve">6.6170768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66870641708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.572350025177</t>
@@ -6759,6 +6759,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.54800033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5649995803833</t>
   </si>
 </sst>
 </file>
@@ -71889,7 +71892,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6510416667</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>16196299</v>
@@ -71910,6 +71913,32 @@
         <v>2248</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6512037037</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>11256686</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>8.61900043487549</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>8.55099964141846</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>8.55500030517578</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>8.5649995803833</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2249</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="2255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2256">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697376251221</t>
+    <t xml:space="preserve">2.23697304725647</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958250045776</t>
+    <t xml:space="preserve">2.27958273887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.22277021408081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23223876953125</t>
+    <t xml:space="preserve">2.23223924636841</t>
   </si>
   <si>
     <t xml:space="preserve">2.21448540687561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21685218811035</t>
+    <t xml:space="preserve">2.21685242652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.20146608352661</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">2.21211814880371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17187666893005</t>
+    <t xml:space="preserve">2.1718761920929</t>
   </si>
   <si>
     <t xml:space="preserve">2.13281798362732</t>
@@ -77,70 +77,70 @@
     <t xml:space="preserve">2.15767312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0925760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16004014015198</t>
+    <t xml:space="preserve">2.09257626533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16004037857056</t>
   </si>
   <si>
     <t xml:space="preserve">2.20620036125183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19436430931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513794898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236010551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987198829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849429130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07008790969849</t>
+    <t xml:space="preserve">2.19436478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25235962867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17305970191956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395420074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081330299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702153205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07008838653564</t>
   </si>
   <si>
     <t xml:space="preserve">2.06772065162659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08665871620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090931892395</t>
+    <t xml:space="preserve">2.0866584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090884208679</t>
   </si>
   <si>
     <t xml:space="preserve">2.09376001358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16477489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15057158470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648937225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228653907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1529393196106</t>
+    <t xml:space="preserve">2.16477465629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15057182312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15649008750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228677749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15293884277344</t>
   </si>
   <si>
     <t xml:space="preserve">2.0949432849884</t>
@@ -149,67 +149,67 @@
     <t xml:space="preserve">2.18016147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19199728965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791531562805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714239120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542719841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24170756340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31509017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30798840522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3020703792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30562090873718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31745719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153964996338</t>
+    <t xml:space="preserve">2.19199752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330142021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791507720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16714215278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542695999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24170804023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25354361534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31508994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30798816680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30207085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30562138557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574248313904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745743751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3115394115448</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088710784912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31390643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059714317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36716747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680537223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496908187866</t>
+    <t xml:space="preserve">2.31390619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3505973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36716771125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.306804895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496932029724</t>
   </si>
   <si>
     <t xml:space="preserve">2.27366471290588</t>
@@ -218,55 +218,55 @@
     <t xml:space="preserve">2.20738387107849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16595864295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22632122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21921992301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26182842254639</t>
+    <t xml:space="preserve">2.16595792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22632169723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21921968460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26182913780212</t>
   </si>
   <si>
     <t xml:space="preserve">2.27129769325256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32337522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29615306854248</t>
+    <t xml:space="preserve">2.32337498664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2961528301239</t>
   </si>
   <si>
     <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39912438392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231233596802</t>
+    <t xml:space="preserve">2.39912390708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3423125743866</t>
   </si>
   <si>
     <t xml:space="preserve">2.34112930297852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3292932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30917191505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941411018372</t>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3091721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941458702087</t>
   </si>
   <si>
     <t xml:space="preserve">2.37071847915649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37663650512695</t>
+    <t xml:space="preserve">2.37663626670837</t>
   </si>
   <si>
     <t xml:space="preserve">2.33757829666138</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.33166027069092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36125040054321</t>
+    <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
     <t xml:space="preserve">2.3399453163147</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">2.40385890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42989778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42516350746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43699908256531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38965559005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794111251831</t>
+    <t xml:space="preserve">2.41096067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42989754676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42516326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43699860572815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38965582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794039726257</t>
   </si>
   <si>
     <t xml:space="preserve">2.37782001495361</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">2.43463230133057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44173359870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43936657905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651516914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31864047050476</t>
+    <t xml:space="preserve">2.44173383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43936634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651564598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31864070892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.27839875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37900328636169</t>
+    <t xml:space="preserve">2.37900352478027</t>
   </si>
   <si>
     <t xml:space="preserve">2.43817090988159</t>
@@ -335,55 +335,55 @@
     <t xml:space="preserve">2.44433355331421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40735483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875929832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013116836548</t>
+    <t xml:space="preserve">2.4073543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21875905990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21013140678406</t>
   </si>
   <si>
     <t xml:space="preserve">2.30627751350403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40365648269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296192169189</t>
+    <t xml:space="preserve">2.40365600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296263694763</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049715042114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45419454574585</t>
+    <t xml:space="preserve">2.45419502258301</t>
   </si>
   <si>
     <t xml:space="preserve">2.39256262779236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37653803825378</t>
+    <t xml:space="preserve">2.37653779983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.42214608192444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43940305709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45912623405457</t>
+    <t xml:space="preserve">2.43940353393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45912575721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.4603579044342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46282362937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467990398407</t>
+    <t xml:space="preserve">2.46282315254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44679951667786</t>
   </si>
   <si>
     <t xml:space="preserve">2.4800808429718</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">2.47268438339233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53801441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5256884098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240636825562</t>
+    <t xml:space="preserve">2.53801465034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240684509277</t>
   </si>
   <si>
     <t xml:space="preserve">2.48131275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911744594574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52322316169739</t>
+    <t xml:space="preserve">2.49117374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52322292327881</t>
   </si>
   <si>
     <t xml:space="preserve">2.51089644432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350046157837</t>
+    <t xml:space="preserve">2.50350022315979</t>
   </si>
   <si>
     <t xml:space="preserve">2.49856972694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53308391571045</t>
+    <t xml:space="preserve">2.53308439254761</t>
   </si>
   <si>
     <t xml:space="preserve">2.52938604354858</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">2.47021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42461180686951</t>
+    <t xml:space="preserve">2.42461109161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.42707681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39749312400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40242385864258</t>
+    <t xml:space="preserve">2.39749360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40242314338684</t>
   </si>
   <si>
     <t xml:space="preserve">2.42830944061279</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">2.42954182624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43570518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45172905921936</t>
+    <t xml:space="preserve">2.43570470809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172953605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.41351771354675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43200731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48747611045837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48994112014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761464118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541039466858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5306191444397</t>
+    <t xml:space="preserve">2.43200707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48747634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48994135856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541063308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53061890602112</t>
   </si>
   <si>
     <t xml:space="preserve">2.49610471725464</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">2.44556641578674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41105270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475009918213</t>
+    <t xml:space="preserve">2.41105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475033760071</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913300037384</t>
@@ -500,37 +500,37 @@
     <t xml:space="preserve">2.40981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44803142547607</t>
+    <t xml:space="preserve">2.4480311870575</t>
   </si>
   <si>
     <t xml:space="preserve">2.41721534729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42091345787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926428794861</t>
+    <t xml:space="preserve">2.42091393470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926404953003</t>
   </si>
   <si>
     <t xml:space="preserve">2.4122850894928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37284016609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35928106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32476687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051368713379</t>
+    <t xml:space="preserve">2.3728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35928130149841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32476758956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
     <t xml:space="preserve">2.33832573890686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31983637809753</t>
+    <t xml:space="preserve">2.31983685493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36421179771423</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">2.43693780899048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40858674049377</t>
+    <t xml:space="preserve">2.40858721733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.43077421188354</t>
@@ -557,58 +557,58 @@
     <t xml:space="preserve">2.36297917366028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35311794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36667704582214</t>
+    <t xml:space="preserve">2.35311818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36667680740356</t>
   </si>
   <si>
     <t xml:space="preserve">2.38393425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32723236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24711036682129</t>
+    <t xml:space="preserve">2.327232837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24711084365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.24341249465942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080847740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2828574180603</t>
+    <t xml:space="preserve">2.22369050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957585334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28285717964172</t>
   </si>
   <si>
     <t xml:space="preserve">2.22862076759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24834322929382</t>
+    <t xml:space="preserve">2.2483434677124</t>
   </si>
   <si>
     <t xml:space="preserve">2.31860399246216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30751013755798</t>
+    <t xml:space="preserve">2.30750966072083</t>
   </si>
   <si>
     <t xml:space="preserve">2.29764914512634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30257964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065293312073</t>
+    <t xml:space="preserve">2.30257987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586072921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065245628357</t>
   </si>
   <si>
     <t xml:space="preserve">2.33339595794678</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.51952505111694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51336169242859</t>
+    <t xml:space="preserve">2.51336193084717</t>
   </si>
   <si>
     <t xml:space="preserve">2.47884798049927</t>
@@ -629,100 +629,100 @@
     <t xml:space="preserve">2.53924703598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56513261795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54910826683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266784667969</t>
+    <t xml:space="preserve">2.56513285636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5491087436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266713142395</t>
   </si>
   <si>
     <t xml:space="preserve">2.58115744590759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60211205482483</t>
+    <t xml:space="preserve">2.60211229324341</t>
   </si>
   <si>
     <t xml:space="preserve">2.56883096694946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57252836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622647285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896973609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54048037528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56636548042297</t>
+    <t xml:space="preserve">2.57252883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622671127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664301872253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56636571884155</t>
   </si>
   <si>
     <t xml:space="preserve">2.55403900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55650448799133</t>
+    <t xml:space="preserve">2.55650424957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.55157351493835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57299399375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56795454025269</t>
+    <t xml:space="preserve">2.57299447059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56795406341553</t>
   </si>
   <si>
     <t xml:space="preserve">2.52763295173645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50873208045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47849178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42557001113892</t>
+    <t xml:space="preserve">2.50873303413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47849154472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4255702495575</t>
   </si>
   <si>
     <t xml:space="preserve">2.43439030647278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43565058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825077056885</t>
+    <t xml:space="preserve">2.43565034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825053215027</t>
   </si>
   <si>
     <t xml:space="preserve">2.46715140342712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41927003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54401326179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55031394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023313522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53267288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49361205101013</t>
+    <t xml:space="preserve">2.41926980018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069027900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54401397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55031418800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53267312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49361228942871</t>
   </si>
   <si>
     <t xml:space="preserve">2.53141331672668</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">2.5452733039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52133321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52637314796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50369238853455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283403396606</t>
+    <t xml:space="preserve">2.52133297920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52637338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50369215011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52007293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787396430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283355712891</t>
   </si>
   <si>
     <t xml:space="preserve">2.57803440093994</t>
@@ -755,400 +755,400 @@
     <t xml:space="preserve">2.59945511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60323548316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6082751750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62717628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63347601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473653793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237712860107</t>
+    <t xml:space="preserve">2.6032350063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62717580795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757725715637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6523768901825</t>
   </si>
   <si>
     <t xml:space="preserve">2.63977599143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65867638587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151829719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7342791557312</t>
+    <t xml:space="preserve">2.6586766242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71033835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7153787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73427939414978</t>
   </si>
   <si>
     <t xml:space="preserve">2.74183940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75191950798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78090000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964043617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77460050582886</t>
+    <t xml:space="preserve">2.75191926956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78090047836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77460026741028</t>
   </si>
   <si>
     <t xml:space="preserve">2.76199960708618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75947999954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75821924209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72671866416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67253708839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7090790271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80484104156494</t>
+    <t xml:space="preserve">2.77207970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7594792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75821995735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67253756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907807350159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8048415184021</t>
   </si>
   <si>
     <t xml:space="preserve">2.79098033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7771201133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7708203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939942359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7872006893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650277137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792277336121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8665828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87918281555176</t>
+    <t xml:space="preserve">2.77712082862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77082014083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939894676208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78719997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7935004234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650229454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88422393798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792325019836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86658310890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87918305397034</t>
   </si>
   <si>
     <t xml:space="preserve">2.87414288520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87666296958923</t>
+    <t xml:space="preserve">2.87666273117065</t>
   </si>
   <si>
     <t xml:space="preserve">2.88044333457947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94974541664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91572403907776</t>
+    <t xml:space="preserve">2.9497447013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9157247543335</t>
   </si>
   <si>
     <t xml:space="preserve">2.92202425003052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95100545883179</t>
+    <t xml:space="preserve">2.95100569725037</t>
   </si>
   <si>
     <t xml:space="preserve">2.9799861907959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01526713371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518655776978</t>
+    <t xml:space="preserve">3.01526665687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628640174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0051863193512</t>
   </si>
   <si>
     <t xml:space="preserve">3.02912759780884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96108555793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872638702393</t>
+    <t xml:space="preserve">2.9610857963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872567176819</t>
   </si>
   <si>
     <t xml:space="preserve">2.99762654304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01274728775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990609169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148772239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156662940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11354970932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582925796509</t>
+    <t xml:space="preserve">3.01274657249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990656852722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148724555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156710624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11354994773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582878112793</t>
   </si>
   <si>
     <t xml:space="preserve">3.05180835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05558800697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810880661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440782546997</t>
+    <t xml:space="preserve">3.05558848381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810809135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440806388855</t>
   </si>
   <si>
     <t xml:space="preserve">3.09968996047974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10724949836731</t>
+    <t xml:space="preserve">3.10724997520447</t>
   </si>
   <si>
     <t xml:space="preserve">3.08204960823059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13749003410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10346984863281</t>
+    <t xml:space="preserve">3.13749074935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10346961021423</t>
   </si>
   <si>
     <t xml:space="preserve">3.1185896396637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02408719062805</t>
+    <t xml:space="preserve">3.02408790588379</t>
   </si>
   <si>
     <t xml:space="preserve">3.04928827285767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98754692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95730566978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99888730049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9888060092926</t>
+    <t xml:space="preserve">2.98754644393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99888706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880648612976</t>
   </si>
   <si>
     <t xml:space="preserve">2.95478558540344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97368597984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282691001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778674125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06944918632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1324508190155</t>
+    <t xml:space="preserve">2.97368574142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02282738685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778697967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06944942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13245105743408</t>
   </si>
   <si>
     <t xml:space="preserve">3.13119029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10095000267029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12488985061646</t>
+    <t xml:space="preserve">3.10094976425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12488961219788</t>
   </si>
   <si>
     <t xml:space="preserve">3.12867069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09338927268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906027793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07926940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777710914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831353187561</t>
+    <t xml:space="preserve">3.09338998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.119060754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07927012443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831329345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.08953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09595632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703012466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13189673423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040371894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864201545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735836982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.215327501297</t>
+    <t xml:space="preserve">3.09595656394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13703036308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13189625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040324211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864153862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735765457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532726287842</t>
   </si>
   <si>
     <t xml:space="preserve">3.19222354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16013407707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2281641960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383520126343</t>
+    <t xml:space="preserve">3.16013431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383496284485</t>
   </si>
   <si>
     <t xml:space="preserve">3.23458099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19607400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025223731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987934112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26346182823181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29875922203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950596809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271508216858</t>
+    <t xml:space="preserve">3.19607424736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2602527141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987910270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26346135139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29875898361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271532058716</t>
   </si>
   <si>
     <t xml:space="preserve">3.30196833610535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3308482170105</t>
+    <t xml:space="preserve">3.33084869384766</t>
   </si>
   <si>
     <t xml:space="preserve">3.32122230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36614656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405804634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159520149231</t>
+    <t xml:space="preserve">3.36614727973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405709266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159496307373</t>
   </si>
   <si>
     <t xml:space="preserve">3.27629709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28592395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28913331031799</t>
+    <t xml:space="preserve">3.30517721176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28592371940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28913354873657</t>
   </si>
   <si>
     <t xml:space="preserve">3.27308797836304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24099946022034</t>
+    <t xml:space="preserve">3.2409987449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23779058456421</t>
+    <t xml:space="preserve">3.23779034614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.25704336166382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3148045539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801342964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32763910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3083860874176</t>
+    <t xml:space="preserve">3.31480383872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32763934135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30838656425476</t>
   </si>
   <si>
     <t xml:space="preserve">3.32443118095398</t>
@@ -1157,334 +1157,334 @@
     <t xml:space="preserve">3.35010194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39502692222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39181804656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748881340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4559965133667</t>
+    <t xml:space="preserve">3.39502668380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3918182849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41428065299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599627494812</t>
   </si>
   <si>
     <t xml:space="preserve">3.44316029548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44957828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46241354942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995237350464</t>
+    <t xml:space="preserve">3.44957876205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920443534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46241426467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995213508606</t>
   </si>
   <si>
     <t xml:space="preserve">3.42390704154968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38540053367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256455421448</t>
+    <t xml:space="preserve">3.38540077209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256407737732</t>
   </si>
   <si>
     <t xml:space="preserve">3.37898206710815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39823579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689354896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786290168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883153915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.513756275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44636845588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584574699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56189036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816677570343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50412964820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107106208801</t>
+    <t xml:space="preserve">3.39823603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331082344055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674230575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883225440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51375651359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092172622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44636869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054787635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5458459854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114385604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5362184047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166751861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5041298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107130050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.36293768882751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234147071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711544036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40144467353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44611406326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047908782959</t>
+    <t xml:space="preserve">3.29234218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711687088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40144491195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44611430168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047932624817</t>
   </si>
   <si>
     <t xml:space="preserve">3.37738847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35382533073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31717133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34466195106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31586265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302720069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146615982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019269943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070324897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310441970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0684494972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04619431495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12866640090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1810290813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212014198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630395889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466522216797</t>
+    <t xml:space="preserve">3.35382485389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3171718120575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34466218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31586337089539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302672386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310091018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146639823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019198417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070348739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06844902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04619479179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12866568565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652014732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18102884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735724449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212109565735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630372047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466498374939</t>
   </si>
   <si>
     <t xml:space="preserve">3.15877461433411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16597485542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801146507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688470840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815888404846</t>
+    <t xml:space="preserve">3.16597437858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11688446998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04815912246704</t>
   </si>
   <si>
     <t xml:space="preserve">3.07695841789246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09528470039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12670183181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16793823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16531991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1633563041687</t>
+    <t xml:space="preserve">3.09528493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12670278549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16793847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16532039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16335654258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.18757390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17448306083679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673705101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684574127197</t>
+    <t xml:space="preserve">3.17448377609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673776626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684597969055</t>
   </si>
   <si>
     <t xml:space="preserve">3.1915009021759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13913822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17513728141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2562997341156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320936203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844527244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30539011955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277180671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764410972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240843772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324410438538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34728002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095138549805</t>
+    <t xml:space="preserve">3.1391384601593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.175137758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259291648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979315757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630021095276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320960044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538988113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3027720451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764387130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240796089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597158432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34727954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095210075378</t>
   </si>
   <si>
     <t xml:space="preserve">3.39833307266235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38393425941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487885475159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3930971622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44284224510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43629598617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.448077917099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48211407661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52531290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662110328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891477584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109880447388</t>
+    <t xml:space="preserve">3.38393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487933158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39309740066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44284176826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43629622459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44807839393616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520468711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48211431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52531337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52662181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109785079956</t>
   </si>
   <si>
     <t xml:space="preserve">3.31848096847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34335231781006</t>
+    <t xml:space="preserve">3.3433530330658</t>
   </si>
   <si>
     <t xml:space="preserve">3.36298894882202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2379732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20590114593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19542765617371</t>
+    <t xml:space="preserve">3.23797297477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153540611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2059006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655608177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19542860984802</t>
   </si>
   <si>
     <t xml:space="preserve">3.1921558380127</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">3.18037438392639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10772132873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08415794372559</t>
+    <t xml:space="preserve">3.10772109031677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08415770530701</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888657569885</t>
@@ -1505,46 +1505,46 @@
     <t xml:space="preserve">3.11033916473389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07826733589172</t>
+    <t xml:space="preserve">3.0782675743103</t>
   </si>
   <si>
     <t xml:space="preserve">3.09855771064758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13324785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564806938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386733055115</t>
+    <t xml:space="preserve">3.13324856758118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564854621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386780738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.00692272186279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11557579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12932085990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18953776359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888330459595</t>
+    <t xml:space="preserve">3.11557555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12932109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888354301453</t>
   </si>
   <si>
     <t xml:space="preserve">3.16401100158691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16204690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481240272522</t>
+    <t xml:space="preserve">3.16204714775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746569633484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481216430664</t>
   </si>
   <si>
     <t xml:space="preserve">3.10641169548035</t>
@@ -1559,103 +1559,103 @@
     <t xml:space="preserve">3.12342977523804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10313987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11361193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510277748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15550208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739246368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1836462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19411969184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048283576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113753318787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17952394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13647556304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656400680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212462425232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08400988578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08333826065063</t>
+    <t xml:space="preserve">3.1031391620636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11361169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710185050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739270210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186522483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364667892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251944541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1941192150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113681793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952418327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530824661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647532463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656472206116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1721248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338086128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844674110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08401036262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347350120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499650001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468270301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08333730697632</t>
   </si>
   <si>
     <t xml:space="preserve">3.06921243667603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00598478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99051427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01203846931458</t>
+    <t xml:space="preserve">3.00598526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99051380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01203870773315</t>
   </si>
   <si>
     <t xml:space="preserve">2.98042511940002</t>
@@ -1664,109 +1664,109 @@
     <t xml:space="preserve">2.97638940811157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96629977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791359901428</t>
+    <t xml:space="preserve">2.96629953384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99791288375854</t>
   </si>
   <si>
     <t xml:space="preserve">2.9851336479187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95082974433899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9629373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150184631348</t>
+    <t xml:space="preserve">2.95082902908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96293663978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150208473206</t>
   </si>
   <si>
     <t xml:space="preserve">2.92997789382935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94006705284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836430549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540532112122</t>
+    <t xml:space="preserve">2.94006729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836406707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540555953979</t>
   </si>
   <si>
     <t xml:space="preserve">2.85397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88558411598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94477534294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719374656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584906578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06652116775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05979514122009</t>
+    <t xml:space="preserve">2.8862566947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88558387756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94477605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894376754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06652212142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05979561805725</t>
   </si>
   <si>
     <t xml:space="preserve">3.03625297546387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05912303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07392072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09342670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10149884223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064675331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96764516830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9474663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562671661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0409619808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99993109703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9750440120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94410252571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94343018531799</t>
+    <t xml:space="preserve">3.05912280082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629605293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07392048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0934271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10149836540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064746856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94746589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04096150398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9999315738678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97504353523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94410300254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94343042373657</t>
   </si>
   <si>
     <t xml:space="preserve">2.92325162887573</t>
@@ -1778,82 +1778,82 @@
     <t xml:space="preserve">2.99589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96899008750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93468594551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9797523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446083068848</t>
+    <t xml:space="preserve">2.96899032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93468618392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97975254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9844605922699</t>
   </si>
   <si>
     <t xml:space="preserve">2.9669725894928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94612145423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95957374572754</t>
+    <t xml:space="preserve">2.94612121582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9595730304718</t>
   </si>
   <si>
     <t xml:space="preserve">2.91518020629883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94544816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96428203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00665736198425</t>
+    <t xml:space="preserve">2.94544839859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96428155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168135643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00665807723999</t>
   </si>
   <si>
     <t xml:space="preserve">3.01540160179138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02280044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99455046653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0685396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275412559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13378500938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13243961334229</t>
+    <t xml:space="preserve">3.02280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99454998970032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06853938102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275388717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378477096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13244032859802</t>
   </si>
   <si>
     <t xml:space="preserve">3.1647253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19835758209229</t>
+    <t xml:space="preserve">3.19835734367371</t>
   </si>
   <si>
     <t xml:space="preserve">3.20441079139709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2151734828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037531852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22189927101135</t>
+    <t xml:space="preserve">3.21517300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037508010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22189950942993</t>
   </si>
   <si>
     <t xml:space="preserve">3.23804235458374</t>
@@ -1862,292 +1862,292 @@
     <t xml:space="preserve">3.22727990150452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24880456924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1929759979248</t>
+    <t xml:space="preserve">3.24880480766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19297671318054</t>
   </si>
   <si>
     <t xml:space="preserve">3.19364881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333430290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31674003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37660384178162</t>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3167405128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3766040802002</t>
   </si>
   <si>
     <t xml:space="preserve">3.37525916099548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37256860733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122321128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270108222961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48826050758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39543771743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.392746925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099738121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808218955994</t>
+    <t xml:space="preserve">3.3725688457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655776023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270060539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48826122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39543700218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39274764060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965246200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099785804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808171272278</t>
   </si>
   <si>
     <t xml:space="preserve">3.46673679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4815354347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47346329689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5313093662262</t>
+    <t xml:space="preserve">3.48153400421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47346353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53130888938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.49767804145813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50440430641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51112985610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978493690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032155990601</t>
+    <t xml:space="preserve">3.50440382957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51113057136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978446006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458262443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5703227519989</t>
   </si>
   <si>
     <t xml:space="preserve">3.58275675773621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57446622848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683303833008</t>
+    <t xml:space="preserve">3.57446694374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683256149292</t>
   </si>
   <si>
     <t xml:space="preserve">3.57861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58690214157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56755876541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6214451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61591815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63802528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137536048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545140266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472615242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097770690918</t>
+    <t xml:space="preserve">3.58690237998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5675585269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62144494056702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61591792106628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6380250453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57170343399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545116424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097723007202</t>
   </si>
   <si>
     <t xml:space="preserve">3.5910472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61730051040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282633781433</t>
+    <t xml:space="preserve">3.60348320007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071921348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282657623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.61039161682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61453628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420773506165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64631509780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6698043346405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66151475906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533135414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118620872498</t>
+    <t xml:space="preserve">3.61453604698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6242082118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64631485939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66980409622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66151428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533183097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118692398071</t>
   </si>
   <si>
     <t xml:space="preserve">3.66427779197693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68085813522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72921752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80106663703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205061912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7983033657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79001259803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79139423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895879745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83008170127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225840568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258671760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752740859985</t>
+    <t xml:space="preserve">3.68085908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921776771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80106687545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205038070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79830360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79001235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79139447212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895903587341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350159645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8549530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258719444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752669334412</t>
   </si>
   <si>
     <t xml:space="preserve">3.92818307876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94061851501465</t>
+    <t xml:space="preserve">3.94061875343323</t>
   </si>
   <si>
     <t xml:space="preserve">3.90883874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91091179847717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.934401512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92127513885498</t>
+    <t xml:space="preserve">3.91091156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9344003200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93370938301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92127418518066</t>
   </si>
   <si>
     <t xml:space="preserve">3.91022086143494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89847683906555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87567853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564351081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419253349304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695628166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281065940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244874954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593679428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8362991809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571261405945</t>
+    <t xml:space="preserve">3.89847660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564255714417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379511833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419229507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281113624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8024480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593703269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840749740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83630013465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571356773376</t>
   </si>
   <si>
     <t xml:space="preserve">3.85288047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86531567573547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182596206665</t>
+    <t xml:space="preserve">3.86531519889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182643890381</t>
   </si>
   <si>
     <t xml:space="preserve">3.87015175819397</t>
@@ -2156,34 +2156,34 @@
     <t xml:space="preserve">3.85218977928162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83491826057434</t>
+    <t xml:space="preserve">3.83491706848145</t>
   </si>
   <si>
     <t xml:space="preserve">3.80452084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8514986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88880467414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93094635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690485954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068833351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403745651245</t>
+    <t xml:space="preserve">3.85149812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8888041973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93094658851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068761825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403817176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.99934077262878</t>
@@ -2192,49 +2192,49 @@
     <t xml:space="preserve">3.83906292915344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84804487228394</t>
+    <t xml:space="preserve">3.84804439544678</t>
   </si>
   <si>
     <t xml:space="preserve">3.87844204902649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94407367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9558162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108694076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06980752944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02628517150879</t>
+    <t xml:space="preserve">3.94407248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06980800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02628421783447</t>
   </si>
   <si>
     <t xml:space="preserve">4.04010105133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06911659240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13889360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19347047805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20037889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30884170532227</t>
+    <t xml:space="preserve">4.06911706924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13889265060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19347095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20037984848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30884265899658</t>
   </si>
   <si>
     <t xml:space="preserve">4.26255559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27637195587158</t>
+    <t xml:space="preserve">4.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.3053879737854</t>
@@ -2243,49 +2243,49 @@
     <t xml:space="preserve">4.3005518913269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28397178649902</t>
+    <t xml:space="preserve">4.28397226333618</t>
   </si>
   <si>
     <t xml:space="preserve">4.19692420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2031421661377</t>
+    <t xml:space="preserve">4.20314168930054</t>
   </si>
   <si>
     <t xml:space="preserve">4.24182987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2321572303772</t>
+    <t xml:space="preserve">4.23215770721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.32473230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42697858810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4214506149292</t>
+    <t xml:space="preserve">4.42697763442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45392084121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42145204544067</t>
   </si>
   <si>
     <t xml:space="preserve">4.4283595085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42766904830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43941307067871</t>
+    <t xml:space="preserve">4.42766952514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43941354751587</t>
   </si>
   <si>
     <t xml:space="preserve">4.49744510650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45668601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48501014709473</t>
+    <t xml:space="preserve">4.45668506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48500967025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.4995174407959</t>
@@ -2294,28 +2294,28 @@
     <t xml:space="preserve">4.5312967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34407520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43239831924438</t>
+    <t xml:space="preserve">4.34407567977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43239879608154</t>
   </si>
   <si>
     <t xml:space="preserve">4.43310594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47267484664917</t>
+    <t xml:space="preserve">4.47267389297485</t>
   </si>
   <si>
     <t xml:space="preserve">4.41402816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38788461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41332054138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35891532897949</t>
+    <t xml:space="preserve">4.38788366317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41332101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35891485214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.38011169433594</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">4.40908145904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37940454483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711839675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33418273925781</t>
+    <t xml:space="preserve">4.37940502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33418369293213</t>
   </si>
   <si>
     <t xml:space="preserve">4.33842277526855</t>
@@ -2339,70 +2339,70 @@
     <t xml:space="preserve">4.26493835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28472280502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29461479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24586009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44087743759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49316549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40625524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419477462769</t>
+    <t xml:space="preserve">4.28472328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29461526870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24586057662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44087791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49316501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40625476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419525146484</t>
   </si>
   <si>
     <t xml:space="preserve">4.4401707649231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39707088470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5920877456665</t>
+    <t xml:space="preserve">4.39706945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59208679199219</t>
   </si>
   <si>
     <t xml:space="preserve">4.5935001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68606281280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65921211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71997833251953</t>
+    <t xml:space="preserve">4.68606185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65921258926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71997880935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.72068548202515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76095962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70937967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58572673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181074142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263698577881</t>
+    <t xml:space="preserve">4.76096057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70937919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758274078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62458944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58572816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263746261597</t>
   </si>
   <si>
     <t xml:space="preserve">4.65779876708984</t>
@@ -2411,64 +2411,64 @@
     <t xml:space="preserve">4.58007478713989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480546951294</t>
+    <t xml:space="preserve">4.60480499267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67405080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64649295806885</t>
+    <t xml:space="preserve">4.67404985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64649391174316</t>
   </si>
   <si>
     <t xml:space="preserve">4.71361923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78215742111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75530815124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82737874984741</t>
+    <t xml:space="preserve">4.78215837478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75530767440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82737970352173</t>
   </si>
   <si>
     <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81678009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220636367798</t>
+    <t xml:space="preserve">4.84080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81677961349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220588684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.69100856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77226638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8365650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81536722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78145122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78992986679077</t>
+    <t xml:space="preserve">4.77226591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83656454086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78498411178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81536817550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78145170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78993082046509</t>
   </si>
   <si>
     <t xml:space="preserve">4.83161878585815</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">4.80830144882202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78357028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8245530128479</t>
+    <t xml:space="preserve">4.78357124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82455253601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.76590633392334</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">4.84221696853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86129474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84998989105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85564231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87754583358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90369081497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89733123779297</t>
+    <t xml:space="preserve">4.86129522323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84998941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85564279556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8775463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90368986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89733076095581</t>
   </si>
   <si>
     <t xml:space="preserve">4.92347431182861</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">4.88249254226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87472009658813</t>
+    <t xml:space="preserve">4.87472057342529</t>
   </si>
   <si>
     <t xml:space="preserve">4.77085256576538</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">4.85140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84716415405273</t>
+    <t xml:space="preserve">4.84716367721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.93407344818115</t>
@@ -2531,64 +2531,64 @@
     <t xml:space="preserve">4.89662408828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8577618598938</t>
+    <t xml:space="preserve">4.85776233673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82596588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78710460662842</t>
+    <t xml:space="preserve">4.87401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8259654045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759477615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78710412979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.76943969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83303260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85493612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84433794021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66698503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71785831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75601434707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83727169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89309215545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95315170288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94679164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09164094924927</t>
+    <t xml:space="preserve">4.83303117752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85493516921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84433698654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66698455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71785879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75601482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83727121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89309167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9531512260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9333667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9467921257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09164142608643</t>
   </si>
   <si>
     <t xml:space="preserve">5.06973743438721</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">5.04359340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09588050842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09517478942871</t>
+    <t xml:space="preserve">4.9969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09588098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09517431259155</t>
   </si>
   <si>
     <t xml:space="preserve">5.10577297210693</t>
@@ -2612,25 +2612,25 @@
     <t xml:space="preserve">5.10860013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13686227798462</t>
+    <t xml:space="preserve">5.13686275482178</t>
   </si>
   <si>
     <t xml:space="preserve">5.16159296035767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24072980880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22871875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24355745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45835781097412</t>
+    <t xml:space="preserve">5.24073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22871828079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2435564994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37780714035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45835828781128</t>
   </si>
   <si>
     <t xml:space="preserve">5.50453615188599</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">5.49804162979126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64162588119507</t>
+    <t xml:space="preserve">5.64162635803223</t>
   </si>
   <si>
     <t xml:space="preserve">5.5370044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69934844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871608734131</t>
+    <t xml:space="preserve">5.69934892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871704101562</t>
   </si>
   <si>
     <t xml:space="preserve">5.83571767807007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66760158538818</t>
+    <t xml:space="preserve">5.66760110855103</t>
   </si>
   <si>
     <t xml:space="preserve">5.74769067764282</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">5.77222347259521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82272958755493</t>
+    <t xml:space="preserve">5.82273006439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602163314819</t>
@@ -2681,154 +2681,154 @@
     <t xml:space="preserve">5.91652774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91147756576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86746501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9215784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97208642959595</t>
+    <t xml:space="preserve">5.91147708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86746454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92157888412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97208595275879</t>
   </si>
   <si>
     <t xml:space="preserve">6.05650472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10917568206787</t>
+    <t xml:space="preserve">6.10917615890503</t>
   </si>
   <si>
     <t xml:space="preserve">6.18060779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08464431762695</t>
+    <t xml:space="preserve">6.08464479446411</t>
   </si>
   <si>
     <t xml:space="preserve">6.09258079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79386901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975515365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51247215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62286710739136</t>
+    <t xml:space="preserve">5.79386806488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152456283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71161460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51247262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62286615371704</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538879394531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87684488296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69357538223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1271767616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712291717529</t>
+    <t xml:space="preserve">5.87684440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69357585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12717628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712339401245</t>
   </si>
   <si>
     <t xml:space="preserve">4.70436191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7707052230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426502227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830178260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12713861465454</t>
+    <t xml:space="preserve">3.77070498466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1271390914917</t>
   </si>
   <si>
     <t xml:space="preserve">4.2497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20650768280029</t>
+    <t xml:space="preserve">4.20650720596313</t>
   </si>
   <si>
     <t xml:space="preserve">4.24907732009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30896425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55356168746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54562568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53047323226929</t>
+    <t xml:space="preserve">4.30896472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5535626411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54562520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53047370910645</t>
   </si>
   <si>
     <t xml:space="preserve">4.44100427627563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6076774597168</t>
+    <t xml:space="preserve">4.60767698287964</t>
   </si>
   <si>
     <t xml:space="preserve">4.57376480102539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37823104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378877639771</t>
+    <t xml:space="preserve">4.37823057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378829956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.37895250320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43018054962158</t>
+    <t xml:space="preserve">4.4301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.59974050521851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53480195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65601968765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6516900062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47852230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50882720947266</t>
+    <t xml:space="preserve">4.53480243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65601873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65168905258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47852373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50882816314697</t>
   </si>
   <si>
     <t xml:space="preserve">4.47996616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46770048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33277463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3183445930481</t>
+    <t xml:space="preserve">4.46770000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3327751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31834411621094</t>
   </si>
   <si>
     <t xml:space="preserve">4.2757740020752</t>
@@ -2840,94 +2840,94 @@
     <t xml:space="preserve">4.37967443466187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43739652633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52397918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49944829940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33421754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39266109466553</t>
+    <t xml:space="preserve">4.43739604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52397966384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4994478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33421802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">4.37750911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46481466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47347211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081338882446</t>
+    <t xml:space="preserve">4.46481418609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47347259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508129119873</t>
   </si>
   <si>
     <t xml:space="preserve">4.24547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15672254562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30319261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35586357116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5109920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56727123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62499332427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69714641571045</t>
+    <t xml:space="preserve">4.15672206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30319213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35586404800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51099157333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56727027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62499284744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69714689254761</t>
   </si>
   <si>
     <t xml:space="preserve">4.70147562026978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04925155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18706369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40063619613647</t>
+    <t xml:space="preserve">4.75198221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04925203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40063571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.46773815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46701622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011785507202</t>
+    <t xml:space="preserve">5.46701669692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176197052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011690139771</t>
   </si>
   <si>
     <t xml:space="preserve">5.28663444519043</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">5.31188821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4590802192688</t>
+    <t xml:space="preserve">5.45907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">5.41506671905518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39197731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361110687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63585376739502</t>
+    <t xml:space="preserve">5.39197826385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361158370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63585424423218</t>
   </si>
   <si>
     <t xml:space="preserve">5.50092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52906799316406</t>
+    <t xml:space="preserve">5.5290675163269</t>
   </si>
   <si>
     <t xml:space="preserve">5.51175117492676</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">5.57308101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53989124298096</t>
+    <t xml:space="preserve">5.5398907661438</t>
   </si>
   <si>
     <t xml:space="preserve">5.55720806121826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73398160934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68131065368652</t>
+    <t xml:space="preserve">5.73398208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68130970001221</t>
   </si>
   <si>
     <t xml:space="preserve">5.71017122268677</t>
@@ -2984,58 +2984,58 @@
     <t xml:space="preserve">5.75418424606323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83427476882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232431411743</t>
+    <t xml:space="preserve">5.83427381515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86024856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232383728027</t>
   </si>
   <si>
     <t xml:space="preserve">5.89416074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95476961135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08031511306763</t>
+    <t xml:space="preserve">5.9547700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08031558990479</t>
   </si>
   <si>
     <t xml:space="preserve">6.12669610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13258647918701</t>
+    <t xml:space="preserve">6.1325855255127</t>
   </si>
   <si>
     <t xml:space="preserve">6.03246164321899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98829030990601</t>
+    <t xml:space="preserve">5.98828935623169</t>
   </si>
   <si>
     <t xml:space="preserve">5.84841012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83147764205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8712329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69601631164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6901273727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362464904785</t>
+    <t xml:space="preserve">5.83147811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123250961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69012641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362512588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.7931957244873</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">5.7666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69086265563965</t>
+    <t xml:space="preserve">5.69086313247681</t>
   </si>
   <si>
     <t xml:space="preserve">5.75344038009644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79024982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97062063217163</t>
+    <t xml:space="preserve">5.79025030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313486099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062015533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.89552783966064</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">5.70926809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69159936904907</t>
+    <t xml:space="preserve">5.69159984588623</t>
   </si>
   <si>
     <t xml:space="preserve">5.79098701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74534130096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092388153076</t>
+    <t xml:space="preserve">5.74534177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092435836792</t>
   </si>
   <si>
     <t xml:space="preserve">5.60767221450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62460374832153</t>
+    <t xml:space="preserve">5.62460470199585</t>
   </si>
   <si>
     <t xml:space="preserve">5.58705759048462</t>
@@ -3098,70 +3098,70 @@
     <t xml:space="preserve">5.52448081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043193817139</t>
+    <t xml:space="preserve">5.63049459457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043241500854</t>
   </si>
   <si>
     <t xml:space="preserve">5.45674991607666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.590003490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165796279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63270330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5981011390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63932847976685</t>
+    <t xml:space="preserve">5.59000301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63270282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59810161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63932800292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.56644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5767502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319129943848</t>
+    <t xml:space="preserve">5.61650657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57675075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319082260132</t>
   </si>
   <si>
     <t xml:space="preserve">5.46263933181763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3441104888916</t>
+    <t xml:space="preserve">5.34411001205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.38975524902344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49208784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.400062084198</t>
+    <t xml:space="preserve">5.49208831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40006256103516</t>
   </si>
   <si>
     <t xml:space="preserve">5.48325252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52153635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46116781234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49797630310059</t>
+    <t xml:space="preserve">5.52153539657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4611668586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49797677993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.44349813461304</t>
@@ -3173,133 +3173,133 @@
     <t xml:space="preserve">5.59221172332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55613708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5392050743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65920543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67761087417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429655075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5414137840271</t>
+    <t xml:space="preserve">5.5561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53920412063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65920639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67761135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54141330718994</t>
   </si>
   <si>
     <t xml:space="preserve">5.49871301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58190441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5325779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57233381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44423389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662244796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10705184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03122329711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31318998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42435693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6032543182373</t>
+    <t xml:space="preserve">5.58190393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57233333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4442343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662340164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10705232620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0312237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31318950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42435741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60325479507446</t>
   </si>
   <si>
     <t xml:space="preserve">5.92718410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92424011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04571294784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90436315536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95515966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97209358215332</t>
+    <t xml:space="preserve">5.92423963546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04571390151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90436267852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95515918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97209310531616</t>
   </si>
   <si>
     <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01037549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0611743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737195968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24817037582397</t>
+    <t xml:space="preserve">6.0103759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24816989898682</t>
   </si>
   <si>
     <t xml:space="preserve">6.23565435409546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2592134475708</t>
+    <t xml:space="preserve">6.25921201705933</t>
   </si>
   <si>
     <t xml:space="preserve">6.16203355789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522315979004</t>
+    <t xml:space="preserve">6.12522268295288</t>
   </si>
   <si>
     <t xml:space="preserve">6.09724807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04350423812866</t>
+    <t xml:space="preserve">6.04350471496582</t>
   </si>
   <si>
     <t xml:space="preserve">6.04129648208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0228910446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00743055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97798204421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04424142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9257116317749</t>
+    <t xml:space="preserve">6.02289152145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00743103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97798299789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92571210861206</t>
   </si>
   <si>
     <t xml:space="preserve">5.922767162323</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">6.00890302658081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01700115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94190883636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08914947509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14362812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09283065795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22608423233032</t>
+    <t xml:space="preserve">6.01700162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9419093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08914995193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14362859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09283018112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22608375549316</t>
   </si>
   <si>
     <t xml:space="preserve">6.18043947219849</t>
@@ -3332,34 +3332,34 @@
     <t xml:space="preserve">6.57357168197632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166944503784</t>
+    <t xml:space="preserve">6.46167087554932</t>
   </si>
   <si>
     <t xml:space="preserve">6.58019828796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58756017684937</t>
+    <t xml:space="preserve">6.58755970001221</t>
   </si>
   <si>
     <t xml:space="preserve">6.48081159591675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57062864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50289678573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52203798294067</t>
+    <t xml:space="preserve">6.57062816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50289630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52203702926636</t>
   </si>
   <si>
     <t xml:space="preserve">6.44768476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43942356109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44242763519287</t>
+    <t xml:space="preserve">6.43942403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44242811203003</t>
   </si>
   <si>
     <t xml:space="preserve">6.3530535697937</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">6.26743507385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.259925365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3087420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932771682739</t>
+    <t xml:space="preserve">6.25992488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932676315308</t>
   </si>
   <si>
     <t xml:space="preserve">6.30949306488037</t>
@@ -3386,52 +3386,52 @@
     <t xml:space="preserve">6.17430591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15853404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42290163040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42590427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3440408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38384628295898</t>
+    <t xml:space="preserve">6.15853357315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42290067672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42590475082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34404134750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38384675979614</t>
   </si>
   <si>
     <t xml:space="preserve">6.22162199020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24715757369995</t>
+    <t xml:space="preserve">6.24715662002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.35530662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23589181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15553045272827</t>
+    <t xml:space="preserve">6.35981225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756063461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23589134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15552997589111</t>
   </si>
   <si>
     <t xml:space="preserve">6.06615591049194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99105215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94824314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88816022872925</t>
+    <t xml:space="preserve">5.99105262756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88815975189209</t>
   </si>
   <si>
     <t xml:space="preserve">5.89116334915161</t>
@@ -3440,31 +3440,31 @@
     <t xml:space="preserve">5.9685206413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85962057113647</t>
+    <t xml:space="preserve">5.85962009429932</t>
   </si>
   <si>
     <t xml:space="preserve">5.72743701934814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89041376113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9129433631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1697998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19984102249146</t>
+    <t xml:space="preserve">5.89041328430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91294384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16979932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19984197616577</t>
   </si>
   <si>
     <t xml:space="preserve">6.14426469802856</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">6.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12999391555786</t>
+    <t xml:space="preserve">6.12999486923218</t>
   </si>
   <si>
     <t xml:space="preserve">6.05639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23814487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166320800781</t>
+    <t xml:space="preserve">6.2381443977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166368484497</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826948165894</t>
@@ -3494,40 +3494,40 @@
     <t xml:space="preserve">6.32902050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38910436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33352708816528</t>
+    <t xml:space="preserve">6.38910388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33352661132812</t>
   </si>
   <si>
     <t xml:space="preserve">6.37858867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440271377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44843673706055</t>
+    <t xml:space="preserve">6.33502912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44843578338623</t>
   </si>
   <si>
     <t xml:space="preserve">6.49725294113159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45444393157959</t>
+    <t xml:space="preserve">6.45444488525391</t>
   </si>
   <si>
     <t xml:space="preserve">6.44392967224121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47472381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39060592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44468069076538</t>
+    <t xml:space="preserve">6.47472333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39060544967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44468212127686</t>
   </si>
   <si>
     <t xml:space="preserve">6.50326251983643</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">6.50551509857178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42515468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37408351898193</t>
+    <t xml:space="preserve">6.42515420913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">6.54757404327393</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">6.5603404045105</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4889931678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217794418335</t>
+    <t xml:space="preserve">6.48899269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479188919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217746734619</t>
   </si>
   <si>
     <t xml:space="preserve">6.20885419845581</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">6.27569675445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16304063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22537660598755</t>
+    <t xml:space="preserve">6.16304111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22537612915039</t>
   </si>
   <si>
     <t xml:space="preserve">6.20960474014282</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">6.214111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00231790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16153955459595</t>
+    <t xml:space="preserve">6.00231742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07742118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16153907775879</t>
   </si>
   <si>
     <t xml:space="preserve">6.12623929977417</t>
@@ -3590,34 +3590,34 @@
     <t xml:space="preserve">6.10445928573608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98279047012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06390285491943</t>
+    <t xml:space="preserve">5.98279094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06390380859375</t>
   </si>
   <si>
     <t xml:space="preserve">6.14952182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12774181365967</t>
+    <t xml:space="preserve">6.12774229049683</t>
   </si>
   <si>
     <t xml:space="preserve">6.13374996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572456359863</t>
+    <t xml:space="preserve">6.11872863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572504043579</t>
   </si>
   <si>
     <t xml:space="preserve">6.05038404464722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99405670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92721366882324</t>
+    <t xml:space="preserve">5.99405574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92721462249756</t>
   </si>
   <si>
     <t xml:space="preserve">5.95650434494019</t>
@@ -3626,82 +3626,82 @@
     <t xml:space="preserve">6.01057910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01733875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01808977127075</t>
+    <t xml:space="preserve">6.01733827590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01808929443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.9790358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0248498916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08493232727051</t>
+    <t xml:space="preserve">6.02484941482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08493185043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.06840991973877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06765842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04888248443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09845018386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9865460395813</t>
+    <t xml:space="preserve">6.16829824447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0676589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04888296127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09845161437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08943891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98654651641846</t>
   </si>
   <si>
     <t xml:space="preserve">6.03386163711548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01508474349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879957199097</t>
+    <t xml:space="preserve">6.01508569717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879861831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.03686571121216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88215065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89491891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89642095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93772840499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96401405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9204535484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95124673843384</t>
+    <t xml:space="preserve">5.88215112686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89491939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8964204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93772888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96401453018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92045450210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.951247215271</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489063262939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0518856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02635097503662</t>
+    <t xml:space="preserve">6.05188608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02635145187378</t>
   </si>
   <si>
     <t xml:space="preserve">5.95725536346436</t>
@@ -3710,55 +3710,55 @@
     <t xml:space="preserve">6.01583623886108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84443950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8513560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00277042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11575412750244</t>
+    <t xml:space="preserve">5.8444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85135698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00276947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1157546043396</t>
   </si>
   <si>
     <t xml:space="preserve">6.18723440170288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21106100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11959743499756</t>
+    <t xml:space="preserve">6.21106147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11959791183472</t>
   </si>
   <si>
     <t xml:space="preserve">6.19107723236084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16033315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97971296310425</t>
+    <t xml:space="preserve">6.16033363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97971248626709</t>
   </si>
   <si>
     <t xml:space="preserve">5.94819927215576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92053079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99354648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98586130142212</t>
+    <t xml:space="preserve">5.91361284255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92052984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96357202529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9935474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98586082458496</t>
   </si>
   <si>
     <t xml:space="preserve">6.02044820785522</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">6.02890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06349039077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03120899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97740697860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735733032227</t>
+    <t xml:space="preserve">6.06348991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03120946884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97740650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735780715942</t>
   </si>
   <si>
     <t xml:space="preserve">6.08885383605957</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">6.14957332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01967906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96510887145996</t>
+    <t xml:space="preserve">6.0196795463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9651083946228</t>
   </si>
   <si>
     <t xml:space="preserve">5.90131521224976</t>
@@ -3803,46 +3803,46 @@
     <t xml:space="preserve">5.93129062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99815845489502</t>
+    <t xml:space="preserve">5.99815893173218</t>
   </si>
   <si>
     <t xml:space="preserve">5.935133934021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92975330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77833938598633</t>
+    <t xml:space="preserve">5.92975378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77833890914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756284713745</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76373624801636</t>
+    <t xml:space="preserve">5.66842889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7637357711792</t>
   </si>
   <si>
     <t xml:space="preserve">5.71454572677612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3994197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38097238540649</t>
+    <t xml:space="preserve">5.39941930770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38097286224365</t>
   </si>
   <si>
     <t xml:space="preserve">5.34869194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25722789764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30257511138916</t>
+    <t xml:space="preserve">5.25722742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30257606506348</t>
   </si>
   <si>
     <t xml:space="preserve">5.33408784866333</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">5.44092321395874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39403915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33946847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25492143630981</t>
+    <t xml:space="preserve">5.39403867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33946800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25492191314697</t>
   </si>
   <si>
     <t xml:space="preserve">5.22110366821289</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">5.11196279525757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17191362380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17883014678955</t>
+    <t xml:space="preserve">5.17191314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">5.30564975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31794786453247</t>
+    <t xml:space="preserve">5.31794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">5.18651676177979</t>
@@ -3890,46 +3890,46 @@
     <t xml:space="preserve">5.24954128265381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30795526504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44246053695679</t>
+    <t xml:space="preserve">5.30795621871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44246006011963</t>
   </si>
   <si>
     <t xml:space="preserve">5.54161024093628</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5131721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708873748779</t>
+    <t xml:space="preserve">5.51317167282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708826065063</t>
   </si>
   <si>
     <t xml:space="preserve">5.49165105819702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54622220993042</t>
+    <t xml:space="preserve">5.5462212562561</t>
   </si>
   <si>
     <t xml:space="preserve">5.58772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56159400939941</t>
+    <t xml:space="preserve">5.56159353256226</t>
   </si>
   <si>
     <t xml:space="preserve">5.59925508499146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55775117874146</t>
+    <t xml:space="preserve">5.5577507019043</t>
   </si>
   <si>
     <t xml:space="preserve">5.57696580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389163970947</t>
+    <t xml:space="preserve">5.57389116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.60617256164551</t>
@@ -3941,22 +3941,22 @@
     <t xml:space="preserve">5.45245265960693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50318050384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45629501342773</t>
+    <t xml:space="preserve">5.50318002700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45629453659058</t>
   </si>
   <si>
     <t xml:space="preserve">5.49549436569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44707202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43246936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41248464584351</t>
+    <t xml:space="preserve">5.44707250595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4324688911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41248512268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.34177398681641</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23878192901611</t>
+    <t xml:space="preserve">5.23878145217896</t>
   </si>
   <si>
     <t xml:space="preserve">5.21802949905396</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">5.19189739227295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06507778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01588773727417</t>
+    <t xml:space="preserve">5.0650782585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01588726043701</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730165481567</t>
@@ -3998,34 +3998,34 @@
     <t xml:space="preserve">5.23493814468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039253234863</t>
+    <t xml:space="preserve">5.15039348602295</t>
   </si>
   <si>
     <t xml:space="preserve">5.1511607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14193725585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0758376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0927472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1473183631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1096568107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18497943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1134991645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25338459014893</t>
+    <t xml:space="preserve">5.14193773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07583808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09274768829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14731788635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18497896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11349964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25338506698608</t>
   </si>
   <si>
     <t xml:space="preserve">5.28489780426025</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">5.32486486434937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40787315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38788986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41555976867676</t>
+    <t xml:space="preserve">5.40787363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38789033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4155592918396</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
@@ -4052,34 +4052,34 @@
     <t xml:space="preserve">5.47243642807007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34100484848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
+    <t xml:space="preserve">5.34100532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026172637939</t>
   </si>
   <si>
     <t xml:space="preserve">5.32640171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32717132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025289535522</t>
+    <t xml:space="preserve">5.32717037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025337219238</t>
   </si>
   <si>
     <t xml:space="preserve">5.35022878646851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23186349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38250970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30718755722046</t>
+    <t xml:space="preserve">5.2318639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27490520477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3825101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
     <t xml:space="preserve">5.26766967773438</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">5.41546487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33643007278442</t>
+    <t xml:space="preserve">5.33642959594727</t>
   </si>
   <si>
     <t xml:space="preserve">5.35934972763062</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">5.08272838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00369310379028</t>
+    <t xml:space="preserve">5.00369358062744</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908435821533</t>
@@ -4130,22 +4130,22 @@
     <t xml:space="preserve">4.99499940872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08114767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14516544342041</t>
+    <t xml:space="preserve">5.08114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">5.12303590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08588981628418</t>
+    <t xml:space="preserve">5.08589029312134</t>
   </si>
   <si>
     <t xml:space="preserve">4.97603178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01396751403809</t>
+    <t xml:space="preserve">5.01396799087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.99025726318359</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">4.8764476776123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7065224647522</t>
+    <t xml:space="preserve">4.70652294158936</t>
   </si>
   <si>
     <t xml:space="preserve">4.48127365112305</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">4.53580665588379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52711391448975</t>
+    <t xml:space="preserve">4.5271143913269</t>
   </si>
   <si>
     <t xml:space="preserve">4.59903526306152</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">4.51209735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56030797958374</t>
+    <t xml:space="preserve">4.5603084564209</t>
   </si>
   <si>
     <t xml:space="preserve">4.64566516876221</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">4.8187518119812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79583168029785</t>
+    <t xml:space="preserve">4.79583120346069</t>
   </si>
   <si>
     <t xml:space="preserve">4.82428455352783</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">4.92544889450073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90648078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87486696243286</t>
+    <t xml:space="preserve">4.90648126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8748664855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.98709583282471</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">4.91596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91438388824463</t>
+    <t xml:space="preserve">4.91438436508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.87881851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93888521194458</t>
+    <t xml:space="preserve">4.93888473510742</t>
   </si>
   <si>
     <t xml:space="preserve">4.89541530609131</t>
@@ -4292,16 +4292,16 @@
     <t xml:space="preserve">4.74841070175171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64171409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72628164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6140513420105</t>
+    <t xml:space="preserve">4.64171361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6172137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61405181884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.69229555130005</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">4.83930063247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84720420837402</t>
+    <t xml:space="preserve">4.84720468521118</t>
   </si>
   <si>
     <t xml:space="preserve">4.84641408920288</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">4.88909292221069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87012529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77686405181885</t>
+    <t xml:space="preserve">4.87012481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77686357498169</t>
   </si>
   <si>
     <t xml:space="preserve">4.68202114105225</t>
@@ -4355,28 +4355,28 @@
     <t xml:space="preserve">4.73260402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62037467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52790498733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33189725875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25839471817017</t>
+    <t xml:space="preserve">4.62037420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52790451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3318977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25839519500732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492624282837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39117383956909</t>
+    <t xml:space="preserve">4.39117431640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.26787900924683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30107355117798</t>
+    <t xml:space="preserve">4.30107402801514</t>
   </si>
   <si>
     <t xml:space="preserve">4.33822059631348</t>
@@ -4397,10 +4397,10 @@
     <t xml:space="preserve">4.2749924659729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32794570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26945924758911</t>
+    <t xml:space="preserve">4.32794618606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26945972442627</t>
   </si>
   <si>
     <t xml:space="preserve">4.12561702728271</t>
@@ -4412,10 +4412,10 @@
     <t xml:space="preserve">4.173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01259708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09084177017212</t>
+    <t xml:space="preserve">4.01259660720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09084129333496</t>
   </si>
   <si>
     <t xml:space="preserve">4.15960168838501</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">4.15090799331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14300489425659</t>
+    <t xml:space="preserve">4.14300441741943</t>
   </si>
   <si>
     <t xml:space="preserve">4.09242153167725</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82133221626282</t>
+    <t xml:space="preserve">3.82133269309998</t>
   </si>
   <si>
     <t xml:space="preserve">3.951740026474</t>
@@ -6777,6 +6777,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.48799991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55599975585938</t>
   </si>
 </sst>
 </file>
@@ -72011,7 +72014,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6513657407</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>13293814</v>
@@ -72032,6 +72035,32 @@
         <v>2254</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.693900463</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>19589983</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>8.5649995803833</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>8.43200016021729</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>8.47999954223633</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>8.55599975585938</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2255</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="2257">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697304725647</t>
+    <t xml:space="preserve">2.23697328567505</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958273887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22277021408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21685242652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20146608352661</t>
+    <t xml:space="preserve">2.27958202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22277092933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23223948478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448493003845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21685218811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20146632194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.23460626602173</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">2.21211814880371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1718761920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281798362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767312049866</t>
+    <t xml:space="preserve">2.17187643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13281846046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767383575439</t>
   </si>
   <si>
     <t xml:space="preserve">2.09257626533508</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">2.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20620036125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19436478614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25235962867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305970191956</t>
+    <t xml:space="preserve">2.20620012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19436430931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25236058235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17305994033813</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987174987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22395420074463</t>
+    <t xml:space="preserve">2.22395396232605</t>
   </si>
   <si>
     <t xml:space="preserve">2.19081330299377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14702153205872</t>
+    <t xml:space="preserve">2.14702105522156</t>
   </si>
   <si>
     <t xml:space="preserve">2.09849405288696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07008838653564</t>
+    <t xml:space="preserve">2.07008814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.06772065162659</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">2.0866584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01090884208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09376001358032</t>
+    <t xml:space="preserve">2.01090908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0937602519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.16477465629578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057182312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15649008750916</t>
+    <t xml:space="preserve">2.15057158470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648937225342</t>
   </si>
   <si>
     <t xml:space="preserve">2.14228677749634</t>
@@ -146,133 +146,133 @@
     <t xml:space="preserve">2.0949432849884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18016147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19199752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330142021179</t>
+    <t xml:space="preserve">2.18016123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19199728965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330189704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.19791507720947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16714215278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542695999146</t>
+    <t xml:space="preserve">2.16714191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542672157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.24170804023743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25354361534119</t>
+    <t xml:space="preserve">2.25354337692261</t>
   </si>
   <si>
     <t xml:space="preserve">2.31508994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30798816680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30207085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30562138557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574248313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31745743751526</t>
+    <t xml:space="preserve">2.30798840522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3020703792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30562090873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745719909668</t>
   </si>
   <si>
     <t xml:space="preserve">2.31982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3115394115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088710784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390619277954</t>
+    <t xml:space="preserve">2.31153917312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088686943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3139066696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.3505973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36716771125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.306804895401</t>
+    <t xml:space="preserve">2.36716794967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30680513381958</t>
   </si>
   <si>
     <t xml:space="preserve">2.29496932029724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27366471290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595792770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22632169723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578953742981</t>
+    <t xml:space="preserve">2.2736644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738339424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22632098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578929901123</t>
   </si>
   <si>
     <t xml:space="preserve">2.21921968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26182913780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129769325256</t>
+    <t xml:space="preserve">2.26182889938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129745483398</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337498664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2961528301239</t>
+    <t xml:space="preserve">2.29615235328674</t>
   </si>
   <si>
     <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39912390708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3423125743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32929301261902</t>
+    <t xml:space="preserve">2.39912438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112858772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929348945618</t>
   </si>
   <si>
     <t xml:space="preserve">2.3091721534729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34941458702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37663626670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33757829666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3529646396637</t>
+    <t xml:space="preserve">2.34941434860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071871757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37663650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757853507996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.33166027069092</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.36124992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3399453163147</t>
+    <t xml:space="preserve">2.33994555473328</t>
   </si>
   <si>
     <t xml:space="preserve">2.40385890007019</t>
@@ -293,67 +293,67 @@
     <t xml:space="preserve">2.42989754676819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42516326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43699860572815</t>
+    <t xml:space="preserve">2.42516374588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43699932098389</t>
   </si>
   <si>
     <t xml:space="preserve">2.38965582847595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39794039726257</t>
+    <t xml:space="preserve">2.39794063568115</t>
   </si>
   <si>
     <t xml:space="preserve">2.37782001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43463230133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44173383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43936634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651564598083</t>
+    <t xml:space="preserve">2.43463182449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44173336029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43936657905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651540756226</t>
   </si>
   <si>
     <t xml:space="preserve">2.31864070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27839875221252</t>
+    <t xml:space="preserve">2.2783989906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.37900352478027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43817090988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44433355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4073543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875905990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013140678406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627751350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296263694763</t>
+    <t xml:space="preserve">2.43817043304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44433403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40735411643982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652102470398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21875953674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21013116836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627679824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365624427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296216011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049715042114</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">2.45419502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39256262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37653779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42214608192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43940353393555</t>
+    <t xml:space="preserve">2.3925621509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37653875350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42214632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43940258026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.45912575721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4603579044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282315254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44679951667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4800808429718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254585266113</t>
+    <t xml:space="preserve">2.46035766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282362937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44679927825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48008060455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254561424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.47638273239136</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">2.47268438339233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53801465034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52568793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240684509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48131275177002</t>
+    <t xml:space="preserve">2.53801488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568864822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240732192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4813129901886</t>
   </si>
   <si>
     <t xml:space="preserve">2.49117374420166</t>
@@ -416,79 +416,79 @@
     <t xml:space="preserve">2.52322292327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51089644432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350022315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49856972694397</t>
+    <t xml:space="preserve">2.51089692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50350046157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49856996536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.53308439254761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52938604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47021913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42461109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39749360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40242314338684</t>
+    <t xml:space="preserve">2.52938580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.470219373703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42461156845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707657814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39749312400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40242409706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.42830944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42954182624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43570470809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45172953605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41351771354675</t>
+    <t xml:space="preserve">2.42954206466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43570518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172929763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41351747512817</t>
   </si>
   <si>
     <t xml:space="preserve">2.43200707435608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48747634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48994135856628</t>
+    <t xml:space="preserve">2.48747587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48994159698486</t>
   </si>
   <si>
     <t xml:space="preserve">2.47761535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54541063308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53061890602112</t>
+    <t xml:space="preserve">2.54541039466858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53061866760254</t>
   </si>
   <si>
     <t xml:space="preserve">2.49610471725464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44556641578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475033760071</t>
+    <t xml:space="preserve">2.44556617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105246543884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475009918213</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913300037384</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">2.41968083381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4480311870575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41721534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42091393470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926404953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4122850894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3728404045105</t>
+    <t xml:space="preserve">2.40981984138489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44803166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41721558570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42091369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926381111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41228461265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37284064292908</t>
   </si>
   <si>
     <t xml:space="preserve">2.35928130149841</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33832573890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31983685493469</t>
+    <t xml:space="preserve">2.33832621574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31983709335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36421179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35435080528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43693780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858721733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43077421188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41598320007324</t>
+    <t xml:space="preserve">2.35435056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43693804740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43077445030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41598272323608</t>
   </si>
   <si>
     <t xml:space="preserve">2.37037467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36297917366028</t>
+    <t xml:space="preserve">2.36297941207886</t>
   </si>
   <si>
     <t xml:space="preserve">2.35311818122864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36667680740356</t>
+    <t xml:space="preserve">2.36667704582214</t>
   </si>
   <si>
     <t xml:space="preserve">2.38393425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.327232837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24711084365845</t>
+    <t xml:space="preserve">2.32723236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24711108207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.24341249465942</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">2.22369050979614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24957585334778</t>
+    <t xml:space="preserve">2.2495756149292</t>
   </si>
   <si>
     <t xml:space="preserve">2.25080823898315</t>
@@ -587,58 +587,58 @@
     <t xml:space="preserve">2.28285717964172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22862076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2483434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860399246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30750966072083</t>
+    <t xml:space="preserve">2.22862100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24834322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860375404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30751013755798</t>
   </si>
   <si>
     <t xml:space="preserve">2.29764914512634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30257987976074</t>
+    <t xml:space="preserve">2.30257964134216</t>
   </si>
   <si>
     <t xml:space="preserve">2.33586072921753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35065245628357</t>
+    <t xml:space="preserve">2.35065269470215</t>
   </si>
   <si>
     <t xml:space="preserve">2.33339595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51952505111694</t>
+    <t xml:space="preserve">2.51952528953552</t>
   </si>
   <si>
     <t xml:space="preserve">2.51336193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47884798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49980282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53924703598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56513285636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5491087436676</t>
+    <t xml:space="preserve">2.47884750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49980306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53924679756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5651330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910850524902</t>
   </si>
   <si>
     <t xml:space="preserve">2.56266713142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58115744590759</t>
+    <t xml:space="preserve">2.58115696907043</t>
   </si>
   <si>
     <t xml:space="preserve">2.60211229324341</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">2.57252883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57622671127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896949768066</t>
+    <t xml:space="preserve">2.57622647285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5589702129364</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048013687134</t>
@@ -662,28 +662,28 @@
     <t xml:space="preserve">2.54664301872253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56636571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55403900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55157351493835</t>
+    <t xml:space="preserve">2.56636548042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55403876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5565037727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55157375335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.57299447059631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56795406341553</t>
+    <t xml:space="preserve">2.56795454025269</t>
   </si>
   <si>
     <t xml:space="preserve">2.52763295173645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50873303413391</t>
+    <t xml:space="preserve">2.50873255729675</t>
   </si>
   <si>
     <t xml:space="preserve">2.47849154472351</t>
@@ -692,73 +692,73 @@
     <t xml:space="preserve">2.4255702495575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43439030647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43565034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715140342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41926980018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069027900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54401397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55031418800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023361206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53267312049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49361228942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53141331672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5452733039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52133297920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52637338638306</t>
+    <t xml:space="preserve">2.43439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43565011024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825029373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41927003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54401350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5503134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023337364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53267335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49361157417297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53141355514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54527354240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52133274078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52637267112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.50369215011597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787396430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283355712891</t>
+    <t xml:space="preserve">2.52007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787348747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283379554749</t>
   </si>
   <si>
     <t xml:space="preserve">2.57803440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59945511817932</t>
+    <t xml:space="preserve">2.59945487976074</t>
   </si>
   <si>
     <t xml:space="preserve">2.6032350063324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60827493667603</t>
+    <t xml:space="preserve">2.60827565193176</t>
   </si>
   <si>
     <t xml:space="preserve">2.62717580795288</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">2.63851594924927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63347625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473606109619</t>
+    <t xml:space="preserve">2.63347601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473582267761</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67757725715637</t>
+    <t xml:space="preserve">2.67757749557495</t>
   </si>
   <si>
     <t xml:space="preserve">2.6523768901825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63977599143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6586766242981</t>
+    <t xml:space="preserve">2.63977670669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65867686271667</t>
   </si>
   <si>
     <t xml:space="preserve">2.71033835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70151805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73427939414978</t>
+    <t xml:space="preserve">2.70151829719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71537852287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7342791557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.74183940887451</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">2.75191926956177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78090047836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77460026741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76199960708618</t>
+    <t xml:space="preserve">2.7809009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964043617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7746000289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7619993686676</t>
   </si>
   <si>
     <t xml:space="preserve">2.77207970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74309897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7594792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75821995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72671890258789</t>
+    <t xml:space="preserve">2.74309921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75947999954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75821948051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72671866416931</t>
   </si>
   <si>
     <t xml:space="preserve">2.67253756523132</t>
@@ -839,109 +839,109 @@
     <t xml:space="preserve">2.70907807350159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8048415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79098033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77712082862854</t>
+    <t xml:space="preserve">2.80484127998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79098057746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77712035179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.77082014083862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74939894676208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78719997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7935004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650229454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792325019836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658310890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87918305397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87414288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87666273117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88044333457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9497447013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9157247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92202425003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100569725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9799861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526665687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628640174866</t>
+    <t xml:space="preserve">2.74939918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7872006893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350113868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650300979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88422298431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8665828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87918376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87414240837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87666296958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88044309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94974517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9220244884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998547554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526713371277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628616333008</t>
   </si>
   <si>
     <t xml:space="preserve">3.0051863193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02912759780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9610857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872567176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762654304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274657249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990656852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148724555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156710624695</t>
+    <t xml:space="preserve">3.02912735939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96108531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762678146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274704933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990609169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156734466553</t>
   </si>
   <si>
     <t xml:space="preserve">3.11354994773865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08582878112793</t>
+    <t xml:space="preserve">3.08582901954651</t>
   </si>
   <si>
     <t xml:space="preserve">3.05180835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05558848381042</t>
+    <t xml:space="preserve">3.05558824539185</t>
   </si>
   <si>
     <t xml:space="preserve">3.05810809135437</t>
@@ -950,115 +950,115 @@
     <t xml:space="preserve">3.06440806388855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09968996047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10724997520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204960823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10346961021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1185896396637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02408790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04928827285767</t>
+    <t xml:space="preserve">3.09968972206116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10724925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10346984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11859011650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02408766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04928874969482</t>
   </si>
   <si>
     <t xml:space="preserve">2.98754644393921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95730543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99888706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478558540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97368574142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282738685608</t>
+    <t xml:space="preserve">2.95730519294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99888682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97368597984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228271484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.01778697967529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06944942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13245105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13119029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10094976425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12488961219788</t>
+    <t xml:space="preserve">3.06944894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13245058059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13119053840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094928741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12488985061646</t>
   </si>
   <si>
     <t xml:space="preserve">3.12867069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09338998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.119060754776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07927012443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831329345703</t>
+    <t xml:space="preserve">3.09338974952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777663230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.08953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09595656394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703036308289</t>
+    <t xml:space="preserve">3.09595632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13703083992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.13189625740051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17040324211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864153862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735765457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532726287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19222354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16013431549072</t>
+    <t xml:space="preserve">3.17040300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735789299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532797813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16013479232788</t>
   </si>
   <si>
     <t xml:space="preserve">3.22816324234009</t>
@@ -1067,73 +1067,73 @@
     <t xml:space="preserve">3.25062608718872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25383496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23458099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607424736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2602527141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987910270691</t>
+    <t xml:space="preserve">3.25383424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607377052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">3.26346135139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29875898361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30196833610535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33084869384766</t>
+    <t xml:space="preserve">3.29875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950596809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271508216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3019688129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3308482170105</t>
   </si>
   <si>
     <t xml:space="preserve">3.32122230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36614727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405709266663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517721176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28592371940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28913354873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27308797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2409987449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18708992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23779034614563</t>
+    <t xml:space="preserve">3.36614656448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405804634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629733085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517745018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28592395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28913283348083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27308821678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18708968162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23779010772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.25704336166382</t>
@@ -1145,70 +1145,70 @@
     <t xml:space="preserve">3.31801319122314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32763934135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30838656425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32443118095398</t>
+    <t xml:space="preserve">3.32763910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32443070411682</t>
   </si>
   <si>
     <t xml:space="preserve">3.35010194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39502668380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3918182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428065299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748857498169</t>
+    <t xml:space="preserve">3.39502644538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4142804145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748833656311</t>
   </si>
   <si>
     <t xml:space="preserve">3.45599627494812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44316029548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957876205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920443534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46241426467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42390704154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38540077209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256407737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37898206710815</t>
+    <t xml:space="preserve">3.44316077232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46241402626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4239068031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38540005683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898254394531</t>
   </si>
   <si>
     <t xml:space="preserve">3.39823603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34689331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331082344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786218643188</t>
+    <t xml:space="preserve">3.34689378738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331130027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786242485046</t>
   </si>
   <si>
     <t xml:space="preserve">3.43674230575562</t>
@@ -1217,82 +1217,82 @@
     <t xml:space="preserve">3.46883225440979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51375651359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092172622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44636869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054787635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5458459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56189012527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114385604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5362184047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166751861572</t>
+    <t xml:space="preserve">3.51375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.446368932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5618908405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114361763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53621888160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4816677570343</t>
   </si>
   <si>
     <t xml:space="preserve">3.5041298866272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107130050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234218597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711687088013</t>
+    <t xml:space="preserve">3.41107082366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2923424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711567878723</t>
   </si>
   <si>
     <t xml:space="preserve">3.40144491195679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44611430168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047932624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382485389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3171718120575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34466218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31586337089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302672386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310091018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146639823914</t>
+    <t xml:space="preserve">3.44611477851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738919258118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31717133522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34466171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31586265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146592140198</t>
   </si>
   <si>
     <t xml:space="preserve">3.19019198417664</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">3.09070348739624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03310394287109</t>
+    <t xml:space="preserve">3.03310418128967</t>
   </si>
   <si>
     <t xml:space="preserve">3.06844902038574</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">3.04619479179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12866568565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652014732361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18102884292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735724449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212109565735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630372047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466498374939</t>
+    <t xml:space="preserve">3.12866616249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652086257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1810290813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735676765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212014198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466522216797</t>
   </si>
   <si>
     <t xml:space="preserve">3.15877461433411</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">3.11688446998596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04815912246704</t>
+    <t xml:space="preserve">3.04815888404846</t>
   </si>
   <si>
     <t xml:space="preserve">3.07695841789246</t>
@@ -1355,436 +1355,436 @@
     <t xml:space="preserve">3.12670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16793847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16532039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16335654258728</t>
+    <t xml:space="preserve">3.16793870925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16532015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1633563041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.18757390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17448377609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684597969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1915009021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1391384601593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.175137758255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259291648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979315757751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630021095276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320960044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30538988113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3027720451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764387130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240796089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324434280396</t>
+    <t xml:space="preserve">3.17448329925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684621810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13913869857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17513751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979363441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2562997341156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844622612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30277180671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764410972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">3.34597158432007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34727954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095210075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39833307266235</t>
+    <t xml:space="preserve">3.3472797870636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095186233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39833331108093</t>
   </si>
   <si>
     <t xml:space="preserve">3.38393402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40487933158875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39309740066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44284176826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43629622459412</t>
+    <t xml:space="preserve">3.40487885475159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39309692382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44284129142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4362964630127</t>
   </si>
   <si>
     <t xml:space="preserve">3.44807839393616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49520468711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48211431503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52531337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31848096847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3433530330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36298894882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23797297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153540611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2059006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655608177185</t>
+    <t xml:space="preserve">3.49520421028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4821138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52531290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5266215801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109904289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31848001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34335231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36298823356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23797273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153635978699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590090751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655560493469</t>
   </si>
   <si>
     <t xml:space="preserve">3.19542860984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1921558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037438392639</t>
+    <t xml:space="preserve">3.19215512275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037462234497</t>
   </si>
   <si>
     <t xml:space="preserve">3.10772109031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08415770530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888657569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0782675743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855771064758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324856758118</t>
+    <t xml:space="preserve">3.08415746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888681411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826685905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.098557472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13324785232544</t>
   </si>
   <si>
     <t xml:space="preserve">3.07564854621887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06386780738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692272186279</t>
+    <t xml:space="preserve">3.06386756896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692248344421</t>
   </si>
   <si>
     <t xml:space="preserve">3.11557555198669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12932109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18953800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888354301453</t>
+    <t xml:space="preserve">3.12932062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.189537525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888330459595</t>
   </si>
   <si>
     <t xml:space="preserve">3.16401100158691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16204714775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746569633484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481216430664</t>
+    <t xml:space="preserve">3.1620466709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746545791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0848126411438</t>
   </si>
   <si>
     <t xml:space="preserve">3.10641169548035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06452226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808493614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12342977523804</t>
+    <t xml:space="preserve">3.06452202796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808469772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12342929840088</t>
   </si>
   <si>
     <t xml:space="preserve">3.1031391620636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510301589966</t>
+    <t xml:space="preserve">3.11361122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">3.15550231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710185050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739270210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186522483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364667892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251944541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1941192150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113681793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17952418327332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13647532463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656472206116</t>
+    <t xml:space="preserve">3.14437484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1973922252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644715309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186498641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1489565372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364644050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17252016067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113729476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952370643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530896186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647556304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656519889832</t>
   </si>
   <si>
     <t xml:space="preserve">3.1721248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16338086128235</t>
+    <t xml:space="preserve">3.16338038444519</t>
   </si>
   <si>
     <t xml:space="preserve">3.20844674110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08401036262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347350120544</t>
+    <t xml:space="preserve">3.08401012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347373962402</t>
   </si>
   <si>
     <t xml:space="preserve">3.04432487487793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04499650001526</t>
+    <t xml:space="preserve">3.04499745368958</t>
   </si>
   <si>
     <t xml:space="preserve">3.08468270301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08333730697632</t>
+    <t xml:space="preserve">3.0833375453949</t>
   </si>
   <si>
     <t xml:space="preserve">3.06921243667603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00598526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99051380157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01203870773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98042511940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638940811157</t>
+    <t xml:space="preserve">3.00598549842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99051451683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.012038230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98042559623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638916969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.96629953384399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99791288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9851336479187</t>
+    <t xml:space="preserve">2.99791312217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98513340950012</t>
   </si>
   <si>
     <t xml:space="preserve">2.95082902908325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96293663978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150208473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94006729125977</t>
+    <t xml:space="preserve">2.96293759346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92997765541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94006705284119</t>
   </si>
   <si>
     <t xml:space="preserve">2.89836406707764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86540555953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8862566947937</t>
+    <t xml:space="preserve">2.86540532112122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8539707660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88625693321228</t>
   </si>
   <si>
     <t xml:space="preserve">2.88558387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94477605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091914176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584930419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894376754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06652212142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05979561805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03625297546387</t>
+    <t xml:space="preserve">2.94477581977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091890335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719470024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894352912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06652164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05979537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03625321388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.05912280082703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11629605293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07392048835754</t>
+    <t xml:space="preserve">3.11629629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0739209651947</t>
   </si>
   <si>
     <t xml:space="preserve">3.0934271812439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10149836540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94746589660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562719345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04096150398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9999315738678</t>
+    <t xml:space="preserve">3.10149884223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064675331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96764540672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9474663734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562671661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04096221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99993133544922</t>
   </si>
   <si>
     <t xml:space="preserve">2.97504353523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94410300254822</t>
+    <t xml:space="preserve">2.94410252571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.94343042373657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92325162887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88423895835876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99589538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96899032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93468618392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975254058838</t>
+    <t xml:space="preserve">2.92325139045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88423919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99589514732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96899056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93468594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9797523021698</t>
   </si>
   <si>
     <t xml:space="preserve">2.9844605922699</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">2.9669725894928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94612121582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9595730304718</t>
+    <t xml:space="preserve">2.94612073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95957374572754</t>
   </si>
   <si>
     <t xml:space="preserve">2.91518020629883</t>
@@ -1805,49 +1805,49 @@
     <t xml:space="preserve">2.94544839859009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96428155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168135643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00665807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01540160179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99454998970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06853938102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13378477096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13244032859802</t>
+    <t xml:space="preserve">2.96428203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00665736198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01540184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02280044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9945502281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683687210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0685396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.133784532547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13244009017944</t>
   </si>
   <si>
     <t xml:space="preserve">3.1647253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19835734367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20441079139709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21517300605774</t>
+    <t xml:space="preserve">3.19835758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20441126823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21517276763916</t>
   </si>
   <si>
     <t xml:space="preserve">3.20037508010864</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">3.22189950942993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23804235458374</t>
+    <t xml:space="preserve">3.23804259300232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22727990150452</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">3.24880480766296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19297671318054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19364881515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961358070374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333382606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3167405128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3766040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37525916099548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3725688457489</t>
+    <t xml:space="preserve">3.1929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19364929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.189612865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333430290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31674003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37660336494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3752589225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256836891174</t>
   </si>
   <si>
     <t xml:space="preserve">3.37122368812561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44655776023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270060539246</t>
+    <t xml:space="preserve">3.44655752182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270084381104</t>
   </si>
   <si>
     <t xml:space="preserve">3.48826122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39543700218201</t>
+    <t xml:space="preserve">3.39543795585632</t>
   </si>
   <si>
     <t xml:space="preserve">3.39274764060974</t>
@@ -1910,151 +1910,151 @@
     <t xml:space="preserve">3.41965246200562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42099785804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808171272278</t>
+    <t xml:space="preserve">3.42099833488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808218955994</t>
   </si>
   <si>
     <t xml:space="preserve">3.46673679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48153400421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47346353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53130888938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767804145813</t>
+    <t xml:space="preserve">3.48153424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47346305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53130912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767756462097</t>
   </si>
   <si>
     <t xml:space="preserve">3.50440382957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51113057136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978446006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458262443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5703227519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275675773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446694374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683256149292</t>
+    <t xml:space="preserve">3.51113080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458214759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032179832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275723457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446646690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683303833008</t>
   </si>
   <si>
     <t xml:space="preserve">3.57861185073853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58690237998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5675585269928</t>
+    <t xml:space="preserve">3.58690214157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755828857422</t>
   </si>
   <si>
     <t xml:space="preserve">3.62144494056702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61591792106628</t>
+    <t xml:space="preserve">3.61591839790344</t>
   </si>
   <si>
     <t xml:space="preserve">3.6380250453949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57170343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545116424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5910472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348320007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071921348572</t>
+    <t xml:space="preserve">3.5717031955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545164108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472615242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097770690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59104704856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60348296165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071897506714</t>
   </si>
   <si>
     <t xml:space="preserve">3.61729955673218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62282657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61039161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61453604698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6242082118988</t>
+    <t xml:space="preserve">3.62282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61039113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61453652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420797348022</t>
   </si>
   <si>
     <t xml:space="preserve">3.64631485939026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66980409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66151428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533183097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118692398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66427779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72921776771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80106687545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863120079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205038070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79830360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79001235961914</t>
+    <t xml:space="preserve">3.6698043346405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66151404380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533135414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118644714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66427707672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085741996765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921800613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80106639862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863072395325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205061912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79830241203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79001212120056</t>
   </si>
   <si>
     <t xml:space="preserve">3.79139447212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77895903587341</t>
+    <t xml:space="preserve">3.77895855903625</t>
   </si>
   <si>
     <t xml:space="preserve">3.81350159645081</t>
@@ -2063,64 +2063,64 @@
     <t xml:space="preserve">3.83008241653442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8549530506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225888252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258719444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923664093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752669334412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92818307876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94061875343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90883874893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9344003200531</t>
+    <t xml:space="preserve">3.85495352745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225816726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923711776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752645492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92818331718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94061851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90883946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091060638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93440008163452</t>
   </si>
   <si>
     <t xml:space="preserve">3.93370938301086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92127418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91022086143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564255714417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379511833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419229507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695604324341</t>
+    <t xml:space="preserve">3.92127466201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847636222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87567901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564351081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419205665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695532798767</t>
   </si>
   <si>
     <t xml:space="preserve">3.81281113624573</t>
@@ -2129,190 +2129,190 @@
     <t xml:space="preserve">3.8024480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82593703269958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840749740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83630013465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571356773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85218977928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83491706848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452084541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85149812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080718994141</t>
+    <t xml:space="preserve">3.82593679428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840725898743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015128135681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85218930244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8514986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080766677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.86186170578003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8888041973114</t>
+    <t xml:space="preserve">3.88880467414856</t>
   </si>
   <si>
     <t xml:space="preserve">3.93094658851624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98690557479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068761825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403817176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99934077262878</t>
+    <t xml:space="preserve">3.98690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068690299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99934053421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.83906292915344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84804439544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407248497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06980800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02628421783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13889265060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19347095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20037984848022</t>
+    <t xml:space="preserve">3.84804463386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844228744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407200813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581698417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108598709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06980752944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02628374099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010152816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13889312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19347047805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20037841796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.30884265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26255559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2763729095459</t>
+    <t xml:space="preserve">4.26255464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27637147903442</t>
   </si>
   <si>
     <t xml:space="preserve">4.3053879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3005518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397226333618</t>
+    <t xml:space="preserve">4.30055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397274017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.19692420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20314168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24182987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23215770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32473230361938</t>
+    <t xml:space="preserve">4.2031421661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24182939529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23215818405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3247332572937</t>
   </si>
   <si>
     <t xml:space="preserve">4.42697763442993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45392084121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42145204544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4283595085144</t>
+    <t xml:space="preserve">4.45392036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42145109176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42836046218872</t>
   </si>
   <si>
     <t xml:space="preserve">4.42766952514648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43941354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49744510650635</t>
+    <t xml:space="preserve">4.43941307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49744462966919</t>
   </si>
   <si>
     <t xml:space="preserve">4.45668506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48500967025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5312967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34407567977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43239879608154</t>
+    <t xml:space="preserve">4.48500919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49951791763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53129720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34407663345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4323992729187</t>
   </si>
   <si>
     <t xml:space="preserve">4.43310594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47267389297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41402816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38788366317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41332101821899</t>
+    <t xml:space="preserve">4.47267436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41402769088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38788318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41332149505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.35891485214233</t>
@@ -2321,22 +2321,22 @@
     <t xml:space="preserve">4.38011169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940502166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33418369293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493835449219</t>
+    <t xml:space="preserve">4.40908193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33418321609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842325210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2649393081665</t>
   </si>
   <si>
     <t xml:space="preserve">4.28472328186035</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">4.24586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44087791442871</t>
+    <t xml:space="preserve">4.44087696075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.49316501617432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40625476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419525146484</t>
+    <t xml:space="preserve">4.40625524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.464195728302</t>
   </si>
   <si>
     <t xml:space="preserve">4.4401707649231</t>
@@ -2372,82 +2372,82 @@
     <t xml:space="preserve">4.5935001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68606185913086</t>
+    <t xml:space="preserve">4.68606233596802</t>
   </si>
   <si>
     <t xml:space="preserve">4.65921258926392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71997880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72068548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76096057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70937919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758274078369</t>
+    <t xml:space="preserve">4.71997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7206859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76095962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70937967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758369445801</t>
   </si>
   <si>
     <t xml:space="preserve">4.62458944320679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58572816848755</t>
+    <t xml:space="preserve">4.58572721481323</t>
   </si>
   <si>
     <t xml:space="preserve">4.55181169509888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67263746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65779876708984</t>
+    <t xml:space="preserve">4.67263698577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65779972076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.58007478713989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480499267578</t>
+    <t xml:space="preserve">4.6048059463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67404985427856</t>
+    <t xml:space="preserve">4.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">4.64649391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71361923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215837478638</t>
+    <t xml:space="preserve">4.71361875534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215742111206</t>
   </si>
   <si>
     <t xml:space="preserve">4.75530767440796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82737970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79487609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84080362319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81677961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69100856781006</t>
+    <t xml:space="preserve">4.82737922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79487562179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84080457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81678104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6910080909729</t>
   </si>
   <si>
     <t xml:space="preserve">4.77226591110229</t>
@@ -2456,25 +2456,25 @@
     <t xml:space="preserve">4.83656454086304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78498411178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81536817550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78145170211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78993082046509</t>
+    <t xml:space="preserve">4.78498363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81536722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78993034362793</t>
   </si>
   <si>
     <t xml:space="preserve">4.83161878585815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80830144882202</t>
+    <t xml:space="preserve">4.80830097198486</t>
   </si>
   <si>
     <t xml:space="preserve">4.78357124328613</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">4.76590633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84221696853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86129522323608</t>
+    <t xml:space="preserve">4.84221744537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86129570007324</t>
   </si>
   <si>
     <t xml:space="preserve">4.84998941421509</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">4.85564279556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8775463104248</t>
+    <t xml:space="preserve">4.87754583358765</t>
   </si>
   <si>
     <t xml:space="preserve">4.90368986129761</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">4.92347431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88249254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87472057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085256576538</t>
+    <t xml:space="preserve">4.882493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87472009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085161209106</t>
   </si>
   <si>
     <t xml:space="preserve">4.85140323638916</t>
@@ -2537,28 +2537,28 @@
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8259654045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759477615356</t>
+    <t xml:space="preserve">4.87401294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82596635818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759429931641</t>
   </si>
   <si>
     <t xml:space="preserve">4.78710412979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76943969726562</t>
+    <t xml:space="preserve">4.76943874359131</t>
   </si>
   <si>
     <t xml:space="preserve">4.83303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85493516921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84433698654175</t>
+    <t xml:space="preserve">4.85493612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84433650970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.66698455810547</t>
@@ -2570,46 +2570,46 @@
     <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75601482391357</t>
+    <t xml:space="preserve">4.75601434707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.83727121353149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89309167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9531512260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9333667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9467921257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09164142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973743438721</t>
+    <t xml:space="preserve">4.89309215545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95315074920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93336582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94679164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09164190292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973791122437</t>
   </si>
   <si>
     <t xml:space="preserve">5.04359340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9969596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09588098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09517431259155</t>
+    <t xml:space="preserve">4.99695873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09588050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09517478942871</t>
   </si>
   <si>
     <t xml:space="preserve">5.10577297210693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10860013961792</t>
+    <t xml:space="preserve">5.1085991859436</t>
   </si>
   <si>
     <t xml:space="preserve">5.13686275482178</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">5.24073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22871828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2435564994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37780714035034</t>
+    <t xml:space="preserve">5.22871875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3778076171875</t>
   </si>
   <si>
     <t xml:space="preserve">5.45835828781128</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">5.50453615188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4908275604248</t>
+    <t xml:space="preserve">5.49082660675049</t>
   </si>
   <si>
     <t xml:space="preserve">5.44464921951294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49804162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64162635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871704101562</t>
+    <t xml:space="preserve">5.49804306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64162540435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53700494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934797286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871608734131</t>
   </si>
   <si>
     <t xml:space="preserve">5.83571767807007</t>
@@ -2663,31 +2663,31 @@
     <t xml:space="preserve">5.66760110855103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74769067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77222347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82273006439209</t>
+    <t xml:space="preserve">5.74769163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7722225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82272958755493</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602163314819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89993333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91652774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91147708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86746454238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92157888412476</t>
+    <t xml:space="preserve">5.89993381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91652822494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91147756576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86746406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92157936096191</t>
   </si>
   <si>
     <t xml:space="preserve">5.97208595275879</t>
@@ -2702,85 +2702,85 @@
     <t xml:space="preserve">6.18060779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08464479446411</t>
+    <t xml:space="preserve">6.08464431762695</t>
   </si>
   <si>
     <t xml:space="preserve">6.09258079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79386806488037</t>
+    <t xml:space="preserve">5.79386758804321</t>
   </si>
   <si>
     <t xml:space="preserve">5.63152456283569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73975372314453</t>
+    <t xml:space="preserve">5.73975324630737</t>
   </si>
   <si>
     <t xml:space="preserve">5.71161460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46629571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51247262954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62286615371704</t>
+    <t xml:space="preserve">5.46629476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51247215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6228666305542</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538879394531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87684440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69357585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12717628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712339401245</t>
+    <t xml:space="preserve">5.87684488296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69357633590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1271767616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712291717529</t>
   </si>
   <si>
     <t xml:space="preserve">4.70436191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77070498466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830202102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1271390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2497992515564</t>
+    <t xml:space="preserve">3.77070426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426502227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830130577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12713956832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24979877471924</t>
   </si>
   <si>
     <t xml:space="preserve">4.20650720596313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24907732009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30896472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5535626411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54562520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53047370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44100427627563</t>
+    <t xml:space="preserve">4.24907779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30896425247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55356121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54562568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53047323226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44100379943848</t>
   </si>
   <si>
     <t xml:space="preserve">4.60767698287964</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">4.57376480102539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37823057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378829956055</t>
+    <t xml:space="preserve">4.37823104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378877639771</t>
   </si>
   <si>
     <t xml:space="preserve">4.37895250320435</t>
@@ -2801,28 +2801,28 @@
     <t xml:space="preserve">4.4301815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59974050521851</t>
+    <t xml:space="preserve">4.59973955154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.53480243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65601873397827</t>
+    <t xml:space="preserve">4.65601921081543</t>
   </si>
   <si>
     <t xml:space="preserve">4.65168905258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50882816314697</t>
+    <t xml:space="preserve">4.47852277755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50882720947266</t>
   </si>
   <si>
     <t xml:space="preserve">4.47996616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46770000457764</t>
+    <t xml:space="preserve">4.46770095825195</t>
   </si>
   <si>
     <t xml:space="preserve">4.3327751159668</t>
@@ -2831,121 +2831,121 @@
     <t xml:space="preserve">4.31834411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2757740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25701427459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37967443466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43739604949951</t>
+    <t xml:space="preserve">4.27577352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25701475143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37967395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43739652633667</t>
   </si>
   <si>
     <t xml:space="preserve">4.52397966384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4994478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39266061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37750911712646</t>
+    <t xml:space="preserve">4.49944734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33421754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39266109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37750959396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.46481418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47347259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688993453979</t>
+    <t xml:space="preserve">4.473473072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688898086548</t>
   </si>
   <si>
     <t xml:space="preserve">4.3508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672206878662</t>
+    <t xml:space="preserve">4.24546957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672254562378</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35586404800415</t>
+    <t xml:space="preserve">4.35586452484131</t>
   </si>
   <si>
     <t xml:space="preserve">4.51099157333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56727027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62499284744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69714689254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90061712265015</t>
+    <t xml:space="preserve">4.56727170944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62499380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69714641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061664581299</t>
   </si>
   <si>
     <t xml:space="preserve">4.97926330566406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04925203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18706321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40063571929932</t>
+    <t xml:space="preserve">5.0492525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40063619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.46773815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46701669692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176197052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28663444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29962205886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41506671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197826385498</t>
+    <t xml:space="preserve">5.46701622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176244735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011785507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28663492202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29962158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41506719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197731018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48361158370972</t>
@@ -2957,37 +2957,37 @@
     <t xml:space="preserve">5.50092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5290675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51175117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57308101654053</t>
+    <t xml:space="preserve">5.52906799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51175165176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57308149337769</t>
   </si>
   <si>
     <t xml:space="preserve">5.5398907661438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55720806121826</t>
+    <t xml:space="preserve">5.55720710754395</t>
   </si>
   <si>
     <t xml:space="preserve">5.73398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68130970001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71017122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75418424606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83427381515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604560852051</t>
+    <t xml:space="preserve">5.68131065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71017074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75418472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83427429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604513168335</t>
   </si>
   <si>
     <t xml:space="preserve">5.86024856567383</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">5.89416074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9547700881958</t>
+    <t xml:space="preserve">5.95476961135864</t>
   </si>
   <si>
     <t xml:space="preserve">6.08031558990479</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">6.12669610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1325855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246164321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98828935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84841012954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83147811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123250961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69601583480835</t>
+    <t xml:space="preserve">6.13258504867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246212005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98828887939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84841108322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83147764205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8712329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69601631164551</t>
   </si>
   <si>
     <t xml:space="preserve">5.69012641906738</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">5.7666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69086313247681</t>
+    <t xml:space="preserve">5.69086265563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.75344038009644</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">5.97062015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89552783966064</t>
+    <t xml:space="preserve">5.8955283164978</t>
   </si>
   <si>
     <t xml:space="preserve">5.8049750328064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74828672409058</t>
+    <t xml:space="preserve">5.74828720092773</t>
   </si>
   <si>
     <t xml:space="preserve">5.73356294631958</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">5.70926809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69159984588623</t>
+    <t xml:space="preserve">5.69159841537476</t>
   </si>
   <si>
     <t xml:space="preserve">5.79098701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74534177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460470199585</t>
+    <t xml:space="preserve">5.74534225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460374832153</t>
   </si>
   <si>
     <t xml:space="preserve">5.58705759048462</t>
@@ -3101,70 +3101,70 @@
     <t xml:space="preserve">5.63049459457397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58043241500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45674991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59000301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165843963623</t>
+    <t xml:space="preserve">5.58043146133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4567494392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000253677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165796279907</t>
   </si>
   <si>
     <t xml:space="preserve">5.63270282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59810161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63932800292969</t>
+    <t xml:space="preserve">5.59810066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.639328956604</t>
   </si>
   <si>
     <t xml:space="preserve">5.56644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61650657653809</t>
+    <t xml:space="preserve">5.61650609970093</t>
   </si>
   <si>
     <t xml:space="preserve">5.57675075531006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43319082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263933181763</t>
+    <t xml:space="preserve">5.43319177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263885498047</t>
   </si>
   <si>
     <t xml:space="preserve">5.34411001205444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38975524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208831787109</t>
+    <t xml:space="preserve">5.38975477218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208736419678</t>
   </si>
   <si>
     <t xml:space="preserve">5.42582893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40006256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48325252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52153539657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4611668586731</t>
+    <t xml:space="preserve">5.400062084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48325300216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52153587341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46116781234741</t>
   </si>
   <si>
     <t xml:space="preserve">5.49797677993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44349813461304</t>
+    <t xml:space="preserve">5.4434986114502</t>
   </si>
   <si>
     <t xml:space="preserve">5.42141151428223</t>
@@ -3173,25 +3173,25 @@
     <t xml:space="preserve">5.59221172332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5561375617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53920412063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65920639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67761135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54141330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49871301651001</t>
+    <t xml:space="preserve">5.55613708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53920459747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6592059135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67761039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429655075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54141283035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49871349334717</t>
   </si>
   <si>
     <t xml:space="preserve">5.58190393447876</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">5.57233333587646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4442343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662340164185</t>
+    <t xml:space="preserve">5.44423484802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662292480469</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705232620239</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">5.0312237739563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312601089478</t>
+    <t xml:space="preserve">5.14312696456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60325479507446</t>
+    <t xml:space="preserve">5.42435693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6032543182373</t>
   </si>
   <si>
     <t xml:space="preserve">5.92718410491943</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">5.92423963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04571390151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853401184082</t>
+    <t xml:space="preserve">6.0457124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">5.90436267852783</t>
@@ -3248,37 +3248,37 @@
     <t xml:space="preserve">5.95515918731689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97209310531616</t>
+    <t xml:space="preserve">5.97209358215332</t>
   </si>
   <si>
     <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0103759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06117343902588</t>
+    <t xml:space="preserve">6.01037454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06117296218872</t>
   </si>
   <si>
     <t xml:space="preserve">6.19737148284912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24816989898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23565435409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25921201705933</t>
+    <t xml:space="preserve">6.24817085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25921249389648</t>
   </si>
   <si>
     <t xml:space="preserve">6.16203355789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09724807739258</t>
+    <t xml:space="preserve">6.12522315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09724760055542</t>
   </si>
   <si>
     <t xml:space="preserve">6.04350471496582</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">6.04129648208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02289152145386</t>
+    <t xml:space="preserve">6.02289056777954</t>
   </si>
   <si>
     <t xml:space="preserve">6.00743103027344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97798299789429</t>
+    <t xml:space="preserve">5.97798204421997</t>
   </si>
   <si>
     <t xml:space="preserve">6.04424095153809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92571210861206</t>
+    <t xml:space="preserve">5.9257116317749</t>
   </si>
   <si>
     <t xml:space="preserve">5.922767162323</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">6.01700162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9419093132019</t>
+    <t xml:space="preserve">5.94190788269043</t>
   </si>
   <si>
     <t xml:space="preserve">6.08914995193481</t>
@@ -3320,28 +3320,28 @@
     <t xml:space="preserve">6.14362859725952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09283018112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22608375549316</t>
+    <t xml:space="preserve">6.09283065795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22608327865601</t>
   </si>
   <si>
     <t xml:space="preserve">6.18043947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57357168197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46167087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58755970001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081159591675</t>
+    <t xml:space="preserve">6.57357215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46166944503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081111907959</t>
   </si>
   <si>
     <t xml:space="preserve">6.57062816619873</t>
@@ -3359,34 +3359,34 @@
     <t xml:space="preserve">6.43942403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44242811203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3530535697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26743507385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25992488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30874252319336</t>
+    <t xml:space="preserve">6.44242763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30874156951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.18932676315308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30949306488037</t>
+    <t xml:space="preserve">6.30949354171753</t>
   </si>
   <si>
     <t xml:space="preserve">6.15177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17430591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15853357315063</t>
+    <t xml:space="preserve">6.17430543899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15853404998779</t>
   </si>
   <si>
     <t xml:space="preserve">6.42290067672729</t>
@@ -3395,64 +3395,64 @@
     <t xml:space="preserve">6.42590475082397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34404134750366</t>
+    <t xml:space="preserve">6.3440408706665</t>
   </si>
   <si>
     <t xml:space="preserve">6.38384675979614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22162199020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24715662002563</t>
+    <t xml:space="preserve">6.2216215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24715709686279</t>
   </si>
   <si>
     <t xml:space="preserve">6.35530662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35981225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23589134216309</t>
+    <t xml:space="preserve">6.35981369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23589181900024</t>
   </si>
   <si>
     <t xml:space="preserve">6.15552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06615591049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105262756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9482421875</t>
+    <t xml:space="preserve">6.0661563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105215072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94824314117432</t>
   </si>
   <si>
     <t xml:space="preserve">5.88815975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9685206413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85962009429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72743701934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89041328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91294384002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141351699829</t>
+    <t xml:space="preserve">5.89116382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96852111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85961961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72743654251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8904128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91294431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141399383545</t>
   </si>
   <si>
     <t xml:space="preserve">6.08568334579468</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">6.16979932785034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25316619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19984197616577</t>
+    <t xml:space="preserve">6.25316572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19984149932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.14426469802856</t>
@@ -3473,100 +3473,100 @@
     <t xml:space="preserve">6.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12999486923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05639266967773</t>
+    <t xml:space="preserve">6.12999391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05639314651489</t>
   </si>
   <si>
     <t xml:space="preserve">6.2381443977356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25166368484497</t>
+    <t xml:space="preserve">6.25166320800781</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826948165894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34028625488281</t>
+    <t xml:space="preserve">6.34028673171997</t>
   </si>
   <si>
     <t xml:space="preserve">6.32902050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38910388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33352661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37858867645264</t>
+    <t xml:space="preserve">6.38910341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33352613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">6.33502912521362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42440223693848</t>
+    <t xml:space="preserve">6.42440271377563</t>
   </si>
   <si>
     <t xml:space="preserve">6.44843578338623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49725294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444488525391</t>
+    <t xml:space="preserve">6.49725389480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444440841675</t>
   </si>
   <si>
     <t xml:space="preserve">6.44392967224121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47472333908081</t>
+    <t xml:space="preserve">6.47472286224365</t>
   </si>
   <si>
     <t xml:space="preserve">6.39060544967651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44468212127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50551509857178</t>
+    <t xml:space="preserve">6.44468116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326204299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50551462173462</t>
   </si>
   <si>
     <t xml:space="preserve">6.42515420913696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37408399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54757404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479188919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217746734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885419845581</t>
+    <t xml:space="preserve">6.37408351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54757452011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4889931678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885467529297</t>
   </si>
   <si>
     <t xml:space="preserve">6.27569675445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16304111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22537612915039</t>
+    <t xml:space="preserve">6.16304063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22537660598755</t>
   </si>
   <si>
     <t xml:space="preserve">6.20960474014282</t>
@@ -3575,16 +3575,16 @@
     <t xml:space="preserve">6.214111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00231742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07742118835449</t>
+    <t xml:space="preserve">6.00231838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07742214202881</t>
   </si>
   <si>
     <t xml:space="preserve">6.16153907775879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12623929977417</t>
+    <t xml:space="preserve">6.12623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">6.10445928573608</t>
@@ -3593,31 +3593,31 @@
     <t xml:space="preserve">5.98279094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06390380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14952182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11872863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572504043579</t>
+    <t xml:space="preserve">6.06390428543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13374948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11872911453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572408676147</t>
   </si>
   <si>
     <t xml:space="preserve">6.05038404464722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99405574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92721462249756</t>
+    <t xml:space="preserve">5.994056224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9272141456604</t>
   </si>
   <si>
     <t xml:space="preserve">5.95650434494019</t>
@@ -3626,67 +3626,67 @@
     <t xml:space="preserve">6.01057910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01733827590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01808929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9790358543396</t>
+    <t xml:space="preserve">6.01733875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01808977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">6.02484941482544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08493185043335</t>
+    <t xml:space="preserve">6.08493232727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.06840991973877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829824447632</t>
+    <t xml:space="preserve">6.16829872131348</t>
   </si>
   <si>
     <t xml:space="preserve">6.0676589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04888296127319</t>
+    <t xml:space="preserve">6.04888248443604</t>
   </si>
   <si>
     <t xml:space="preserve">6.09845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08943891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98654651641846</t>
+    <t xml:space="preserve">6.08943796157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98654556274414</t>
   </si>
   <si>
     <t xml:space="preserve">6.03386163711548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01508569717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03686571121216</t>
+    <t xml:space="preserve">6.01508474349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03686618804932</t>
   </si>
   <si>
     <t xml:space="preserve">5.88215112686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89491939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8964204788208</t>
+    <t xml:space="preserve">5.89491844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89642143249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.93772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401453018188</t>
+    <t xml:space="preserve">5.96401500701904</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
@@ -3695,55 +3695,55 @@
     <t xml:space="preserve">5.951247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05188608169556</t>
+    <t xml:space="preserve">6.05489110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05188655853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.02635145187378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95725536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01583623886108</t>
+    <t xml:space="preserve">5.95725584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
     <t xml:space="preserve">5.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85135698318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00276947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1157546043396</t>
+    <t xml:space="preserve">5.8513560295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.002769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11575508117676</t>
   </si>
   <si>
     <t xml:space="preserve">6.18723440170288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21106147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11959791183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19107723236084</t>
+    <t xml:space="preserve">6.21106195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11959743499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19107818603516</t>
   </si>
   <si>
     <t xml:space="preserve">6.16033363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97971248626709</t>
+    <t xml:space="preserve">5.97971200942993</t>
   </si>
   <si>
     <t xml:space="preserve">5.94819927215576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361284255981</t>
+    <t xml:space="preserve">5.91361236572266</t>
   </si>
   <si>
     <t xml:space="preserve">5.92052984237671</t>
@@ -3755,28 +3755,28 @@
     <t xml:space="preserve">5.96357202529907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9935474395752</t>
+    <t xml:space="preserve">5.99354696273804</t>
   </si>
   <si>
     <t xml:space="preserve">5.98586082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02044820785522</t>
+    <t xml:space="preserve">6.02044868469238</t>
   </si>
   <si>
     <t xml:space="preserve">6.02890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06348991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03120946884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97740650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735780715942</t>
+    <t xml:space="preserve">6.06349039077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03120899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97740697860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735733032227</t>
   </si>
   <si>
     <t xml:space="preserve">6.08885383605957</t>
@@ -3788,61 +3788,61 @@
     <t xml:space="preserve">6.0196795463562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9651083946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90131521224976</t>
+    <t xml:space="preserve">5.96510934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9013147354126</t>
   </si>
   <si>
     <t xml:space="preserve">5.90208339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95511722564697</t>
+    <t xml:space="preserve">5.95511674880981</t>
   </si>
   <si>
     <t xml:space="preserve">5.93129062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99815893173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.935133934021</t>
+    <t xml:space="preserve">5.99815845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93513345718384</t>
   </si>
   <si>
     <t xml:space="preserve">5.92975378036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83367872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77833890914917</t>
+    <t xml:space="preserve">5.83367824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77833938598633</t>
   </si>
   <si>
     <t xml:space="preserve">5.78756284713745</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66842889785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71454572677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39941930770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38097286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34869194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25722742080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30257606506348</t>
+    <t xml:space="preserve">5.66842937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76373672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71454477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39941883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38097238540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34869146347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25722789764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30257558822632</t>
   </si>
   <si>
     <t xml:space="preserve">5.33408784866333</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">5.39403867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33946800231934</t>
+    <t xml:space="preserve">5.33946847915649</t>
   </si>
   <si>
     <t xml:space="preserve">5.25492191314697</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">5.22110366821289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11196279525757</t>
+    <t xml:space="preserve">5.11196231842041</t>
   </si>
   <si>
     <t xml:space="preserve">5.17191314697266</t>
@@ -3875,43 +3875,43 @@
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30564975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31794834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18651676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958257675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24954128265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30795621871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44246006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54161024093628</t>
+    <t xml:space="preserve">5.3056492805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31794738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18651628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24954175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30795574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44246053695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54160976409912</t>
   </si>
   <si>
     <t xml:space="preserve">5.51317167282104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47781658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708826065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165105819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5462212562561</t>
+    <t xml:space="preserve">5.4778151512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54622173309326</t>
   </si>
   <si>
     <t xml:space="preserve">5.58772659301758</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">5.57696580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389116287231</t>
+    <t xml:space="preserve">5.57389068603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.60617256164551</t>
@@ -3938,34 +3938,34 @@
     <t xml:space="preserve">5.53008127212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45245265960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50318002700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45629453659058</t>
+    <t xml:space="preserve">5.45245170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50318050384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45629501342773</t>
   </si>
   <si>
     <t xml:space="preserve">5.49549436569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44707250595093</t>
+    <t xml:space="preserve">5.44707202911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.4324688911438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41248512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34177398681641</t>
+    <t xml:space="preserve">5.41248559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34177350997925</t>
   </si>
   <si>
     <t xml:space="preserve">5.34331130981445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30872440338135</t>
+    <t xml:space="preserve">5.30872392654419</t>
   </si>
   <si>
     <t xml:space="preserve">5.41479158401489</t>
@@ -3974,49 +3974,49 @@
     <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23878145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21802949905396</t>
+    <t xml:space="preserve">5.23878192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2180290222168</t>
   </si>
   <si>
     <t xml:space="preserve">5.15500402450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0650782585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01588726043701</t>
+    <t xml:space="preserve">5.19189691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06507778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01588773727417</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23493814468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039348602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1511607170105</t>
+    <t xml:space="preserve">5.234938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15116119384766</t>
   </si>
   <si>
     <t xml:space="preserve">5.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07583808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09274768829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14731788635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10965633392334</t>
+    <t xml:space="preserve">5.07583856582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0927472114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14731740951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965585708618</t>
   </si>
   <si>
     <t xml:space="preserve">5.18497896194458</t>
@@ -4034,55 +4034,55 @@
     <t xml:space="preserve">5.3156418800354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32486486434937</t>
+    <t xml:space="preserve">5.32486534118652</t>
   </si>
   <si>
     <t xml:space="preserve">5.40787363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38789033889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4155592918396</t>
+    <t xml:space="preserve">5.38788986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41556024551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47243642807007</t>
+    <t xml:space="preserve">5.47243547439575</t>
   </si>
   <si>
     <t xml:space="preserve">5.34100532531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31026172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32640171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32717037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35022878646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2318639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27490520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3825101852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3071870803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26766967773438</t>
+    <t xml:space="preserve">5.31026124954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32640266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32717084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35022926330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23186445236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27490568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38250923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30718612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26766920089722</t>
   </si>
   <si>
     <t xml:space="preserve">5.26845979690552</t>
@@ -4094,73 +4094,73 @@
     <t xml:space="preserve">5.41546487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33642959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35934972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41704511642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41309356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35776901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24712085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08272838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00369358062744</t>
+    <t xml:space="preserve">5.33642911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35934925079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41309404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35776948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24712038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08272743225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908435821533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08351898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05348587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99499940872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08114814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14516592025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12303590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08589029312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01396799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99025726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89383459091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17598915100098</t>
+    <t xml:space="preserve">5.08351850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05348491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99499988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08114767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14516639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12303638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08588981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9760308265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01396751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99025774002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89383506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17599010467529</t>
   </si>
   <si>
     <t xml:space="preserve">5.2155065536499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87960863113403</t>
+    <t xml:space="preserve">4.87960815429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.8764476776123</t>
@@ -4169,34 +4169,34 @@
     <t xml:space="preserve">4.70652294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127365112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52237176895142</t>
+    <t xml:space="preserve">4.48127412796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5223708152771</t>
   </si>
   <si>
     <t xml:space="preserve">4.77291202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53580665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5271143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59903526306152</t>
+    <t xml:space="preserve">4.53580713272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52711391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59903478622437</t>
   </si>
   <si>
     <t xml:space="preserve">4.604567527771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60298633575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52079105377197</t>
+    <t xml:space="preserve">4.60298681259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52079057693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.55240488052368</t>
@@ -4208,10 +4208,10 @@
     <t xml:space="preserve">4.51209735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566516876221</t>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566564559937</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294513702393</t>
@@ -4220,19 +4220,19 @@
     <t xml:space="preserve">4.8187518119812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79583120346069</t>
+    <t xml:space="preserve">4.79583168029785</t>
   </si>
   <si>
     <t xml:space="preserve">4.82428455352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82902669906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92544889450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90648126602173</t>
+    <t xml:space="preserve">4.82902574539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92544841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90648078918457</t>
   </si>
   <si>
     <t xml:space="preserve">4.8748664855957</t>
@@ -4241,28 +4241,28 @@
     <t xml:space="preserve">4.98709583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
+    <t xml:space="preserve">4.96891832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.89857721328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9017391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88514184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87249517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75236320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82349443435669</t>
+    <t xml:space="preserve">4.90173864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88514041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87249565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82349348068237</t>
   </si>
   <si>
     <t xml:space="preserve">4.81559038162231</t>
@@ -4274,10 +4274,10 @@
     <t xml:space="preserve">4.91596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91438436508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87881851196289</t>
+    <t xml:space="preserve">4.91438388824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87881803512573</t>
   </si>
   <si>
     <t xml:space="preserve">4.93888473510742</t>
@@ -4286,40 +4286,40 @@
     <t xml:space="preserve">4.89541530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78555679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74841070175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64171361923218</t>
+    <t xml:space="preserve">4.78555727005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74841022491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64171409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.6172137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72628116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61405181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69229555130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73181295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74999141693115</t>
+    <t xml:space="preserve">4.7262806892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61405229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69229602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73181343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74999189376831</t>
   </si>
   <si>
     <t xml:space="preserve">4.69308662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69150590896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83930063247681</t>
+    <t xml:space="preserve">4.69150638580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83930110931396</t>
   </si>
   <si>
     <t xml:space="preserve">4.84720468521118</t>
@@ -4328,43 +4328,43 @@
     <t xml:space="preserve">4.84641408920288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88909292221069</t>
+    <t xml:space="preserve">4.88751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88909339904785</t>
   </si>
   <si>
     <t xml:space="preserve">4.87012481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77686357498169</t>
+    <t xml:space="preserve">4.77686309814453</t>
   </si>
   <si>
     <t xml:space="preserve">4.68202114105225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70573234558105</t>
+    <t xml:space="preserve">4.7057318687439</t>
   </si>
   <si>
     <t xml:space="preserve">4.66700553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76500749588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73260402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62037420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52790451049805</t>
+    <t xml:space="preserve">4.76500797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73260354995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62037467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52790403366089</t>
   </si>
   <si>
     <t xml:space="preserve">4.3318977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25839519500732</t>
+    <t xml:space="preserve">4.25839567184448</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492624282837</t>
@@ -4382,13 +4382,13 @@
     <t xml:space="preserve">4.33822059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31925249099731</t>
+    <t xml:space="preserve">4.31925201416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.2291522026062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28526639938354</t>
+    <t xml:space="preserve">4.2852668762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.35718870162964</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">4.2749924659729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32794618606567</t>
+    <t xml:space="preserve">4.32794570922852</t>
   </si>
   <si>
     <t xml:space="preserve">4.26945972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12561702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911909103394</t>
+    <t xml:space="preserve">4.12561655044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911956787109</t>
   </si>
   <si>
     <t xml:space="preserve">4.173828125</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">4.15960168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15090799331665</t>
+    <t xml:space="preserve">4.15090751647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.14300441741943</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">3.82133269309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.951740026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0330753326416</t>
+    <t xml:space="preserve">3.95174050331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03307485580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.08606624603271</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">3.95831251144409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90080285072327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88108491897583</t>
+    <t xml:space="preserve">3.90080308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88108515739441</t>
   </si>
   <si>
     <t xml:space="preserve">3.90244626998901</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">3.89053344726562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88683700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818402290344</t>
+    <t xml:space="preserve">3.88683676719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9381844997406</t>
   </si>
   <si>
     <t xml:space="preserve">4.06922435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99610495567322</t>
+    <t xml:space="preserve">3.99610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.00514221191406</t>
@@ -4481,25 +4481,25 @@
     <t xml:space="preserve">4.06758117675781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13412809371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11440992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09756851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10783815383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13659286499023</t>
+    <t xml:space="preserve">4.13412857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11441040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09756803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10783863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13659334182739</t>
   </si>
   <si>
     <t xml:space="preserve">4.19163846969604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18752956390381</t>
+    <t xml:space="preserve">4.18753004074097</t>
   </si>
   <si>
     <t xml:space="preserve">4.18342208862305</t>
@@ -4508,19 +4508,19 @@
     <t xml:space="preserve">4.11030292510986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05443668365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05854368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06265211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06347322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97022533416748</t>
+    <t xml:space="preserve">4.05443620681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05854415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06265163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06347370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97022557258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.94639992713928</t>
@@ -4529,61 +4529,61 @@
     <t xml:space="preserve">3.95461559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85767078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81412696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90614318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86136770248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84288191795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94845390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10085439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06593704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04211282730103</t>
+    <t xml:space="preserve">3.85767030715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81412768363953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90614295005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86136746406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84288215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90162491798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94845414161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98871040344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10085487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06593799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04211235046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.02321672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04170179367065</t>
+    <t xml:space="preserve">4.04170227050781</t>
   </si>
   <si>
     <t xml:space="preserve">4.05073881149292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97679781913757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419213294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97186827659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81535959243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73607873916626</t>
+    <t xml:space="preserve">3.97679829597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97186851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8153600692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607850074768</t>
   </si>
   <si>
     <t xml:space="preserve">3.53438353538513</t>
@@ -4595,34 +4595,34 @@
     <t xml:space="preserve">3.49001908302307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47030162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57957029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66706705093384</t>
+    <t xml:space="preserve">3.47030138969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57956981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66706681251526</t>
   </si>
   <si>
     <t xml:space="preserve">3.55040431022644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42593717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38609075546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44154667854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34870958328247</t>
+    <t xml:space="preserve">3.42593669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38609099388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44154644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">3.28873491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34542346000671</t>
+    <t xml:space="preserve">3.34542322158813</t>
   </si>
   <si>
     <t xml:space="preserve">3.37910747528076</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">3.46290755271912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49823474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51918482780457</t>
+    <t xml:space="preserve">3.49823427200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51918506622314</t>
   </si>
   <si>
     <t xml:space="preserve">3.48426842689514</t>
@@ -4643,97 +4643,97 @@
     <t xml:space="preserve">3.44606518745422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52740001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764456748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60257387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71512866020203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67405009269714</t>
+    <t xml:space="preserve">3.52740025520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764432907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60257411003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71512818336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">3.7126636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72950625419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7730495929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784945487976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217638969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95913362503052</t>
+    <t xml:space="preserve">3.72950577735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77304935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452605247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037915229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913457870483</t>
   </si>
   <si>
     <t xml:space="preserve">4.11605405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14727354049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1982102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22203636169434</t>
+    <t xml:space="preserve">4.14727306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274188995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19821071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22203588485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.23682451248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1776704788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15959644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23353719711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518085479736</t>
+    <t xml:space="preserve">4.17767143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15959739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2335376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518037796021</t>
   </si>
   <si>
     <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19492387771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2179274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32719707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33623361587524</t>
+    <t xml:space="preserve">4.19492435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21792793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31322956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32719659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33623313903809</t>
   </si>
   <si>
     <t xml:space="preserve">4.27708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29186868667603</t>
+    <t xml:space="preserve">4.29186916351318</t>
   </si>
   <si>
     <t xml:space="preserve">4.2507905960083</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">4.29022550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31158638000488</t>
+    <t xml:space="preserve">4.27050828933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31158685684204</t>
   </si>
   <si>
     <t xml:space="preserve">4.31487274169922</t>
@@ -4754,25 +4754,25 @@
     <t xml:space="preserve">4.1530237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14891576766968</t>
+    <t xml:space="preserve">4.14891624450684</t>
   </si>
   <si>
     <t xml:space="preserve">4.1456298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14645195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21464157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16863298416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1908164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17192077636719</t>
+    <t xml:space="preserve">4.14645147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21464204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16863393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19081592559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17192029953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.14809465408325</t>
@@ -4787,37 +4787,37 @@
     <t xml:space="preserve">4.35430812835693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50794076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50054693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60160064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59995651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54819822311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62542533874512</t>
+    <t xml:space="preserve">4.50794172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50054740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60159969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59995698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54819774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62542629241943</t>
   </si>
   <si>
     <t xml:space="preserve">4.68868589401245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70593881607056</t>
+    <t xml:space="preserve">4.70593929290771</t>
   </si>
   <si>
     <t xml:space="preserve">4.7716646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73222970962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73551511764526</t>
+    <t xml:space="preserve">4.73222923278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73551607131958</t>
   </si>
   <si>
     <t xml:space="preserve">4.64760780334473</t>
@@ -4826,10 +4826,10 @@
     <t xml:space="preserve">4.64185667037964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65548467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68103551864624</t>
+    <t xml:space="preserve">4.65548419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68103504180908</t>
   </si>
   <si>
     <t xml:space="preserve">4.66570520401001</t>
@@ -4838,70 +4838,70 @@
     <t xml:space="preserve">4.66996335983276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67166709899902</t>
+    <t xml:space="preserve">4.67166662216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.62737798690796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5916051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58394002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5669059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58138513565063</t>
+    <t xml:space="preserve">4.59160566329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58394050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56690549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58138561248779</t>
   </si>
   <si>
     <t xml:space="preserve">4.56435060501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55327844619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54816818237305</t>
+    <t xml:space="preserve">4.55327892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54816770553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.60864019393921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60182619094849</t>
+    <t xml:space="preserve">4.60182571411133</t>
   </si>
   <si>
     <t xml:space="preserve">4.58223676681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58819913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57712697982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55924034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55668544769287</t>
+    <t xml:space="preserve">4.5881986618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57712602615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55924081802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55668497085571</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48003101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45788621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51920986175537</t>
+    <t xml:space="preserve">4.46214437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48003053665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51921033859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.52857875823975</t>
@@ -4913,25 +4913,25 @@
     <t xml:space="preserve">4.48428916931152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5149507522583</t>
+    <t xml:space="preserve">4.51495122909546</t>
   </si>
   <si>
     <t xml:space="preserve">4.54305744171143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.509840965271</t>
+    <t xml:space="preserve">4.50984048843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.5311336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4519248008728</t>
+    <t xml:space="preserve">4.53028154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53624486923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45192432403564</t>
   </si>
   <si>
     <t xml:space="preserve">4.5686092376709</t>
@@ -4946,31 +4946,31 @@
     <t xml:space="preserve">4.50302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58905076980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66740894317627</t>
+    <t xml:space="preserve">4.58905029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66740846633911</t>
   </si>
   <si>
     <t xml:space="preserve">4.68784999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69040441513062</t>
+    <t xml:space="preserve">4.69040489196777</t>
   </si>
   <si>
     <t xml:space="preserve">4.59245777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65378141403198</t>
+    <t xml:space="preserve">4.65378093719482</t>
   </si>
   <si>
     <t xml:space="preserve">4.64185619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69125652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77813148498535</t>
+    <t xml:space="preserve">4.69125604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77813100814819</t>
   </si>
   <si>
     <t xml:space="preserve">4.79261112213135</t>
@@ -4991,25 +4991,25 @@
     <t xml:space="preserve">5.02853631973267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10348749160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90333414077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86159992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87181997299194</t>
+    <t xml:space="preserve">5.10348701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90333366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86160087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87182092666626</t>
   </si>
   <si>
     <t xml:space="preserve">4.90503740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97402667999268</t>
+    <t xml:space="preserve">4.94762372970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97402715682983</t>
   </si>
   <si>
     <t xml:space="preserve">5.05153274536133</t>
@@ -5021,16 +5021,16 @@
     <t xml:space="preserve">5.15799760818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25083446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1937689781189</t>
+    <t xml:space="preserve">5.18695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25083494186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19376945495605</t>
   </si>
   <si>
     <t xml:space="preserve">5.19462156295776</t>
@@ -5039,43 +5039,43 @@
     <t xml:space="preserve">5.18440055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24827909469604</t>
+    <t xml:space="preserve">5.2482795715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.21165561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20569372177124</t>
+    <t xml:space="preserve">5.20569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">5.18951082229614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14777708053589</t>
+    <t xml:space="preserve">5.14777755737305</t>
   </si>
   <si>
     <t xml:space="preserve">5.15970087051392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12563228607178</t>
+    <t xml:space="preserve">5.12563180923462</t>
   </si>
   <si>
     <t xml:space="preserve">5.12733554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09156370162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02598094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1179666519165</t>
+    <t xml:space="preserve">5.09156322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02598142623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11796712875366</t>
   </si>
   <si>
     <t xml:space="preserve">5.14351797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13670492172241</t>
+    <t xml:space="preserve">5.13670444488525</t>
   </si>
   <si>
     <t xml:space="preserve">5.08049154281616</t>
@@ -5093,16 +5093,16 @@
     <t xml:space="preserve">5.12052202224731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98935699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07452964782715</t>
+    <t xml:space="preserve">4.98935747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
     <t xml:space="preserve">5.14948034286499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10774612426758</t>
+    <t xml:space="preserve">5.10774660110474</t>
   </si>
   <si>
     <t xml:space="preserve">5.15288734436035</t>
@@ -5117,16 +5117,16 @@
     <t xml:space="preserve">5.20484209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16992139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20228624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19632482528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15884971618652</t>
+    <t xml:space="preserve">5.169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20228672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19632434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15884923934937</t>
   </si>
   <si>
     <t xml:space="preserve">5.17843866348267</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">5.2269868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23635578155518</t>
+    <t xml:space="preserve">5.23635482788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.25338983535767</t>
@@ -5147,10 +5147,10 @@
     <t xml:space="preserve">5.3990330696106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14266681671143</t>
+    <t xml:space="preserve">5.28916215896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14266633987427</t>
   </si>
   <si>
     <t xml:space="preserve">5.1929178237915</t>
@@ -5159,7 +5159,7 @@
     <t xml:space="preserve">5.17503213882446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21250677108765</t>
+    <t xml:space="preserve">5.2125072479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.30619621276855</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">5.31300973892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34622669219971</t>
+    <t xml:space="preserve">5.34622716903687</t>
   </si>
   <si>
     <t xml:space="preserve">5.34452342987061</t>
@@ -5180,34 +5180,34 @@
     <t xml:space="preserve">5.36070585250854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39647817611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44836759567261</t>
+    <t xml:space="preserve">5.39647769927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44836711883545</t>
   </si>
   <si>
     <t xml:space="preserve">5.45012617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4703540802002</t>
+    <t xml:space="preserve">5.47035360336304</t>
   </si>
   <si>
     <t xml:space="preserve">5.55038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51872587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51608753204346</t>
+    <t xml:space="preserve">5.51872539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51608657836914</t>
   </si>
   <si>
     <t xml:space="preserve">5.46155977249146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34370946884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28214597702026</t>
+    <t xml:space="preserve">5.34370994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28214645385742</t>
   </si>
   <si>
     <t xml:space="preserve">5.22673845291138</t>
@@ -5216,28 +5216,28 @@
     <t xml:space="preserve">5.21706438064575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20914888381958</t>
+    <t xml:space="preserve">5.20914936065674</t>
   </si>
   <si>
     <t xml:space="preserve">5.28302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36129903793335</t>
+    <t xml:space="preserve">5.36129951477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.32436084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23553419113159</t>
+    <t xml:space="preserve">5.23553371429443</t>
   </si>
   <si>
     <t xml:space="preserve">5.17484951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21002864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26719522476196</t>
+    <t xml:space="preserve">5.21002912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26719427108765</t>
   </si>
   <si>
     <t xml:space="preserve">5.33227634429932</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">5.45892095565796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43957233428955</t>
+    <t xml:space="preserve">5.43957281112671</t>
   </si>
   <si>
     <t xml:space="preserve">5.41406774520874</t>
@@ -5267,7 +5267,7 @@
     <t xml:space="preserve">5.39383983612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36745548248291</t>
+    <t xml:space="preserve">5.36745500564575</t>
   </si>
   <si>
     <t xml:space="preserve">5.46068000793457</t>
@@ -5282,22 +5282,22 @@
     <t xml:space="preserve">5.38768291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56006145477295</t>
+    <t xml:space="preserve">5.56006097793579</t>
   </si>
   <si>
     <t xml:space="preserve">5.52752017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48442649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47475147247314</t>
+    <t xml:space="preserve">5.48442602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4747519493103</t>
   </si>
   <si>
     <t xml:space="preserve">5.35338401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31644582748413</t>
+    <t xml:space="preserve">5.31644535064697</t>
   </si>
   <si>
     <t xml:space="preserve">5.25488185882568</t>
@@ -5309,13 +5309,13 @@
     <t xml:space="preserve">5.14582633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09041976928711</t>
+    <t xml:space="preserve">5.09041929244995</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856269836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97872638702393</t>
+    <t xml:space="preserve">4.97872591018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
@@ -5324,16 +5324,16 @@
     <t xml:space="preserve">4.88726043701172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88462162017822</t>
+    <t xml:space="preserve">4.88462209701538</t>
   </si>
   <si>
     <t xml:space="preserve">4.92595720291138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92859554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02269983291626</t>
+    <t xml:space="preserve">4.92859506607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02270030975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.08426332473755</t>
@@ -5348,16 +5348,16 @@
     <t xml:space="preserve">5.05172252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04996347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96641302108765</t>
+    <t xml:space="preserve">5.04996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01390504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99719476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9664134979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.00511026382446</t>
@@ -5366,13 +5366,13 @@
     <t xml:space="preserve">5.0772271156311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05875825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08250427246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06139707565308</t>
+    <t xml:space="preserve">5.05875873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08250379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06139755249023</t>
   </si>
   <si>
     <t xml:space="preserve">5.17660903930664</t>
@@ -5387,43 +5387,43 @@
     <t xml:space="preserve">5.37712955474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41758489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40527296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38152742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35426330566406</t>
+    <t xml:space="preserve">5.4175853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3542628288269</t>
   </si>
   <si>
     <t xml:space="preserve">5.39032173156738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43869256973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49585914611816</t>
+    <t xml:space="preserve">5.43869304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49585962295532</t>
   </si>
   <si>
     <t xml:space="preserve">5.54247140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63305759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70781326293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64273166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6207447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61282920837402</t>
+    <t xml:space="preserve">5.63305807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70781373977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62074518203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61282968521118</t>
   </si>
   <si>
     <t xml:space="preserve">5.64097309112549</t>
@@ -5432,7 +5432,7 @@
     <t xml:space="preserve">5.65680408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66559839248657</t>
+    <t xml:space="preserve">5.66559791564941</t>
   </si>
   <si>
     <t xml:space="preserve">5.65768337249756</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">5.70429563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72276449203491</t>
+    <t xml:space="preserve">5.72276496887207</t>
   </si>
   <si>
     <t xml:space="preserve">5.74738931655884</t>
@@ -5456,10 +5456,10 @@
     <t xml:space="preserve">5.7535457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77465343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73155975341797</t>
+    <t xml:space="preserve">5.77465391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73155927658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.81510972976685</t>
@@ -5468,22 +5468,22 @@
     <t xml:space="preserve">5.91185235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86611938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85996294021606</t>
+    <t xml:space="preserve">5.86611986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85996341705322</t>
   </si>
   <si>
     <t xml:space="preserve">5.89250373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86436033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86963701248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90921401977539</t>
+    <t xml:space="preserve">5.86436080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86963748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90921354293823</t>
   </si>
   <si>
     <t xml:space="preserve">5.91097259521484</t>
@@ -5501,7 +5501,7 @@
     <t xml:space="preserve">5.91361093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88458824157715</t>
+    <t xml:space="preserve">5.88458871841431</t>
   </si>
   <si>
     <t xml:space="preserve">5.89162397384644</t>
@@ -5519,13 +5519,13 @@
     <t xml:space="preserve">5.98660802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93647813796997</t>
+    <t xml:space="preserve">5.93647766113281</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8239049911499</t>
+    <t xml:space="preserve">5.82390451431274</t>
   </si>
   <si>
     <t xml:space="preserve">5.85908365249634</t>
@@ -5534,19 +5534,19 @@
     <t xml:space="preserve">5.80092000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75638818740845</t>
+    <t xml:space="preserve">5.75638866424561</t>
   </si>
   <si>
     <t xml:space="preserve">5.74002981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72185373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69913291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551042556763</t>
+    <t xml:space="preserve">5.72185325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69913339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551090240479</t>
   </si>
   <si>
     <t xml:space="preserve">5.68550109863281</t>
@@ -5555,13 +5555,13 @@
     <t xml:space="preserve">5.76275014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63824319839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61824941635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56826448440552</t>
+    <t xml:space="preserve">5.63824367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61824989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56826496124268</t>
   </si>
   <si>
     <t xml:space="preserve">5.52191591262817</t>
@@ -5570,16 +5570,16 @@
     <t xml:space="preserve">5.48011064529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41013240814209</t>
+    <t xml:space="preserve">5.41013288497925</t>
   </si>
   <si>
     <t xml:space="preserve">5.33833694458008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37741565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34651613235474</t>
+    <t xml:space="preserve">5.3774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34651565551758</t>
   </si>
   <si>
     <t xml:space="preserve">5.37468910217285</t>
@@ -5606,10 +5606,10 @@
     <t xml:space="preserve">5.34015417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39831781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31925249099731</t>
+    <t xml:space="preserve">5.39831829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31925201416016</t>
   </si>
   <si>
     <t xml:space="preserve">5.35469532012939</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">5.5900764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64278697967529</t>
+    <t xml:space="preserve">5.64278745651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.57008266448975</t>
@@ -5642,13 +5642,13 @@
     <t xml:space="preserve">5.57190036773682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5200982093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54645347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51646327972412</t>
+    <t xml:space="preserve">5.52009773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54645395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51646280288696</t>
   </si>
   <si>
     <t xml:space="preserve">5.52645969390869</t>
@@ -5657,10 +5657,10 @@
     <t xml:space="preserve">5.51373624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5291862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60552644729614</t>
+    <t xml:space="preserve">5.52918672561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60552597045898</t>
   </si>
   <si>
     <t xml:space="preserve">5.56099462509155</t>
@@ -5669,10 +5669,10 @@
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49465131759644</t>
+    <t xml:space="preserve">5.44375848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49465179443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.36832761764526</t>
@@ -5681,7 +5681,7 @@
     <t xml:space="preserve">5.36105728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29380512237549</t>
+    <t xml:space="preserve">5.29380464553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.17929553985596</t>
@@ -5690,16 +5690,16 @@
     <t xml:space="preserve">5.18656587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3374285697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31470823287964</t>
+    <t xml:space="preserve">5.33742761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31470775604248</t>
   </si>
   <si>
     <t xml:space="preserve">5.26563262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25836181640625</t>
+    <t xml:space="preserve">5.25836133956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.33651924133301</t>
@@ -5708,19 +5708,19 @@
     <t xml:space="preserve">5.41195011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49737739562988</t>
+    <t xml:space="preserve">5.49737787246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.56190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53282117843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50737476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63460779190063</t>
+    <t xml:space="preserve">5.53282165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50737524032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63460826873779</t>
   </si>
   <si>
     <t xml:space="preserve">5.61734104156494</t>
@@ -5729,13 +5729,13 @@
     <t xml:space="preserve">5.67277812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68004846572876</t>
+    <t xml:space="preserve">5.68004894256592</t>
   </si>
   <si>
     <t xml:space="preserve">5.74820852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80182838439941</t>
+    <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
     <t xml:space="preserve">5.8581748008728</t>
@@ -5744,10 +5744,10 @@
     <t xml:space="preserve">5.91452074050903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13899612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13627004623413</t>
+    <t xml:space="preserve">6.13899660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13626956939697</t>
   </si>
   <si>
     <t xml:space="preserve">6.10173511505127</t>
@@ -5756,7 +5756,7 @@
     <t xml:space="preserve">6.21806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19715976715088</t>
+    <t xml:space="preserve">6.19715929031372</t>
   </si>
   <si>
     <t xml:space="preserve">6.17989253997803</t>
@@ -5768,7 +5768,7 @@
     <t xml:space="preserve">6.12082052230835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06538248062134</t>
+    <t xml:space="preserve">6.0653829574585</t>
   </si>
   <si>
     <t xml:space="preserve">6.00358390808105</t>
@@ -5780,10 +5780,10 @@
     <t xml:space="preserve">6.0535683631897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05265951156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97086715698242</t>
+    <t xml:space="preserve">6.052659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97086668014526</t>
   </si>
   <si>
     <t xml:space="preserve">6.01630687713623</t>
@@ -5792,37 +5792,37 @@
     <t xml:space="preserve">6.04902458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13445234298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12172889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19170713424683</t>
+    <t xml:space="preserve">6.1344518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12172937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19170761108398</t>
   </si>
   <si>
     <t xml:space="preserve">6.17807483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09810018539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06992673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904897689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03539228439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95632553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75911426544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74275588989258</t>
+    <t xml:space="preserve">6.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03539180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95632600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75911474227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74275541305542</t>
   </si>
   <si>
     <t xml:space="preserve">5.86180973052979</t>
@@ -5831,22 +5831,22 @@
     <t xml:space="preserve">5.81636953353882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89725303649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87907743453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9454197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97813701629639</t>
+    <t xml:space="preserve">5.89725351333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87907695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94542026519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97813749313354</t>
   </si>
   <si>
     <t xml:space="preserve">5.95087289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9045238494873</t>
+    <t xml:space="preserve">5.90452432632446</t>
   </si>
   <si>
     <t xml:space="preserve">5.9017972946167</t>
@@ -5855,10 +5855,10 @@
     <t xml:space="preserve">6.00449275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98449897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02812147140503</t>
+    <t xml:space="preserve">5.98449945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02812194824219</t>
   </si>
   <si>
     <t xml:space="preserve">6.04266262054443</t>
@@ -5867,10 +5867,10 @@
     <t xml:space="preserve">6.09446430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11809349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16989612579346</t>
+    <t xml:space="preserve">6.11809396743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1698956489563</t>
   </si>
   <si>
     <t xml:space="preserve">6.25714159011841</t>
@@ -5891,22 +5891,22 @@
     <t xml:space="preserve">6.16179513931274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25191259384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2613000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24252510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22375059127808</t>
+    <t xml:space="preserve">6.18150854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468996047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25191211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26129961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24252557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22375106811523</t>
   </si>
   <si>
     <t xml:space="preserve">6.18995666503906</t>
@@ -5924,40 +5924,40 @@
     <t xml:space="preserve">5.91209363937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03600549697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03412818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01629209518433</t>
+    <t xml:space="preserve">6.03600597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03412866592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01629257202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.04351568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10641050338745</t>
+    <t xml:space="preserve">6.10641002655029</t>
   </si>
   <si>
     <t xml:space="preserve">6.09139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16742753982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18714094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17587566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20216035842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30260419845581</t>
+    <t xml:space="preserve">6.16742706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17587614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19840526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2021598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30260372161865</t>
   </si>
   <si>
     <t xml:space="preserve">6.29791021347046</t>
@@ -5969,10 +5969,10 @@
     <t xml:space="preserve">6.41149616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42651605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44341278076172</t>
+    <t xml:space="preserve">6.42651557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44341230392456</t>
   </si>
   <si>
     <t xml:space="preserve">6.46594190597534</t>
@@ -5981,13 +5981,13 @@
     <t xml:space="preserve">6.47063589096069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46030950546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56638526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6189546585083</t>
+    <t xml:space="preserve">6.4603099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5663857460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61895418167114</t>
   </si>
   <si>
     <t xml:space="preserve">6.62177038192749</t>
@@ -6026,10 +6026,10 @@
     <t xml:space="preserve">6.71752071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7710280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535633087158</t>
+    <t xml:space="preserve">6.77102756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535680770874</t>
   </si>
   <si>
     <t xml:space="preserve">6.7785382270813</t>
@@ -6041,7 +6041,7 @@
     <t xml:space="preserve">6.55605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52883672714233</t>
+    <t xml:space="preserve">6.52883625030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147557258606</t>
@@ -6053,7 +6053,7 @@
     <t xml:space="preserve">6.57201766967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55418252944946</t>
+    <t xml:space="preserve">6.5541820526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.63303518295288</t>
@@ -6062,7 +6062,7 @@
     <t xml:space="preserve">6.73629522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76727342605591</t>
+    <t xml:space="preserve">6.76727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.83861589431763</t>
@@ -6074,22 +6074,22 @@
     <t xml:space="preserve">6.88273620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88743019104004</t>
+    <t xml:space="preserve">6.88742971420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.73066282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73723363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75976371765137</t>
+    <t xml:space="preserve">6.73723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75976324081421</t>
   </si>
   <si>
     <t xml:space="preserve">6.74756002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76633453369141</t>
+    <t xml:space="preserve">6.76633405685425</t>
   </si>
   <si>
     <t xml:space="preserve">6.70062351226807</t>
@@ -6104,7 +6104,7 @@
     <t xml:space="preserve">6.58234405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60017967224121</t>
+    <t xml:space="preserve">6.60018014907837</t>
   </si>
   <si>
     <t xml:space="preserve">6.56920194625854</t>
@@ -6122,10 +6122,10 @@
     <t xml:space="preserve">6.34109163284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37206935882568</t>
+    <t xml:space="preserve">6.21436309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37206983566284</t>
   </si>
   <si>
     <t xml:space="preserve">6.28852272033691</t>
@@ -6143,10 +6143,10 @@
     <t xml:space="preserve">6.32888841629028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072641372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32607221603394</t>
+    <t xml:space="preserve">6.30072593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32607173919678</t>
   </si>
   <si>
     <t xml:space="preserve">6.3551721572876</t>
@@ -6179,7 +6179,7 @@
     <t xml:space="preserve">6.48565530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58891487121582</t>
+    <t xml:space="preserve">6.58891534805298</t>
   </si>
   <si>
     <t xml:space="preserve">6.49222612380981</t>
@@ -6200,7 +6200,7 @@
     <t xml:space="preserve">6.4640645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59454727172852</t>
+    <t xml:space="preserve">6.59454774856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.58328247070312</t>
@@ -6212,22 +6212,22 @@
     <t xml:space="preserve">6.5654468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5588755607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60205698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46312570571899</t>
+    <t xml:space="preserve">6.55887603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60205745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46312618255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.49692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6170768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66870641708374</t>
+    <t xml:space="preserve">6.61707639694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6687068939209</t>
   </si>
   <si>
     <t xml:space="preserve">6.572350025177</t>
@@ -6780,6 +6780,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.55599975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66499996185303</t>
   </si>
 </sst>
 </file>
@@ -72040,7 +72043,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.693900463</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>19589983</v>
@@ -72061,6 +72064,32 @@
         <v>2255</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.693275463</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>16689995</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>8.66499996185303</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>8.54199981689453</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>8.66499996185303</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697376251221</t>
+    <t xml:space="preserve">2.23697352409363</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
@@ -50,67 +50,67 @@
     <t xml:space="preserve">2.22277045249939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23223948478699</t>
+    <t xml:space="preserve">2.23223900794983</t>
   </si>
   <si>
     <t xml:space="preserve">2.21448540687561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21685242652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20146584510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23460626602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21211791038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17187714576721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281798362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09257626533508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16004061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20619988441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19436430931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513794898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081330299377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702153205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849405288696</t>
+    <t xml:space="preserve">2.21685314178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20146560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23460650444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21211814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17187643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1328182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09257650375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16004037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20620012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19436454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25235986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17305970191956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987222671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395396232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081377983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702081680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849381446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.07008790969849</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">2.06772089004517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08665823936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090884208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09375977516174</t>
+    <t xml:space="preserve">2.08665871620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09376001358032</t>
   </si>
   <si>
     <t xml:space="preserve">2.16477513313293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15057158470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648984909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228677749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15293908119202</t>
+    <t xml:space="preserve">2.15057182312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.156489610672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228653907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1529393196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.09494352340698</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">2.18016123771667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19199728965759</t>
+    <t xml:space="preserve">2.19199752807617</t>
   </si>
   <si>
     <t xml:space="preserve">2.21330189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19791483879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714215278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542719841003</t>
+    <t xml:space="preserve">2.19791507720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1671416759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542743682861</t>
   </si>
   <si>
     <t xml:space="preserve">2.24170804023743</t>
@@ -173,106 +173,106 @@
     <t xml:space="preserve">2.31508994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30798888206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30207085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30562090873718</t>
+    <t xml:space="preserve">2.30798864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30207061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30562114715576</t>
   </si>
   <si>
     <t xml:space="preserve">2.32574200630188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31745743751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982469558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088663101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390690803528</t>
+    <t xml:space="preserve">2.31745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982445716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3115394115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390643119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.3505973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36716794967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680537223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496932029724</t>
+    <t xml:space="preserve">2.36716747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30680561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496908187866</t>
   </si>
   <si>
     <t xml:space="preserve">2.2736644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20738315582275</t>
+    <t xml:space="preserve">2.20738410949707</t>
   </si>
   <si>
     <t xml:space="preserve">2.16595840454102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22632169723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21921968460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26182889938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129745483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32337498664856</t>
+    <t xml:space="preserve">2.22632098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23579001426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21921992301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26182866096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129769325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32337546348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.2961528301239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39912438392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231233596802</t>
+    <t xml:space="preserve">2.35769867897034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231209754944</t>
   </si>
   <si>
     <t xml:space="preserve">2.34112906455994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32929301261902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3091721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941387176514</t>
+    <t xml:space="preserve">2.32929348945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30917191505432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941363334656</t>
   </si>
   <si>
     <t xml:space="preserve">2.37071847915649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37663650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3375780582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3529646396637</t>
+    <t xml:space="preserve">2.37663602828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296440124512</t>
   </si>
   <si>
     <t xml:space="preserve">2.33166027069092</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">2.3399453163147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40385866165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42989730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42516374588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43699884414673</t>
+    <t xml:space="preserve">2.40385890007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095995903015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42989706993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42516350746155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43699908256531</t>
   </si>
   <si>
     <t xml:space="preserve">2.38965582847595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39794111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37781977653503</t>
+    <t xml:space="preserve">2.39794087409973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37782001495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463158607483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44173359870911</t>
+    <t xml:space="preserve">2.44173336029053</t>
   </si>
   <si>
     <t xml:space="preserve">2.43936634063721</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">2.35651540756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31864070892334</t>
+    <t xml:space="preserve">2.31864047050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.27839875221252</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">2.37900328636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43817067146301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44433355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40735483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652150154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013116836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627751350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365672111511</t>
+    <t xml:space="preserve">2.43817090988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44433403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40735411643982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21875977516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21013140678406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365648269653</t>
   </si>
   <si>
     <t xml:space="preserve">2.45296239852905</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">2.45419478416443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39256286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37653779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42214584350586</t>
+    <t xml:space="preserve">2.39256262779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4221465587616</t>
   </si>
   <si>
     <t xml:space="preserve">2.43940281867981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45912551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46035814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282362937927</t>
+    <t xml:space="preserve">2.45912528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4603579044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282315254211</t>
   </si>
   <si>
     <t xml:space="preserve">2.44679880142212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48008012771606</t>
+    <t xml:space="preserve">2.48008060455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254537582397</t>
@@ -395,49 +395,49 @@
     <t xml:space="preserve">2.47638249397278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47268486022949</t>
+    <t xml:space="preserve">2.47268438339233</t>
   </si>
   <si>
     <t xml:space="preserve">2.53801465034485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52568864822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240636825562</t>
+    <t xml:space="preserve">2.52568793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240660667419</t>
   </si>
   <si>
     <t xml:space="preserve">2.48131275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4911744594574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52322292327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51089668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350069999695</t>
+    <t xml:space="preserve">2.49117422103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52322316169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5108962059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50350046157837</t>
   </si>
   <si>
     <t xml:space="preserve">2.49856996536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53308415412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52938628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47021961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42461156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4270761013031</t>
+    <t xml:space="preserve">2.53308367729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52938580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47021913528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42461180686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707633972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.39749336242676</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.42954182624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4357054233551</t>
+    <t xml:space="preserve">2.43570518493652</t>
   </si>
   <si>
     <t xml:space="preserve">2.4517297744751</t>
@@ -467,67 +467,67 @@
     <t xml:space="preserve">2.48747587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48994183540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541063308716</t>
+    <t xml:space="preserve">2.48994135856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761511802673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541039466858</t>
   </si>
   <si>
     <t xml:space="preserve">2.53061842918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49610495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44556641578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475009918213</t>
+    <t xml:space="preserve">2.49610471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44556665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105198860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41474962234497</t>
   </si>
   <si>
     <t xml:space="preserve">2.39133024215698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41968083381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40982007980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44803142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41721534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4209132194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41228485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37284016609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35928153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32476735115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33832573890686</t>
+    <t xml:space="preserve">2.41968107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40981984138489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44803166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4172158241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42091369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926404953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4122850894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35928106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32476758956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051392555237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33832621574402</t>
   </si>
   <si>
     <t xml:space="preserve">2.31983661651611</t>
@@ -536,37 +536,37 @@
     <t xml:space="preserve">2.36421155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35435032844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858721733093</t>
+    <t xml:space="preserve">2.35435056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43693804740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858697891235</t>
   </si>
   <si>
     <t xml:space="preserve">2.43077445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41598272323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37037539482117</t>
+    <t xml:space="preserve">2.41598296165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37037491798401</t>
   </si>
   <si>
     <t xml:space="preserve">2.36297917366028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35311841964722</t>
+    <t xml:space="preserve">2.35311818122864</t>
   </si>
   <si>
     <t xml:space="preserve">2.36667680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38393449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32723236083984</t>
+    <t xml:space="preserve">2.38393378257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32723259925842</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711060523987</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">2.243412733078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369050979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2495756149292</t>
+    <t xml:space="preserve">2.22369027137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957585334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.25080847740173</t>
@@ -590,34 +590,34 @@
     <t xml:space="preserve">2.22862100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24834275245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860446929932</t>
+    <t xml:space="preserve">2.24834299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860399246216</t>
   </si>
   <si>
     <t xml:space="preserve">2.30751037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29764890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30257964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065293312073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33339619636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51952481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336216926575</t>
+    <t xml:space="preserve">2.29764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30257940292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586072921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065245628357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336169242859</t>
   </si>
   <si>
     <t xml:space="preserve">2.47884750366211</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">2.5392472743988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5491087436676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266784667969</t>
+    <t xml:space="preserve">2.56513261795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266760826111</t>
   </si>
   <si>
     <t xml:space="preserve">2.58115720748901</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">2.60211205482483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56883096694946</t>
+    <t xml:space="preserve">2.56883025169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.57252812385559</t>
@@ -656,34 +656,34 @@
     <t xml:space="preserve">2.55896973609924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047989845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664254188538</t>
+    <t xml:space="preserve">2.54048013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">2.56636548042297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55403923988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650424957275</t>
+    <t xml:space="preserve">2.55403876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55650401115417</t>
   </si>
   <si>
     <t xml:space="preserve">2.55157375335693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57299470901489</t>
+    <t xml:space="preserve">2.57299423217773</t>
   </si>
   <si>
     <t xml:space="preserve">2.56795430183411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52763319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50873303413391</t>
+    <t xml:space="preserve">2.52763271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50873231887817</t>
   </si>
   <si>
     <t xml:space="preserve">2.47849178314209</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">2.43439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43565011024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715092658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41927003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069051742554</t>
+    <t xml:space="preserve">2.43565034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825053215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41926956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4406909942627</t>
   </si>
   <si>
     <t xml:space="preserve">2.54401326179504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5503134727478</t>
+    <t xml:space="preserve">2.55031371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023385047913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53267335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49361228942871</t>
+    <t xml:space="preserve">2.53267312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49361181259155</t>
   </si>
   <si>
     <t xml:space="preserve">2.53141307830811</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">2.54527354240417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52133274078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52637267112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50369262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200731754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787372589111</t>
+    <t xml:space="preserve">2.52133297920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5263729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50369215011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787420272827</t>
   </si>
   <si>
     <t xml:space="preserve">2.55283403396606</t>
@@ -752,61 +752,61 @@
     <t xml:space="preserve">2.5780348777771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5994553565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60323452949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60827541351318</t>
+    <t xml:space="preserve">2.59945511817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6032350063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6082751750946</t>
   </si>
   <si>
     <t xml:space="preserve">2.62717604637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63851594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63347578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473606109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237641334534</t>
+    <t xml:space="preserve">2.63851618766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473677635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961579322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65237665176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.6397762298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65867686271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151829719543</t>
+    <t xml:space="preserve">2.6586766242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71033835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151805877686</t>
   </si>
   <si>
     <t xml:space="preserve">2.71537828445435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7342791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74183940887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75191926956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78090023994446</t>
+    <t xml:space="preserve">2.73427891731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74183964729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75191950798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78090000152588</t>
   </si>
   <si>
     <t xml:space="preserve">2.77964019775391</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">2.77460026741028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7619993686676</t>
+    <t xml:space="preserve">2.76199913024902</t>
   </si>
   <si>
     <t xml:space="preserve">2.77208018302917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74309921264648</t>
+    <t xml:space="preserve">2.74309897422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.75947976112366</t>
@@ -833,64 +833,64 @@
     <t xml:space="preserve">2.72671890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67253684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907855033875</t>
+    <t xml:space="preserve">2.67253756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7090790271759</t>
   </si>
   <si>
     <t xml:space="preserve">2.80484104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79098033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77712035179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77081990242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939870834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78720021247864</t>
+    <t xml:space="preserve">2.79098105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77082014083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78720045089722</t>
   </si>
   <si>
     <t xml:space="preserve">2.7935004234314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85650229454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8842236995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658310890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87918305397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87414288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87666344642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94974493980408</t>
+    <t xml:space="preserve">2.85650277137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88422346115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792325019836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8665828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87918257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87414312362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87666296958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88044309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94974565505981</t>
   </si>
   <si>
     <t xml:space="preserve">2.91572427749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92202425003052</t>
+    <t xml:space="preserve">2.92202472686768</t>
   </si>
   <si>
     <t xml:space="preserve">2.95100545883179</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">2.9799861907959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01526761054993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9862859249115</t>
+    <t xml:space="preserve">3.01526713371277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628640174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.00518679618835</t>
@@ -911,82 +911,82 @@
     <t xml:space="preserve">3.02912759780884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9610857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872614860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990609169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148748397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156662940979</t>
+    <t xml:space="preserve">2.96108508110046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156710624695</t>
   </si>
   <si>
     <t xml:space="preserve">3.11354994773865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180764198303</t>
+    <t xml:space="preserve">3.08582925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180859565735</t>
   </si>
   <si>
     <t xml:space="preserve">3.05558824539185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05810832977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440901756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968972206116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10724902153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749003410339</t>
+    <t xml:space="preserve">3.05810856819153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440854072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10724949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749051094055</t>
   </si>
   <si>
     <t xml:space="preserve">3.10346961021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11858987808228</t>
+    <t xml:space="preserve">3.1185896396637</t>
   </si>
   <si>
     <t xml:space="preserve">3.02408742904663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04928827285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98754692077637</t>
+    <t xml:space="preserve">3.04928803443909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98754572868347</t>
   </si>
   <si>
     <t xml:space="preserve">2.95730519294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99888634681702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478510856628</t>
+    <t xml:space="preserve">2.99888682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478558540344</t>
   </si>
   <si>
     <t xml:space="preserve">2.97368621826172</t>
@@ -995,88 +995,88 @@
     <t xml:space="preserve">3.02282738685608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01778745651245</t>
+    <t xml:space="preserve">3.01778721809387</t>
   </si>
   <si>
     <t xml:space="preserve">3.06944847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1324508190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13119006156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10094928741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12867069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09338927268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.119060754776</t>
+    <t xml:space="preserve">3.13245105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13118982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094976425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12489008903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12867045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0933895111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906099319458</t>
   </si>
   <si>
     <t xml:space="preserve">3.07927012443542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11777687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595632553101</t>
+    <t xml:space="preserve">3.11777710914612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953881263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595680236816</t>
   </si>
   <si>
     <t xml:space="preserve">3.13703036308289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13189673423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040324211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864201545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735813140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16013431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2281641960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383567810059</t>
+    <t xml:space="preserve">3.13189601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735789299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532797813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16013479232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816300392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383496284485</t>
   </si>
   <si>
     <t xml:space="preserve">3.23458123207092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19607400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025199890137</t>
+    <t xml:space="preserve">3.19607448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025247573853</t>
   </si>
   <si>
     <t xml:space="preserve">3.26987934112549</t>
@@ -1085,37 +1085,37 @@
     <t xml:space="preserve">3.26346158981323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29875993728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271508216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30196857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33084893226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122206687927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405780792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629661560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517721176147</t>
+    <t xml:space="preserve">3.29875922203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950596809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3019688129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33084917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614632606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405756950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159543991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629685401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517745018005</t>
   </si>
   <si>
     <t xml:space="preserve">3.28592395782471</t>
@@ -1124,52 +1124,52 @@
     <t xml:space="preserve">3.28913307189941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27308797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2409987449646</t>
+    <t xml:space="preserve">3.2730884552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099898338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708944320679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23779058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704383850098</t>
+    <t xml:space="preserve">3.23778986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25704312324524</t>
   </si>
   <si>
     <t xml:space="preserve">3.31480407714844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31801319122314</t>
+    <t xml:space="preserve">3.31801342964172</t>
   </si>
   <si>
     <t xml:space="preserve">3.32763957977295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3083860874176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32443046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35010170936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39502692222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3918182849884</t>
+    <t xml:space="preserve">3.30838632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3244309425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.350102186203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39502668380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181804656982</t>
   </si>
   <si>
     <t xml:space="preserve">3.4142804145813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41748929023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45599627494812</t>
+    <t xml:space="preserve">3.41748905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599675178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.44316029548645</t>
@@ -1178,43 +1178,43 @@
     <t xml:space="preserve">3.44957804679871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45920491218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46241402626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995261192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42390727996826</t>
+    <t xml:space="preserve">3.45920562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46241354942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4239068031311</t>
   </si>
   <si>
     <t xml:space="preserve">3.38539958000183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37256455421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37898230552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39823603630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331082344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786218643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674230575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883177757263</t>
+    <t xml:space="preserve">3.37256407737732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898206710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39823579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3468930721283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331130027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786290168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674302101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883201599121</t>
   </si>
   <si>
     <t xml:space="preserve">3.513756275177</t>
@@ -1223,148 +1223,148 @@
     <t xml:space="preserve">3.50092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44636869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5458459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56188988685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114385604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166728019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50412964820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107106208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234170913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711544036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44611382484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047932624817</t>
+    <t xml:space="preserve">3.446368932724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054787635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584622383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56188941001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114361763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5362184047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166751861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50413060188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107153892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293816566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234194755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711567878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40144538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44611430168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35382509231567</t>
+    <t xml:space="preserve">3.35382533073425</t>
   </si>
   <si>
     <t xml:space="preserve">3.31717133522034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34466218948364</t>
+    <t xml:space="preserve">3.34466195106506</t>
   </si>
   <si>
     <t xml:space="preserve">3.31586217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25302672386169</t>
+    <t xml:space="preserve">3.25302648544312</t>
   </si>
   <si>
     <t xml:space="preserve">3.21310067176819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12146592140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019246101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070348739624</t>
+    <t xml:space="preserve">3.12146615982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019198417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070324897766</t>
   </si>
   <si>
     <t xml:space="preserve">3.03310394287109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06844902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0461950302124</t>
+    <t xml:space="preserve">3.0684494972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04619431495667</t>
   </si>
   <si>
     <t xml:space="preserve">3.12866592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13652062416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18102860450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.127357006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0763041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466498374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15877437591553</t>
+    <t xml:space="preserve">3.13652038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1810290813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212061882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630324363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15877485275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.16597437858582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12801074981689</t>
+    <t xml:space="preserve">3.12801098823547</t>
   </si>
   <si>
     <t xml:space="preserve">3.11688423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0481584072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07695817947388</t>
+    <t xml:space="preserve">3.04815912246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0769579410553</t>
   </si>
   <si>
     <t xml:space="preserve">3.09528517723083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12670230865479</t>
+    <t xml:space="preserve">3.12670207023621</t>
   </si>
   <si>
     <t xml:space="preserve">3.1679379940033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16531991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16335606575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18757438659668</t>
+    <t xml:space="preserve">3.16532015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1633563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18757390975952</t>
   </si>
   <si>
     <t xml:space="preserve">3.17448329925537</t>
@@ -1373,277 +1373,277 @@
     <t xml:space="preserve">3.19673705101013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22684574127197</t>
+    <t xml:space="preserve">3.22684597969055</t>
   </si>
   <si>
     <t xml:space="preserve">3.19150114059448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13913798332214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17513799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259267807007</t>
+    <t xml:space="preserve">3.1391384601593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17513823509216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259315490723</t>
   </si>
   <si>
     <t xml:space="preserve">3.13979315757751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25629997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320936203003</t>
+    <t xml:space="preserve">3.25629925727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24321007728577</t>
   </si>
   <si>
     <t xml:space="preserve">3.24844527244568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30538940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277228355408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764458656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240843772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597086906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34728050231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095210075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39833354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393402099609</t>
+    <t xml:space="preserve">3.30538988113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3027720451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764387130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3224081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3132438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597063064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3472797870636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39833307266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393449783325</t>
   </si>
   <si>
     <t xml:space="preserve">3.40487933158875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39309740066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44284129142761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4362964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.448077917099</t>
+    <t xml:space="preserve">3.39309692382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44284200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43629598617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44807839393616</t>
   </si>
   <si>
     <t xml:space="preserve">3.49520444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4821138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891477584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31848073005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34335255622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36298871040344</t>
+    <t xml:space="preserve">3.48211431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52531290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52662110328674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891501426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109808921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3184802532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34335231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3629891872406</t>
   </si>
   <si>
     <t xml:space="preserve">3.23797297477722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26153612136841</t>
+    <t xml:space="preserve">3.26153588294983</t>
   </si>
   <si>
     <t xml:space="preserve">3.20590090751648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20655560493469</t>
+    <t xml:space="preserve">3.20655536651611</t>
   </si>
   <si>
     <t xml:space="preserve">3.19542860984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1921558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10772156715393</t>
+    <t xml:space="preserve">3.19215536117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10772085189819</t>
   </si>
   <si>
     <t xml:space="preserve">3.08415746688843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00888729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0782675743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.098557472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324809074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386780738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692296028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11557531356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12932085990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18953800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888306617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401076316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746545791626</t>
+    <t xml:space="preserve">3.00888681411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826733589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855771064758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1332483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564902305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386756896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692272186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11557555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12932157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953776359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401124000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204714775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15746593475342</t>
   </si>
   <si>
     <t xml:space="preserve">3.08481287956238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1064121723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452202796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12342977523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10313892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15550184249878</t>
+    <t xml:space="preserve">3.10641145706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06452250480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808493614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12342953681946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1031391620636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11361193656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510325431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15550208091736</t>
   </si>
   <si>
     <t xml:space="preserve">3.14437437057495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739270210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186522483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1941192150116</t>
+    <t xml:space="preserve">3.17710208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644667625427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186570167542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251944541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411897659302</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048283576965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20917320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113657951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17952394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530920028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13647532463074</t>
+    <t xml:space="preserve">3.20917391777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113705635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952370643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530896186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647556304932</t>
   </si>
   <si>
     <t xml:space="preserve">3.14656472206116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1721248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338038444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844697952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08401036262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499793052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468317985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08333730697632</t>
+    <t xml:space="preserve">3.17212438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08401012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347350120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432439804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499745368958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08333778381348</t>
   </si>
   <si>
     <t xml:space="preserve">3.06921219825745</t>
@@ -1655,364 +1655,364 @@
     <t xml:space="preserve">2.99051427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01203870773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98042559623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638964653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96629977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95082926750183</t>
+    <t xml:space="preserve">3.01203918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98042488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638916969299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96630001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9979133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9851336479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95082950592041</t>
   </si>
   <si>
     <t xml:space="preserve">2.96293663978577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95150184631348</t>
+    <t xml:space="preserve">2.9515016078949</t>
   </si>
   <si>
     <t xml:space="preserve">2.92997789382935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94006681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836406707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540508270264</t>
+    <t xml:space="preserve">2.94006705284119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836430549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540532112122</t>
   </si>
   <si>
     <t xml:space="preserve">2.85397028923035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88625645637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88558411598206</t>
+    <t xml:space="preserve">2.88625693321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88558435440063</t>
   </si>
   <si>
     <t xml:space="preserve">2.94477534294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96091890335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719422340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06585001945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894400596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06652212142944</t>
+    <t xml:space="preserve">2.96091866493225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894352912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06652140617371</t>
   </si>
   <si>
     <t xml:space="preserve">3.05979537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03625297546387</t>
+    <t xml:space="preserve">3.0362536907196</t>
   </si>
   <si>
     <t xml:space="preserve">3.05912303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11629605293274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07392024993896</t>
+    <t xml:space="preserve">3.11629629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07392001152039</t>
   </si>
   <si>
     <t xml:space="preserve">3.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1014986038208</t>
+    <t xml:space="preserve">3.10149836540222</t>
   </si>
   <si>
     <t xml:space="preserve">3.08064675331116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96764540672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94746565818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562695503235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04096150398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9999315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9750440120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94410276412964</t>
+    <t xml:space="preserve">2.96764492988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94746613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0409619808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99993133544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97504377365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94410252571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.94343042373657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92325162887573</t>
+    <t xml:space="preserve">2.92325115203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.88423895835876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99589586257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96898984909058</t>
+    <t xml:space="preserve">2.99589562416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96899008750916</t>
   </si>
   <si>
     <t xml:space="preserve">2.93468618392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9797523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96697282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612121582031</t>
+    <t xml:space="preserve">2.97975277900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9669725894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612097740173</t>
   </si>
   <si>
     <t xml:space="preserve">2.95957350730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91518020629883</t>
+    <t xml:space="preserve">2.91517996788025</t>
   </si>
   <si>
     <t xml:space="preserve">2.94544816017151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96428203582764</t>
+    <t xml:space="preserve">2.96428179740906</t>
   </si>
   <si>
     <t xml:space="preserve">2.97168111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00665760040283</t>
+    <t xml:space="preserve">3.00665712356567</t>
   </si>
   <si>
     <t xml:space="preserve">3.0154013633728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0228009223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99454998970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683639526367</t>
+    <t xml:space="preserve">3.02280044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99455046653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683687210083</t>
   </si>
   <si>
     <t xml:space="preserve">3.06853985786438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09275412559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.133784532547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13244009017944</t>
+    <t xml:space="preserve">3.09275436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378500938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13243985176086</t>
   </si>
   <si>
     <t xml:space="preserve">3.16472554206848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19835734367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20441055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2151734828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037508010864</t>
+    <t xml:space="preserve">3.19835686683655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20441102981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21517300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037460327148</t>
   </si>
   <si>
     <t xml:space="preserve">3.22189950942993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23804211616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22728061676025</t>
+    <t xml:space="preserve">3.23804235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22728037834167</t>
   </si>
   <si>
     <t xml:space="preserve">3.24880456924438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19297695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19364905357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961310386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3167405128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37660431861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37525939941406</t>
+    <t xml:space="preserve">3.19297623634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19364857673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961262702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333430290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31673979759216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37660479545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37525868415833</t>
   </si>
   <si>
     <t xml:space="preserve">3.3725688457489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37122368812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655776023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270132064819</t>
+    <t xml:space="preserve">3.37122344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270060539246</t>
   </si>
   <si>
     <t xml:space="preserve">3.4882607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39543795585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.392746925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965222358704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099761962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153448104858</t>
+    <t xml:space="preserve">3.39543771743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39274740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965246200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099738121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808218955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46673655509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153519630432</t>
   </si>
   <si>
     <t xml:space="preserve">3.47346329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53130912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51113104820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.524582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032132148743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446694374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683327674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690237998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5675585269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61591839790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63802552223206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57170367240906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545164108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097818374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59104681015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348272323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071969032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61730027198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282705307007</t>
+    <t xml:space="preserve">3.53130865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767851829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440430641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978541374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458310127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032179832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275723457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446646690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57861161231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58690166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755876541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62144541740417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61591863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63802480697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57170414924622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545116424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472615242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097794532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59104704856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60348320007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282657623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.61039113998413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61453580856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64631533622742</t>
+    <t xml:space="preserve">3.61453676223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64631509780884</t>
   </si>
   <si>
     <t xml:space="preserve">3.6698043346405</t>
@@ -2021,70 +2021,70 @@
     <t xml:space="preserve">3.66151475906372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67533159255981</t>
+    <t xml:space="preserve">3.67533183097839</t>
   </si>
   <si>
     <t xml:space="preserve">3.67118668556213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66427850723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72921752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80106663703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78863215446472</t>
+    <t xml:space="preserve">3.66427755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085837364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921776771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80106687545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78863167762756</t>
   </si>
   <si>
     <t xml:space="preserve">3.77205109596252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79830288887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79001307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79139518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895998954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350255012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83008217811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495328903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225888252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258671760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752621650696</t>
+    <t xml:space="preserve">3.79830360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7900128364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79139471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350159645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8549530506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225840568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923664093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752740859985</t>
   </si>
   <si>
     <t xml:space="preserve">3.92818307876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94061827659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90883922576904</t>
+    <t xml:space="preserve">3.94061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90883874893188</t>
   </si>
   <si>
     <t xml:space="preserve">3.91091156005859</t>
@@ -2093,118 +2093,118 @@
     <t xml:space="preserve">3.94338130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93440079689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93370985984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92127394676208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91022038459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87567830085754</t>
+    <t xml:space="preserve">3.93440103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93370962142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92127513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847683906555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87567901611328</t>
   </si>
   <si>
     <t xml:space="preserve">3.8556432723999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78379511833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8141930103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281113624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244851112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593750953674</t>
+    <t xml:space="preserve">3.78379535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419229507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8024480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593655586243</t>
   </si>
   <si>
     <t xml:space="preserve">3.85840749740601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83630013465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182667732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8349187374115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452084541321</t>
+    <t xml:space="preserve">3.83629941940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571261405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015175819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85219025611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452108383179</t>
   </si>
   <si>
     <t xml:space="preserve">3.8514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85080814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8888041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93094706535339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068761825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403817176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99934077262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906316757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84804487228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407296180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108646392822</t>
+    <t xml:space="preserve">3.85080718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88880491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93094682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690581321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068785667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99934029579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84804391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844157218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108598709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.0698070526123</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">4.02628469467163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13889217376709</t>
+    <t xml:space="preserve">4.04010105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13889265060425</t>
   </si>
   <si>
     <t xml:space="preserve">4.19347047805786</t>
@@ -2228,25 +2228,25 @@
     <t xml:space="preserve">4.20037889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30884218215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26255559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27637195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30538749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3005518913269</t>
+    <t xml:space="preserve">4.30884265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2625560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30538845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.28397178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19692420959473</t>
+    <t xml:space="preserve">4.19692468643188</t>
   </si>
   <si>
     <t xml:space="preserve">4.20314168930054</t>
@@ -2255,25 +2255,25 @@
     <t xml:space="preserve">4.24183034896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23215770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32473182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42697715759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539213180542</t>
+    <t xml:space="preserve">4.2321572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32473134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42697858810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45392084121704</t>
   </si>
   <si>
     <t xml:space="preserve">4.42145109176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42835903167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42766857147217</t>
+    <t xml:space="preserve">4.42835855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42766952514648</t>
   </si>
   <si>
     <t xml:space="preserve">4.43941307067871</t>
@@ -2282,154 +2282,154 @@
     <t xml:space="preserve">4.49744462966919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45668458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48500967025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49951696395874</t>
+    <t xml:space="preserve">4.45668411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48501062393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49951791763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.5312967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34407615661621</t>
+    <t xml:space="preserve">4.34407567977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.43239879608154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47267389297485</t>
+    <t xml:space="preserve">4.43310499191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47267484664917</t>
   </si>
   <si>
     <t xml:space="preserve">4.41402816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38788414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41332101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35891389846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3801121711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40908193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711744308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33418321609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493740081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28472280502319</t>
+    <t xml:space="preserve">4.38788461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41332054138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35891437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38011169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40908145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711839675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33418273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842372894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28472328186035</t>
   </si>
   <si>
     <t xml:space="preserve">4.29461479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24586057662964</t>
+    <t xml:space="preserve">4.24586009979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.44087791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49316549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40625476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419477462769</t>
+    <t xml:space="preserve">4.49316501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40625524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419525146484</t>
   </si>
   <si>
     <t xml:space="preserve">4.44017171859741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39706993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59208726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59349966049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68606233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65921258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71997737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72068548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76096057891846</t>
+    <t xml:space="preserve">4.39707040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59208679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59350061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68606185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65921211242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72068452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7609601020813</t>
   </si>
   <si>
     <t xml:space="preserve">4.70937967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67758321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58572673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181074142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263698577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65779876708984</t>
+    <t xml:space="preserve">4.67758369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62458992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58572721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263746261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.657799243927</t>
   </si>
   <si>
     <t xml:space="preserve">4.58007478713989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480499267578</t>
+    <t xml:space="preserve">4.60480451583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67404985427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64649391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71361875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215742111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75530767440796</t>
+    <t xml:space="preserve">4.67405033111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64649438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71361923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215837478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7553071975708</t>
   </si>
   <si>
     <t xml:space="preserve">4.82737922668457</t>
@@ -2438,43 +2438,43 @@
     <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81678056716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220541000366</t>
+    <t xml:space="preserve">4.84080457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81678009033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220588684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.69100761413574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77226543426514</t>
+    <t xml:space="preserve">4.77226591110229</t>
   </si>
   <si>
     <t xml:space="preserve">4.83656454086304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78498411178589</t>
+    <t xml:space="preserve">4.78498363494873</t>
   </si>
   <si>
     <t xml:space="preserve">4.81536769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78145027160645</t>
+    <t xml:space="preserve">4.78145170211792</t>
   </si>
   <si>
     <t xml:space="preserve">4.80476856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78992986679077</t>
+    <t xml:space="preserve">4.78993082046509</t>
   </si>
   <si>
     <t xml:space="preserve">4.83161783218384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80830097198486</t>
+    <t xml:space="preserve">4.80830144882202</t>
   </si>
   <si>
     <t xml:space="preserve">4.78357076644897</t>
@@ -2483,64 +2483,64 @@
     <t xml:space="preserve">4.82455253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7659068107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84221696853638</t>
+    <t xml:space="preserve">4.76590633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84221744537354</t>
   </si>
   <si>
     <t xml:space="preserve">4.86129474639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84998989105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8556432723999</t>
+    <t xml:space="preserve">4.84998941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85564279556274</t>
   </si>
   <si>
     <t xml:space="preserve">4.8775463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90368986129761</t>
+    <t xml:space="preserve">4.90369033813477</t>
   </si>
   <si>
     <t xml:space="preserve">4.89733123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.882493019104</t>
+    <t xml:space="preserve">4.92347478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249254226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.87472009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77085304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140371322632</t>
+    <t xml:space="preserve">4.77085256576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85140323638916</t>
   </si>
   <si>
     <t xml:space="preserve">4.84716320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93407392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8577618598938</t>
+    <t xml:space="preserve">4.93407297134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662313461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85776233673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82596492767334</t>
+    <t xml:space="preserve">4.87401390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">4.80759429931641</t>
@@ -2549,52 +2549,52 @@
     <t xml:space="preserve">4.7871036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76943922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83303213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85493564605713</t>
+    <t xml:space="preserve">4.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85493612289429</t>
   </si>
   <si>
     <t xml:space="preserve">4.84433698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71785831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036096572876</t>
+    <t xml:space="preserve">4.66698503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71785879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.75601434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83727169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89309167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95315027236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9333667755127</t>
+    <t xml:space="preserve">4.83727121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89309215545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9531512260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93336725234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.94679164886475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09164190292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973791122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04359340667725</t>
+    <t xml:space="preserve">5.09164142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04359292984009</t>
   </si>
   <si>
     <t xml:space="preserve">4.99695920944214</t>
@@ -2603,28 +2603,28 @@
     <t xml:space="preserve">5.09588050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09517383575439</t>
+    <t xml:space="preserve">5.09517431259155</t>
   </si>
   <si>
     <t xml:space="preserve">5.10577297210693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1085991859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13686418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16159296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24072980880737</t>
+    <t xml:space="preserve">5.10859966278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13686323165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16159343719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24073076248169</t>
   </si>
   <si>
     <t xml:space="preserve">5.22871923446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24355745315552</t>
+    <t xml:space="preserve">5.2435564994812</t>
   </si>
   <si>
     <t xml:space="preserve">5.3778076171875</t>
@@ -2633,109 +2633,109 @@
     <t xml:space="preserve">5.45835781097412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50453662872314</t>
+    <t xml:space="preserve">5.50453615188599</t>
   </si>
   <si>
     <t xml:space="preserve">5.49082708358765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44464874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49804258346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64162635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934892654419</t>
+    <t xml:space="preserve">5.44464921951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49804210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64162588119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53700494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934844970703</t>
   </si>
   <si>
     <t xml:space="preserve">5.77871608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83571767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66760110855103</t>
+    <t xml:space="preserve">5.83571720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66760063171387</t>
   </si>
   <si>
     <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77222299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82272911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602115631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89993333816528</t>
+    <t xml:space="preserve">5.7722225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82272958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89993381500244</t>
   </si>
   <si>
     <t xml:space="preserve">5.91652774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91147708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86746406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92157888412476</t>
+    <t xml:space="preserve">5.91147756576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86746454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9215784072876</t>
   </si>
   <si>
     <t xml:space="preserve">5.97208642959595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05650520324707</t>
+    <t xml:space="preserve">6.05650472640991</t>
   </si>
   <si>
     <t xml:space="preserve">6.10917568206787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18060779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08464479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09258079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386854171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975372314453</t>
+    <t xml:space="preserve">6.18060731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08464431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09258127212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152456283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975419998169</t>
   </si>
   <si>
     <t xml:space="preserve">5.71161413192749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46629524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51247310638428</t>
+    <t xml:space="preserve">5.46629476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51247262954712</t>
   </si>
   <si>
     <t xml:space="preserve">5.62286615371704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94539022445679</t>
+    <t xml:space="preserve">5.94538974761963</t>
   </si>
   <si>
     <t xml:space="preserve">5.87684440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69357585906982</t>
+    <t xml:space="preserve">5.69357633590698</t>
   </si>
   <si>
     <t xml:space="preserve">5.1271767616272</t>
@@ -2744,40 +2744,40 @@
     <t xml:space="preserve">4.83712291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70436191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77070426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426502227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1271390914917</t>
+    <t xml:space="preserve">4.70436143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77070450782776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426454544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830178260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12713861465454</t>
   </si>
   <si>
     <t xml:space="preserve">4.24979972839355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20650672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24907732009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30896425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5535626411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54562520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53047323226929</t>
+    <t xml:space="preserve">4.20650720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24907684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30896520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55356216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54562568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5304741859436</t>
   </si>
   <si>
     <t xml:space="preserve">4.44100427627563</t>
@@ -2795,37 +2795,37 @@
     <t xml:space="preserve">4.43378877639771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3789529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43018054962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59973955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480291366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65601873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65168952941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47852325439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50882863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47996520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46770048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33277463912964</t>
+    <t xml:space="preserve">4.37895202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59974050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65601921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65169048309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47852277755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50882720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47996616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46770095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">4.31834363937378</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">4.27577352523804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25701427459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37967395782471</t>
+    <t xml:space="preserve">4.25701379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37967443466187</t>
   </si>
   <si>
     <t xml:space="preserve">4.43739604949951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52397871017456</t>
+    <t xml:space="preserve">4.52397918701172</t>
   </si>
   <si>
     <t xml:space="preserve">4.4994478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39266061782837</t>
+    <t xml:space="preserve">4.33421754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39266157150269</t>
   </si>
   <si>
     <t xml:space="preserve">4.37750911712646</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">4.46481418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.473473072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688850402832</t>
+    <t xml:space="preserve">4.47347211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688945770264</t>
   </si>
   <si>
     <t xml:space="preserve">4.3508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24547052383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672302246094</t>
+    <t xml:space="preserve">4.24547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672206878662</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
@@ -2882,43 +2882,43 @@
     <t xml:space="preserve">4.35586309432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51099109649658</t>
+    <t xml:space="preserve">4.51099157333374</t>
   </si>
   <si>
     <t xml:space="preserve">4.56727123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62499380111694</t>
+    <t xml:space="preserve">4.62499284744263</t>
   </si>
   <si>
     <t xml:space="preserve">4.69714641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70147514343262</t>
+    <t xml:space="preserve">4.70147562026978</t>
   </si>
   <si>
     <t xml:space="preserve">4.75198268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926330566406</t>
+    <t xml:space="preserve">4.90061664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926378250122</t>
   </si>
   <si>
     <t xml:space="preserve">5.04925155639648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18706369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434478759766</t>
+    <t xml:space="preserve">5.18706321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434526443481</t>
   </si>
   <si>
     <t xml:space="preserve">5.40063571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46773862838745</t>
+    <t xml:space="preserve">5.46773815155029</t>
   </si>
   <si>
     <t xml:space="preserve">5.46701622009277</t>
@@ -2930,34 +2930,34 @@
     <t xml:space="preserve">5.42011690139771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28663396835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29962205886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188774108887</t>
+    <t xml:space="preserve">5.28663444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29962253570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188821792603</t>
   </si>
   <si>
     <t xml:space="preserve">5.4590802192688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361158370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63585329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50092792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906799316406</t>
+    <t xml:space="preserve">5.41506671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361253738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63585376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906847000122</t>
   </si>
   <si>
     <t xml:space="preserve">5.5117506980896</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">5.57308101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5398907661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55720806121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73398113250732</t>
+    <t xml:space="preserve">5.53989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5572075843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73398160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.68131065368652</t>
@@ -2984,46 +2984,46 @@
     <t xml:space="preserve">5.75418376922607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83427429199219</t>
+    <t xml:space="preserve">5.83427476882935</t>
   </si>
   <si>
     <t xml:space="preserve">5.72604513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89416027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9547700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08031558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12669610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13258647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246212005615</t>
+    <t xml:space="preserve">5.86024951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232431411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89416074752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95476961135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08031511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12669563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13258600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246164321899</t>
   </si>
   <si>
     <t xml:space="preserve">5.98828983306885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84841012954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83147764205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601810455322</t>
+    <t xml:space="preserve">5.84841108322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83147859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601715087891</t>
   </si>
   <si>
     <t xml:space="preserve">5.87123250961304</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">5.69601583480835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69012641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362512588501</t>
+    <t xml:space="preserve">5.69012689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">5.79319524765015</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">5.79024982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86313486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97062063217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89552783966064</t>
+    <t xml:space="preserve">5.86313438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062015533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89552736282349</t>
   </si>
   <si>
     <t xml:space="preserve">5.80497455596924</t>
@@ -3068,64 +3068,64 @@
     <t xml:space="preserve">5.74828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70926761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69159889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79098701477051</t>
+    <t xml:space="preserve">5.73356246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70926809310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69159841537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79098749160767</t>
   </si>
   <si>
     <t xml:space="preserve">5.74534177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74092388153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6076717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58705711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52448034286499</t>
+    <t xml:space="preserve">5.74092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58705806732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52448081970215</t>
   </si>
   <si>
     <t xml:space="preserve">5.63049411773682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58043193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45675039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59000253677368</t>
+    <t xml:space="preserve">5.58043241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4567494392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000301361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.50165796279907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63270282745361</t>
+    <t xml:space="preserve">5.6327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">5.5981011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63932800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5664439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650657653809</t>
+    <t xml:space="preserve">5.639328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56644487380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650609970093</t>
   </si>
   <si>
     <t xml:space="preserve">5.5767502784729</t>
@@ -3137,43 +3137,43 @@
     <t xml:space="preserve">5.46263933181763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34411001205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975477218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582845687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.400062084198</t>
+    <t xml:space="preserve">5.3441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38975524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582941055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40006256103516</t>
   </si>
   <si>
     <t xml:space="preserve">5.48325300216675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52153587341309</t>
+    <t xml:space="preserve">5.52153539657593</t>
   </si>
   <si>
     <t xml:space="preserve">5.46116733551025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49797630310059</t>
+    <t xml:space="preserve">5.49797677993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.4434986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42141151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59221124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55613708496094</t>
+    <t xml:space="preserve">5.42141199111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59221172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5561375617981</t>
   </si>
   <si>
     <t xml:space="preserve">5.53920459747314</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">5.6592059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67761135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429607391357</t>
+    <t xml:space="preserve">5.67761087417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429655075073</t>
   </si>
   <si>
     <t xml:space="preserve">5.54141283035278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5819034576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53257846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472499847412</t>
+    <t xml:space="preserve">5.49871349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58190393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5325779914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472547531128</t>
   </si>
   <si>
     <t xml:space="preserve">5.57233333587646</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">5.4442343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11662244796753</t>
+    <t xml:space="preserve">5.11662292480469</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705184936523</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">5.03122329711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31319046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42435646057129</t>
+    <t xml:space="preserve">5.14312648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31318950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42435693740845</t>
   </si>
   <si>
     <t xml:space="preserve">5.6032543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92718362808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92423963546753</t>
+    <t xml:space="preserve">5.92718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92424011230469</t>
   </si>
   <si>
     <t xml:space="preserve">6.04571342468262</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">5.95516014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97209310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97945499420166</t>
+    <t xml:space="preserve">5.97209358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
     <t xml:space="preserve">6.01037549972534</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">6.06117343902588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19737195968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24817085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23565435409546</t>
+    <t xml:space="preserve">6.19737100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24817037582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23565483093262</t>
   </si>
   <si>
     <t xml:space="preserve">6.25921297073364</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">6.16203355789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1252236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09724807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04350471496582</t>
+    <t xml:space="preserve">6.12522315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09724760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04350423812866</t>
   </si>
   <si>
     <t xml:space="preserve">6.04129648208618</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">6.0228910446167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97798252105713</t>
+    <t xml:space="preserve">6.00743103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97798204421997</t>
   </si>
   <si>
     <t xml:space="preserve">6.04424142837524</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">5.92571210861206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92276668548584</t>
+    <t xml:space="preserve">5.922767162323</t>
   </si>
   <si>
     <t xml:space="preserve">6.00890302658081</t>
@@ -3326,25 +3326,25 @@
     <t xml:space="preserve">6.22608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18043994903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57357168197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46166944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57062816619873</t>
+    <t xml:space="preserve">6.18043947219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57357263565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756113052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57062768936157</t>
   </si>
   <si>
     <t xml:space="preserve">6.50289678573608</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">6.52203750610352</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44768476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44242858886719</t>
+    <t xml:space="preserve">6.4476842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43942451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44242763519287</t>
   </si>
   <si>
     <t xml:space="preserve">6.35305404663086</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">6.25992488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30874156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932676315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30949306488037</t>
+    <t xml:space="preserve">6.3087420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30949401855469</t>
   </si>
   <si>
     <t xml:space="preserve">6.15177488327026</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">6.17430591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15853357315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42290067672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42590427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34404134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3838472366333</t>
+    <t xml:space="preserve">6.15853452682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42290115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42590379714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34404182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38384771347046</t>
   </si>
   <si>
     <t xml:space="preserve">6.22162199020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24715709686279</t>
+    <t xml:space="preserve">6.24715757369995</t>
   </si>
   <si>
     <t xml:space="preserve">6.35530662536621</t>
@@ -3416,19 +3416,19 @@
     <t xml:space="preserve">6.35756015777588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23589181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15553045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06615591049194</t>
+    <t xml:space="preserve">6.23589134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15552997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06615543365479</t>
   </si>
   <si>
     <t xml:space="preserve">5.99105215072632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94824266433716</t>
+    <t xml:space="preserve">5.94824314117432</t>
   </si>
   <si>
     <t xml:space="preserve">5.88815975189209</t>
@@ -3440,22 +3440,22 @@
     <t xml:space="preserve">5.9685206413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85962009429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72743654251099</t>
+    <t xml:space="preserve">5.85961961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72743701934814</t>
   </si>
   <si>
     <t xml:space="preserve">5.89041328430176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91294431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07141399383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568334579468</t>
+    <t xml:space="preserve">5.91294384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07141351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568382263184</t>
   </si>
   <si>
     <t xml:space="preserve">6.1697998046875</t>
@@ -3467,43 +3467,43 @@
     <t xml:space="preserve">6.19984149932861</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14426422119141</t>
+    <t xml:space="preserve">6.14426469802856</t>
   </si>
   <si>
     <t xml:space="preserve">6.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12999486923218</t>
+    <t xml:space="preserve">6.12999439239502</t>
   </si>
   <si>
     <t xml:space="preserve">6.05639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2381443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826948165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34028673171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902050018311</t>
+    <t xml:space="preserve">6.23814487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902002334595</t>
   </si>
   <si>
     <t xml:space="preserve">6.38910388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33352708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37858915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502960205078</t>
+    <t xml:space="preserve">6.33352661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37858867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502912521362</t>
   </si>
   <si>
     <t xml:space="preserve">6.42440319061279</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">6.44843626022339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49725294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444345474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44393014907837</t>
+    <t xml:space="preserve">6.49725341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392967224121</t>
   </si>
   <si>
     <t xml:space="preserve">6.47472286224365</t>
@@ -3527,13 +3527,13 @@
     <t xml:space="preserve">6.39060592651367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44468116760254</t>
+    <t xml:space="preserve">6.4446816444397</t>
   </si>
   <si>
     <t xml:space="preserve">6.50326204299927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50551509857178</t>
+    <t xml:space="preserve">6.50551462173462</t>
   </si>
   <si>
     <t xml:space="preserve">6.42515420913696</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54757404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56034088134766</t>
+    <t xml:space="preserve">6.54757356643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5603404045105</t>
   </si>
   <si>
     <t xml:space="preserve">6.48899269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34479188919067</t>
+    <t xml:space="preserve">6.34479236602783</t>
   </si>
   <si>
     <t xml:space="preserve">6.26217794418335</t>
@@ -3572,55 +3572,55 @@
     <t xml:space="preserve">6.20960474014282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00231742858887</t>
+    <t xml:space="preserve">6.21411085128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00231838226318</t>
   </si>
   <si>
     <t xml:space="preserve">6.07742166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16153955459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12623929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10445928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98279047012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06390380859375</t>
+    <t xml:space="preserve">6.16153907775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12623977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10445976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98279094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06390333175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.14952182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12774229049683</t>
+    <t xml:space="preserve">6.12774181365967</t>
   </si>
   <si>
     <t xml:space="preserve">6.13374996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05038452148438</t>
+    <t xml:space="preserve">6.11872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572408676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05038404464722</t>
   </si>
   <si>
     <t xml:space="preserve">5.99405670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92721366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95650482177734</t>
+    <t xml:space="preserve">5.92721319198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95650434494019</t>
   </si>
   <si>
     <t xml:space="preserve">6.01057958602905</t>
@@ -3629,40 +3629,40 @@
     <t xml:space="preserve">6.01733875274658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01808977127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97903537750244</t>
+    <t xml:space="preserve">6.01808929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9790358543396</t>
   </si>
   <si>
     <t xml:space="preserve">6.02484941482544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08493328094482</t>
+    <t xml:space="preserve">6.08493232727051</t>
   </si>
   <si>
     <t xml:space="preserve">6.06840944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829872131348</t>
+    <t xml:space="preserve">6.16829776763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0676589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04888248443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09845066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98654651641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03386163711548</t>
+    <t xml:space="preserve">6.04888200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09845018386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08943891525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9865460395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03386116027832</t>
   </si>
   <si>
     <t xml:space="preserve">6.01508522033691</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">5.98879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03686618804932</t>
+    <t xml:space="preserve">6.03686571121216</t>
   </si>
   <si>
     <t xml:space="preserve">5.88215112686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89491939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89642095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93772888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96401500701904</t>
+    <t xml:space="preserve">5.89491891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89642143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93772792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96401453018188</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
@@ -3695,37 +3695,37 @@
     <t xml:space="preserve">5.951247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05188608169556</t>
+    <t xml:space="preserve">6.05489110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05188655853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.02635145187378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9572548866272</t>
+    <t xml:space="preserve">5.95725536346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8444390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8513560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00277042388916</t>
+    <t xml:space="preserve">5.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85135555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.002769947052</t>
   </si>
   <si>
     <t xml:space="preserve">6.1157546043396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18723487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21106147766113</t>
+    <t xml:space="preserve">6.18723440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">6.11959743499756</t>
@@ -3734,19 +3734,19 @@
     <t xml:space="preserve">6.191077709198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16033363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97971200942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94819927215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92052984237671</t>
+    <t xml:space="preserve">6.16033315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97971248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9136118888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92053031921387</t>
   </si>
   <si>
     <t xml:space="preserve">5.95819187164307</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">5.96357202529907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99354648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98586177825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02044820785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02890300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348896026611</t>
+    <t xml:space="preserve">5.9935474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98586130142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02044916152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02890348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348943710327</t>
   </si>
   <si>
     <t xml:space="preserve">6.03120851516724</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">5.97740650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03735780715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08885383605957</t>
+    <t xml:space="preserve">6.03735685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08885431289673</t>
   </si>
   <si>
     <t xml:space="preserve">6.149573802948</t>
@@ -3788,64 +3788,64 @@
     <t xml:space="preserve">6.01967906951904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96510887145996</t>
+    <t xml:space="preserve">5.96510934829712</t>
   </si>
   <si>
     <t xml:space="preserve">5.90131568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90208339691162</t>
+    <t xml:space="preserve">5.90208387374878</t>
   </si>
   <si>
     <t xml:space="preserve">5.95511722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93129110336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99815845489502</t>
+    <t xml:space="preserve">5.93129062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99815893173218</t>
   </si>
   <si>
     <t xml:space="preserve">5.93513441085815</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92975330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77833890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756237030029</t>
+    <t xml:space="preserve">5.92975378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756284713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.66842889785767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76373624801636</t>
+    <t xml:space="preserve">5.7637357711792</t>
   </si>
   <si>
     <t xml:space="preserve">5.71454524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39941883087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38097286224365</t>
+    <t xml:space="preserve">5.3994197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38097190856934</t>
   </si>
   <si>
     <t xml:space="preserve">5.34869146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25722789764404</t>
+    <t xml:space="preserve">5.25722742080688</t>
   </si>
   <si>
     <t xml:space="preserve">5.30257511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33408832550049</t>
+    <t xml:space="preserve">5.33408784866333</t>
   </si>
   <si>
     <t xml:space="preserve">5.44092416763306</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">5.17191362380981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17883014678955</t>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
@@ -3878,43 +3878,43 @@
     <t xml:space="preserve">5.30564975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31794738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18651676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24954128265381</t>
+    <t xml:space="preserve">5.31794786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18651723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24954175949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.30795526504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44246006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54160976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51317167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708826065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165105819702</t>
+    <t xml:space="preserve">5.44246101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54161024093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5131721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">5.54622220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58772611618042</t>
+    <t xml:space="preserve">5.58772659301758</t>
   </si>
   <si>
     <t xml:space="preserve">5.56159400939941</t>
@@ -3923,40 +3923,40 @@
     <t xml:space="preserve">5.5992546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55775022506714</t>
+    <t xml:space="preserve">5.55775117874146</t>
   </si>
   <si>
     <t xml:space="preserve">5.57696533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60617208480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53008079528809</t>
+    <t xml:space="preserve">5.57389163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60617256164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5300817489624</t>
   </si>
   <si>
     <t xml:space="preserve">5.45245218276978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5031795501709</t>
+    <t xml:space="preserve">5.50318050384521</t>
   </si>
   <si>
     <t xml:space="preserve">5.45629501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4954948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44707250595093</t>
+    <t xml:space="preserve">5.49549436569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44707202911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.4324688911438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41248512268066</t>
+    <t xml:space="preserve">5.41248464584351</t>
   </si>
   <si>
     <t xml:space="preserve">5.34177398681641</t>
@@ -3968,58 +3968,58 @@
     <t xml:space="preserve">5.30872392654419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41479063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49472522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21802949905396</t>
+    <t xml:space="preserve">5.41479110717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49472618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23878145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21802997589111</t>
   </si>
   <si>
     <t xml:space="preserve">5.15500402450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19189739227295</t>
+    <t xml:space="preserve">5.19189691543579</t>
   </si>
   <si>
     <t xml:space="preserve">5.0650782585144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01588726043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16730165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23493814468384</t>
+    <t xml:space="preserve">5.01588678359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16730117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.234938621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1511607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14193773269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07583808898926</t>
+    <t xml:space="preserve">5.15116119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14193820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0758376121521</t>
   </si>
   <si>
     <t xml:space="preserve">5.0927472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14731788635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1096568107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18497943878174</t>
+    <t xml:space="preserve">5.1473183631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18497896194458</t>
   </si>
   <si>
     <t xml:space="preserve">5.1134991645813</t>
@@ -4043,109 +4043,109 @@
     <t xml:space="preserve">5.38788986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555881500244</t>
+    <t xml:space="preserve">5.4155592918396</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34100532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32640218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32717037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025337219238</t>
+    <t xml:space="preserve">5.47243547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34100484848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3264012336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32717084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.35022830963135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23186445236206</t>
+    <t xml:space="preserve">5.23186349868774</t>
   </si>
   <si>
     <t xml:space="preserve">5.27490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38250923156738</t>
+    <t xml:space="preserve">5.38250970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30718755722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26766967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26766920089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26845932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30718660354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41546487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33642911911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35934925079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41704511642456</t>
+    <t xml:space="preserve">5.41546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33643007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35935020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41704559326172</t>
   </si>
   <si>
     <t xml:space="preserve">5.41309356689453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35776901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24712038040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08272790908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00369310379028</t>
+    <t xml:space="preserve">5.35776948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24711990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08272838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00369262695312</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908435821533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08351802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05348491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99499940872192</t>
+    <t xml:space="preserve">5.08351898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05348539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99499893188477</t>
   </si>
   <si>
     <t xml:space="preserve">5.08114767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14516496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1230354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08588981628418</t>
+    <t xml:space="preserve">5.14516592025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12303590774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08588933944702</t>
   </si>
   <si>
     <t xml:space="preserve">4.97603130340576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01396751403809</t>
+    <t xml:space="preserve">5.01396799087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.99025726318359</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">4.7065224647522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127412796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
+    <t xml:space="preserve">4.48127317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.52237129211426</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">4.52711343765259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59903478622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60456800460815</t>
+    <t xml:space="preserve">4.59903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.604567527771</t>
   </si>
   <si>
     <t xml:space="preserve">4.60298681259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52079105377197</t>
+    <t xml:space="preserve">4.52079010009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.55240535736084</t>
@@ -4205,19 +4205,19 @@
     <t xml:space="preserve">4.60219669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51209735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566612243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81875228881836</t>
+    <t xml:space="preserve">4.51209688186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">4.79583215713501</t>
@@ -4226,67 +4226,67 @@
     <t xml:space="preserve">4.82428455352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.829026222229</t>
+    <t xml:space="preserve">4.82902669906616</t>
   </si>
   <si>
     <t xml:space="preserve">4.92544889450073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90647983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8748664855957</t>
+    <t xml:space="preserve">4.90648078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.98709630966187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8985767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90173816680908</t>
+    <t xml:space="preserve">4.96891832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89857721328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90173864364624</t>
   </si>
   <si>
     <t xml:space="preserve">4.88514137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87249517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75236320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81558990478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79978275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91596460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91438388824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87881803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93888473510742</t>
+    <t xml:space="preserve">4.87249565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7523627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82349443435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81559085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79978370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91596412658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91438436508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87881851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93888521194458</t>
   </si>
   <si>
     <t xml:space="preserve">4.89541530609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78555727005005</t>
+    <t xml:space="preserve">4.78555679321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.74841070175171</t>
@@ -4295,49 +4295,49 @@
     <t xml:space="preserve">4.64171409606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6172137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7262806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61405181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69229555130005</t>
+    <t xml:space="preserve">4.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6140513420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69229602813721</t>
   </si>
   <si>
     <t xml:space="preserve">4.73181343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74999141693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69308614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69150543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83930063247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84720468521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84641361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88751173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88909292221069</t>
+    <t xml:space="preserve">4.74999189376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69150638580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83930015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84720420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84641408920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88909339904785</t>
   </si>
   <si>
     <t xml:space="preserve">4.87012481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77686309814453</t>
+    <t xml:space="preserve">4.77686357498169</t>
   </si>
   <si>
     <t xml:space="preserve">4.6820216178894</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">4.7057318687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66700553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76500749588013</t>
+    <t xml:space="preserve">4.66700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76500797271729</t>
   </si>
   <si>
     <t xml:space="preserve">4.73260402679443</t>
@@ -4364,22 +4364,22 @@
     <t xml:space="preserve">4.33189725875854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25839567184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39117383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26787948608398</t>
+    <t xml:space="preserve">4.25839424133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39117336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26787900924683</t>
   </si>
   <si>
     <t xml:space="preserve">4.30107355117798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33822107315063</t>
+    <t xml:space="preserve">4.33822059631348</t>
   </si>
   <si>
     <t xml:space="preserve">4.31925249099731</t>
@@ -4391,10 +4391,10 @@
     <t xml:space="preserve">4.28526735305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3571891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2749924659729</t>
+    <t xml:space="preserve">4.35718870162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27499341964722</t>
   </si>
   <si>
     <t xml:space="preserve">4.32794570922852</t>
@@ -4403,43 +4403,43 @@
     <t xml:space="preserve">4.26945972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12561702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17382860183716</t>
+    <t xml:space="preserve">4.12561655044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.173828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09084224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15960168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15090751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14300489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0924220085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05211448669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8213324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.951740026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03307485580444</t>
+    <t xml:space="preserve">4.09084177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15960216522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15090799331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14300441741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09242248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05211400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82133269309998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95173978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0330753326416</t>
   </si>
   <si>
     <t xml:space="preserve">4.08606576919556</t>
@@ -4448,25 +4448,25 @@
     <t xml:space="preserve">3.95831251144409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90080285072327</t>
+    <t xml:space="preserve">3.90080261230469</t>
   </si>
   <si>
     <t xml:space="preserve">3.88108491897583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90244626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89053344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818402290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06922483444214</t>
+    <t xml:space="preserve">3.90244603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89053297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683581352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9381844997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06922388076782</t>
   </si>
   <si>
     <t xml:space="preserve">3.99610447883606</t>
@@ -4475,19 +4475,19 @@
     <t xml:space="preserve">4.00514221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03636169433594</t>
+    <t xml:space="preserve">4.0363621711731</t>
   </si>
   <si>
     <t xml:space="preserve">4.06758165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13412857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11441040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09756851196289</t>
+    <t xml:space="preserve">4.13412809371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11441087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09756898880005</t>
   </si>
   <si>
     <t xml:space="preserve">4.10783767700195</t>
@@ -4496,16 +4496,16 @@
     <t xml:space="preserve">4.13659238815308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18753051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18342256546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11030244827271</t>
+    <t xml:space="preserve">4.19163846969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18752956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18342208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11030292510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.05443620681763</t>
@@ -4514,22 +4514,22 @@
     <t xml:space="preserve">4.05854415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06265211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06347322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97022533416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94639992713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95461511611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85767006874084</t>
+    <t xml:space="preserve">4.06265163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06347274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97022557258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94640016555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95461535453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.857670545578</t>
   </si>
   <si>
     <t xml:space="preserve">3.81412720680237</t>
@@ -4538,19 +4538,19 @@
     <t xml:space="preserve">3.90614318847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86136794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84288144111633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9484543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98871064186096</t>
+    <t xml:space="preserve">3.86136746406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84288215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90162491798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94845414161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98871088027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.10085439682007</t>
@@ -4571,22 +4571,22 @@
     <t xml:space="preserve">4.05073881149292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97679781913757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419165611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97186827659607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81535935401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53438401222229</t>
+    <t xml:space="preserve">3.97679758071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97186851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81535983085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53438377380371</t>
   </si>
   <si>
     <t xml:space="preserve">3.54835033416748</t>
@@ -4604,16 +4604,16 @@
     <t xml:space="preserve">3.66706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55040431022644</t>
+    <t xml:space="preserve">3.55040407180786</t>
   </si>
   <si>
     <t xml:space="preserve">3.42593717575073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38609051704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44154715538025</t>
+    <t xml:space="preserve">3.38609075546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44154691696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.34870982170105</t>
@@ -4622,13 +4622,13 @@
     <t xml:space="preserve">3.28873491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34542298316956</t>
+    <t xml:space="preserve">3.34542322158813</t>
   </si>
   <si>
     <t xml:space="preserve">3.37910771369934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46290755271912</t>
+    <t xml:space="preserve">3.4629077911377</t>
   </si>
   <si>
     <t xml:space="preserve">3.49823474884033</t>
@@ -4637,31 +4637,31 @@
     <t xml:space="preserve">3.51918482780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48426842689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44606518745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52740001678467</t>
+    <t xml:space="preserve">3.48426818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4460654258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52740049362183</t>
   </si>
   <si>
     <t xml:space="preserve">3.59764456748962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60257387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71512866020203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6740505695343</t>
+    <t xml:space="preserve">3.60257363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71512889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">3.71266412734985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72950625419617</t>
+    <t xml:space="preserve">3.72950649261475</t>
   </si>
   <si>
     <t xml:space="preserve">3.77304935455322</t>
@@ -4670,16 +4670,16 @@
     <t xml:space="preserve">3.7578501701355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84452533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037939071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95913410186768</t>
+    <t xml:space="preserve">3.84452605247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217638969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913434028625</t>
   </si>
   <si>
     <t xml:space="preserve">4.11605405807495</t>
@@ -4691,16 +4691,16 @@
     <t xml:space="preserve">4.17274188995361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19821071624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22203636169434</t>
+    <t xml:space="preserve">4.1982102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22203540802002</t>
   </si>
   <si>
     <t xml:space="preserve">4.23682451248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17767143249512</t>
+    <t xml:space="preserve">4.17767095565796</t>
   </si>
   <si>
     <t xml:space="preserve">4.15959692001343</t>
@@ -4709,22 +4709,22 @@
     <t xml:space="preserve">4.2335376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518085479736</t>
+    <t xml:space="preserve">4.23518133163452</t>
   </si>
   <si>
     <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19492435455322</t>
+    <t xml:space="preserve">4.19492387771606</t>
   </si>
   <si>
     <t xml:space="preserve">4.21792793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31323003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32719707489014</t>
+    <t xml:space="preserve">4.31322908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32719612121582</t>
   </si>
   <si>
     <t xml:space="preserve">4.33623361587524</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">4.29022598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27050828933716</t>
+    <t xml:space="preserve">4.2705078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.31158685684204</t>
@@ -4751,16 +4751,16 @@
     <t xml:space="preserve">4.31487321853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1530237197876</t>
+    <t xml:space="preserve">4.15302419662476</t>
   </si>
   <si>
     <t xml:space="preserve">4.14891624450684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1456298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14645195007324</t>
+    <t xml:space="preserve">4.14563035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14645099639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.21464157104492</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">4.16863346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19081687927246</t>
+    <t xml:space="preserve">4.1908164024353</t>
   </si>
   <si>
     <t xml:space="preserve">4.17192029953003</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">4.14809465408325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13248538970947</t>
+    <t xml:space="preserve">4.13248491287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.24832630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35430812835693</t>
+    <t xml:space="preserve">4.35430860519409</t>
   </si>
   <si>
     <t xml:space="preserve">4.50794124603271</t>
@@ -4793,7 +4793,7 @@
     <t xml:space="preserve">4.50054740905762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6016001701355</t>
+    <t xml:space="preserve">4.60159921646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.59995698928833</t>
@@ -4802,22 +4802,22 @@
     <t xml:space="preserve">4.54819822311401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62542533874512</t>
+    <t xml:space="preserve">4.62542581558228</t>
   </si>
   <si>
     <t xml:space="preserve">4.68868637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70593929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77166414260864</t>
+    <t xml:space="preserve">4.70593881607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7716646194458</t>
   </si>
   <si>
     <t xml:space="preserve">4.73222970962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73551607131958</t>
+    <t xml:space="preserve">4.73551559448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.64760828018188</t>
@@ -4826,40 +4826,40 @@
     <t xml:space="preserve">4.6418571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65548467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68103647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66570568084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66996383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62737798690796</t>
+    <t xml:space="preserve">4.65548419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6810359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66570520401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66996335983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67166709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6273775100708</t>
   </si>
   <si>
     <t xml:space="preserve">4.59160566329956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110269546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58394002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56690645217896</t>
+    <t xml:space="preserve">4.49110317230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58394050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5669059753418</t>
   </si>
   <si>
     <t xml:space="preserve">4.58138513565063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56435108184814</t>
+    <t xml:space="preserve">4.56435060501099</t>
   </si>
   <si>
     <t xml:space="preserve">4.55327844619751</t>
@@ -4868,37 +4868,37 @@
     <t xml:space="preserve">4.54816818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60864019393921</t>
+    <t xml:space="preserve">4.60863971710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.60182619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58223724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58819913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57712697982788</t>
+    <t xml:space="preserve">4.58223676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5881986618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57712602615356</t>
   </si>
   <si>
     <t xml:space="preserve">4.55924081802368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55668544769287</t>
+    <t xml:space="preserve">4.55668497085571</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48003101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45788669586182</t>
+    <t xml:space="preserve">4.46214437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48003053665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4578857421875</t>
   </si>
   <si>
     <t xml:space="preserve">4.51920986175537</t>
@@ -4910,10 +4910,10 @@
     <t xml:space="preserve">4.42892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48428964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51495122909546</t>
+    <t xml:space="preserve">4.48428869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5149507522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.54305744171143</t>
@@ -4925,34 +4925,34 @@
     <t xml:space="preserve">4.5311336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4519248008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5686092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810674667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51069259643555</t>
+    <t xml:space="preserve">4.53028154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53624391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45192432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56860876083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810626983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51069211959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.50302743911743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58905076980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66740846633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68784999847412</t>
+    <t xml:space="preserve">4.58904981613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66740798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68784952163696</t>
   </si>
   <si>
     <t xml:space="preserve">4.69040489196777</t>
@@ -4970,19 +4970,19 @@
     <t xml:space="preserve">4.69125699996948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77813196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79261112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77131843566895</t>
+    <t xml:space="preserve">4.77813148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79261064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77131795883179</t>
   </si>
   <si>
     <t xml:space="preserve">4.75683879852295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82242155075073</t>
+    <t xml:space="preserve">4.82242107391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.98169231414795</t>
@@ -4991,31 +4991,31 @@
     <t xml:space="preserve">5.02853631973267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10348701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90333461761475</t>
+    <t xml:space="preserve">5.10348749160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90333414077759</t>
   </si>
   <si>
     <t xml:space="preserve">4.86159992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8718204498291</t>
+    <t xml:space="preserve">4.87181997299194</t>
   </si>
   <si>
     <t xml:space="preserve">4.90503740310669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97402715682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05153226852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13414859771729</t>
+    <t xml:space="preserve">4.94762372970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97402667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05153274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13414907455444</t>
   </si>
   <si>
     <t xml:space="preserve">5.15799760818481</t>
@@ -5024,25 +5024,25 @@
     <t xml:space="preserve">5.18695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2508339881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979326248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1937689781189</t>
+    <t xml:space="preserve">5.25083494186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19376945495605</t>
   </si>
   <si>
     <t xml:space="preserve">5.19462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18440055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24827909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21165561676025</t>
+    <t xml:space="preserve">5.18440103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2482795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21165609359741</t>
   </si>
   <si>
     <t xml:space="preserve">5.20569324493408</t>
@@ -5057,49 +5057,49 @@
     <t xml:space="preserve">5.15970087051392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12563180923462</t>
+    <t xml:space="preserve">5.12563228607178</t>
   </si>
   <si>
     <t xml:space="preserve">5.12733554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09156322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02598142623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11796617507935</t>
+    <t xml:space="preserve">5.09156370162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02598094940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1179666519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.14351797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13670492172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080491065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00809574127197</t>
+    <t xml:space="preserve">5.13670444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08049154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00809526443481</t>
   </si>
   <si>
     <t xml:space="preserve">5.07112216949463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07367706298828</t>
+    <t xml:space="preserve">5.07367753982544</t>
   </si>
   <si>
     <t xml:space="preserve">5.12052154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98935747146606</t>
+    <t xml:space="preserve">4.98935699462891</t>
   </si>
   <si>
     <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14947938919067</t>
+    <t xml:space="preserve">5.14948034286499</t>
   </si>
   <si>
     <t xml:space="preserve">5.10774612426758</t>
@@ -5108,13 +5108,13 @@
     <t xml:space="preserve">5.15288734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1733283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17247581481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20484161376953</t>
+    <t xml:space="preserve">5.17332792282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17247676849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20484209060669</t>
   </si>
   <si>
     <t xml:space="preserve">5.16992139816284</t>
@@ -5135,25 +5135,25 @@
     <t xml:space="preserve">5.22698640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25338983535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31471252441406</t>
+    <t xml:space="preserve">5.23635530471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25339031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31471300125122</t>
   </si>
   <si>
     <t xml:space="preserve">5.3990330696106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14266681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19291734695435</t>
+    <t xml:space="preserve">5.28916215896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14266633987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1929178237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.17503213882446</t>
@@ -5165,16 +5165,16 @@
     <t xml:space="preserve">5.30619621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39136743545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31300926208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34622621536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34452342987061</t>
+    <t xml:space="preserve">5.39136791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31301021575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34622669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34452295303345</t>
   </si>
   <si>
     <t xml:space="preserve">5.36070585250854</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">5.45012617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4703540802002</t>
+    <t xml:space="preserve">5.47035360336304</t>
   </si>
   <si>
     <t xml:space="preserve">5.55038642883301</t>
@@ -5198,13 +5198,13 @@
     <t xml:space="preserve">5.51872539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5160870552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4615592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34370946884155</t>
+    <t xml:space="preserve">5.51608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46155977249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34370994567871</t>
   </si>
   <si>
     <t xml:space="preserve">5.28214597702026</t>
@@ -5213,10 +5213,10 @@
     <t xml:space="preserve">5.22673892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21706485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20914936065674</t>
+    <t xml:space="preserve">5.21706438064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20914888381958</t>
   </si>
   <si>
     <t xml:space="preserve">5.28302526473999</t>
@@ -5225,7 +5225,7 @@
     <t xml:space="preserve">5.36129903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32436037063599</t>
+    <t xml:space="preserve">5.32436084747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.23553371429443</t>
@@ -5237,16 +5237,16 @@
     <t xml:space="preserve">5.21002864837646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2671947479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33227634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34195041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37273216247559</t>
+    <t xml:space="preserve">5.26719522476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33227682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34194993972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37273263931274</t>
   </si>
   <si>
     <t xml:space="preserve">5.39120149612427</t>
@@ -5255,22 +5255,22 @@
     <t xml:space="preserve">5.4589204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43957233428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41406774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40791130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39383935928345</t>
+    <t xml:space="preserve">5.43957281112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4140682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40791177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39383983612061</t>
   </si>
   <si>
     <t xml:space="preserve">5.36745548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46067953109741</t>
+    <t xml:space="preserve">5.46068048477173</t>
   </si>
   <si>
     <t xml:space="preserve">5.44484901428223</t>
@@ -5279,10 +5279,10 @@
     <t xml:space="preserve">5.45188522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38768291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56006097793579</t>
+    <t xml:space="preserve">5.38768339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56006145477295</t>
   </si>
   <si>
     <t xml:space="preserve">5.52752017974854</t>
@@ -5291,16 +5291,16 @@
     <t xml:space="preserve">5.48442602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47475147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35338354110718</t>
+    <t xml:space="preserve">5.4747519493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35338401794434</t>
   </si>
   <si>
     <t xml:space="preserve">5.31644535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25488233566284</t>
+    <t xml:space="preserve">5.25488138198853</t>
   </si>
   <si>
     <t xml:space="preserve">5.23113632202148</t>
@@ -5309,40 +5309,40 @@
     <t xml:space="preserve">5.14582681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09042024612427</t>
+    <t xml:space="preserve">5.09041976928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856317520142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97872638702393</t>
+    <t xml:space="preserve">4.97872591018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88726091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88462162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92595720291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92859601974487</t>
+    <t xml:space="preserve">4.88726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88462209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92595672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92859554290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.02270030975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08426332473755</t>
+    <t xml:space="preserve">5.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">5.06051778793335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03325414657593</t>
+    <t xml:space="preserve">5.03325366973877</t>
   </si>
   <si>
     <t xml:space="preserve">5.05172300338745</t>
@@ -5351,13 +5351,13 @@
     <t xml:space="preserve">5.04996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9664134979248</t>
+    <t xml:space="preserve">5.01390504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99719572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96641254425049</t>
   </si>
   <si>
     <t xml:space="preserve">5.00511026382446</t>
@@ -5372,10 +5372,10 @@
     <t xml:space="preserve">5.0825047492981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06139755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17660903930664</t>
+    <t xml:space="preserve">5.06139659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17660856246948</t>
   </si>
   <si>
     <t xml:space="preserve">5.26631546020508</t>
@@ -5387,52 +5387,52 @@
     <t xml:space="preserve">5.37712955474854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41758489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40527248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38152694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3542628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39032125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43869256973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49585914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54247093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63305759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70781278610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64273166656494</t>
+    <t xml:space="preserve">5.4175853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40527296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38152742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39032173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43869304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49585962295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54247140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63305807113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70781326293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">5.6207447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61282920837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65680360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66559839248657</t>
+    <t xml:space="preserve">5.61282968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64097356796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65680408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66559791564941</t>
   </si>
   <si>
     <t xml:space="preserve">5.65768337249756</t>
@@ -5444,13 +5444,13 @@
     <t xml:space="preserve">5.72276449203491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74738931655884</t>
+    <t xml:space="preserve">5.747389793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.760582447052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75882291793823</t>
+    <t xml:space="preserve">5.75882244110107</t>
   </si>
   <si>
     <t xml:space="preserve">5.7535457611084</t>
@@ -5465,46 +5465,46 @@
     <t xml:space="preserve">5.81510972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91185235977173</t>
+    <t xml:space="preserve">5.91185283660889</t>
   </si>
   <si>
     <t xml:space="preserve">5.86611938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85996294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89250373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86436033248901</t>
+    <t xml:space="preserve">5.85996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89250326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86436128616333</t>
   </si>
   <si>
     <t xml:space="preserve">5.86963701248169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90921354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91097259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90041971206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91888809204102</t>
+    <t xml:space="preserve">5.90921401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.910973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90041923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91888856887817</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361093521118</t>
+    <t xml:space="preserve">5.91361141204834</t>
   </si>
   <si>
     <t xml:space="preserve">5.88458871841431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89162397384644</t>
+    <t xml:space="preserve">5.89162445068359</t>
   </si>
   <si>
     <t xml:space="preserve">5.92504453659058</t>
@@ -5513,7 +5513,7 @@
     <t xml:space="preserve">5.86787843704224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97165679931641</t>
+    <t xml:space="preserve">5.97165727615356</t>
   </si>
   <si>
     <t xml:space="preserve">5.98660755157471</t>
@@ -5525,7 +5525,7 @@
     <t xml:space="preserve">5.83621740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82390451431274</t>
+    <t xml:space="preserve">5.8239049911499</t>
   </si>
   <si>
     <t xml:space="preserve">5.85908365249634</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">5.80092000961304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75638818740845</t>
+    <t xml:space="preserve">5.75638866424561</t>
   </si>
   <si>
     <t xml:space="preserve">5.74002981185913</t>
@@ -5543,10 +5543,10 @@
     <t xml:space="preserve">5.72185373306274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69913291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551042556763</t>
+    <t xml:space="preserve">5.69913339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551090240479</t>
   </si>
   <si>
     <t xml:space="preserve">5.68550109863281</t>
@@ -5561,19 +5561,19 @@
     <t xml:space="preserve">5.61824941635132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56826448440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52191591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48011064529419</t>
+    <t xml:space="preserve">5.56826496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52191638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48011112213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.41013240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33833694458008</t>
+    <t xml:space="preserve">5.33833646774292</t>
   </si>
   <si>
     <t xml:space="preserve">5.37741565704346</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">5.34651613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37468910217285</t>
+    <t xml:space="preserve">5.37468957901001</t>
   </si>
   <si>
     <t xml:space="preserve">5.38468599319458</t>
@@ -5594,10 +5594,10 @@
     <t xml:space="preserve">5.36469221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41376733779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3919563293457</t>
+    <t xml:space="preserve">5.41376781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39195680618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.41467666625977</t>
@@ -5606,13 +5606,13 @@
     <t xml:space="preserve">5.34015417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39831781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31925249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35469532012939</t>
+    <t xml:space="preserve">5.39831829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31925201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35469579696655</t>
   </si>
   <si>
     <t xml:space="preserve">5.48738145828247</t>
@@ -5624,7 +5624,7 @@
     <t xml:space="preserve">5.57917070388794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57099151611328</t>
+    <t xml:space="preserve">5.57099199295044</t>
   </si>
   <si>
     <t xml:space="preserve">5.59462070465088</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">5.5900764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64278697967529</t>
+    <t xml:space="preserve">5.64278745651245</t>
   </si>
   <si>
     <t xml:space="preserve">5.57008266448975</t>
@@ -5645,22 +5645,22 @@
     <t xml:space="preserve">5.5200982093811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54645347595215</t>
+    <t xml:space="preserve">5.54645395278931</t>
   </si>
   <si>
     <t xml:space="preserve">5.51646327972412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52645969390869</t>
+    <t xml:space="preserve">5.52646017074585</t>
   </si>
   <si>
     <t xml:space="preserve">5.51373624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5291862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60552644729614</t>
+    <t xml:space="preserve">5.52918672561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6055269241333</t>
   </si>
   <si>
     <t xml:space="preserve">5.56099462509155</t>
@@ -5669,16 +5669,16 @@
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49465131759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36832761764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36105728149414</t>
+    <t xml:space="preserve">5.44375848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49465179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36105680465698</t>
   </si>
   <si>
     <t xml:space="preserve">5.29380512237549</t>
@@ -5687,19 +5687,19 @@
     <t xml:space="preserve">5.17929553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18656587600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3374285697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31470823287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26563262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25836181640625</t>
+    <t xml:space="preserve">5.18656539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33742809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31470775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26563215255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25836133956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.33651924133301</t>
@@ -5708,7 +5708,7 @@
     <t xml:space="preserve">5.41195011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49737739562988</t>
+    <t xml:space="preserve">5.49737787246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.56190299987793</t>
@@ -5732,10 +5732,10 @@
     <t xml:space="preserve">5.68004846572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74820852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80182838439941</t>
+    <t xml:space="preserve">5.74820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
     <t xml:space="preserve">5.8581748008728</t>
@@ -5750,7 +5750,7 @@
     <t xml:space="preserve">6.13627004623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10173511505127</t>
+    <t xml:space="preserve">6.10173559188843</t>
   </si>
   <si>
     <t xml:space="preserve">6.21806240081787</t>
@@ -5759,7 +5759,7 @@
     <t xml:space="preserve">6.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17989253997803</t>
+    <t xml:space="preserve">6.17989301681519</t>
   </si>
   <si>
     <t xml:space="preserve">6.14444923400879</t>
@@ -5771,7 +5771,7 @@
     <t xml:space="preserve">6.06538248062134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00358390808105</t>
+    <t xml:space="preserve">6.00358438491821</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814371109009</t>
@@ -5780,7 +5780,7 @@
     <t xml:space="preserve">6.0535683631897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05265951156616</t>
+    <t xml:space="preserve">6.05265998840332</t>
   </si>
   <si>
     <t xml:space="preserve">5.97086715698242</t>
@@ -5792,31 +5792,31 @@
     <t xml:space="preserve">6.04902458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13445234298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12172889709473</t>
+    <t xml:space="preserve">6.1344518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12172937393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.19170713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17807483673096</t>
+    <t xml:space="preserve">6.17807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">6.09810018539429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06992673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96904897689819</t>
+    <t xml:space="preserve">6.06992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96904945373535</t>
   </si>
   <si>
     <t xml:space="preserve">6.03539228439331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95632553100586</t>
+    <t xml:space="preserve">5.95632600784302</t>
   </si>
   <si>
     <t xml:space="preserve">5.75911426544189</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">5.81636953353882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89725303649902</t>
+    <t xml:space="preserve">5.89725351333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.87907743453979</t>
@@ -5840,31 +5840,31 @@
     <t xml:space="preserve">5.9454197883606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97813701629639</t>
+    <t xml:space="preserve">5.97813749313354</t>
   </si>
   <si>
     <t xml:space="preserve">5.95087289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9045238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9017972946167</t>
+    <t xml:space="preserve">5.90452432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90179777145386</t>
   </si>
   <si>
     <t xml:space="preserve">6.00449275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98449897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02812147140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04266262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09446430206299</t>
+    <t xml:space="preserve">5.98449850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02812194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04266309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09446477890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.11809349060059</t>
@@ -5879,34 +5879,34 @@
     <t xml:space="preserve">6.17171335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1262731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15081071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13081693649292</t>
+    <t xml:space="preserve">6.12627363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15081119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13081741333008</t>
   </si>
   <si>
     <t xml:space="preserve">6.16179513931274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22468948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25191259384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2613000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24252510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22375059127808</t>
+    <t xml:space="preserve">6.18150854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22468996047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25191211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26129961013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24252557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22375106811523</t>
   </si>
   <si>
     <t xml:space="preserve">6.18995666503906</t>
@@ -5924,40 +5924,40 @@
     <t xml:space="preserve">5.91209363937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03600549697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03412818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01629209518433</t>
+    <t xml:space="preserve">6.03600597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03412866592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01629257202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.04351568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10641050338745</t>
+    <t xml:space="preserve">6.10641002655029</t>
   </si>
   <si>
     <t xml:space="preserve">6.09139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16742753982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18714094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17587566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20216035842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30260419845581</t>
+    <t xml:space="preserve">6.16742706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17587614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19840526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2021598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30260372161865</t>
   </si>
   <si>
     <t xml:space="preserve">6.29791021347046</t>
@@ -5969,10 +5969,10 @@
     <t xml:space="preserve">6.41149616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42651605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44341278076172</t>
+    <t xml:space="preserve">6.42651557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44341230392456</t>
   </si>
   <si>
     <t xml:space="preserve">6.46594190597534</t>
@@ -5981,13 +5981,13 @@
     <t xml:space="preserve">6.47063589096069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46030950546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56638526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6189546585083</t>
+    <t xml:space="preserve">6.4603099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5663857460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61895418167114</t>
   </si>
   <si>
     <t xml:space="preserve">6.62177038192749</t>
@@ -6026,10 +6026,10 @@
     <t xml:space="preserve">6.71752071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7710280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73535633087158</t>
+    <t xml:space="preserve">6.77102756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73535680770874</t>
   </si>
   <si>
     <t xml:space="preserve">6.7785382270813</t>
@@ -6041,7 +6041,7 @@
     <t xml:space="preserve">6.55605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52883672714233</t>
+    <t xml:space="preserve">6.52883625030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147557258606</t>
@@ -6053,7 +6053,7 @@
     <t xml:space="preserve">6.57201766967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55418252944946</t>
+    <t xml:space="preserve">6.5541820526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.63303518295288</t>
@@ -6062,7 +6062,7 @@
     <t xml:space="preserve">6.73629522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76727342605591</t>
+    <t xml:space="preserve">6.76727294921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.83861589431763</t>
@@ -6074,22 +6074,22 @@
     <t xml:space="preserve">6.88273620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88743019104004</t>
+    <t xml:space="preserve">6.88742971420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.73066282272339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73723363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75976371765137</t>
+    <t xml:space="preserve">6.73723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75976324081421</t>
   </si>
   <si>
     <t xml:space="preserve">6.74756002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76633453369141</t>
+    <t xml:space="preserve">6.76633405685425</t>
   </si>
   <si>
     <t xml:space="preserve">6.70062351226807</t>
@@ -6104,7 +6104,7 @@
     <t xml:space="preserve">6.58234405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60017967224121</t>
+    <t xml:space="preserve">6.60018014907837</t>
   </si>
   <si>
     <t xml:space="preserve">6.56920194625854</t>
@@ -6122,10 +6122,10 @@
     <t xml:space="preserve">6.34109163284302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37206935882568</t>
+    <t xml:space="preserve">6.21436309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37206983566284</t>
   </si>
   <si>
     <t xml:space="preserve">6.28852272033691</t>
@@ -6143,10 +6143,10 @@
     <t xml:space="preserve">6.32888841629028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072641372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32607221603394</t>
+    <t xml:space="preserve">6.30072593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32607173919678</t>
   </si>
   <si>
     <t xml:space="preserve">6.3551721572876</t>
@@ -6179,7 +6179,7 @@
     <t xml:space="preserve">6.48565530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58891487121582</t>
+    <t xml:space="preserve">6.58891534805298</t>
   </si>
   <si>
     <t xml:space="preserve">6.49222612380981</t>
@@ -6200,7 +6200,7 @@
     <t xml:space="preserve">6.4640645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59454727172852</t>
+    <t xml:space="preserve">6.59454774856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.58328247070312</t>
@@ -6212,22 +6212,22 @@
     <t xml:space="preserve">6.5654468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5588755607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60205698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46312570571899</t>
+    <t xml:space="preserve">6.55887603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60205745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46312618255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.49692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6170768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66870641708374</t>
+    <t xml:space="preserve">6.61707639694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6687068939209</t>
   </si>
   <si>
     <t xml:space="preserve">6.572350025177</t>
@@ -6800,7 +6800,7 @@
     <t xml:space="preserve">8.95699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93599987030029</t>
+    <t xml:space="preserve">8.89200019836426</t>
   </si>
 </sst>
 </file>
@@ -72243,22 +72243,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911805556</v>
+        <v>45967.6918518519</v>
       </c>
       <c r="B2505" t="n">
-        <v>16203200</v>
+        <v>16462950</v>
       </c>
       <c r="C2505" t="n">
-        <v>8.96300029754639</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="D2505" t="n">
-        <v>8.89099979400635</v>
+        <v>8.86200046539307</v>
       </c>
       <c r="E2505" t="n">
-        <v>8.94299983978271</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="F2505" t="n">
-        <v>8.93599987030029</v>
+        <v>8.89200019836426</v>
       </c>
       <c r="G2505" t="s">
         <v>2262</v>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="2261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="2264">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,130 +38,130 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697352409363</t>
+    <t xml:space="preserve">2.23697328567505</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958273887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22277069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23223900794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21685242652893</t>
+    <t xml:space="preserve">2.27958202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22277045249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448564529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21685338020325</t>
   </si>
   <si>
     <t xml:space="preserve">2.20146608352661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23460578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21211838722229</t>
+    <t xml:space="preserve">2.23460626602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21211791038513</t>
   </si>
   <si>
     <t xml:space="preserve">2.17187643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13281869888306</t>
+    <t xml:space="preserve">2.13281798362732</t>
   </si>
   <si>
     <t xml:space="preserve">2.15767312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09257650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16004061698914</t>
+    <t xml:space="preserve">2.09257674217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16004037857056</t>
   </si>
   <si>
     <t xml:space="preserve">2.20620012283325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19436454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513747215271</t>
+    <t xml:space="preserve">2.19436430931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513794898987</t>
   </si>
   <si>
     <t xml:space="preserve">2.25236010551453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987174987793</t>
+    <t xml:space="preserve">2.17305970191956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987198829651</t>
   </si>
   <si>
     <t xml:space="preserve">2.22395396232605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19081401824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702105522156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849429130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07008814811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06772112846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08665800094604</t>
+    <t xml:space="preserve">2.19081354141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702081680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0984935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07008862495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06772065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0866584777832</t>
   </si>
   <si>
     <t xml:space="preserve">2.01090908050537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09375953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16477489471436</t>
+    <t xml:space="preserve">2.09375977516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16477465629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.15057182312012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15648984909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228677749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09494304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18016123771667</t>
+    <t xml:space="preserve">2.15649008750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228653907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15293908119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09494376182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18016171455383</t>
   </si>
   <si>
     <t xml:space="preserve">2.19199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791483879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714215278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542719841003</t>
+    <t xml:space="preserve">2.21330142021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791531562805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16714191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542743682861</t>
   </si>
   <si>
     <t xml:space="preserve">2.24170804023743</t>
@@ -170,61 +170,61 @@
     <t xml:space="preserve">2.25354385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31508994102478</t>
+    <t xml:space="preserve">2.3150897026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.30798840522766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30207061767578</t>
+    <t xml:space="preserve">2.3020703792572</t>
   </si>
   <si>
     <t xml:space="preserve">2.30562114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32574224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3174569606781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088663101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3139066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059762001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36716771125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496908187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27366471290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595864295959</t>
+    <t xml:space="preserve">2.32574200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3115394115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088686943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390690803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35059714317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36716747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.306804895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496884346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2736644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738387107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595816612244</t>
   </si>
   <si>
     <t xml:space="preserve">2.22632122039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23579001426697</t>
+    <t xml:space="preserve">2.23578977584839</t>
   </si>
   <si>
     <t xml:space="preserve">2.21921968460083</t>
@@ -233,58 +233,58 @@
     <t xml:space="preserve">2.26182889938354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27129745483398</t>
+    <t xml:space="preserve">2.27129721641541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29615259170532</t>
+    <t xml:space="preserve">2.2961528301239</t>
   </si>
   <si>
     <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112858772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32929277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30917191505432</t>
+    <t xml:space="preserve">2.39912438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112882614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3091721534729</t>
   </si>
   <si>
     <t xml:space="preserve">2.34941411018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37071800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37663650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33757829666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35296440124512</t>
+    <t xml:space="preserve">2.37071871757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37663626670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.33166027069092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36124968528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3399453163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385890007019</t>
+    <t xml:space="preserve">2.36124920845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33994555473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385866165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.41096043586731</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">2.42989778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42516303062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43699860572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38965630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794135093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37782025337219</t>
+    <t xml:space="preserve">2.42516326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43699932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38965582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794087409973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37782049179077</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463182449341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44173336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43936610221863</t>
+    <t xml:space="preserve">2.44173359870911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43936657905579</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651540756226</t>
@@ -323,43 +323,43 @@
     <t xml:space="preserve">2.31864070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27839875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37900328636169</t>
+    <t xml:space="preserve">2.2783989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37900352478027</t>
   </si>
   <si>
     <t xml:space="preserve">2.43817043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44433379173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40735411643982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875977516174</t>
+    <t xml:space="preserve">2.44433403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40735387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21876001358032</t>
   </si>
   <si>
     <t xml:space="preserve">2.21013140678406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30627703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365648269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296263694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049643516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45419478416443</t>
+    <t xml:space="preserve">2.30627727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296216011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049715042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45419526100159</t>
   </si>
   <si>
     <t xml:space="preserve">2.39256286621094</t>
@@ -371,91 +371,91 @@
     <t xml:space="preserve">2.42214632034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43940281867981</t>
+    <t xml:space="preserve">2.43940305709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.45912551879883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46035814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282291412354</t>
+    <t xml:space="preserve">2.46035838127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282362937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44679927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48008012771606</t>
+    <t xml:space="preserve">2.48008060455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47638273239136</t>
+    <t xml:space="preserve">2.4763822555542</t>
   </si>
   <si>
     <t xml:space="preserve">2.47268462181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53801441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52568793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240684509277</t>
+    <t xml:space="preserve">2.53801465034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240636825562</t>
   </si>
   <si>
     <t xml:space="preserve">2.4813129901886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49117422103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52322292327881</t>
+    <t xml:space="preserve">2.49117374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52322268486023</t>
   </si>
   <si>
     <t xml:space="preserve">2.51089644432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350069999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49856972694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53308391571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52938628196716</t>
+    <t xml:space="preserve">2.50350022315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49857020378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53308463096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52938604354858</t>
   </si>
   <si>
     <t xml:space="preserve">2.47021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42461156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707657814026</t>
+    <t xml:space="preserve">2.42461109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.39749312400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40242385864258</t>
+    <t xml:space="preserve">2.402423620224</t>
   </si>
   <si>
     <t xml:space="preserve">2.42830944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42954134941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43570470809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4517297744751</t>
+    <t xml:space="preserve">2.42954230308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43570518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172953605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.41351771354675</t>
@@ -464,70 +464,70 @@
     <t xml:space="preserve">2.43200755119324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48747587203979</t>
+    <t xml:space="preserve">2.48747611045837</t>
   </si>
   <si>
     <t xml:space="preserve">2.48994159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47761464118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541039466858</t>
+    <t xml:space="preserve">2.47761487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541063308716</t>
   </si>
   <si>
     <t xml:space="preserve">2.53061866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49610471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44556641578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105246543884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475009918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39133024215698</t>
+    <t xml:space="preserve">2.49610495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44556593894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41474962234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39132976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.41968107223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981984138489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44803166389465</t>
+    <t xml:space="preserve">2.40981936454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44803142547607</t>
   </si>
   <si>
     <t xml:space="preserve">2.41721534729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42091369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926404953003</t>
+    <t xml:space="preserve">2.42091345787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926428794861</t>
   </si>
   <si>
     <t xml:space="preserve">2.41228485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37284016609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35928153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32476711273193</t>
+    <t xml:space="preserve">2.3728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35928106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32476782798767</t>
   </si>
   <si>
     <t xml:space="preserve">2.36051368713379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33832669258118</t>
+    <t xml:space="preserve">2.33832621574402</t>
   </si>
   <si>
     <t xml:space="preserve">2.31983685493469</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">2.36421179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35435032844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43693780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858721733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4307746887207</t>
+    <t xml:space="preserve">2.35435056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4369375705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43077492713928</t>
   </si>
   <si>
     <t xml:space="preserve">2.41598320007324</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">2.36297941207886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35311770439148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36667728424072</t>
+    <t xml:space="preserve">2.35311794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36667704582214</t>
   </si>
   <si>
     <t xml:space="preserve">2.38393425941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32723212242126</t>
+    <t xml:space="preserve">2.32723259925842</t>
   </si>
   <si>
     <t xml:space="preserve">2.24711036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24341249465942</t>
+    <t xml:space="preserve">2.24341225624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369050979614</t>
@@ -581,88 +581,88 @@
     <t xml:space="preserve">2.24957609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25080847740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28285694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22862100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24834322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860375404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3075098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29764890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30257964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065293312073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33339524269104</t>
+    <t xml:space="preserve">2.25080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28285717964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2286205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2483434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860423088074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30751061439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29764866828918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30257940292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586096763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065245628357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33339595794678</t>
   </si>
   <si>
     <t xml:space="preserve">2.51952457427979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51336193084717</t>
+    <t xml:space="preserve">2.51336169242859</t>
   </si>
   <si>
     <t xml:space="preserve">2.47884774208069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49980282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53924703598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56513285636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54910850524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266760826111</t>
+    <t xml:space="preserve">2.49980330467224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53924751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5651330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266736984253</t>
   </si>
   <si>
     <t xml:space="preserve">2.58115720748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60211229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622647285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896973609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047989845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664278030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56636548042297</t>
+    <t xml:space="preserve">2.60211181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622671127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896925926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664301872253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56636571884155</t>
   </si>
   <si>
     <t xml:space="preserve">2.55403900146484</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.55157327651978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57299518585205</t>
+    <t xml:space="preserve">2.57299423217773</t>
   </si>
   <si>
     <t xml:space="preserve">2.56795430183411</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">2.50873279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47849202156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42556977272034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43439030647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43565082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44825053215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715116500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41926980018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069075584412</t>
+    <t xml:space="preserve">2.47849154472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42557001113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43438982963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43565034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44825077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715140342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41926956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069027900696</t>
   </si>
   <si>
     <t xml:space="preserve">2.54401397705078</t>
@@ -719,40 +719,40 @@
     <t xml:space="preserve">2.54023361206055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5326726436615</t>
+    <t xml:space="preserve">2.53267312049866</t>
   </si>
   <si>
     <t xml:space="preserve">2.49361205101013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53141331672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54527378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52133250236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5263729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50369215011597</t>
+    <t xml:space="preserve">2.53141307830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5452733039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52133297920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52637314796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50369238853455</t>
   </si>
   <si>
     <t xml:space="preserve">2.52007269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55787372589111</t>
+    <t xml:space="preserve">2.55787444114685</t>
   </si>
   <si>
     <t xml:space="preserve">2.55283403396606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57803440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59945511817932</t>
+    <t xml:space="preserve">2.57803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5994553565979</t>
   </si>
   <si>
     <t xml:space="preserve">2.6032350063324</t>
@@ -761,67 +761,67 @@
     <t xml:space="preserve">2.6082751750946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62717580795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63347578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473606109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961579322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757749557495</t>
+    <t xml:space="preserve">2.62717604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473629951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757725715637</t>
   </si>
   <si>
     <t xml:space="preserve">2.65237641334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63977646827698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65867638587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7015175819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7342791557312</t>
+    <t xml:space="preserve">2.63977670669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6586766242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71033787727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151782035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71537828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73427939414978</t>
   </si>
   <si>
     <t xml:space="preserve">2.74183940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75191974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78090071678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77963995933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77460026741028</t>
+    <t xml:space="preserve">2.75191903114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78090047836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7746000289917</t>
   </si>
   <si>
     <t xml:space="preserve">2.76200008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309921264648</t>
+    <t xml:space="preserve">2.77208065986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309897422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.7594792842865</t>
@@ -836,40 +836,40 @@
     <t xml:space="preserve">2.67253732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907855033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80484104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79098057746887</t>
+    <t xml:space="preserve">2.70907807350159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80484127998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79098081588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.7771201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77081966400146</t>
+    <t xml:space="preserve">2.77081990242004</t>
   </si>
   <si>
     <t xml:space="preserve">2.74939918518066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78720021247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792348861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658239364624</t>
+    <t xml:space="preserve">2.78720045089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650229454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8842236995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86658310890198</t>
   </si>
   <si>
     <t xml:space="preserve">2.87918305397034</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">2.87414288520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87666273117065</t>
+    <t xml:space="preserve">2.87666392326355</t>
   </si>
   <si>
     <t xml:space="preserve">2.88044357299805</t>
@@ -887,70 +887,70 @@
     <t xml:space="preserve">2.94974493980408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92202496528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998666763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526713371277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518727302551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02912759780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96108508110046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990609169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156782150269</t>
+    <t xml:space="preserve">2.91572427749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9220244884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998642921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526665687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9862859249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0051863193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02912735939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96108531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762654304504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156710624695</t>
   </si>
   <si>
     <t xml:space="preserve">3.11354947090149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180859565735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05558800697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810856819153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440854072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968972206116</t>
+    <t xml:space="preserve">3.08582925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180811882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05558753013611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810880661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968948364258</t>
   </si>
   <si>
     <t xml:space="preserve">3.10725021362305</t>
@@ -959,163 +959,163 @@
     <t xml:space="preserve">3.08204913139343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10347008705139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11859011650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02408790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04928874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98754668235779</t>
+    <t xml:space="preserve">3.13749003410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10346937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02408719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04928779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98754692077637</t>
   </si>
   <si>
     <t xml:space="preserve">2.95730543136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99888730049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880624771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778721809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06944870948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13245153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13119053840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10094928741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12867045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09338903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07927012443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1177773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831448554993</t>
+    <t xml:space="preserve">2.99888682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478510856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97368597984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02282762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06944847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1324508190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13119077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12489056587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12867093086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09338974952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.119060754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.079270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.08953881263733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09595632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703036308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13189649581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040324211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864225387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735789299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.192223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16013407707214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22816371917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23458123207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987910270691</t>
+    <t xml:space="preserve">3.09595608711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13702988624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13189601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864153862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735765457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.215327501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222378730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16013431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816348075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062584877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383520126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2345814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607377052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025247573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987981796265</t>
   </si>
   <si>
     <t xml:space="preserve">3.26346135139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29875898361206</t>
+    <t xml:space="preserve">3.2987596988678</t>
   </si>
   <si>
     <t xml:space="preserve">3.27950620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28271436691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3019688129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33084869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122182846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3661470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405804634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159543991089</t>
+    <t xml:space="preserve">3.28271508216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30196857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33084845542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122230529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614656448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405780792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159472465515</t>
   </si>
   <si>
     <t xml:space="preserve">3.27629733085632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30517768859863</t>
+    <t xml:space="preserve">3.30517745018005</t>
   </si>
   <si>
     <t xml:space="preserve">3.28592371940613</t>
@@ -1127,310 +1127,310 @@
     <t xml:space="preserve">3.27308797836304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24099898338318</t>
+    <t xml:space="preserve">3.2409987449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23778986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704431533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31480383872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801295280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32763934135437</t>
+    <t xml:space="preserve">3.23779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2570436000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31480431556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801342964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32763981819153</t>
   </si>
   <si>
     <t xml:space="preserve">3.30838632583618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32443022727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35010170936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39502739906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3918182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41749000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45599627494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44316077232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957947731018</t>
+    <t xml:space="preserve">3.32443070411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39502668380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4142804145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748976707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599675178528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44316029548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957780838013</t>
   </si>
   <si>
     <t xml:space="preserve">3.45920515060425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46241474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4399516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4239068031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38540029525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256407737732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.378981590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3982355594635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331034660339</t>
+    <t xml:space="preserve">3.46241354942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995141983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42390727996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38540053367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898230552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39823579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331130027771</t>
   </si>
   <si>
     <t xml:space="preserve">3.40786266326904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43674302101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883106231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51375603675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092124938965</t>
+    <t xml:space="preserve">3.43674206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883225440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51375699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092077255249</t>
   </si>
   <si>
     <t xml:space="preserve">3.44636964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51054811477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5458459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5618908405304</t>
+    <t xml:space="preserve">3.51054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584622383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189012527466</t>
   </si>
   <si>
     <t xml:space="preserve">3.58114385604858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53621888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166751861572</t>
+    <t xml:space="preserve">3.53621864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166799545288</t>
   </si>
   <si>
     <t xml:space="preserve">3.50412940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107153892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29234194755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711591720581</t>
+    <t xml:space="preserve">3.41107201576233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293816566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2923424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711615562439</t>
   </si>
   <si>
     <t xml:space="preserve">3.40144491195679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44611382484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047861099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382533073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31717109680176</t>
+    <t xml:space="preserve">3.4461145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4297513961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738823890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382509231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31717133522034</t>
   </si>
   <si>
     <t xml:space="preserve">3.34466171264648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31586289405823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019198417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070324897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310441970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06844925880432</t>
+    <t xml:space="preserve">3.31586217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310114860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146592140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070372581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">3.0461950302124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.128666639328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652062416077</t>
+    <t xml:space="preserve">3.12866616249084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652038574219</t>
   </si>
   <si>
     <t xml:space="preserve">3.18102884292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12735724449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630395889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466498374939</t>
+    <t xml:space="preserve">3.12735676765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630324363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466522216797</t>
   </si>
   <si>
     <t xml:space="preserve">3.15877461433411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16597414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801194190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688446998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07695865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09528541564941</t>
+    <t xml:space="preserve">3.16597437858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11688470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0481584072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07695841789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09528493881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.12670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16793847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1653196811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16335725784302</t>
+    <t xml:space="preserve">3.16793751716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16532015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16335654258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.18757390975952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17448377609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684597969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13913869857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17513823509216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630021095276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320936203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30538964271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277228355408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764410972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240843772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324458122253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597182273865</t>
+    <t xml:space="preserve">3.17448258399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150137901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13913822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17513751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259243965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979315757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25629925727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844479560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3027720451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3224081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324505805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597063064575</t>
   </si>
   <si>
     <t xml:space="preserve">3.34728002548218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40095233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39833378791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487885475159</t>
+    <t xml:space="preserve">3.40095114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39833354949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487909317017</t>
   </si>
   <si>
     <t xml:space="preserve">3.39309763908386</t>
@@ -1439,283 +1439,283 @@
     <t xml:space="preserve">3.44284200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43629670143127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44807815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48211359977722</t>
+    <t xml:space="preserve">3.4362964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44807767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520468711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4821138381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.52531290054321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52662229537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891453742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109928131104</t>
+    <t xml:space="preserve">3.52662181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891477584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3210985660553</t>
   </si>
   <si>
     <t xml:space="preserve">3.31848073005676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3433530330658</t>
+    <t xml:space="preserve">3.34335255622864</t>
   </si>
   <si>
     <t xml:space="preserve">3.3629891872406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2059006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19542837142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19215607643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10772156715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08415770530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888681411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07826685905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855818748474</t>
+    <t xml:space="preserve">3.2379732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1954288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19215512275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037390708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10772085189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08415746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888657569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.098557472229</t>
   </si>
   <si>
     <t xml:space="preserve">3.13324809074402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07564878463745</t>
+    <t xml:space="preserve">3.07564830780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.06386733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00692272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11557555198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12932062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401124000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204690933228</t>
+    <t xml:space="preserve">3.00692319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11557579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12932085990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953776359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401076316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204714775085</t>
   </si>
   <si>
     <t xml:space="preserve">3.15746521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08481240272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10641193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452226638794</t>
+    <t xml:space="preserve">3.08481216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10641121864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06452178955078</t>
   </si>
   <si>
     <t xml:space="preserve">3.08808493614197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12342953681946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10313963890076</t>
+    <t xml:space="preserve">3.12342977523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10313987731934</t>
   </si>
   <si>
     <t xml:space="preserve">3.11361193656921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10510230064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15550184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437532424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739294052124</t>
+    <t xml:space="preserve">3.10510277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15550136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437437057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710185050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739246368408</t>
   </si>
   <si>
     <t xml:space="preserve">3.17644715309143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17186498641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14895629882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364667892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113801002502</t>
+    <t xml:space="preserve">3.17186570167542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895606040955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17252039909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411897659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917439460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113681793213</t>
   </si>
   <si>
     <t xml:space="preserve">3.17952370643616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15530848503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13647484779358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656519889832</t>
+    <t xml:space="preserve">3.15530872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13647532463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656448364258</t>
   </si>
   <si>
     <t xml:space="preserve">3.17212462425232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16338014602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844697952271</t>
+    <t xml:space="preserve">3.16338038444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844626426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.08401036262512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02347326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432511329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04499745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468294143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08333778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0692126750946</t>
+    <t xml:space="preserve">3.02347302436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432463645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499769210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0833375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06921219825745</t>
   </si>
   <si>
     <t xml:space="preserve">3.00598478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99051427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01203846931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9804253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638964653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96629977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791312217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98513340950012</t>
+    <t xml:space="preserve">2.99051451683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01203894615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98042559623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96629953384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99791288375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">2.95082926750183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96293711662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150208473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94006705284119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836430549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540532112122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397052764893</t>
+    <t xml:space="preserve">2.96293663978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92997741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94006681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836382865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540579795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85397028923035</t>
   </si>
   <si>
     <t xml:space="preserve">2.88625645637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88558435440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94477534294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719446182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584930419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894376754761</t>
+    <t xml:space="preserve">2.8855836391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94477558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0658495426178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894400596619</t>
   </si>
   <si>
     <t xml:space="preserve">3.06652164459229</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">3.05979490280151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03625345230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05912280082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1162965297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07392048835754</t>
+    <t xml:space="preserve">3.03625321388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05912256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0739209651947</t>
   </si>
   <si>
     <t xml:space="preserve">3.09342694282532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10149836540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96764469146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94746613502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562695503235</t>
+    <t xml:space="preserve">3.10149788856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064699172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94746589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562671661377</t>
   </si>
   <si>
     <t xml:space="preserve">3.04096150398254</t>
@@ -1760,100 +1760,100 @@
     <t xml:space="preserve">2.99993109703064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97504377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94410276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94343042373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92325139045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88423848152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99589586257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96899032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93468570709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9797523021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9669725894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95957374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94544863700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96428203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00665736198425</t>
+    <t xml:space="preserve">2.97504448890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9441032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94343066215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92325162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88423871994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99589538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96899080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93468594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97975206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98446035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96697211265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612050056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95957350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91517996788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94544816017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96428179740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168135643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00665783882141</t>
   </si>
   <si>
     <t xml:space="preserve">3.01540184020996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0228009223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99454998970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683639526367</t>
+    <t xml:space="preserve">3.02280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99455046653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683663368225</t>
   </si>
   <si>
     <t xml:space="preserve">3.0685396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09275484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.133784532547</t>
+    <t xml:space="preserve">3.09275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378477096558</t>
   </si>
   <si>
     <t xml:space="preserve">3.13243961334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16472578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19835734367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20441126823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21517372131348</t>
+    <t xml:space="preserve">3.16472601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19835758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20441102981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21517300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.20037484169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22189879417419</t>
+    <t xml:space="preserve">3.22189974784851</t>
   </si>
   <si>
     <t xml:space="preserve">3.2380428314209</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">3.22728037834167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24880456924438</t>
+    <t xml:space="preserve">3.24880504608154</t>
   </si>
   <si>
     <t xml:space="preserve">3.19297623634338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19364929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961358070374</t>
+    <t xml:space="preserve">3.19364833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961334228516</t>
   </si>
   <si>
     <t xml:space="preserve">3.23333382606506</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31674027442932</t>
+    <t xml:space="preserve">3.31674003601074</t>
   </si>
   <si>
     <t xml:space="preserve">3.37660455703735</t>
@@ -1886,22 +1886,22 @@
     <t xml:space="preserve">3.3752589225769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37256813049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655776023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4882607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39543795585632</t>
+    <t xml:space="preserve">3.37256908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270060539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48826146125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39543747901917</t>
   </si>
   <si>
     <t xml:space="preserve">3.39274716377258</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">3.42099785804749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673703193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153448104858</t>
+    <t xml:space="preserve">3.46808266639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46673679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4815354347229</t>
   </si>
   <si>
     <t xml:space="preserve">3.47346329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5313093662262</t>
+    <t xml:space="preserve">3.53130960464478</t>
   </si>
   <si>
     <t xml:space="preserve">3.49767756462097</t>
@@ -1934,34 +1934,34 @@
     <t xml:space="preserve">3.50440359115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5111300945282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458238601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57861113548279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690237998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5675585269928</t>
+    <t xml:space="preserve">3.51113033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978493690491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.524582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275675773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446694374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5786120891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5869026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.6214451789856</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">3.61591839790344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63802528381348</t>
+    <t xml:space="preserve">3.63802456855774</t>
   </si>
   <si>
     <t xml:space="preserve">3.57170367240906</t>
@@ -1979,76 +1979,76 @@
     <t xml:space="preserve">3.58137583732605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54545187950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5509774684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5910472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348272323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071921348572</t>
+    <t xml:space="preserve">3.54545164108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472567558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097818374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59104704856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6034824848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071897506714</t>
   </si>
   <si>
     <t xml:space="preserve">3.61729979515076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62282705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61039137840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61453652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64631533622742</t>
+    <t xml:space="preserve">3.62282681465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61039161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61453628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420773506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64631581306458</t>
   </si>
   <si>
     <t xml:space="preserve">3.66980457305908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66151475906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533111572266</t>
+    <t xml:space="preserve">3.66151428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533135414124</t>
   </si>
   <si>
     <t xml:space="preserve">3.67118644714355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66427826881409</t>
+    <t xml:space="preserve">3.66427779197693</t>
   </si>
   <si>
     <t xml:space="preserve">3.68085813522339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72921705245972</t>
+    <t xml:space="preserve">3.72921752929688</t>
   </si>
   <si>
     <t xml:space="preserve">3.80106616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78863096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205061912537</t>
+    <t xml:space="preserve">3.78863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205038070679</t>
   </si>
   <si>
     <t xml:space="preserve">3.79830288887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79001259803772</t>
+    <t xml:space="preserve">3.79001331329346</t>
   </si>
   <si>
     <t xml:space="preserve">3.79139447212219</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">3.77895927429199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81350183486938</t>
+    <t xml:space="preserve">3.81350159645081</t>
   </si>
   <si>
     <t xml:space="preserve">3.83008217811584</t>
@@ -2066,40 +2066,40 @@
     <t xml:space="preserve">3.85495281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.892258644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258767127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923687934875</t>
+    <t xml:space="preserve">3.89225888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258671760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923664093018</t>
   </si>
   <si>
     <t xml:space="preserve">3.94752669334412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92818331718445</t>
+    <t xml:space="preserve">3.92818307876587</t>
   </si>
   <si>
     <t xml:space="preserve">3.94061827659607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90883946418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091132164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338202476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93440127372742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9337100982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92127346992493</t>
+    <t xml:space="preserve">3.9088397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9344003200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93370938301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92127418518066</t>
   </si>
   <si>
     <t xml:space="preserve">3.91022086143494</t>
@@ -2111,61 +2111,61 @@
     <t xml:space="preserve">3.87567782402039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85564279556274</t>
+    <t xml:space="preserve">3.85564255714417</t>
   </si>
   <si>
     <t xml:space="preserve">3.78379511833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81419277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244755744934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593655586243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840725898743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83629965782166</t>
+    <t xml:space="preserve">3.8141918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281113624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80244874954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593703269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840749740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83629989624023</t>
   </si>
   <si>
     <t xml:space="preserve">3.89571261405945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85288000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015128135681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85218930244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8349187374115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80451989173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85149812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080718994141</t>
+    <t xml:space="preserve">3.85288047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182715415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85218906402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452084541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85149931907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080766677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.86186194419861</t>
@@ -2174,106 +2174,106 @@
     <t xml:space="preserve">3.88880467414856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93094635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690485954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068737983704</t>
+    <t xml:space="preserve">3.93094706535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068761825562</t>
   </si>
   <si>
     <t xml:space="preserve">3.92403769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99934101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906388282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84804439544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581674575806</t>
+    <t xml:space="preserve">3.99934124946594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906412124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84804391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844157218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407296180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581722259521</t>
   </si>
   <si>
     <t xml:space="preserve">4.01108503341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06980752944946</t>
+    <t xml:space="preserve">4.0698070526123</t>
   </si>
   <si>
     <t xml:space="preserve">4.02628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911706924438</t>
+    <t xml:space="preserve">4.04010105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911611557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.13889265060425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346952438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20037841796875</t>
+    <t xml:space="preserve">4.1934700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20037889480591</t>
   </si>
   <si>
     <t xml:space="preserve">4.30884265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27637195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30538845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20314168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24182891845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23215675354004</t>
+    <t xml:space="preserve">4.2625560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27637243270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30538749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2031421661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24182939529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23215770721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.32473278045654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42697811126709</t>
+    <t xml:space="preserve">4.42697858810425</t>
   </si>
   <si>
     <t xml:space="preserve">4.4539213180542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42145109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42835998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42766904830933</t>
+    <t xml:space="preserve">4.42145156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4283595085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42766857147217</t>
   </si>
   <si>
     <t xml:space="preserve">4.43941354751587</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">4.45668506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48500967025757</t>
+    <t xml:space="preserve">4.48500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.4995174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53129625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34407663345337</t>
+    <t xml:space="preserve">4.5312967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34407567977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.4323992729187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47267389297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41402816772461</t>
+    <t xml:space="preserve">4.43310594558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47267436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41402769088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41332054138184</t>
+    <t xml:space="preserve">4.41332149505615</t>
   </si>
   <si>
     <t xml:space="preserve">4.35891485214233</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">4.38011169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940502166748</t>
+    <t xml:space="preserve">4.40908098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940454483032</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711791992188</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">4.33418369293213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3384222984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493883132935</t>
+    <t xml:space="preserve">4.33842277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493740081787</t>
   </si>
   <si>
     <t xml:space="preserve">4.28472280502319</t>
@@ -2348,49 +2348,49 @@
     <t xml:space="preserve">4.24586057662964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49316549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40625524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44017028808594</t>
+    <t xml:space="preserve">4.44087743759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49316453933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4062557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44017124176025</t>
   </si>
   <si>
     <t xml:space="preserve">4.39707040786743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59208631515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5935001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68606233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65921211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71997785568237</t>
+    <t xml:space="preserve">4.59208726882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59349966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68606185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6592116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71997833251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.72068500518799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7609601020813</t>
+    <t xml:space="preserve">4.76096057891846</t>
   </si>
   <si>
     <t xml:space="preserve">4.70937919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67758369445801</t>
+    <t xml:space="preserve">4.67758321762085</t>
   </si>
   <si>
     <t xml:space="preserve">4.62458944320679</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">4.58572721481323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55181074142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.657799243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58007526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480451583862</t>
+    <t xml:space="preserve">4.55181217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263698577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58007478713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480499267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
@@ -2423,31 +2423,31 @@
     <t xml:space="preserve">4.64649438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71361875534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215789794922</t>
+    <t xml:space="preserve">4.71361923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215885162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.75530767440796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82737874984741</t>
+    <t xml:space="preserve">4.82737922668457</t>
   </si>
   <si>
     <t xml:space="preserve">4.79487609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84080505371094</t>
+    <t xml:space="preserve">4.84080410003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.81678009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71220636367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6910080909729</t>
+    <t xml:space="preserve">4.71220588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69100856781006</t>
   </si>
   <si>
     <t xml:space="preserve">4.77226591110229</t>
@@ -2459,31 +2459,31 @@
     <t xml:space="preserve">4.78498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81536722183228</t>
+    <t xml:space="preserve">4.81536674499512</t>
   </si>
   <si>
     <t xml:space="preserve">4.7814507484436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80476856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78992938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.831618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80830144882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78357124328613</t>
+    <t xml:space="preserve">4.80476808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78993034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83161783218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80830097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78357076644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.82455253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590633392334</t>
+    <t xml:space="preserve">4.76590585708618</t>
   </si>
   <si>
     <t xml:space="preserve">4.84221744537354</t>
@@ -2495,100 +2495,100 @@
     <t xml:space="preserve">4.84998989105225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85564184188843</t>
+    <t xml:space="preserve">4.85564231872559</t>
   </si>
   <si>
     <t xml:space="preserve">4.87754678726196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90368986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89733123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92347478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.882493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87472105026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140323638916</t>
+    <t xml:space="preserve">4.90369081497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89733076095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92347526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249254226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87472057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.851402759552</t>
   </si>
   <si>
     <t xml:space="preserve">4.84716320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93407297134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8577618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84857654571533</t>
+    <t xml:space="preserve">4.93407344818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85776281356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84857797622681</t>
   </si>
   <si>
     <t xml:space="preserve">4.87401342391968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82596635818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78710460662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83303213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85493564605713</t>
+    <t xml:space="preserve">4.82596588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78710412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76943874359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85493469238281</t>
   </si>
   <si>
     <t xml:space="preserve">4.84433746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71785831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75036191940308</t>
+    <t xml:space="preserve">4.66698408126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71785879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.75601387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83727121353149</t>
+    <t xml:space="preserve">4.83727169036865</t>
   </si>
   <si>
     <t xml:space="preserve">4.89309120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9531512260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94679164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09164094924927</t>
+    <t xml:space="preserve">4.95315074920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93336582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9467921257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09164142608643</t>
   </si>
   <si>
     <t xml:space="preserve">5.06973791122437</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">5.10577297210693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10860061645508</t>
+    <t xml:space="preserve">5.10859966278076</t>
   </si>
   <si>
     <t xml:space="preserve">5.13686227798462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16159296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22871828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2435564994812</t>
+    <t xml:space="preserve">5.16159248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24073076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22871875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355697631836</t>
   </si>
   <si>
     <t xml:space="preserve">5.37780809402466</t>
@@ -2636,85 +2636,85 @@
     <t xml:space="preserve">5.50453615188599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49082708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44464921951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49804162979126</t>
+    <t xml:space="preserve">5.49082660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44464874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49804210662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.64162635803223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83571767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66760158538818</t>
+    <t xml:space="preserve">5.53700399398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83571672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66760015487671</t>
   </si>
   <si>
     <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7722225189209</t>
+    <t xml:space="preserve">5.77222299575806</t>
   </si>
   <si>
     <t xml:space="preserve">5.82272911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602163314819</t>
+    <t xml:space="preserve">5.86602115631104</t>
   </si>
   <si>
     <t xml:space="preserve">5.89993333816528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91652822494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91147804260254</t>
+    <t xml:space="preserve">5.91652870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91147708892822</t>
   </si>
   <si>
     <t xml:space="preserve">5.86746501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92157936096191</t>
+    <t xml:space="preserve">5.92157888412476</t>
   </si>
   <si>
     <t xml:space="preserve">5.97208642959595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05650424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917663574219</t>
+    <t xml:space="preserve">6.05650472640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917615890503</t>
   </si>
   <si>
     <t xml:space="preserve">6.18060731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08464431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0925817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386854171753</t>
+    <t xml:space="preserve">6.08464479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09258079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386806488037</t>
   </si>
   <si>
     <t xml:space="preserve">5.63152503967285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73975372314453</t>
+    <t xml:space="preserve">5.73975324630737</t>
   </si>
   <si>
     <t xml:space="preserve">5.71161460876465</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">5.46629524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51247215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6228666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87684535980225</t>
+    <t xml:space="preserve">5.51247262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62286710739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87684488296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.69357633590698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1271767616272</t>
+    <t xml:space="preserve">5.12717580795288</t>
   </si>
   <si>
     <t xml:space="preserve">4.83712291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70436096191406</t>
+    <t xml:space="preserve">4.70436239242554</t>
   </si>
   <si>
     <t xml:space="preserve">3.77070474624634</t>
@@ -2753,43 +2753,43 @@
     <t xml:space="preserve">4.05426502227783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95830154418945</t>
+    <t xml:space="preserve">3.95830249786377</t>
   </si>
   <si>
     <t xml:space="preserve">4.1271390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2497992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20650768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24907732009888</t>
+    <t xml:space="preserve">4.24979829788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20650720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24907779693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.30896472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55356168746948</t>
+    <t xml:space="preserve">4.55356216430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.54562568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53047323226929</t>
+    <t xml:space="preserve">4.53047275543213</t>
   </si>
   <si>
     <t xml:space="preserve">4.44100427627563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60767650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57376480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37823057174683</t>
+    <t xml:space="preserve">4.6076774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57376575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37823104858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.43378877639771</t>
@@ -2798,13 +2798,13 @@
     <t xml:space="preserve">4.37895202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43018007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59974002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480243682861</t>
+    <t xml:space="preserve">4.43018054962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59974050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480195999146</t>
   </si>
   <si>
     <t xml:space="preserve">4.65601921081543</t>
@@ -2813,25 +2813,25 @@
     <t xml:space="preserve">4.6516900062561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47852277755737</t>
+    <t xml:space="preserve">4.47852325439453</t>
   </si>
   <si>
     <t xml:space="preserve">4.50882768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47996664047241</t>
+    <t xml:space="preserve">4.47996616363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.46770048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33277463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3183445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27577447891235</t>
+    <t xml:space="preserve">4.3327751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31834411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2757740020752</t>
   </si>
   <si>
     <t xml:space="preserve">4.25701427459717</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">4.37967348098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43739604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52398014068604</t>
+    <t xml:space="preserve">4.43739652633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52397966384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.4994478225708</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">4.33421754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39266109466553</t>
+    <t xml:space="preserve">4.39266157150269</t>
   </si>
   <si>
     <t xml:space="preserve">4.37750959396362</t>
@@ -2861,298 +2861,298 @@
     <t xml:space="preserve">4.46481418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47347211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688993453979</t>
+    <t xml:space="preserve">4.473473072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688945770264</t>
   </si>
   <si>
     <t xml:space="preserve">4.35081338882446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672159194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30319118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35586357116699</t>
+    <t xml:space="preserve">4.24547052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30319213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35586404800415</t>
   </si>
   <si>
     <t xml:space="preserve">4.5109920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56727075576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62499380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69714546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9006175994873</t>
+    <t xml:space="preserve">4.56727123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62499332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69714689254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061712265015</t>
   </si>
   <si>
     <t xml:space="preserve">4.97926378250122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0492525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1870641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434574127197</t>
+    <t xml:space="preserve">5.04925203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434478759766</t>
   </si>
   <si>
     <t xml:space="preserve">5.40063619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46773815155029</t>
+    <t xml:space="preserve">5.46773862838745</t>
   </si>
   <si>
     <t xml:space="preserve">5.46701669692993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44176340103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011737823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28663492202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29962158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31188821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4590802192688</t>
+    <t xml:space="preserve">5.44176292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011690139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28663444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29962205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31188726425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">5.41506671905518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39197778701782</t>
+    <t xml:space="preserve">5.39197826385498</t>
   </si>
   <si>
     <t xml:space="preserve">5.48361158370972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63585376739502</t>
+    <t xml:space="preserve">5.63585424423218</t>
   </si>
   <si>
     <t xml:space="preserve">5.50092792510986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52906847000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51175117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57308149337769</t>
+    <t xml:space="preserve">5.52906799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57308053970337</t>
   </si>
   <si>
     <t xml:space="preserve">5.53989028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55720710754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73398113250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68131065368652</t>
+    <t xml:space="preserve">5.55720806121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73398208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68130970001221</t>
   </si>
   <si>
     <t xml:space="preserve">5.71017169952393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75418376922607</t>
+    <t xml:space="preserve">5.75418472290039</t>
   </si>
   <si>
     <t xml:space="preserve">5.83427429199219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72604513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86024856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232336044312</t>
+    <t xml:space="preserve">5.72604465484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86024808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232383728027</t>
   </si>
   <si>
     <t xml:space="preserve">5.89416074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95476913452148</t>
+    <t xml:space="preserve">5.9547700881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.08031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12669563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13258504867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246212005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98828983306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84841060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83147859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69601678848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69012594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362417221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7931957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76669263839722</t>
+    <t xml:space="preserve">6.12669515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1325855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246164321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98828935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84841108322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83147811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8712329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69601631164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69012641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79319524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76669216156006</t>
   </si>
   <si>
     <t xml:space="preserve">5.69086265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75344038009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79025077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97062015533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89552736282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80497455596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74828672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356294631958</t>
+    <t xml:space="preserve">5.75344085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79025030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062110900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8955283164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8049750328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74828720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356246948242</t>
   </si>
   <si>
     <t xml:space="preserve">5.70926809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69159841537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79098701477051</t>
+    <t xml:space="preserve">5.69159889221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79098749160767</t>
   </si>
   <si>
     <t xml:space="preserve">5.74534225463867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58705806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52447986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6304931640625</t>
+    <t xml:space="preserve">5.74092483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58705759048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52448081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63049411773682</t>
   </si>
   <si>
     <t xml:space="preserve">5.58043193817139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4567494392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.590003490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165796279907</t>
+    <t xml:space="preserve">5.45674991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000253677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165891647339</t>
   </si>
   <si>
     <t xml:space="preserve">5.63270235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5981011390686</t>
+    <t xml:space="preserve">5.59810066223145</t>
   </si>
   <si>
     <t xml:space="preserve">5.63932800292969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56644439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57675123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319129943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263933181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34411001205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975477218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582941055298</t>
+    <t xml:space="preserve">5.5664439201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57675075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38975524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582893371582</t>
   </si>
   <si>
     <t xml:space="preserve">5.400062084198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48325300216675</t>
+    <t xml:space="preserve">5.48325347900391</t>
   </si>
   <si>
     <t xml:space="preserve">5.52153587341309</t>
@@ -3161,16 +3161,16 @@
     <t xml:space="preserve">5.4611668586731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4979772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44349718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42141151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59221124649048</t>
+    <t xml:space="preserve">5.49797677993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44349813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42141199111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59221220016479</t>
   </si>
   <si>
     <t xml:space="preserve">5.55613708496094</t>
@@ -3179,67 +3179,67 @@
     <t xml:space="preserve">5.53920459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6592059135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67761182785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429559707642</t>
+    <t xml:space="preserve">5.65920639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67761135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429607391357</t>
   </si>
   <si>
     <t xml:space="preserve">5.54141330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49871349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58190441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53257894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57233333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4442343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662340164185</t>
+    <t xml:space="preserve">5.49871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58190488815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472547531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57233381271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44423341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662244796753</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705232620239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0312237739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
+    <t xml:space="preserve">5.03122329711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312696456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42435646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6032543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92718458175659</t>
+    <t xml:space="preserve">5.42435693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60325479507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92718362808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.92423963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04571342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853401184082</t>
+    <t xml:space="preserve">6.04571294784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853544235229</t>
   </si>
   <si>
     <t xml:space="preserve">5.90436220169067</t>
@@ -3248,25 +3248,25 @@
     <t xml:space="preserve">5.95516014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97209310531616</t>
+    <t xml:space="preserve">5.97209358215332</t>
   </si>
   <si>
     <t xml:space="preserve">5.97945499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0103759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0611743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737195968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24817037582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2356538772583</t>
+    <t xml:space="preserve">6.01037549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06117391586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24817085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">6.25921249389648</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">6.09724712371826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0435037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04129648208618</t>
+    <t xml:space="preserve">6.04350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04129695892334</t>
   </si>
   <si>
     <t xml:space="preserve">6.0228910446167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00743055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97798252105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04424047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92571210861206</t>
+    <t xml:space="preserve">6.00743103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97798299789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04423999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9257116317749</t>
   </si>
   <si>
     <t xml:space="preserve">5.922767162323</t>
@@ -3308,43 +3308,43 @@
     <t xml:space="preserve">6.00890302658081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01700162887573</t>
+    <t xml:space="preserve">6.01700210571289</t>
   </si>
   <si>
     <t xml:space="preserve">5.94190883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08914995193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14362907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09283018112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22608423233032</t>
+    <t xml:space="preserve">6.08914947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14362859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09283065795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22608375549316</t>
   </si>
   <si>
     <t xml:space="preserve">6.18043947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57357215881348</t>
+    <t xml:space="preserve">6.57357358932495</t>
   </si>
   <si>
     <t xml:space="preserve">6.46166944503784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58019781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57062673568726</t>
+    <t xml:space="preserve">6.58019828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58755970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081159591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57062721252441</t>
   </si>
   <si>
     <t xml:space="preserve">6.50289678573608</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">6.52203798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4476842880249</t>
+    <t xml:space="preserve">6.44768571853638</t>
   </si>
   <si>
     <t xml:space="preserve">6.43942356109619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44242811203003</t>
+    <t xml:space="preserve">6.44242763519287</t>
   </si>
   <si>
     <t xml:space="preserve">6.3530535697937</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">6.25992488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30874156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30949306488037</t>
+    <t xml:space="preserve">6.30874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30949401855469</t>
   </si>
   <si>
     <t xml:space="preserve">6.15177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17430543899536</t>
+    <t xml:space="preserve">6.17430639266968</t>
   </si>
   <si>
     <t xml:space="preserve">6.15853357315063</t>
@@ -3392,37 +3392,37 @@
     <t xml:space="preserve">6.42290067672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42590522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34404134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38384580612183</t>
+    <t xml:space="preserve">6.42590379714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34404182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38384675979614</t>
   </si>
   <si>
     <t xml:space="preserve">6.22162199020386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24715757369995</t>
+    <t xml:space="preserve">6.24715662002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.35530662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35981369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756063461304</t>
+    <t xml:space="preserve">6.35981321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756015777588</t>
   </si>
   <si>
     <t xml:space="preserve">6.23589181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15552997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06615591049194</t>
+    <t xml:space="preserve">6.15553045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0661563873291</t>
   </si>
   <si>
     <t xml:space="preserve">5.99105262756348</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">5.94824266433716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88815927505493</t>
+    <t xml:space="preserve">5.88815975189209</t>
   </si>
   <si>
     <t xml:space="preserve">5.89116334915161</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">5.9685206413269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85962009429932</t>
+    <t xml:space="preserve">5.85962057113647</t>
   </si>
   <si>
     <t xml:space="preserve">5.72743654251099</t>
@@ -3452,112 +3452,112 @@
     <t xml:space="preserve">5.91294431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07141256332397</t>
+    <t xml:space="preserve">6.07141351699829</t>
   </si>
   <si>
     <t xml:space="preserve">6.08568334579468</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16980028152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19984197616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14426422119141</t>
+    <t xml:space="preserve">6.16979932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19984102249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14426469802856</t>
   </si>
   <si>
     <t xml:space="preserve">6.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12999439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05639266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2381443977356</t>
+    <t xml:space="preserve">6.12999486923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05639314651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23814392089844</t>
   </si>
   <si>
     <t xml:space="preserve">6.25166368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32826900482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34028577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33352661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37858867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44843673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49725389480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444488525391</t>
+    <t xml:space="preserve">6.32826948165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33352613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37858915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44843626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49725294113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444440841675</t>
   </si>
   <si>
     <t xml:space="preserve">6.44393014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47472333908081</t>
+    <t xml:space="preserve">6.47472238540649</t>
   </si>
   <si>
     <t xml:space="preserve">6.39060592651367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44468116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50551462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4251537322998</t>
+    <t xml:space="preserve">6.44467973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326204299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50551605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42515325546265</t>
   </si>
   <si>
     <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54757404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56034088134766</t>
+    <t xml:space="preserve">6.54757308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034135818481</t>
   </si>
   <si>
     <t xml:space="preserve">6.48899269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34479284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885467529297</t>
+    <t xml:space="preserve">6.34479236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885419845581</t>
   </si>
   <si>
     <t xml:space="preserve">6.27569675445557</t>
@@ -3566,28 +3566,28 @@
     <t xml:space="preserve">6.16304063796997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22537612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20960426330566</t>
+    <t xml:space="preserve">6.22537660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20960521697998</t>
   </si>
   <si>
     <t xml:space="preserve">6.21411180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00231838226318</t>
+    <t xml:space="preserve">6.00231695175171</t>
   </si>
   <si>
     <t xml:space="preserve">6.07742166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16153907775879</t>
+    <t xml:space="preserve">6.16153860092163</t>
   </si>
   <si>
     <t xml:space="preserve">6.12623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10445976257324</t>
+    <t xml:space="preserve">6.10445928573608</t>
   </si>
   <si>
     <t xml:space="preserve">5.98279094696045</t>
@@ -3605,28 +3605,28 @@
     <t xml:space="preserve">6.13374996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572456359863</t>
+    <t xml:space="preserve">6.11872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572504043579</t>
   </si>
   <si>
     <t xml:space="preserve">6.05038404464722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.994056224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92721366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95650434494019</t>
+    <t xml:space="preserve">5.99405574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92721319198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95650482177734</t>
   </si>
   <si>
     <t xml:space="preserve">6.01057958602905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01733875274658</t>
+    <t xml:space="preserve">6.01733827590942</t>
   </si>
   <si>
     <t xml:space="preserve">6.01808929443359</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">5.9790358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02484893798828</t>
+    <t xml:space="preserve">6.02484941482544</t>
   </si>
   <si>
     <t xml:space="preserve">6.08493280410767</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">6.06840944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829776763916</t>
+    <t xml:space="preserve">6.16829824447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0676589012146</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">5.98654651641846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03386211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01508569717407</t>
+    <t xml:space="preserve">6.03386163711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01508522033691</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879861831665</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">6.03686571121216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88215160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89491939544678</t>
+    <t xml:space="preserve">5.88215112686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89491891860962</t>
   </si>
   <si>
     <t xml:space="preserve">5.89642143249512</t>
@@ -3686,25 +3686,25 @@
     <t xml:space="preserve">5.93772840499878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401405334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92045450210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95124673843384</t>
+    <t xml:space="preserve">5.96401500701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92045402526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.951247215271</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489110946655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05188655853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02635097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95725536346436</t>
+    <t xml:space="preserve">6.05188608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02635145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9572548866272</t>
   </si>
   <si>
     <t xml:space="preserve">6.01583671569824</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">5.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8513560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00277090072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11575508117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18723487854004</t>
+    <t xml:space="preserve">5.85135650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00277042388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1157546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1872353553772</t>
   </si>
   <si>
     <t xml:space="preserve">6.21106100082397</t>
@@ -3731,25 +3731,25 @@
     <t xml:space="preserve">6.11959791183472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.191077709198</t>
+    <t xml:space="preserve">6.19107818603516</t>
   </si>
   <si>
     <t xml:space="preserve">6.16033363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97971200942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94819974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819187164307</t>
+    <t xml:space="preserve">5.97971248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9481987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9136118888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92052984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819139480591</t>
   </si>
   <si>
     <t xml:space="preserve">5.96357202529907</t>
@@ -3761,28 +3761,28 @@
     <t xml:space="preserve">5.98586130142212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02044868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02890253067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348943710327</t>
+    <t xml:space="preserve">6.02044820785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02890300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348896026611</t>
   </si>
   <si>
     <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97740697860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735828399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08885335922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14957332611084</t>
+    <t xml:space="preserve">5.97740650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08885383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.149573802948</t>
   </si>
   <si>
     <t xml:space="preserve">6.0196795463562</t>
@@ -3791,25 +3791,25 @@
     <t xml:space="preserve">5.96510887145996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90131521224976</t>
+    <t xml:space="preserve">5.90131568908691</t>
   </si>
   <si>
     <t xml:space="preserve">5.90208387374878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95511770248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93129014968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99815940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93513345718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92975330352783</t>
+    <t xml:space="preserve">5.95511674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93129110336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99815845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.935133934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92975378036499</t>
   </si>
   <si>
     <t xml:space="preserve">5.83367872238159</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">5.77833938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756237030029</t>
+    <t xml:space="preserve">5.78756284713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.66842937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71454572677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39941930770874</t>
+    <t xml:space="preserve">5.76373624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71454524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3994197845459</t>
   </si>
   <si>
     <t xml:space="preserve">5.38097286224365</t>
@@ -3842,46 +3842,46 @@
     <t xml:space="preserve">5.25722789764404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30257558822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33408832550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44092321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39403820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33946847915649</t>
+    <t xml:space="preserve">5.30257511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33408784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4409236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39403915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33946800231934</t>
   </si>
   <si>
     <t xml:space="preserve">5.25492238998413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22110414505005</t>
+    <t xml:space="preserve">5.22110366821289</t>
   </si>
   <si>
     <t xml:space="preserve">5.11196231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17883014678955</t>
+    <t xml:space="preserve">5.17191362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3056492805481</t>
+    <t xml:space="preserve">5.30564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">5.31794738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18651723861694</t>
+    <t xml:space="preserve">5.18651628494263</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958257675171</t>
@@ -3890,46 +3890,46 @@
     <t xml:space="preserve">5.24954223632812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30795621871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44246053695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54160976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51317167282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781610488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54622173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772706985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56159353256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925603866577</t>
+    <t xml:space="preserve">5.30795574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44246101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54161024093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51317119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5462212562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772611618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56159400939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925413131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.5577507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57696628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57389116287231</t>
+    <t xml:space="preserve">5.57696533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57389163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.60617303848267</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">5.45245218276978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50318002700806</t>
+    <t xml:space="preserve">5.5031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">5.45629501342773</t>
@@ -3950,16 +3950,16 @@
     <t xml:space="preserve">5.49549436569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44707155227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4324688911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41248607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34177446365356</t>
+    <t xml:space="preserve">5.44707202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41248559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34177398681641</t>
   </si>
   <si>
     <t xml:space="preserve">5.34331130981445</t>
@@ -3971,46 +3971,46 @@
     <t xml:space="preserve">5.41479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49472618103027</t>
+    <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
     <t xml:space="preserve">5.23878145217896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21802949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15500450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19189739227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0650782585144</t>
+    <t xml:space="preserve">5.2180290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15500354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19189643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06507778167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.01588726043701</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16730165481567</t>
+    <t xml:space="preserve">5.16730213165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.23493814468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1511607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14193773269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0758376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0927472114563</t>
+    <t xml:space="preserve">5.15039300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15116119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14193820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07583856582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09274768829346</t>
   </si>
   <si>
     <t xml:space="preserve">5.14731788635254</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">5.18497896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11349964141846</t>
+    <t xml:space="preserve">5.11350011825562</t>
   </si>
   <si>
     <t xml:space="preserve">5.25338506698608</t>
@@ -4037,58 +4037,58 @@
     <t xml:space="preserve">5.32486486434937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40787363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38789033889771</t>
+    <t xml:space="preserve">5.40787315368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38788986206055</t>
   </si>
   <si>
     <t xml:space="preserve">5.41555976867676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51240348815918</t>
+    <t xml:space="preserve">5.51240253448486</t>
   </si>
   <si>
     <t xml:space="preserve">5.47243595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34100484848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3264012336731</t>
+    <t xml:space="preserve">5.34100580215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32640218734741</t>
   </si>
   <si>
     <t xml:space="preserve">5.32717084884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32025241851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35022878646851</t>
+    <t xml:space="preserve">5.32025337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35022830963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.23186445236206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27490568161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38250970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30718660354614</t>
+    <t xml:space="preserve">5.27490615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38250923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
     <t xml:space="preserve">5.26766920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26845932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41546535491943</t>
+    <t xml:space="preserve">5.26846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41546487808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.33642959594727</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">5.35776948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24712038040161</t>
+    <t xml:space="preserve">5.24712133407593</t>
   </si>
   <si>
     <t xml:space="preserve">5.08272790908813</t>
@@ -4139,58 +4139,58 @@
     <t xml:space="preserve">5.08588981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97603130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01396799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99025774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89383459091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17598962783813</t>
+    <t xml:space="preserve">4.97603178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01396751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99025726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89383506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17598915100098</t>
   </si>
   <si>
     <t xml:space="preserve">5.2155065536499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87960910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87644672393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7065224647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52237176895142</t>
+    <t xml:space="preserve">4.87960863113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87644720077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70652294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48127365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52237129211426</t>
   </si>
   <si>
     <t xml:space="preserve">4.77291202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53580760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52711391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59903478622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60456848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60298728942871</t>
+    <t xml:space="preserve">4.53580617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52711343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60456800460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60298633575439</t>
   </si>
   <si>
     <t xml:space="preserve">4.52079057693481</t>
@@ -4199,16 +4199,16 @@
     <t xml:space="preserve">4.55240488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60219717025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51209688186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566564559937</t>
+    <t xml:space="preserve">4.60219621658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51209735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566516876221</t>
   </si>
   <si>
     <t xml:space="preserve">4.80294561386108</t>
@@ -4217,82 +4217,82 @@
     <t xml:space="preserve">4.81875228881836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82428407669067</t>
+    <t xml:space="preserve">4.79583215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82428550720215</t>
   </si>
   <si>
     <t xml:space="preserve">4.829026222229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90648078918457</t>
+    <t xml:space="preserve">4.92544889450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90648031234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.87486696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98709583282471</t>
+    <t xml:space="preserve">4.98709630966187</t>
   </si>
   <si>
     <t xml:space="preserve">4.96891784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93809509277344</t>
+    <t xml:space="preserve">4.93809461593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90173816680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88514089584351</t>
+    <t xml:space="preserve">4.90173864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88514137268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.87249565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7523627281189</t>
+    <t xml:space="preserve">4.75236320495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.82349443435669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81559085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79978370666504</t>
+    <t xml:space="preserve">4.81559038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79978322982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.91596412658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91438388824463</t>
+    <t xml:space="preserve">4.91438436508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.87881803512573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93888473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89541578292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78555679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74841070175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64171457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721277236938</t>
+    <t xml:space="preserve">4.93888425827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89541482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78555727005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74841117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64171361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6172137260437</t>
   </si>
   <si>
     <t xml:space="preserve">4.72628116607666</t>
@@ -4301,46 +4301,46 @@
     <t xml:space="preserve">4.6140513420105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69229555130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73181438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69308662414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69150590896606</t>
+    <t xml:space="preserve">4.69229602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73181343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74999141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69308710098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69150543212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.83930110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84720468521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84641456604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88909339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87012386322021</t>
+    <t xml:space="preserve">4.84720420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84641408920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88909244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87012481689453</t>
   </si>
   <si>
     <t xml:space="preserve">4.77686357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68202209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70573234558105</t>
+    <t xml:space="preserve">4.6820216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70573282241821</t>
   </si>
   <si>
     <t xml:space="preserve">4.66700506210327</t>
@@ -4349,70 +4349,70 @@
     <t xml:space="preserve">4.76500797271729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73260354995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62037420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52790355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3318977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25839471817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21492576599121</t>
+    <t xml:space="preserve">4.73260402679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62037372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52790403366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33189725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25839519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21492624282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.39117383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26787948608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30107307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33822011947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31925249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2291522026062</t>
+    <t xml:space="preserve">4.26787996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30107402801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33822059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31925201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22915172576904</t>
   </si>
   <si>
     <t xml:space="preserve">4.2852668762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35718822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27499198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32794618606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26945972442627</t>
+    <t xml:space="preserve">4.35718870162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27499294281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32794523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26946020126343</t>
   </si>
   <si>
     <t xml:space="preserve">4.12561655044556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09084177017212</t>
+    <t xml:space="preserve">4.19911956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17382764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09084129333496</t>
   </si>
   <si>
     <t xml:space="preserve">4.15960168838501</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">4.15090799331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14300394058228</t>
+    <t xml:space="preserve">4.14300489425659</t>
   </si>
   <si>
     <t xml:space="preserve">4.09242248535156</t>
@@ -4430,58 +4430,58 @@
     <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82133316993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95173978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831274986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90080332756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88108563423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90244603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89053320884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06922388076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99610424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00514221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03636121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06758165359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13412857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11440992355347</t>
+    <t xml:space="preserve">3.8213324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95173954963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0330753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606624603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90080285072327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88108491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90244579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89053344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683652877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93818402290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06922483444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99610447883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0051417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03636169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06758117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13412809371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11441040039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">4.10783767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13659286499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19163846969604</t>
+    <t xml:space="preserve">4.13659238815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19163751602173</t>
   </si>
   <si>
     <t xml:space="preserve">4.18753004074097</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">4.18342208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11030197143555</t>
+    <t xml:space="preserve">4.11030244827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05443572998047</t>
@@ -4517,25 +4517,25 @@
     <t xml:space="preserve">4.06347322463989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97022533416748</t>
+    <t xml:space="preserve">3.97022581100464</t>
   </si>
   <si>
     <t xml:space="preserve">3.94639992713928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9546160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85767078399658</t>
+    <t xml:space="preserve">3.95461559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.857670545578</t>
   </si>
   <si>
     <t xml:space="preserve">3.81412768363953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90614366531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86136770248413</t>
+    <t xml:space="preserve">3.90614318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86136722564697</t>
   </si>
   <si>
     <t xml:space="preserve">3.84288239479065</t>
@@ -4547,61 +4547,61 @@
     <t xml:space="preserve">3.94845390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10085439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06593751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04211235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02321577072144</t>
+    <t xml:space="preserve">3.98871064186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10085487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06593799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04211282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02321672439575</t>
   </si>
   <si>
     <t xml:space="preserve">4.0417013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679829597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419260978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97186851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81535935401917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73607921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5483500957489</t>
+    <t xml:space="preserve">4.05073881149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679781913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419213294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97186827659607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81536030769348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73607850074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53438401222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54835057258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.49001932144165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47030162811279</t>
+    <t xml:space="preserve">3.47030138969421</t>
   </si>
   <si>
     <t xml:space="preserve">3.57956981658936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66706705093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55040407180786</t>
+    <t xml:space="preserve">3.66706728935242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55040383338928</t>
   </si>
   <si>
     <t xml:space="preserve">3.42593693733215</t>
@@ -4610,115 +4610,115 @@
     <t xml:space="preserve">3.38609075546265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44154691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34870982170105</t>
+    <t xml:space="preserve">3.44154620170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34870934486389</t>
   </si>
   <si>
     <t xml:space="preserve">3.28873491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34542298316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37910723686218</t>
+    <t xml:space="preserve">3.34542322158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37910771369934</t>
   </si>
   <si>
     <t xml:space="preserve">3.46290707588196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49823474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51918530464172</t>
+    <t xml:space="preserve">3.49823451042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51918458938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.48426818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44606494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52740001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764432907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60257411003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71512842178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6740505695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7126636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72950577735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77304935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784945487976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84452533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217591285706</t>
+    <t xml:space="preserve">3.44606518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52740049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60257387161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71512818336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405033111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71266412734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72950625419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77304887771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75785040855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8445258140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217638969421</t>
   </si>
   <si>
     <t xml:space="preserve">3.93037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95913410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11605405807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14727306365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274188995361</t>
+    <t xml:space="preserve">3.95913362503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11605358123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14727258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274236679077</t>
   </si>
   <si>
     <t xml:space="preserve">4.1982102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22203540802002</t>
+    <t xml:space="preserve">4.22203636169434</t>
   </si>
   <si>
     <t xml:space="preserve">4.23682451248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17767143249512</t>
+    <t xml:space="preserve">4.17767095565796</t>
   </si>
   <si>
     <t xml:space="preserve">4.15959739685059</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23353815078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16534757614136</t>
+    <t xml:space="preserve">4.2335376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
     <t xml:space="preserve">4.19492387771606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2179274559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31323003768921</t>
+    <t xml:space="preserve">4.21792793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31323051452637</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
@@ -4730,37 +4730,37 @@
     <t xml:space="preserve">4.27708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29186964035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25079011917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29022645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27050876617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31158685684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31487274169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15302419662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14891672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14563035964966</t>
+    <t xml:space="preserve">4.29186868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2507905960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29022598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27050828933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31158638000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31487321853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1530237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14891719818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1456298828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.14645147323608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21464204788208</t>
+    <t xml:space="preserve">4.21464157104492</t>
   </si>
   <si>
     <t xml:space="preserve">4.16863346099854</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">4.13248491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24832630157471</t>
+    <t xml:space="preserve">4.24832582473755</t>
   </si>
   <si>
     <t xml:space="preserve">4.35430860519409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50794219970703</t>
+    <t xml:space="preserve">4.50794124603271</t>
   </si>
   <si>
     <t xml:space="preserve">4.50054740905762</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">4.6016001701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59995698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54819822311401</t>
+    <t xml:space="preserve">4.59995746612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54819774627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.62542581558228</t>
@@ -4811,25 +4811,25 @@
     <t xml:space="preserve">4.7716646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73222923278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73551559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64760828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6418571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65548467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6810359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66570520401001</t>
+    <t xml:space="preserve">4.73222970962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73551511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64760780334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64185667037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65548515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68103551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66570472717285</t>
   </si>
   <si>
     <t xml:space="preserve">4.66996335983276</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">4.67166709899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6273775100708</t>
+    <t xml:space="preserve">4.62737798690796</t>
   </si>
   <si>
     <t xml:space="preserve">4.59160566329956</t>
@@ -4856,13 +4856,13 @@
     <t xml:space="preserve">4.58138513565063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56435060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55327796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54816865921021</t>
+    <t xml:space="preserve">4.5643515586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55327844619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54816818237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.60864019393921</t>
@@ -4883,13 +4883,13 @@
     <t xml:space="preserve">4.55924034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55668544769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52687549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46214437484741</t>
+    <t xml:space="preserve">4.55668592453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46214485168457</t>
   </si>
   <si>
     <t xml:space="preserve">4.48003149032593</t>
@@ -4898,40 +4898,40 @@
     <t xml:space="preserve">4.45788669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51920938491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52857828140259</t>
+    <t xml:space="preserve">4.51920986175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">4.42892742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48428964614868</t>
+    <t xml:space="preserve">4.48428916931152</t>
   </si>
   <si>
     <t xml:space="preserve">4.5149507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54305791854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.509840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53113412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53028154373169</t>
+    <t xml:space="preserve">4.54305744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50984144210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5311336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53028202056885</t>
   </si>
   <si>
     <t xml:space="preserve">4.53624391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45192384719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5686092376709</t>
+    <t xml:space="preserve">4.45192432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56860971450806</t>
   </si>
   <si>
     <t xml:space="preserve">4.46810674667358</t>
@@ -4943,34 +4943,34 @@
     <t xml:space="preserve">4.50302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58905029296875</t>
+    <t xml:space="preserve">4.58905076980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.66740846633911</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68784952163696</t>
+    <t xml:space="preserve">4.68784999847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.69040489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59245777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65378141403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69125604629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77813148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79261064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77131843566895</t>
+    <t xml:space="preserve">4.59245729446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65378093719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69125652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77813196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79261112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77131795883179</t>
   </si>
   <si>
     <t xml:space="preserve">4.75683879852295</t>
@@ -4991,16 +4991,16 @@
     <t xml:space="preserve">4.90333414077759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86160039901733</t>
+    <t xml:space="preserve">4.86159992218018</t>
   </si>
   <si>
     <t xml:space="preserve">4.8718204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90503787994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94762325286865</t>
+    <t xml:space="preserve">4.90503740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94762372970581</t>
   </si>
   <si>
     <t xml:space="preserve">4.97402667999268</t>
@@ -5009,10 +5009,10 @@
     <t xml:space="preserve">5.05153322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13414859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15799713134766</t>
+    <t xml:space="preserve">5.1341495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15799760818481</t>
   </si>
   <si>
     <t xml:space="preserve">5.18695592880249</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">5.2508339881897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27979278564453</t>
+    <t xml:space="preserve">5.27979326248169</t>
   </si>
   <si>
     <t xml:space="preserve">5.19376945495605</t>
@@ -5030,10 +5030,10 @@
     <t xml:space="preserve">5.19462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18440103530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24827909469604</t>
+    <t xml:space="preserve">5.18440008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2482795715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.21165561676025</t>
@@ -5054,10 +5054,10 @@
     <t xml:space="preserve">5.12563180923462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12733602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09156322479248</t>
+    <t xml:space="preserve">5.12733554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09156370162964</t>
   </si>
   <si>
     <t xml:space="preserve">5.02598142623901</t>
@@ -5066,10 +5066,10 @@
     <t xml:space="preserve">5.1179666519165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14351844787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13670444488525</t>
+    <t xml:space="preserve">5.14351749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13670492172241</t>
   </si>
   <si>
     <t xml:space="preserve">5.08049154281616</t>
@@ -5090,34 +5090,34 @@
     <t xml:space="preserve">4.98935747146606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07452964782715</t>
+    <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
     <t xml:space="preserve">5.14948034286499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10774660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17332792282104</t>
+    <t xml:space="preserve">5.10774612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15288686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1733283996582</t>
   </si>
   <si>
     <t xml:space="preserve">5.17247676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20484161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16992092132568</t>
+    <t xml:space="preserve">5.20484209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16992139816284</t>
   </si>
   <si>
     <t xml:space="preserve">5.20228672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19632482528687</t>
+    <t xml:space="preserve">5.19632387161255</t>
   </si>
   <si>
     <t xml:space="preserve">5.15884971618652</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">5.17843866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22698593139648</t>
+    <t xml:space="preserve">5.22698640823364</t>
   </si>
   <si>
     <t xml:space="preserve">5.23635530471802</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">5.14266633987427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1929178237915</t>
+    <t xml:space="preserve">5.19291830062866</t>
   </si>
   <si>
     <t xml:space="preserve">5.17503213882446</t>
@@ -5168,22 +5168,22 @@
     <t xml:space="preserve">5.34622716903687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34452342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3607063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39647769927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44836711883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4501256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4703540802002</t>
+    <t xml:space="preserve">5.34452390670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36070585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39647817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44836759567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45012664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47035455703735</t>
   </si>
   <si>
     <t xml:space="preserve">5.55038642883301</t>
@@ -5195,7 +5195,7 @@
     <t xml:space="preserve">5.5160870552063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46155977249146</t>
+    <t xml:space="preserve">5.4615592956543</t>
   </si>
   <si>
     <t xml:space="preserve">5.34370946884155</t>
@@ -5210,13 +5210,13 @@
     <t xml:space="preserve">5.21706485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20914936065674</t>
+    <t xml:space="preserve">5.20914888381958</t>
   </si>
   <si>
     <t xml:space="preserve">5.28302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36129903793335</t>
+    <t xml:space="preserve">5.36129951477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.32436037063599</t>
@@ -5225,13 +5225,13 @@
     <t xml:space="preserve">5.23553371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17484998703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21002864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26719427108765</t>
+    <t xml:space="preserve">5.17484903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21002817153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2671947479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.33227634429932</t>
@@ -5246,10 +5246,10 @@
     <t xml:space="preserve">5.39120149612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4589204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43957281112671</t>
+    <t xml:space="preserve">5.45892095565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43957233428955</t>
   </si>
   <si>
     <t xml:space="preserve">5.41406774520874</t>
@@ -5258,19 +5258,19 @@
     <t xml:space="preserve">5.40791130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39383935928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36745500564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46067953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44484901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45188474655151</t>
+    <t xml:space="preserve">5.39383983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36745595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46068000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44484949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45188522338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.38768339157104</t>
@@ -5285,55 +5285,55 @@
     <t xml:space="preserve">5.48442602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47475147247314</t>
+    <t xml:space="preserve">5.4747519493103</t>
   </si>
   <si>
     <t xml:space="preserve">5.35338354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31644582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25488185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23113632202148</t>
+    <t xml:space="preserve">5.31644535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25488233566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23113584518433</t>
   </si>
   <si>
     <t xml:space="preserve">5.14582681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09041976928711</t>
+    <t xml:space="preserve">5.09042024612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856317520142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97872638702393</t>
+    <t xml:space="preserve">4.97872591018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88726091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88462162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92595767974854</t>
+    <t xml:space="preserve">4.88726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88462114334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92595672607422</t>
   </si>
   <si>
     <t xml:space="preserve">4.92859601974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02270030975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08426380157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06051826477051</t>
+    <t xml:space="preserve">5.02269983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08426332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06051731109619</t>
   </si>
   <si>
     <t xml:space="preserve">5.03325366973877</t>
@@ -5342,16 +5342,16 @@
     <t xml:space="preserve">5.05172300338745</t>
   </si>
   <si>
-    <t xml:space="preserve">5.049964427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96641302108765</t>
+    <t xml:space="preserve">5.04996347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01390504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99719476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9664134979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.00511026382446</t>
@@ -5378,16 +5378,16 @@
     <t xml:space="preserve">5.30589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37712955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41758489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40527248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38152694702148</t>
+    <t xml:space="preserve">5.37713003158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4175853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40527296066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38152742385864</t>
   </si>
   <si>
     <t xml:space="preserve">5.3542628288269</t>
@@ -5396,19 +5396,19 @@
     <t xml:space="preserve">5.39032173156738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43869256973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49585914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54247093200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63305807113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70781278610229</t>
+    <t xml:space="preserve">5.43869304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49585962295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54247140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63305759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70781326293945</t>
   </si>
   <si>
     <t xml:space="preserve">5.64273166656494</t>
@@ -5417,40 +5417,40 @@
     <t xml:space="preserve">5.6207447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61282920837402</t>
+    <t xml:space="preserve">5.61282968521118</t>
   </si>
   <si>
     <t xml:space="preserve">5.64097309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65680408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66559839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6576828956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70429515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72276449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.747389793396</t>
+    <t xml:space="preserve">5.65680360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65768337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70429563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72276496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74738931655884</t>
   </si>
   <si>
     <t xml:space="preserve">5.760582447052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75882291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7535457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77465343475342</t>
+    <t xml:space="preserve">5.75882339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75354623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77465391159058</t>
   </si>
   <si>
     <t xml:space="preserve">5.73155927658081</t>
@@ -5468,40 +5468,40 @@
     <t xml:space="preserve">5.85996294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89250373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86436080932617</t>
+    <t xml:space="preserve">5.89250421524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86436033248901</t>
   </si>
   <si>
     <t xml:space="preserve">5.86963701248169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90921354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91097259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90041923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91888809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82742214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88458824157715</t>
+    <t xml:space="preserve">5.90921401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.910973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90041971206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91888856887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82742261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91361141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88458871841431</t>
   </si>
   <si>
     <t xml:space="preserve">5.89162397384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92504453659058</t>
+    <t xml:space="preserve">5.92504501342773</t>
   </si>
   <si>
     <t xml:space="preserve">5.86787843704224</t>
@@ -5510,7 +5510,7 @@
     <t xml:space="preserve">5.97165679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98660755157471</t>
+    <t xml:space="preserve">5.98660802841187</t>
   </si>
   <si>
     <t xml:space="preserve">5.93647766113281</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">5.83621740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82390403747559</t>
+    <t xml:space="preserve">5.8239049911499</t>
   </si>
   <si>
     <t xml:space="preserve">5.85908365249634</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">5.65551042556763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68550109863281</t>
+    <t xml:space="preserve">5.68550157546997</t>
   </si>
   <si>
     <t xml:space="preserve">5.76275014877319</t>
@@ -5555,7 +5555,7 @@
     <t xml:space="preserve">5.61824941635132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56826448440552</t>
+    <t xml:space="preserve">5.56826496124268</t>
   </si>
   <si>
     <t xml:space="preserve">5.52191591262817</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">5.33833694458008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37741565704346</t>
+    <t xml:space="preserve">5.3774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.34651613235474</t>
@@ -5579,7 +5579,7 @@
     <t xml:space="preserve">5.37468910217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38468599319458</t>
+    <t xml:space="preserve">5.38468551635742</t>
   </si>
   <si>
     <t xml:space="preserve">5.32652235031128</t>
@@ -5603,10 +5603,10 @@
     <t xml:space="preserve">5.39831781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31925249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35469532012939</t>
+    <t xml:space="preserve">5.31925201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35469579696655</t>
   </si>
   <si>
     <t xml:space="preserve">5.48738145828247</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">5.54463577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57917070388794</t>
+    <t xml:space="preserve">5.5791711807251</t>
   </si>
   <si>
     <t xml:space="preserve">5.57099151611328</t>
@@ -5627,19 +5627,19 @@
     <t xml:space="preserve">5.5900764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64278697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57008266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57190036773682</t>
+    <t xml:space="preserve">5.64278745651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5700831413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57190084457397</t>
   </si>
   <si>
     <t xml:space="preserve">5.5200982093811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54645347595215</t>
+    <t xml:space="preserve">5.54645395278931</t>
   </si>
   <si>
     <t xml:space="preserve">5.51646327972412</t>
@@ -5648,22 +5648,22 @@
     <t xml:space="preserve">5.52645969390869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51373624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5291862487793</t>
+    <t xml:space="preserve">5.51373672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52918672561646</t>
   </si>
   <si>
     <t xml:space="preserve">5.60552644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56099462509155</t>
+    <t xml:space="preserve">5.56099510192871</t>
   </si>
   <si>
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375801086426</t>
+    <t xml:space="preserve">5.44375848770142</t>
   </si>
   <si>
     <t xml:space="preserve">5.49465131759644</t>
@@ -5675,22 +5675,22 @@
     <t xml:space="preserve">5.36105728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29380512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17929553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18656587600708</t>
+    <t xml:space="preserve">5.29380464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1792950630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18656539916992</t>
   </si>
   <si>
     <t xml:space="preserve">5.3374285697937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31470823287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26563262939453</t>
+    <t xml:space="preserve">5.31470775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26563215255737</t>
   </si>
   <si>
     <t xml:space="preserve">5.25836181640625</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">5.41195011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49737739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56190299987793</t>
+    <t xml:space="preserve">5.49737787246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56190347671509</t>
   </si>
   <si>
     <t xml:space="preserve">5.53282117843628</t>
@@ -5726,34 +5726,34 @@
     <t xml:space="preserve">5.68004846572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74820852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80182838439941</t>
+    <t xml:space="preserve">5.74820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
     <t xml:space="preserve">5.8581748008728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91452074050903</t>
+    <t xml:space="preserve">5.91452121734619</t>
   </si>
   <si>
     <t xml:space="preserve">6.13899612426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13627004623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10173511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21806240081787</t>
+    <t xml:space="preserve">6.13626956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10173559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21806287765503</t>
   </si>
   <si>
     <t xml:space="preserve">6.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17989253997803</t>
+    <t xml:space="preserve">6.17989301681519</t>
   </si>
   <si>
     <t xml:space="preserve">6.14444923400879</t>
@@ -5780,7 +5780,7 @@
     <t xml:space="preserve">5.97086715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01630687713623</t>
+    <t xml:space="preserve">6.01630735397339</t>
   </si>
   <si>
     <t xml:space="preserve">6.04902458190918</t>
@@ -5789,10 +5789,10 @@
     <t xml:space="preserve">6.13445234298706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12172889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19170713424683</t>
+    <t xml:space="preserve">6.12172937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19170761108398</t>
   </si>
   <si>
     <t xml:space="preserve">6.17807483673096</t>
@@ -5807,13 +5807,13 @@
     <t xml:space="preserve">5.96904897689819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03539228439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95632553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75911426544189</t>
+    <t xml:space="preserve">6.03539180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95632600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75911474227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.74275588989258</t>
@@ -5825,28 +5825,28 @@
     <t xml:space="preserve">5.81636953353882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89725303649902</t>
+    <t xml:space="preserve">5.89725351333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.87907743453979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9454197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97813701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95087289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9045238494873</t>
+    <t xml:space="preserve">5.94542026519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97813749313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95087337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90452432632446</t>
   </si>
   <si>
     <t xml:space="preserve">5.9017972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00449275970459</t>
+    <t xml:space="preserve">6.00449323654175</t>
   </si>
   <si>
     <t xml:space="preserve">5.98449897766113</t>
@@ -5858,10 +5858,10 @@
     <t xml:space="preserve">6.04266262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09446430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11809349060059</t>
+    <t xml:space="preserve">6.09446477890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11809396743774</t>
   </si>
   <si>
     <t xml:space="preserve">6.16989612579346</t>
@@ -6794,7 +6794,16 @@
     <t xml:space="preserve">8.95699977874756</t>
   </si>
   <si>
+    <t xml:space="preserve">8.93599987030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89200019836426</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.86400032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90299987792969</t>
   </si>
 </sst>
 </file>
@@ -72237,27 +72246,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6913078704</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>14011903</v>
+        <v>16203200</v>
       </c>
       <c r="C2505" t="n">
-        <v>8.9060001373291</v>
+        <v>8.96300029754639</v>
       </c>
       <c r="D2505" t="n">
-        <v>8.80200004577637</v>
+        <v>8.89099979400635</v>
       </c>
       <c r="E2505" t="n">
-        <v>8.87600040435791</v>
+        <v>8.94299983978271</v>
       </c>
       <c r="F2505" t="n">
-        <v>8.86400032043457</v>
+        <v>8.93599987030029</v>
       </c>
       <c r="G2505" t="s">
         <v>2260</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>16462950</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>8.97999954223633</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>8.86200046539307</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>8.97999954223633</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>8.89200019836426</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>14011903</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>8.9060001373291</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>8.80200004577637</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>8.87600040435791</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>8.86400032043457</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6910763889</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>15985666</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>8.92199993133545</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>8.90299987792969</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>2263</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="2268">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697376251221</t>
+    <t xml:space="preserve">2.23697328567505</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.27958273887634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22277069091797</t>
+    <t xml:space="preserve">2.22277092933655</t>
   </si>
   <si>
     <t xml:space="preserve">2.23223900794983</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">2.21448564529419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21685266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20146632194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23460626602173</t>
+    <t xml:space="preserve">2.21685290336609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20146560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23460602760315</t>
   </si>
   <si>
     <t xml:space="preserve">2.21211814880371</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">2.1718761920929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13281798362732</t>
+    <t xml:space="preserve">2.13281774520874</t>
   </si>
   <si>
     <t xml:space="preserve">2.15767312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09257650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16004061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20620036125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19436430931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513794898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236010551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305946350098</t>
+    <t xml:space="preserve">2.0925760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16004037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20619988441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19436383247375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25235986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17306017875671</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987174987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22395396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081377983093</t>
+    <t xml:space="preserve">2.22395443916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081354141235</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702105522156</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2.09849429130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07008790969849</t>
+    <t xml:space="preserve">2.07008814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.06772089004517</t>
@@ -122,70 +122,70 @@
     <t xml:space="preserve">2.08665823936462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01090908050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09375929832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16477513313293</t>
+    <t xml:space="preserve">2.01090931892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0937602519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16477489471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.15057158470154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.156489610672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09494280815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1801609992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19199681282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791507720947</t>
+    <t xml:space="preserve">2.15648984909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228701591492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15293860435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0949432849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18016147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19199705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330189704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791531562805</t>
   </si>
   <si>
     <t xml:space="preserve">2.16714191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17542719841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24170827865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25354337692261</t>
+    <t xml:space="preserve">2.17542743682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24170804023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25354361534119</t>
   </si>
   <si>
     <t xml:space="preserve">2.31508994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30798888206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30207085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30562138557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574248313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31745672225952</t>
+    <t xml:space="preserve">2.30798864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30207061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30562162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745648384094</t>
   </si>
   <si>
     <t xml:space="preserve">2.31982445716858</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">2.31153893470764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3008873462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390643119812</t>
+    <t xml:space="preserve">2.30088686943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390690803528</t>
   </si>
   <si>
     <t xml:space="preserve">2.35059762001038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36716771125793</t>
+    <t xml:space="preserve">2.36716747283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.306804895401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29496932029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27366471290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595888137817</t>
+    <t xml:space="preserve">2.29496908187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2736644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738363265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595816612244</t>
   </si>
   <si>
     <t xml:space="preserve">2.22632145881653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23579001426697</t>
+    <t xml:space="preserve">2.23579025268555</t>
   </si>
   <si>
     <t xml:space="preserve">2.21921944618225</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.26182889938354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27129721641541</t>
+    <t xml:space="preserve">2.27129745483398</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337498664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2961528301239</t>
+    <t xml:space="preserve">2.29615259170532</t>
   </si>
   <si>
     <t xml:space="preserve">2.35769891738892</t>
@@ -248,46 +248,46 @@
     <t xml:space="preserve">2.39912438392639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112858772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32929277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3091721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941363334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37663578987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33757781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35296440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33166027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3612494468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33994555473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385842323303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41096019744873</t>
+    <t xml:space="preserve">2.3423125743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112882614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30917167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941411018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071824073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37663626670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296511650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33166003227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36124920845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33994579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385866165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41096043586731</t>
   </si>
   <si>
     <t xml:space="preserve">2.42989754676819</t>
@@ -299,70 +299,70 @@
     <t xml:space="preserve">2.43699932098389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38965535163879</t>
+    <t xml:space="preserve">2.38965559005737</t>
   </si>
   <si>
     <t xml:space="preserve">2.39794087409973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37782001495361</t>
+    <t xml:space="preserve">2.37781953811646</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463230133057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44173359870911</t>
+    <t xml:space="preserve">2.44173336029053</t>
   </si>
   <si>
     <t xml:space="preserve">2.43936657905579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3565149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31864070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27839851379395</t>
+    <t xml:space="preserve">2.35651564598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31864047050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2783989906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.37900352478027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43817043304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44433426856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40735411643982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875977516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013140678406</t>
+    <t xml:space="preserve">2.43817067146301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44433379173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4073543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652150154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21876001358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2101309299469</t>
   </si>
   <si>
     <t xml:space="preserve">2.30627751350403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40365648269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049691200256</t>
+    <t xml:space="preserve">2.40365624427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296263694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049643516541</t>
   </si>
   <si>
     <t xml:space="preserve">2.45419454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3925621509552</t>
+    <t xml:space="preserve">2.39256238937378</t>
   </si>
   <si>
     <t xml:space="preserve">2.37653827667236</t>
@@ -374,61 +374,61 @@
     <t xml:space="preserve">2.43940281867981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45912528038025</t>
+    <t xml:space="preserve">2.45912551879883</t>
   </si>
   <si>
     <t xml:space="preserve">2.46035814285278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46282362937927</t>
+    <t xml:space="preserve">2.46282339096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.44679880142212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4825451374054</t>
+    <t xml:space="preserve">2.48008012771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254561424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.47638249397278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47268438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53801488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5256884098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240708351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48131346702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49117398262024</t>
+    <t xml:space="preserve">2.47268486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53801441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568864822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240684509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4813129901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4911744594574</t>
   </si>
   <si>
     <t xml:space="preserve">2.52322292327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51089644432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350046157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49856996536255</t>
+    <t xml:space="preserve">2.51089596748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50349998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49857020378113</t>
   </si>
   <si>
     <t xml:space="preserve">2.53308439254761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52938652038574</t>
+    <t xml:space="preserve">2.52938628196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.47021913528442</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">2.42461133003235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42707657814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39749312400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40242409706116</t>
+    <t xml:space="preserve">2.42707681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3974928855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40242385864258</t>
   </si>
   <si>
     <t xml:space="preserve">2.42830920219421</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">2.42954182624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43570518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45172905921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41351747512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43200731277466</t>
+    <t xml:space="preserve">2.43570494651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41351771354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4320068359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.48747658729553</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">2.48994135856628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47761511802673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541039466858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53061890602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49610471725464</t>
+    <t xml:space="preserve">2.47761464118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53061819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4961051940918</t>
   </si>
   <si>
     <t xml:space="preserve">2.44556593894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475033760071</t>
+    <t xml:space="preserve">2.41105246543884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475009918213</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913300037384</t>
@@ -497,46 +497,46 @@
     <t xml:space="preserve">2.41968083381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981936454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44803166389465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41721534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42091369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926428794861</t>
+    <t xml:space="preserve">2.40981984138489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44803190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4172158241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4209132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926452636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.41228485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37283992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35928130149841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32476687431335</t>
+    <t xml:space="preserve">2.3728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35928058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32476735115051</t>
   </si>
   <si>
     <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3383264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31983661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36421179771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35435032844543</t>
+    <t xml:space="preserve">2.33832621574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31983637809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36421203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35435080528259</t>
   </si>
   <si>
     <t xml:space="preserve">2.43693804740906</t>
@@ -548,205 +548,205 @@
     <t xml:space="preserve">2.43077445030212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41598272323608</t>
+    <t xml:space="preserve">2.41598296165466</t>
   </si>
   <si>
     <t xml:space="preserve">2.37037491798401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3629789352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3531186580658</t>
+    <t xml:space="preserve">2.36297941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35311841964722</t>
   </si>
   <si>
     <t xml:space="preserve">2.36667656898499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38393402099609</t>
+    <t xml:space="preserve">2.38393449783325</t>
   </si>
   <si>
     <t xml:space="preserve">2.32723212242126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24711012840271</t>
+    <t xml:space="preserve">2.24711060523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.243412733078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369027137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24957609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080847740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28285694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22862076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2483434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860375404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30751061439514</t>
+    <t xml:space="preserve">2.22369050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957585334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28285717964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22862029075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24834322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860423088074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30751037597656</t>
   </si>
   <si>
     <t xml:space="preserve">2.29764914512634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30257987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33339548110962</t>
+    <t xml:space="preserve">2.30257940292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586144447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065293312073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3333957195282</t>
   </si>
   <si>
     <t xml:space="preserve">2.51952481269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51336145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47884750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49980282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5392472743988</t>
+    <t xml:space="preserve">2.51336193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47884726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49980306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53924751281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.5651330947876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54910850524902</t>
+    <t xml:space="preserve">2.54910826683044</t>
   </si>
   <si>
     <t xml:space="preserve">2.56266760826111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58115720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60211253166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622671127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896925926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047989845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664301872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56636595726013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.554039478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55157375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57299447059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56795430183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52763319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50873231887817</t>
+    <t xml:space="preserve">2.58115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60211205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883096694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252836227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896997451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56636548042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55403876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55650401115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55157399177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57299423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56795477867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52763342857361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50873255729675</t>
   </si>
   <si>
     <t xml:space="preserve">2.47849154472351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42557001113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43439030647278</t>
+    <t xml:space="preserve">2.42556977272034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43439054489136</t>
   </si>
   <si>
     <t xml:space="preserve">2.43565034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715092658997</t>
+    <t xml:space="preserve">2.44825053215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715140342712</t>
   </si>
   <si>
     <t xml:space="preserve">2.41926956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069051742554</t>
+    <t xml:space="preserve">2.44069075584412</t>
   </si>
   <si>
     <t xml:space="preserve">2.54401326179504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55031371116638</t>
+    <t xml:space="preserve">2.55031394958496</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023361206055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53267359733582</t>
+    <t xml:space="preserve">2.53267288208008</t>
   </si>
   <si>
     <t xml:space="preserve">2.49361205101013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53141355514526</t>
+    <t xml:space="preserve">2.53141307830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.54527354240417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52133274078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5263729095459</t>
+    <t xml:space="preserve">2.52133297920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52637314796448</t>
   </si>
   <si>
     <t xml:space="preserve">2.50369238853455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787396430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283379554749</t>
+    <t xml:space="preserve">2.52007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787348747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283403396606</t>
   </si>
   <si>
     <t xml:space="preserve">2.57803463935852</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">2.59945511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60323476791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6082751750946</t>
+    <t xml:space="preserve">2.6032350063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60827541351318</t>
   </si>
   <si>
     <t xml:space="preserve">2.62717628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63851618766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6334764957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473606109619</t>
+    <t xml:space="preserve">2.63851571083069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63347601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473653793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961555480957</t>
@@ -779,61 +779,61 @@
     <t xml:space="preserve">2.67757749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65237665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63977646827698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65867638587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033787727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71537804603577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73427891731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74183893203735</t>
+    <t xml:space="preserve">2.65237641334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6397762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65867686271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7103385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151782035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71537852287292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73427867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74183988571167</t>
   </si>
   <si>
     <t xml:space="preserve">2.75191950798035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78090071678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77460074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76199960708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77208018302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75948023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75821948051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72671866416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67253684997559</t>
+    <t xml:space="preserve">2.78090000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964043617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7746000289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7619993686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77207970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309945106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75947952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75821924209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72671842575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67253732681274</t>
   </si>
   <si>
     <t xml:space="preserve">2.70907831192017</t>
@@ -842,130 +842,130 @@
     <t xml:space="preserve">2.80484104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79098081588745</t>
+    <t xml:space="preserve">2.79098057746887</t>
   </si>
   <si>
     <t xml:space="preserve">2.7771201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77081966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939942359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7872006893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422346115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792277336121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658310890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87918376922607</t>
+    <t xml:space="preserve">2.77081990242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939966201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78720092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350066184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650277137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8842236995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792325019836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86658263206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87918281555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.87414312362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87666296958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88044309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94974493980408</t>
+    <t xml:space="preserve">2.87666320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88044333457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94974517822266</t>
   </si>
   <si>
     <t xml:space="preserve">2.91572427749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92202472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100522041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9799861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526689529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.029128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9610857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274704933167</t>
+    <t xml:space="preserve">2.9220244884491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998547554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526761054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9862859249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00518655776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02912783622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96108531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9976270198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274728775024</t>
   </si>
   <si>
     <t xml:space="preserve">2.96990609169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01148700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156758308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11354947090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05558824539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968996047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10724925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08204984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10346937179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11859011650085</t>
+    <t xml:space="preserve">3.01148724555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11355066299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180811882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05558800697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810856819153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440806388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968972206116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10724949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08204960823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749098777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10346961021423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11858987808228</t>
   </si>
   <si>
     <t xml:space="preserve">3.02408766746521</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">2.99888682365417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98880624771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478463172913</t>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478558540344</t>
   </si>
   <si>
     <t xml:space="preserve">2.97368621826172</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">3.01778721809387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06944918632507</t>
+    <t xml:space="preserve">3.06944847106934</t>
   </si>
   <si>
     <t xml:space="preserve">3.13245129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13119077682495</t>
+    <t xml:space="preserve">3.13119006156921</t>
   </si>
   <si>
     <t xml:space="preserve">3.10094952583313</t>
@@ -1013,139 +1013,139 @@
     <t xml:space="preserve">3.12489056587219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12867069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09338903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777663230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953905105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703083992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13189578056335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17040348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864177703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735836982727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532845497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19222378730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16013431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22816348075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25062537193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23458099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025247573853</t>
+    <t xml:space="preserve">3.12867045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09338927268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906123161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07926940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953833580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595656394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13703060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13189649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17040324211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864201545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735813140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1601345539093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062584877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383543968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23458170890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2602527141571</t>
   </si>
   <si>
     <t xml:space="preserve">3.26987910270691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26346135139465</t>
+    <t xml:space="preserve">3.26346230506897</t>
   </si>
   <si>
     <t xml:space="preserve">3.2987596988678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27950644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271508216858</t>
+    <t xml:space="preserve">3.27950596809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.3019688129425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33084845542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122206687927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614632606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405780792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629709243774</t>
+    <t xml:space="preserve">3.33084917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3661470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405709266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159567832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629733085632</t>
   </si>
   <si>
     <t xml:space="preserve">3.30517745018005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28592419624329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28913259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27308869361877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24099922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18708920478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23779034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704312324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31480431556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801295280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32763957977295</t>
+    <t xml:space="preserve">3.28592443466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28913307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27308797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099898338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18708944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23779058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25704336166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31480360031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32763981819153</t>
   </si>
   <si>
     <t xml:space="preserve">3.30838680267334</t>
@@ -1154,67 +1154,67 @@
     <t xml:space="preserve">3.32443046569824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.350102186203</t>
+    <t xml:space="preserve">3.35010170936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.39502692222595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39181756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428017616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748881340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45599603652954</t>
+    <t xml:space="preserve">3.39181780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41428065299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599699020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.44316029548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44957828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920538902283</t>
+    <t xml:space="preserve">3.44957780838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920491218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.46241402626038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43995213508606</t>
+    <t xml:space="preserve">3.43995237350464</t>
   </si>
   <si>
     <t xml:space="preserve">3.42390727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38540053367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256526947021</t>
+    <t xml:space="preserve">3.38540005683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256455421448</t>
   </si>
   <si>
     <t xml:space="preserve">3.37898254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689378738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331082344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786194801331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883177757263</t>
+    <t xml:space="preserve">3.3982355594635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689354896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786290168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674302101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883201599121</t>
   </si>
   <si>
     <t xml:space="preserve">3.51375651359558</t>
@@ -1223,37 +1223,37 @@
     <t xml:space="preserve">3.50092077255249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.446368932724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054787635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584574699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56189060211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114361763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166728019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50413012504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2923412322998</t>
+    <t xml:space="preserve">3.44636917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584503173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114314079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5362184047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166799545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5041298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41107106208801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234170913696</t>
   </si>
   <si>
     <t xml:space="preserve">3.42711591720581</t>
@@ -1262,85 +1262,85 @@
     <t xml:space="preserve">3.40144467353821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4461145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047884941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738871574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382533073425</t>
+    <t xml:space="preserve">3.44611406326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047837257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738823890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382509231567</t>
   </si>
   <si>
     <t xml:space="preserve">3.31717157363892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34466218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31586265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302720069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310114860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146639823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19019222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070348739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310418128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0684494972229</t>
+    <t xml:space="preserve">3.34466171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31586241722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302648544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310091018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146663665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19019246101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070324897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06844973564148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04619479179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12866568565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652062416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18102860450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.127357006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212038040161</t>
+    <t xml:space="preserve">3.12866592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652086257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18102884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212085723877</t>
   </si>
   <si>
     <t xml:space="preserve">3.07630324363708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16466546058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15877509117126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16597437858582</t>
+    <t xml:space="preserve">3.16466474533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15877485275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16597533226013</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801122665405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11688423156738</t>
+    <t xml:space="preserve">3.11688494682312</t>
   </si>
   <si>
     <t xml:space="preserve">3.04815912246704</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">3.0769579410553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09528541564941</t>
+    <t xml:space="preserve">3.09528470039368</t>
   </si>
   <si>
     <t xml:space="preserve">3.12670278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16793847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16532015800476</t>
+    <t xml:space="preserve">3.16793775558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1653196811676</t>
   </si>
   <si>
     <t xml:space="preserve">3.16335606575012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18757343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17448329925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673752784729</t>
+    <t xml:space="preserve">3.18757390975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17448306083679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673728942871</t>
   </si>
   <si>
     <t xml:space="preserve">3.22684597969055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19150161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13913822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17513799667358</t>
+    <t xml:space="preserve">3.19150137901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1391384601593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.175137758255</t>
   </si>
   <si>
     <t xml:space="preserve">3.13259339332581</t>
@@ -1391,49 +1391,49 @@
     <t xml:space="preserve">3.13979339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2562997341156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320864677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844479560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30538988113403</t>
+    <t xml:space="preserve">3.25629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844527244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538964271545</t>
   </si>
   <si>
     <t xml:space="preserve">3.30277180671692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32764434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3224081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324410438538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597134590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34728002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39833354949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487909317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39309668540955</t>
+    <t xml:space="preserve">3.32764410972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240748405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34728026390076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095186233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39833402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393378257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487861633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3930971622467</t>
   </si>
   <si>
     <t xml:space="preserve">3.44284152984619</t>
@@ -1442,55 +1442,55 @@
     <t xml:space="preserve">3.43629622459412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.448077917099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48211359977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52531290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52662205696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891453742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3184802532196</t>
+    <t xml:space="preserve">3.44807767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520421028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48211431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52531313896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52662134170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891429901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3210985660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31848096847534</t>
   </si>
   <si>
     <t xml:space="preserve">3.3433530330658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36298847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2379732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26153612136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20590090751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655584335327</t>
+    <t xml:space="preserve">3.36298894882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23797345161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26153588294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20590114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655536651611</t>
   </si>
   <si>
     <t xml:space="preserve">3.19542837142944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19215536117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037462234497</t>
+    <t xml:space="preserve">3.1921558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037390708923</t>
   </si>
   <si>
     <t xml:space="preserve">3.10772085189819</t>
@@ -1499,73 +1499,73 @@
     <t xml:space="preserve">3.08415818214417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00888657569885</t>
+    <t xml:space="preserve">3.00888729095459</t>
   </si>
   <si>
     <t xml:space="preserve">3.11033916473389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07826662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855771064758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324785232544</t>
+    <t xml:space="preserve">3.0782675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855818748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13324809074402</t>
   </si>
   <si>
     <t xml:space="preserve">3.07564902305603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06386804580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692272186279</t>
+    <t xml:space="preserve">3.06386709213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692296028137</t>
   </si>
   <si>
     <t xml:space="preserve">3.11557531356812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12932062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.189537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18888306617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401124000549</t>
+    <t xml:space="preserve">3.12932085990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18953728675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18888330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401076316833</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204738616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15746593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481240272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1064121723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12342977523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1031391620636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11361145973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1051025390625</t>
+    <t xml:space="preserve">3.157466173172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10641169548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06452250480652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808493614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12343001365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10313963890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11361241340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510277748108</t>
   </si>
   <si>
     <t xml:space="preserve">3.15550208091736</t>
@@ -1574,64 +1574,64 @@
     <t xml:space="preserve">3.14437484741211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710137367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19739246368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644667625427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186522483826</t>
+    <t xml:space="preserve">3.17710185050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739174842834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186570167542</t>
   </si>
   <si>
     <t xml:space="preserve">3.1489565372467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18364644050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19411897659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917296409607</t>
+    <t xml:space="preserve">3.18364691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1941192150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917344093323</t>
   </si>
   <si>
     <t xml:space="preserve">3.21113681793213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17952370643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15530872344971</t>
+    <t xml:space="preserve">3.17952418327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15530896186829</t>
   </si>
   <si>
     <t xml:space="preserve">3.13647508621216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14656496047974</t>
+    <t xml:space="preserve">3.14656472206116</t>
   </si>
   <si>
     <t xml:space="preserve">3.17212462425232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16338014602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844626426697</t>
+    <t xml:space="preserve">3.16338062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844674110413</t>
   </si>
   <si>
     <t xml:space="preserve">3.08401036262512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02347326278687</t>
+    <t xml:space="preserve">3.02347350120544</t>
   </si>
   <si>
     <t xml:space="preserve">3.04432487487793</t>
@@ -1646,55 +1646,55 @@
     <t xml:space="preserve">3.08333778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0692126750946</t>
+    <t xml:space="preserve">3.06921243667603</t>
   </si>
   <si>
     <t xml:space="preserve">3.00598502159119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99051451683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01203870773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98042488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96629977226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99791312217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98513317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95082926750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96293711662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150208473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92997789382935</t>
+    <t xml:space="preserve">2.99051380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01203918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9804253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638940811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96630024909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9979133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98513340950012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95082974433899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96293687820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9515016078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92997813224792</t>
   </si>
   <si>
     <t xml:space="preserve">2.94006705284119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89836454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540532112122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397100448608</t>
+    <t xml:space="preserve">2.89836382865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540555953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85397028923035</t>
   </si>
   <si>
     <t xml:space="preserve">2.8862566947937</t>
@@ -1703,46 +1703,46 @@
     <t xml:space="preserve">2.88558435440063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94477534294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091866493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719398498535</t>
+    <t xml:space="preserve">2.94477510452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719422340393</t>
   </si>
   <si>
     <t xml:space="preserve">3.06584930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03894400596619</t>
+    <t xml:space="preserve">3.03894352912903</t>
   </si>
   <si>
     <t xml:space="preserve">3.06652212142944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05979490280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03625392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05912208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629700660706</t>
+    <t xml:space="preserve">3.05979514122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03625321388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05912256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629605293274</t>
   </si>
   <si>
     <t xml:space="preserve">3.07392072677612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09342670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1014986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08064723014832</t>
+    <t xml:space="preserve">3.09342694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10149836540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08064651489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.96764492988586</t>
@@ -1754,244 +1754,244 @@
     <t xml:space="preserve">2.96562719345093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0409619808197</t>
+    <t xml:space="preserve">3.04096150398254</t>
   </si>
   <si>
     <t xml:space="preserve">2.99993133544922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97504425048828</t>
+    <t xml:space="preserve">2.97504353523254</t>
   </si>
   <si>
     <t xml:space="preserve">2.94410252571106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94343018531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92325115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88423895835876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99589610099792</t>
+    <t xml:space="preserve">2.94343042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92325162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88423871994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99589562416077</t>
   </si>
   <si>
     <t xml:space="preserve">2.96899032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93468618392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975182533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96697282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95957374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94544816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96428179740906</t>
+    <t xml:space="preserve">2.93468594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9797523021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9844605922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96697235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612097740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95957326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91518020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94544839859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96428227424622</t>
   </si>
   <si>
     <t xml:space="preserve">2.9716808795929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00665783882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0154013633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99455070495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02683615684509</t>
+    <t xml:space="preserve">3.00665736198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01540160179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228009223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9945502281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02683639526367</t>
   </si>
   <si>
     <t xml:space="preserve">3.0685396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09275388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.133784532547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13243985176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647253036499</t>
+    <t xml:space="preserve">3.09275436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378429412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13244009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16472625732422</t>
   </si>
   <si>
     <t xml:space="preserve">3.19835734367371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20441126823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21517252922058</t>
+    <t xml:space="preserve">3.20441055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21517324447632</t>
   </si>
   <si>
     <t xml:space="preserve">3.20037484169006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22189974784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2380428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2272801399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24880409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19297671318054</t>
+    <t xml:space="preserve">3.22189903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23804235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22727942466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24880504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19297623634338</t>
   </si>
   <si>
     <t xml:space="preserve">3.19364881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961358070374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333382606506</t>
+    <t xml:space="preserve">3.18961310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2333345413208</t>
   </si>
   <si>
     <t xml:space="preserve">3.3167405128479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37660336494446</t>
+    <t xml:space="preserve">3.37660431861877</t>
   </si>
   <si>
     <t xml:space="preserve">3.37525916099548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37256860733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122368812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655776023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4882607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39543867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39274787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099785804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808171272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673703193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47346305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5313093662262</t>
+    <t xml:space="preserve">3.37256908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655799865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270108222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48826026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39543747901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39274716377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965270042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4667375087738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153471946716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4734628200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53131008148193</t>
   </si>
   <si>
     <t xml:space="preserve">3.49767756462097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51113033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978493690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458262443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032179832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275723457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683256149292</t>
+    <t xml:space="preserve">3.50440382957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51112985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978446006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.524582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275675773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446622848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683232307434</t>
   </si>
   <si>
     <t xml:space="preserve">3.57861161231995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58690166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56755828857422</t>
+    <t xml:space="preserve">3.58690285682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.6214451789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61591815948486</t>
+    <t xml:space="preserve">3.61591768264771</t>
   </si>
   <si>
     <t xml:space="preserve">3.63802552223206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58137536048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54545140266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59104776382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348296165466</t>
+    <t xml:space="preserve">3.57170343399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58137488365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54545164108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097794532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59104752540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6034824848175</t>
   </si>
   <si>
     <t xml:space="preserve">3.6007194519043</t>
@@ -2000,82 +2000,82 @@
     <t xml:space="preserve">3.61730027198792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62282609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61039113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61453604698181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62420797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.646315574646</t>
+    <t xml:space="preserve">3.62282729148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61039161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61453652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420773506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64631485939026</t>
   </si>
   <si>
     <t xml:space="preserve">3.66980481147766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66151452064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533183097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118573188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66427779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085837364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72921752929688</t>
+    <t xml:space="preserve">3.6615138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533159255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118549346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66427826881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085741996765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921705245972</t>
   </si>
   <si>
     <t xml:space="preserve">3.80106568336487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78863120079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205061912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79830265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79001307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79139375686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895903587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83008217811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8549530506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.892258644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923664093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752740859985</t>
+    <t xml:space="preserve">3.78863096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7720513343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79830288887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7900128364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79139423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895951271057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350159645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495257377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225912094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258671760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923687934875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752717018127</t>
   </si>
   <si>
     <t xml:space="preserve">3.92818331718445</t>
@@ -2084,160 +2084,160 @@
     <t xml:space="preserve">3.94061827659607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90883994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091108322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338202476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93440079689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93370985984802</t>
+    <t xml:space="preserve">3.90883946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091227531433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338154792786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93440127372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93371057510376</t>
   </si>
   <si>
     <t xml:space="preserve">3.9212749004364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91022062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847612380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419205665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244851112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840725898743</t>
+    <t xml:space="preserve">3.91022038459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847707748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8556444644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419277191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695675849915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281065940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80244779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593703269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840654373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.83629965782166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89571285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288071632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182667732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87015151977539</t>
+    <t xml:space="preserve">3.89571309089661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288000106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182691574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87015175819397</t>
   </si>
   <si>
     <t xml:space="preserve">3.85218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83491802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452084541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85149812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88880443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93094658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690485954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068833351135</t>
+    <t xml:space="preserve">3.83491826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85149931907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88880467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93094539642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068785667419</t>
   </si>
   <si>
     <t xml:space="preserve">3.92403769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99934029579163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906364440918</t>
+    <t xml:space="preserve">3.99934101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906316757202</t>
   </si>
   <si>
     <t xml:space="preserve">3.8480441570282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87844157218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06980657577515</t>
+    <t xml:space="preserve">3.87844133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9558162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06980752944946</t>
   </si>
   <si>
     <t xml:space="preserve">4.02628469467163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911659240723</t>
+    <t xml:space="preserve">4.04010057449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911706924438</t>
   </si>
   <si>
     <t xml:space="preserve">4.13889217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346952438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20037794113159</t>
+    <t xml:space="preserve">4.1934700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20037841796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.30884218215942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26255559921265</t>
+    <t xml:space="preserve">4.26255464553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.2763729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30538749694824</t>
+    <t xml:space="preserve">4.3053879737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.3005518913269</t>
@@ -2246,28 +2246,28 @@
     <t xml:space="preserve">4.28397178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19692420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20314264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24183034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23215818405151</t>
+    <t xml:space="preserve">4.19692373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2031421661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24182987213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2321572303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.32473230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42697858810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45392179489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42145156860352</t>
+    <t xml:space="preserve">4.42697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4539213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42145109176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.42835903167725</t>
@@ -2276,37 +2276,37 @@
     <t xml:space="preserve">4.42766904830933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43941402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49744510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45668411254883</t>
+    <t xml:space="preserve">4.43941307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49744462966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45668506622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.48500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4995174407959</t>
+    <t xml:space="preserve">4.49951791763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.53129720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34407567977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43310594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47267293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41402721405029</t>
+    <t xml:space="preserve">4.34407663345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43239974975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47267436981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41402769088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
@@ -2315,97 +2315,97 @@
     <t xml:space="preserve">4.41332101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35891437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38011121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40908241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3794059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711744308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33418416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842372894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493787765503</t>
+    <t xml:space="preserve">4.35891485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3801121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40908145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711839675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33418369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493835449219</t>
   </si>
   <si>
     <t xml:space="preserve">4.28472328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29461574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24586009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49316549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40625429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44017124176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39706993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59208726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59349966049194</t>
+    <t xml:space="preserve">4.29461526870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2458610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44087839126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49316501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40625476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4401707649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39707040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59208583831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5935001373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.68606185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65921211242676</t>
+    <t xml:space="preserve">4.6592116355896</t>
   </si>
   <si>
     <t xml:space="preserve">4.71997833251953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72068452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7609601020813</t>
+    <t xml:space="preserve">4.72068548202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76096057891846</t>
   </si>
   <si>
     <t xml:space="preserve">4.70937919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67758321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62458992004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58572721481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65779972076416</t>
+    <t xml:space="preserve">4.67758226394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62458944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58572673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181074142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263841629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.657799243927</t>
   </si>
   <si>
     <t xml:space="preserve">4.58007478713989</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">4.60480499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69878101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67405080795288</t>
+    <t xml:space="preserve">4.69878149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67404937744141</t>
   </si>
   <si>
     <t xml:space="preserve">4.64649391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71361970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78215837478638</t>
+    <t xml:space="preserve">4.71361923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78215789794922</t>
   </si>
   <si>
     <t xml:space="preserve">4.7553071975708</t>
@@ -2441,58 +2441,58 @@
     <t xml:space="preserve">4.84080410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81678104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69100904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77226543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83656454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81536769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78145217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78993034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83161878585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80830097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78357124328613</t>
+    <t xml:space="preserve">4.81678056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69100761413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77226591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83656406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78498458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81536722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78992938995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.831618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80830049514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78357076644897</t>
   </si>
   <si>
     <t xml:space="preserve">4.82455253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84221744537354</t>
+    <t xml:space="preserve">4.7659068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84221696853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.86129522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8499903678894</t>
+    <t xml:space="preserve">4.84998989105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.85564231872559</t>
@@ -2501,55 +2501,55 @@
     <t xml:space="preserve">4.8775463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90368986129761</t>
+    <t xml:space="preserve">4.90369033813477</t>
   </si>
   <si>
     <t xml:space="preserve">4.89733171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92347478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.882493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87472009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140371322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84716272354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93407249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8577618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84857654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87401294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82596635818481</t>
+    <t xml:space="preserve">4.92347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87472057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085256576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85140323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84716320037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93407344818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662408828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85776233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84857606887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87401247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">4.80759525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7871036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76944017410278</t>
+    <t xml:space="preserve">4.78710460662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76943874359131</t>
   </si>
   <si>
     <t xml:space="preserve">4.83303213119507</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">4.85493564605713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84433650970459</t>
+    <t xml:space="preserve">4.84433746337891</t>
   </si>
   <si>
     <t xml:space="preserve">4.66698503494263</t>
@@ -2567,79 +2567,79 @@
     <t xml:space="preserve">4.71785879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75036144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7560133934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83727216720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89309120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95315170288086</t>
+    <t xml:space="preserve">4.75036191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75601434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83727169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89309167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95315074920654</t>
   </si>
   <si>
     <t xml:space="preserve">4.93336629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94679164886475</t>
+    <t xml:space="preserve">4.94679117202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.09164047241211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06973838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0435938835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99695920944214</t>
+    <t xml:space="preserve">5.06973743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04359340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9969596862793</t>
   </si>
   <si>
     <t xml:space="preserve">5.09588050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09517383575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10577249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10859966278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13686275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16159296035767</t>
+    <t xml:space="preserve">5.09517431259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10577297210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1085991859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13686323165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16159343719482</t>
   </si>
   <si>
     <t xml:space="preserve">5.24072980880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22871732711792</t>
+    <t xml:space="preserve">5.22871828079224</t>
   </si>
   <si>
     <t xml:space="preserve">5.24355697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37780714035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45835828781128</t>
+    <t xml:space="preserve">5.3778076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45835781097412</t>
   </si>
   <si>
     <t xml:space="preserve">5.50453662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49082803726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44464874267578</t>
+    <t xml:space="preserve">5.4908275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44464921951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.49804210662842</t>
@@ -2651,34 +2651,34 @@
     <t xml:space="preserve">5.53700494766235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69934844970703</t>
+    <t xml:space="preserve">5.69934892654419</t>
   </si>
   <si>
     <t xml:space="preserve">5.77871704101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83571720123291</t>
+    <t xml:space="preserve">5.83571672439575</t>
   </si>
   <si>
     <t xml:space="preserve">5.66760158538818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7476921081543</t>
+    <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
     <t xml:space="preserve">5.77222299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82272958755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8999342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91652917861938</t>
+    <t xml:space="preserve">5.82272911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89993381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91652822494507</t>
   </si>
   <si>
     <t xml:space="preserve">5.91147756576538</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">5.86746454238892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92157888412476</t>
+    <t xml:space="preserve">5.92157936096191</t>
   </si>
   <si>
     <t xml:space="preserve">5.97208642959595</t>
@@ -2702,34 +2702,34 @@
     <t xml:space="preserve">6.18060731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08464384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09258127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79386806488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152456283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629476547241</t>
+    <t xml:space="preserve">6.08464527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09258079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79386854171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975419998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71161460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629524230957</t>
   </si>
   <si>
     <t xml:space="preserve">5.51247310638428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62286710739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538974761963</t>
+    <t xml:space="preserve">5.62286615371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538927078247</t>
   </si>
   <si>
     <t xml:space="preserve">5.87684440612793</t>
@@ -2738,31 +2738,31 @@
     <t xml:space="preserve">5.69357585906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1271767616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70436191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77070426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426502227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95830130577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12713956832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2497992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20650720596313</t>
+    <t xml:space="preserve">5.12717723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70436143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77070474624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95830154418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12714004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24979972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20650672912598</t>
   </si>
   <si>
     <t xml:space="preserve">4.24907779693604</t>
@@ -2774,46 +2774,46 @@
     <t xml:space="preserve">4.5535626411438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54562568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53047323226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44100427627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60767698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57376480102539</t>
+    <t xml:space="preserve">4.54562473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5304741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60767650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57376575469971</t>
   </si>
   <si>
     <t xml:space="preserve">4.37823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43378782272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37895250320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43018198013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59974002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480243682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65601921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65169048309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47852277755737</t>
+    <t xml:space="preserve">4.43378829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3789529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43018102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59973907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480291366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65601825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6516900062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47852325439453</t>
   </si>
   <si>
     <t xml:space="preserve">4.50882768630981</t>
@@ -2822,22 +2822,22 @@
     <t xml:space="preserve">4.47996616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46770000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3327751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31834506988525</t>
+    <t xml:space="preserve">4.46770048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33277463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3183445930481</t>
   </si>
   <si>
     <t xml:space="preserve">4.2757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25701379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37967443466187</t>
+    <t xml:space="preserve">4.25701427459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37967348098755</t>
   </si>
   <si>
     <t xml:space="preserve">4.43739604949951</t>
@@ -2849,139 +2849,139 @@
     <t xml:space="preserve">4.49944734573364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39266109466553</t>
+    <t xml:space="preserve">4.3342170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39266157150269</t>
   </si>
   <si>
     <t xml:space="preserve">4.37750911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46481370925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.473473072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688850402832</t>
+    <t xml:space="preserve">4.46481513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47347211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688898086548</t>
   </si>
   <si>
     <t xml:space="preserve">4.3508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24546957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672206878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30319213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35586452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5109920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56727170944214</t>
+    <t xml:space="preserve">4.24547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30319261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51099157333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56727123260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.62499284744263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69714689254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90061664581299</t>
+    <t xml:space="preserve">4.69714593887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198316574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061807632446</t>
   </si>
   <si>
     <t xml:space="preserve">4.97926425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04925155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18706369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434621810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40063619613647</t>
+    <t xml:space="preserve">5.04925203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40063571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.46773815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46701717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28663492202759</t>
+    <t xml:space="preserve">5.46701669692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176244735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28663444519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.29962158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31188821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41506624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361158370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63585376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50092792510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906847000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51175022125244</t>
+    <t xml:space="preserve">5.31188726425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41506719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361253738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63585329055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5290675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51175165176392</t>
   </si>
   <si>
     <t xml:space="preserve">5.57308101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53989028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5572075843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7339825630188</t>
+    <t xml:space="preserve">5.53989124298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55720710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73398113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.68131065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71017122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75418376922607</t>
+    <t xml:space="preserve">5.71017169952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75418424606323</t>
   </si>
   <si>
     <t xml:space="preserve">5.83427429199219</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">5.72604465484619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86024856567383</t>
+    <t xml:space="preserve">5.86024904251099</t>
   </si>
   <si>
     <t xml:space="preserve">5.78232431411743</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">5.89416074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9547700881958</t>
+    <t xml:space="preserve">5.95476961135864</t>
   </si>
   <si>
     <t xml:space="preserve">6.08031558990479</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">6.13258600234985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03246164321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98828887939453</t>
+    <t xml:space="preserve">6.03246259689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98828983306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.84841060638428</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">5.83147764205933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81601762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8712329864502</t>
+    <t xml:space="preserve">5.81601858139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87123250961304</t>
   </si>
   <si>
     <t xml:space="preserve">5.69601631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69012594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78362369537354</t>
+    <t xml:space="preserve">5.69012689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">5.79319524765015</t>
@@ -3044,31 +3044,31 @@
     <t xml:space="preserve">5.76669216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69086313247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75344085693359</t>
+    <t xml:space="preserve">5.69086265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75343990325928</t>
   </si>
   <si>
     <t xml:space="preserve">5.79024982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86313486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97061967849731</t>
+    <t xml:space="preserve">5.86313438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062015533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.89552783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80497407913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74828767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356294631958</t>
+    <t xml:space="preserve">5.80497455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74828624725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">5.70926809310913</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">5.69159841537476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79098701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74534177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092435836792</t>
+    <t xml:space="preserve">5.79098653793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74534225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092483520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.60767221450806</t>
@@ -3098,13 +3098,13 @@
     <t xml:space="preserve">5.52448081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63049411773682</t>
+    <t xml:space="preserve">5.63049364089966</t>
   </si>
   <si>
     <t xml:space="preserve">5.58043241500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4567494392395</t>
+    <t xml:space="preserve">5.45675039291382</t>
   </si>
   <si>
     <t xml:space="preserve">5.59000253677368</t>
@@ -3113,55 +3113,55 @@
     <t xml:space="preserve">5.50165843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63270282745361</t>
+    <t xml:space="preserve">5.63270235061646</t>
   </si>
   <si>
     <t xml:space="preserve">5.5981011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63932800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56644344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650657653809</t>
+    <t xml:space="preserve">5.63932847976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56644487380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650609970093</t>
   </si>
   <si>
     <t xml:space="preserve">5.57675123214722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43319082260132</t>
+    <t xml:space="preserve">5.43319129943848</t>
   </si>
   <si>
     <t xml:space="preserve">5.46263933181763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34411096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40006160736084</t>
+    <t xml:space="preserve">5.3441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3897557258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.400062084198</t>
   </si>
   <si>
     <t xml:space="preserve">5.48325300216675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52153587341309</t>
+    <t xml:space="preserve">5.52153491973877</t>
   </si>
   <si>
     <t xml:space="preserve">5.4611668586731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49797677993774</t>
+    <t xml:space="preserve">5.4979772567749</t>
   </si>
   <si>
     <t xml:space="preserve">5.44349813461304</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">5.42141199111938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59221172332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5561375617981</t>
+    <t xml:space="preserve">5.59221124649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55613708496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.5392050743103</t>
@@ -3185,40 +3185,40 @@
     <t xml:space="preserve">5.67761135101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49429655075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54141283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49871397018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58190441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5325779914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472547531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57233333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44423484802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662340164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10705280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0312237739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
+    <t xml:space="preserve">5.49429559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54141330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58190393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57233428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44423389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10705184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03122329711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312648773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318998336792</t>
@@ -3230,40 +3230,40 @@
     <t xml:space="preserve">5.60325479507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92423963546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04571294784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90436267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95515966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97209358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9794545173645</t>
+    <t xml:space="preserve">5.92718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92423915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04571342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853448867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90436172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95516014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97209310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97945499420166</t>
   </si>
   <si>
     <t xml:space="preserve">6.01037549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06117248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24816989898682</t>
+    <t xml:space="preserve">6.06117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19737195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24816942214966</t>
   </si>
   <si>
     <t xml:space="preserve">6.23565483093262</t>
@@ -3275,37 +3275,37 @@
     <t xml:space="preserve">6.162034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09724712371826</t>
+    <t xml:space="preserve">6.1252236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09724807739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.04350423812866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04129648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0228910446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00743103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97798252105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92571210861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92276763916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00890254974365</t>
+    <t xml:space="preserve">6.04129600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02289056777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00743055343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97798204421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04424142837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.922767162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00890302658081</t>
   </si>
   <si>
     <t xml:space="preserve">6.01700162887573</t>
@@ -3314,13 +3314,13 @@
     <t xml:space="preserve">5.94190883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08914947509766</t>
+    <t xml:space="preserve">6.0891489982605</t>
   </si>
   <si>
     <t xml:space="preserve">6.14362859725952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09283065795898</t>
+    <t xml:space="preserve">6.09283018112183</t>
   </si>
   <si>
     <t xml:space="preserve">6.22608375549316</t>
@@ -3329,34 +3329,34 @@
     <t xml:space="preserve">6.18043947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57357215881348</t>
+    <t xml:space="preserve">6.57357168197632</t>
   </si>
   <si>
     <t xml:space="preserve">6.461669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58019781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081111907959</t>
+    <t xml:space="preserve">6.58019828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081064224243</t>
   </si>
   <si>
     <t xml:space="preserve">6.57062768936157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50289726257324</t>
+    <t xml:space="preserve">6.50289678573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.52203798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44768476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43942356109619</t>
+    <t xml:space="preserve">6.44768571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43942403793335</t>
   </si>
   <si>
     <t xml:space="preserve">6.44242763519287</t>
@@ -3371,82 +3371,82 @@
     <t xml:space="preserve">6.25992488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30874300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30949354171753</t>
+    <t xml:space="preserve">6.30874109268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30949306488037</t>
   </si>
   <si>
     <t xml:space="preserve">6.15177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17430591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15853404998779</t>
+    <t xml:space="preserve">6.17430543899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15853452682495</t>
   </si>
   <si>
     <t xml:space="preserve">6.42290067672729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42590522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3440408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3838472366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22162246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24715709686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35530662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35981369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23589086532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15552997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06615591049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94824314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88816022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9685206413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85962009429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72743654251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8904128074646</t>
+    <t xml:space="preserve">6.42590427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34404182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38384628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22162199020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24715662002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35530614852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35981321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35755968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23589181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15553045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0661563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105215072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94824266433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88815927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96852111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85961961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72743606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89041233062744</t>
   </si>
   <si>
     <t xml:space="preserve">5.91294384002686</t>
@@ -3455,34 +3455,34 @@
     <t xml:space="preserve">6.07141304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16980075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316619873047</t>
+    <t xml:space="preserve">6.08568382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16980028152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316572189331</t>
   </si>
   <si>
     <t xml:space="preserve">6.19984197616577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14426469802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18707418441772</t>
+    <t xml:space="preserve">6.14426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">6.12999439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05639314651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2381443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25166273117065</t>
+    <t xml:space="preserve">6.05639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23814487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25166320800781</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826948165894</t>
@@ -3491,133 +3491,133 @@
     <t xml:space="preserve">6.34028673171997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32902002334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910341262817</t>
+    <t xml:space="preserve">6.32902097702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910436630249</t>
   </si>
   <si>
     <t xml:space="preserve">6.33352708816528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37858963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42440223693848</t>
+    <t xml:space="preserve">6.37858915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33502912521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42440271377563</t>
   </si>
   <si>
     <t xml:space="preserve">6.44843673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49725389480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444488525391</t>
+    <t xml:space="preserve">6.49725294113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444440841675</t>
   </si>
   <si>
     <t xml:space="preserve">6.44392967224121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39060640335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4446816444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326204299927</t>
+    <t xml:space="preserve">6.47472238540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44468212127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326251983643</t>
   </si>
   <si>
     <t xml:space="preserve">6.50551509857178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42515420913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37408304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54757452011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217889785767</t>
+    <t xml:space="preserve">6.42515468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37408256530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54757404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034135818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48899364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217842102051</t>
   </si>
   <si>
     <t xml:space="preserve">6.20885419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27569580078125</t>
+    <t xml:space="preserve">6.27569675445557</t>
   </si>
   <si>
     <t xml:space="preserve">6.16304063796997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22537660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20960474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21411085128784</t>
+    <t xml:space="preserve">6.22537708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20960521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.214111328125</t>
   </si>
   <si>
     <t xml:space="preserve">6.00231790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07742261886597</t>
+    <t xml:space="preserve">6.07742166519165</t>
   </si>
   <si>
     <t xml:space="preserve">6.16153860092163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12623977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10445880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98279047012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06390380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774133682251</t>
+    <t xml:space="preserve">6.12623882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10445976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98279094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06390285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774181365967</t>
   </si>
   <si>
     <t xml:space="preserve">6.13374948501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11872911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11572360992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05038404464722</t>
+    <t xml:space="preserve">6.11872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11572456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05038452148438</t>
   </si>
   <si>
     <t xml:space="preserve">5.994056224823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92721319198608</t>
+    <t xml:space="preserve">5.9272141456604</t>
   </si>
   <si>
     <t xml:space="preserve">5.95650482177734</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">6.01733922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01808881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9790358543396</t>
+    <t xml:space="preserve">6.01808929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">6.02484941482544</t>
@@ -3641,64 +3641,64 @@
     <t xml:space="preserve">6.08493280410767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06840991973877</t>
+    <t xml:space="preserve">6.06840944290161</t>
   </si>
   <si>
     <t xml:space="preserve">6.16829824447632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06765842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04888200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09845066070557</t>
+    <t xml:space="preserve">6.06765937805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04888248443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09845018386841</t>
   </si>
   <si>
     <t xml:space="preserve">6.08943843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9865460395813</t>
+    <t xml:space="preserve">5.98654651641846</t>
   </si>
   <si>
     <t xml:space="preserve">6.03386163711548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01508569717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88215065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89491939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8964204788208</t>
+    <t xml:space="preserve">6.01508522033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879957199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03686571121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88215160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89491891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89642143249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.93772840499878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401500701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92045402526855</t>
+    <t xml:space="preserve">5.96401405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92045497894287</t>
   </si>
   <si>
     <t xml:space="preserve">5.951247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05188608169556</t>
+    <t xml:space="preserve">6.05489158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05188703536987</t>
   </si>
   <si>
     <t xml:space="preserve">6.02635145187378</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8513560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.002769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11575412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18723392486572</t>
+    <t xml:space="preserve">5.8444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85135555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00277042388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1157546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18723487854004</t>
   </si>
   <si>
     <t xml:space="preserve">6.21106147766113</t>
@@ -3731,28 +3731,28 @@
     <t xml:space="preserve">6.11959743499756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19107818603516</t>
+    <t xml:space="preserve">6.191077709198</t>
   </si>
   <si>
     <t xml:space="preserve">6.16033363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97971296310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94819927215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91361284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96357202529907</t>
+    <t xml:space="preserve">5.97971200942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91361236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92052984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96357154846191</t>
   </si>
   <si>
     <t xml:space="preserve">5.99354696273804</t>
@@ -3764,43 +3764,43 @@
     <t xml:space="preserve">6.02044820785522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02890205383301</t>
+    <t xml:space="preserve">6.02890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03120946884155</t>
+    <t xml:space="preserve">6.03120851516724</t>
   </si>
   <si>
     <t xml:space="preserve">5.97740650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03735780715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08885335922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14957284927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0196795463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96510934829712</t>
+    <t xml:space="preserve">6.03735733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08885288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01968002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96510887145996</t>
   </si>
   <si>
     <t xml:space="preserve">5.90131521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90208435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95511722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93129110336304</t>
+    <t xml:space="preserve">5.90208339691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95511770248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93129014968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.99815893173218</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">5.77833938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756189346313</t>
+    <t xml:space="preserve">5.78756284713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.66842937469482</t>
@@ -3827,28 +3827,28 @@
     <t xml:space="preserve">5.7637357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71454524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39941835403442</t>
+    <t xml:space="preserve">5.71454572677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39941930770874</t>
   </si>
   <si>
     <t xml:space="preserve">5.38097286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34869146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2572283744812</t>
+    <t xml:space="preserve">5.3486909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25722694396973</t>
   </si>
   <si>
     <t xml:space="preserve">5.30257606506348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33408784866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4409236907959</t>
+    <t xml:space="preserve">5.33408832550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44092321395874</t>
   </si>
   <si>
     <t xml:space="preserve">5.39403915405273</t>
@@ -3860,22 +3860,22 @@
     <t xml:space="preserve">5.25492191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22110414505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11196231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17883014678955</t>
+    <t xml:space="preserve">5.22110366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11196184158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17191362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30565023422241</t>
+    <t xml:space="preserve">5.3056492805481</t>
   </si>
   <si>
     <t xml:space="preserve">5.31794738769531</t>
@@ -3884,19 +3884,19 @@
     <t xml:space="preserve">5.18651676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24954175949097</t>
+    <t xml:space="preserve">5.19958257675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24954223632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.30795574188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44246006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54160976409912</t>
+    <t xml:space="preserve">5.44246101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54161071777344</t>
   </si>
   <si>
     <t xml:space="preserve">5.51317167282104</t>
@@ -3905,16 +3905,16 @@
     <t xml:space="preserve">5.47781610488892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42708873748779</t>
+    <t xml:space="preserve">5.42708921432495</t>
   </si>
   <si>
     <t xml:space="preserve">5.49165058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54622173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772563934326</t>
+    <t xml:space="preserve">5.54622268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772706985474</t>
   </si>
   <si>
     <t xml:space="preserve">5.56159353256226</t>
@@ -3923,64 +3923,64 @@
     <t xml:space="preserve">5.59925508499146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55774974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57696580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57389163970947</t>
+    <t xml:space="preserve">5.55775022506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57696628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57389116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.60617303848267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53008127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45245218276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5031795501709</t>
+    <t xml:space="preserve">5.5300817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45245265960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50318002700806</t>
   </si>
   <si>
     <t xml:space="preserve">5.45629549026489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49549436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44707250595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4324688911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41248464584351</t>
+    <t xml:space="preserve">5.49549388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44707155227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41248512268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.34177398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34331130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30872392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41479206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49472522735596</t>
+    <t xml:space="preserve">5.34331083297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30872440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41479158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49472570419312</t>
   </si>
   <si>
     <t xml:space="preserve">5.2387809753418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21802949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15500354766846</t>
+    <t xml:space="preserve">5.21802997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15500402450562</t>
   </si>
   <si>
     <t xml:space="preserve">5.19189691543579</t>
@@ -3998,25 +3998,25 @@
     <t xml:space="preserve">5.234938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039205551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15116214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14193820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07583856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09274768829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1473183631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1096568107605</t>
+    <t xml:space="preserve">5.15039300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15116024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14193725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0758376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0927472114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14731788635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965633392334</t>
   </si>
   <si>
     <t xml:space="preserve">5.18497943878174</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">5.1134991645813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25338506698608</t>
+    <t xml:space="preserve">5.25338459014893</t>
   </si>
   <si>
     <t xml:space="preserve">5.2848973274231</t>
@@ -4034,37 +4034,37 @@
     <t xml:space="preserve">5.31564140319824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32486438751221</t>
+    <t xml:space="preserve">5.32486486434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.40787363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38788986206055</t>
+    <t xml:space="preserve">5.38788938522339</t>
   </si>
   <si>
     <t xml:space="preserve">5.41555976867676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51240253448486</t>
+    <t xml:space="preserve">5.51240396499634</t>
   </si>
   <si>
     <t xml:space="preserve">5.47243547439575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34100532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32640218734741</t>
+    <t xml:space="preserve">5.34100484848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3264012336731</t>
   </si>
   <si>
     <t xml:space="preserve">5.32717084884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32025289535522</t>
+    <t xml:space="preserve">5.32025241851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.35022830963135</t>
@@ -4073,13 +4073,13 @@
     <t xml:space="preserve">5.2318639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27490520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38250875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30718755722046</t>
+    <t xml:space="preserve">5.27490615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38250923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
     <t xml:space="preserve">5.26767015457153</t>
@@ -4088,34 +4088,34 @@
     <t xml:space="preserve">5.26845979690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41546487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33642959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35934972763062</t>
+    <t xml:space="preserve">5.41546535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33643007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35935020446777</t>
   </si>
   <si>
     <t xml:space="preserve">5.41704511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41309356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35776901245117</t>
+    <t xml:space="preserve">5.41309309005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35776948928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.24712038040161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08272886276245</t>
+    <t xml:space="preserve">5.08272790908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11908435821533</t>
+    <t xml:space="preserve">5.11908483505249</t>
   </si>
   <si>
     <t xml:space="preserve">5.08351850509644</t>
@@ -4124,31 +4124,31 @@
     <t xml:space="preserve">5.05348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99499893188477</t>
+    <t xml:space="preserve">4.99499940872192</t>
   </si>
   <si>
     <t xml:space="preserve">5.08114767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14516639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12303590774536</t>
+    <t xml:space="preserve">5.14516592025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1230354309082</t>
   </si>
   <si>
     <t xml:space="preserve">5.08588933944702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9760308265686</t>
+    <t xml:space="preserve">4.97603130340576</t>
   </si>
   <si>
     <t xml:space="preserve">5.01396751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99025726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89383506774902</t>
+    <t xml:space="preserve">4.99025821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89383554458618</t>
   </si>
   <si>
     <t xml:space="preserve">5.17598962783813</t>
@@ -4160,16 +4160,16 @@
     <t xml:space="preserve">4.87960815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8764476776123</t>
+    <t xml:space="preserve">4.87644720077515</t>
   </si>
   <si>
     <t xml:space="preserve">4.70652198791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
+    <t xml:space="preserve">4.48127412796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512491226196</t>
   </si>
   <si>
     <t xml:space="preserve">4.52237129211426</t>
@@ -4181,67 +4181,67 @@
     <t xml:space="preserve">4.53580760955811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5271143913269</t>
+    <t xml:space="preserve">4.52711343765259</t>
   </si>
   <si>
     <t xml:space="preserve">4.59903526306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456800460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60298728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52079105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55240440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60219621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51209688186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56030750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64566516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81875228881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82428503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82902669906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92544889450073</t>
+    <t xml:space="preserve">4.60456848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60298681259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52079010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55240488052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60219717025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51209735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56030797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8187518119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82428407669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.829026222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92544841766357</t>
   </si>
   <si>
     <t xml:space="preserve">4.90648078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8748664855957</t>
+    <t xml:space="preserve">4.87486696243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.98709583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
+    <t xml:space="preserve">4.96891832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.89857721328735</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">4.90173816680908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88514137268066</t>
+    <t xml:space="preserve">4.88514184951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.87249565124512</t>
@@ -4259,37 +4259,37 @@
     <t xml:space="preserve">4.7523627281189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81558990478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79978322982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91596460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91438436508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87881803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93888425827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89541530609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78555679321289</t>
+    <t xml:space="preserve">4.82349443435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81559038162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7997841835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91596412658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91438388824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87881851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93888473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89541578292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78555727005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.74841070175171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64171361923218</t>
+    <t xml:space="preserve">4.64171457290649</t>
   </si>
   <si>
     <t xml:space="preserve">4.61721277236938</t>
@@ -4298,58 +4298,58 @@
     <t xml:space="preserve">4.72628116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61405181884766</t>
+    <t xml:space="preserve">4.6140513420105</t>
   </si>
   <si>
     <t xml:space="preserve">4.69229602813721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73181438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69308614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69150543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83930110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84720468521118</t>
+    <t xml:space="preserve">4.73181390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74999141693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69150590896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83930063247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84720420837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.84641408920288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88751173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88909292221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87012481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77686309814453</t>
+    <t xml:space="preserve">4.88751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88909339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87012434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77686405181885</t>
   </si>
   <si>
     <t xml:space="preserve">4.68202114105225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7057318687439</t>
+    <t xml:space="preserve">4.70573234558105</t>
   </si>
   <si>
     <t xml:space="preserve">4.66700553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76500797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73260402679443</t>
+    <t xml:space="preserve">4.76500844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73260354995728</t>
   </si>
   <si>
     <t xml:space="preserve">4.62037467956543</t>
@@ -4358,10 +4358,10 @@
     <t xml:space="preserve">4.52790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33189725875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25839471817017</t>
+    <t xml:space="preserve">4.3318977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25839519500732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492624282837</t>
@@ -4373,25 +4373,25 @@
     <t xml:space="preserve">4.26787948608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30107402801514</t>
+    <t xml:space="preserve">4.30107355117798</t>
   </si>
   <si>
     <t xml:space="preserve">4.33822059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31925201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2291522026062</t>
+    <t xml:space="preserve">4.31925249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22915172576904</t>
   </si>
   <si>
     <t xml:space="preserve">4.28526735305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35718870162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2749924659729</t>
+    <t xml:space="preserve">4.35718822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27499294281006</t>
   </si>
   <si>
     <t xml:space="preserve">4.32794570922852</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">4.12561655044556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19911956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259660720825</t>
+    <t xml:space="preserve">4.19911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17382860183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">4.09084177017212</t>
@@ -4418,10 +4418,10 @@
     <t xml:space="preserve">4.15960216522217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15090703964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14300441741943</t>
+    <t xml:space="preserve">4.15090799331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14300394058228</t>
   </si>
   <si>
     <t xml:space="preserve">4.0924220085144</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82133293151855</t>
+    <t xml:space="preserve">3.8213324546814</t>
   </si>
   <si>
     <t xml:space="preserve">3.95174026489258</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">4.08606576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95831251144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90080308914185</t>
+    <t xml:space="preserve">3.95831274986267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90080285072327</t>
   </si>
   <si>
     <t xml:space="preserve">3.88108515739441</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">3.90244603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89053344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683581352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93818402290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06922483444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99610495567322</t>
+    <t xml:space="preserve">3.89053320884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683652877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93818426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06922435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.0051417350769</t>
@@ -4475,13 +4475,13 @@
     <t xml:space="preserve">4.03636121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06758165359497</t>
+    <t xml:space="preserve">4.06758117675781</t>
   </si>
   <si>
     <t xml:space="preserve">4.13412761688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11441087722778</t>
+    <t xml:space="preserve">4.11441040039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
@@ -4490,64 +4490,64 @@
     <t xml:space="preserve">4.10783815383911</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13659286499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19163846969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18752956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18342208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11030197143555</t>
+    <t xml:space="preserve">4.13659238815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19163799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18753004074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18342256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11030244827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05443620681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05854368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06265258789062</t>
+    <t xml:space="preserve">4.05854415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06265211105347</t>
   </si>
   <si>
     <t xml:space="preserve">4.06347322463989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9702250957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94640016555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95461583137512</t>
+    <t xml:space="preserve">3.97022533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94639992713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95461559295654</t>
   </si>
   <si>
     <t xml:space="preserve">3.857670545578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81412768363953</t>
+    <t xml:space="preserve">3.81412744522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.90614318847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86136770248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84288239479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90162420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94845366477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98871088027954</t>
+    <t xml:space="preserve">3.86136794090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84288215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90162467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94845414161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98871111869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.10085439682007</t>
@@ -4556,40 +4556,40 @@
     <t xml:space="preserve">4.06593751907349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04211282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02321624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04170227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98419260978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97186803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8153600692749</t>
+    <t xml:space="preserve">4.04211235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02321672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0417013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679781913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98419213294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97186851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81535983085632</t>
   </si>
   <si>
     <t xml:space="preserve">3.73607873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53438353538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5483500957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49001932144165</t>
+    <t xml:space="preserve">3.53438377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54835033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49001908302307</t>
   </si>
   <si>
     <t xml:space="preserve">3.47030138969421</t>
@@ -4598,49 +4598,49 @@
     <t xml:space="preserve">3.57957005500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66706681251526</t>
+    <t xml:space="preserve">3.66706705093384</t>
   </si>
   <si>
     <t xml:space="preserve">3.55040407180786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42593669891357</t>
+    <t xml:space="preserve">3.42593717575073</t>
   </si>
   <si>
     <t xml:space="preserve">3.38609075546265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44154644012451</t>
+    <t xml:space="preserve">3.44154691696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.34870982170105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28873491287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34542346000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37910723686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4629077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49823451042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51918458938599</t>
+    <t xml:space="preserve">3.28873515129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34542322158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37910747528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46290755271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49823474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51918506622314</t>
   </si>
   <si>
     <t xml:space="preserve">3.48426818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4460654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52740001678467</t>
+    <t xml:space="preserve">3.44606518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52740025520325</t>
   </si>
   <si>
     <t xml:space="preserve">3.59764456748962</t>
@@ -4649,52 +4649,52 @@
     <t xml:space="preserve">3.60257387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71512842178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6740505695343</t>
+    <t xml:space="preserve">3.71512866020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">3.71266388893127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72950625419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77304887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75784993171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8445258140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95913338661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11605405807495</t>
+    <t xml:space="preserve">3.72950649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77304911613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7578501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84452557563782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217638969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037939071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11605358123779</t>
   </si>
   <si>
     <t xml:space="preserve">4.14727306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17274188995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1982102394104</t>
+    <t xml:space="preserve">4.17274236679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">4.22203588485718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23682451248169</t>
+    <t xml:space="preserve">4.23682403564453</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767095565796</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">4.23518085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16534757614136</t>
+    <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
     <t xml:space="preserve">4.19492435455322</t>
@@ -4718,37 +4718,37 @@
     <t xml:space="preserve">4.21792793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31323003768921</t>
+    <t xml:space="preserve">4.31322956085205</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3362340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27708005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29186868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25079011917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29022645950317</t>
+    <t xml:space="preserve">4.33623313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27708101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29186916351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2507905960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29022598266602</t>
   </si>
   <si>
     <t xml:space="preserve">4.27050828933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3115873336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31487226486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1530237197876</t>
+    <t xml:space="preserve">4.31158685684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31487274169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15302419662476</t>
   </si>
   <si>
     <t xml:space="preserve">4.14891624450684</t>
@@ -4769,19 +4769,19 @@
     <t xml:space="preserve">4.1908164024353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17191982269287</t>
+    <t xml:space="preserve">4.17192029953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.14809417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13248538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24832630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35430812835693</t>
+    <t xml:space="preserve">4.13248491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24832582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35430860519409</t>
   </si>
   <si>
     <t xml:space="preserve">4.50794172286987</t>
@@ -4793,34 +4793,34 @@
     <t xml:space="preserve">4.60159969329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59995698928833</t>
+    <t xml:space="preserve">4.59995603561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.54819822311401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62542533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68868637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70593976974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7716646194458</t>
+    <t xml:space="preserve">4.62542581558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68868589401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70593881607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77166414260864</t>
   </si>
   <si>
     <t xml:space="preserve">4.73222923278809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73551511764526</t>
+    <t xml:space="preserve">4.73551559448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.64760828018188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64185762405396</t>
+    <t xml:space="preserve">4.6418571472168</t>
   </si>
   <si>
     <t xml:space="preserve">4.65548467636108</t>
@@ -4835,82 +4835,82 @@
     <t xml:space="preserve">4.66996335983276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67166757583618</t>
+    <t xml:space="preserve">4.67166709899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.6273775100708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59160566329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58394050598145</t>
+    <t xml:space="preserve">4.5916051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58394002914429</t>
   </si>
   <si>
     <t xml:space="preserve">4.5669059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58138465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56435108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55327844619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54816865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60863924026489</t>
+    <t xml:space="preserve">4.58138561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56435012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55327892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54816818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60863971710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.60182619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58223724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5881986618042</t>
+    <t xml:space="preserve">4.58223676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58819961547852</t>
   </si>
   <si>
     <t xml:space="preserve">4.57712650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55924081802368</t>
+    <t xml:space="preserve">4.55924034118652</t>
   </si>
   <si>
     <t xml:space="preserve">4.55668497085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52687549591064</t>
+    <t xml:space="preserve">4.52687454223633</t>
   </si>
   <si>
     <t xml:space="preserve">4.46214437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48003053665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45788621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51920938491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5285792350769</t>
+    <t xml:space="preserve">4.48003149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51921033859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52857875823975</t>
   </si>
   <si>
     <t xml:space="preserve">4.42892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51495122909546</t>
+    <t xml:space="preserve">4.48428964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5149507522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.54305791854858</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">4.5311336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53028106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53624439239502</t>
+    <t xml:space="preserve">4.53028154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53624391555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.45192384719849</t>
@@ -4934,34 +4934,34 @@
     <t xml:space="preserve">4.5686092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46810626983643</t>
+    <t xml:space="preserve">4.46810674667358</t>
   </si>
   <si>
     <t xml:space="preserve">4.51069211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58904981613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66740798950195</t>
+    <t xml:space="preserve">4.50302743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58905029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66740846633911</t>
   </si>
   <si>
     <t xml:space="preserve">4.68784952163696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69040441513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59245729446411</t>
+    <t xml:space="preserve">4.69040489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59245777130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.65378141403198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6418571472168</t>
+    <t xml:space="preserve">4.64185667037964</t>
   </si>
   <si>
     <t xml:space="preserve">4.69125699996948</t>
@@ -4976,16 +4976,16 @@
     <t xml:space="preserve">4.77131795883179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75683879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82242059707642</t>
+    <t xml:space="preserve">4.75683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82242155075073</t>
   </si>
   <si>
     <t xml:space="preserve">4.98169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02853631973267</t>
+    <t xml:space="preserve">5.02853584289551</t>
   </si>
   <si>
     <t xml:space="preserve">5.10348749160767</t>
@@ -4994,22 +4994,22 @@
     <t xml:space="preserve">4.90333414077759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86159992218018</t>
+    <t xml:space="preserve">4.86160039901733</t>
   </si>
   <si>
     <t xml:space="preserve">4.87181997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90503787994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94762325286865</t>
+    <t xml:space="preserve">4.90503692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94762372970581</t>
   </si>
   <si>
     <t xml:space="preserve">4.97402667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05153322219849</t>
+    <t xml:space="preserve">5.05153274536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.13414907455444</t>
@@ -5021,64 +5021,64 @@
     <t xml:space="preserve">5.18695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25083494186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979278564453</t>
+    <t xml:space="preserve">5.2508339881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979230880737</t>
   </si>
   <si>
     <t xml:space="preserve">5.19376945495605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19462060928345</t>
+    <t xml:space="preserve">5.19462156295776</t>
   </si>
   <si>
     <t xml:space="preserve">5.18440103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24827909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21165609359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20569372177124</t>
+    <t xml:space="preserve">5.2482795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21165561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">5.18951082229614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14777660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15970134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12563276290894</t>
+    <t xml:space="preserve">5.14777708053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15970087051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12563228607178</t>
   </si>
   <si>
     <t xml:space="preserve">5.12733554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09156322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02598142623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11796617507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14351844787598</t>
+    <t xml:space="preserve">5.09156370162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02598094940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1179666519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14351797103882</t>
   </si>
   <si>
     <t xml:space="preserve">5.13670444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.080491065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00809574127197</t>
+    <t xml:space="preserve">5.08049154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00809478759766</t>
   </si>
   <si>
     <t xml:space="preserve">5.07112216949463</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">5.07367706298828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12052202224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98935747146606</t>
+    <t xml:space="preserve">5.12052154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98935699462891</t>
   </si>
   <si>
     <t xml:space="preserve">5.07452917098999</t>
@@ -5105,76 +5105,76 @@
     <t xml:space="preserve">5.15288734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17332792282104</t>
+    <t xml:space="preserve">5.1733283996582</t>
   </si>
   <si>
     <t xml:space="preserve">5.17247676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20484161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16992092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20228624343872</t>
+    <t xml:space="preserve">5.20484256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20228672027588</t>
   </si>
   <si>
     <t xml:space="preserve">5.19632434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884923934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17843866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22698593139648</t>
+    <t xml:space="preserve">5.15884971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17843818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22698640823364</t>
   </si>
   <si>
     <t xml:space="preserve">5.23635530471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25338983535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31471347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903354644775</t>
+    <t xml:space="preserve">5.25339031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31471252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3990330696106</t>
   </si>
   <si>
     <t xml:space="preserve">5.28916168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14266586303711</t>
+    <t xml:space="preserve">5.14266633987427</t>
   </si>
   <si>
     <t xml:space="preserve">5.1929178237915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1750316619873</t>
+    <t xml:space="preserve">5.17503213882446</t>
   </si>
   <si>
     <t xml:space="preserve">5.21250677108765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30619621276855</t>
+    <t xml:space="preserve">5.30619668960571</t>
   </si>
   <si>
     <t xml:space="preserve">5.39136791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31301021575928</t>
+    <t xml:space="preserve">5.31300973892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.34622669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34452295303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3607063293457</t>
+    <t xml:space="preserve">5.34452342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36070585250854</t>
   </si>
   <si>
     <t xml:space="preserve">5.39647817611694</t>
@@ -5186,22 +5186,22 @@
     <t xml:space="preserve">5.45012617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47035360336304</t>
+    <t xml:space="preserve">5.4703540802002</t>
   </si>
   <si>
     <t xml:space="preserve">5.55038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51872539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51608753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4615592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34370946884155</t>
+    <t xml:space="preserve">5.51872587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5160870552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46155977249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34370994567871</t>
   </si>
   <si>
     <t xml:space="preserve">5.28214597702026</t>
@@ -5225,40 +5225,40 @@
     <t xml:space="preserve">5.32436084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23553419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17484951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21002864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26719522476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33227634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34194993972778</t>
+    <t xml:space="preserve">5.23553371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17484998703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21002817153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2671947479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33227682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34195041656494</t>
   </si>
   <si>
     <t xml:space="preserve">5.37273263931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39120101928711</t>
+    <t xml:space="preserve">5.39120149612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.4589204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43957233428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4140682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40791130065918</t>
+    <t xml:space="preserve">5.43957281112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41406774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40791177749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.39383983612061</t>
@@ -5267,13 +5267,13 @@
     <t xml:space="preserve">5.36745548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46068048477173</t>
+    <t xml:space="preserve">5.46068000793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.44484901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45188522338867</t>
+    <t xml:space="preserve">5.45188474655151</t>
   </si>
   <si>
     <t xml:space="preserve">5.38768339157104</t>
@@ -5285,16 +5285,16 @@
     <t xml:space="preserve">5.52752017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48442554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4747519493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35338401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31644535064697</t>
+    <t xml:space="preserve">5.48442649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47475147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35338354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31644582748413</t>
   </si>
   <si>
     <t xml:space="preserve">5.25488185882568</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">5.23113632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.145827293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09042024612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11856365203857</t>
+    <t xml:space="preserve">5.14582633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09041929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11856269836426</t>
   </si>
   <si>
     <t xml:space="preserve">4.97872591018677</t>
@@ -5318,16 +5318,16 @@
     <t xml:space="preserve">4.85208129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88725996017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88462209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92859601974487</t>
+    <t xml:space="preserve">4.88726091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88462162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92595720291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92859554290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.02270030975342</t>
@@ -5336,7 +5336,7 @@
     <t xml:space="preserve">5.08426380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06051731109619</t>
+    <t xml:space="preserve">5.06051826477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.03325366973877</t>
@@ -5363,16 +5363,16 @@
     <t xml:space="preserve">5.07722759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05875825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08250427246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06139659881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17660856246948</t>
+    <t xml:space="preserve">5.05875873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0825047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06139707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17660903930664</t>
   </si>
   <si>
     <t xml:space="preserve">5.26631546020508</t>
@@ -5381,22 +5381,22 @@
     <t xml:space="preserve">5.30589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37712955474854</t>
+    <t xml:space="preserve">5.37713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">5.4175853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40527296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38152742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39032220840454</t>
+    <t xml:space="preserve">5.40527248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3542628288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39032173156738</t>
   </si>
   <si>
     <t xml:space="preserve">5.43869304656982</t>
@@ -5411,7 +5411,7 @@
     <t xml:space="preserve">5.63305807113647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70781278610229</t>
+    <t xml:space="preserve">5.70781326293945</t>
   </si>
   <si>
     <t xml:space="preserve">5.6427321434021</t>
@@ -5423,16 +5423,16 @@
     <t xml:space="preserve">5.61282968521118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65680360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66559791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6576828956604</t>
+    <t xml:space="preserve">5.64097356796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65680408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66559839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65768337249756</t>
   </si>
   <si>
     <t xml:space="preserve">5.70429515838623</t>
@@ -5450,16 +5450,16 @@
     <t xml:space="preserve">5.75882291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75354623794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77465391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73155927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.815110206604</t>
+    <t xml:space="preserve">5.7535457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77465343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73155975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81510925292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.91185235977173</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">5.85996341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89250326156616</t>
+    <t xml:space="preserve">5.89250373840332</t>
   </si>
   <si>
     <t xml:space="preserve">5.86436080932617</t>
@@ -5483,25 +5483,25 @@
     <t xml:space="preserve">5.90921401977539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91097354888916</t>
+    <t xml:space="preserve">5.910973072052</t>
   </si>
   <si>
     <t xml:space="preserve">5.90041923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91888856887817</t>
+    <t xml:space="preserve">5.91888809204102</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88458824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89162445068359</t>
+    <t xml:space="preserve">5.91361093521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88458871841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89162397384644</t>
   </si>
   <si>
     <t xml:space="preserve">5.92504453659058</t>
@@ -5513,19 +5513,19 @@
     <t xml:space="preserve">5.97165727615356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98660802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93647766113281</t>
+    <t xml:space="preserve">5.98660755157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93647718429565</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8239049911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85908317565918</t>
+    <t xml:space="preserve">5.82390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8590841293335</t>
   </si>
   <si>
     <t xml:space="preserve">5.80092000961304</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">5.74002981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72185325622559</t>
+    <t xml:space="preserve">5.72185373306274</t>
   </si>
   <si>
     <t xml:space="preserve">5.69913339614868</t>
@@ -5549,52 +5549,52 @@
     <t xml:space="preserve">5.68550109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76274967193604</t>
+    <t xml:space="preserve">5.76275014877319</t>
   </si>
   <si>
     <t xml:space="preserve">5.63824319839478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61824989318848</t>
+    <t xml:space="preserve">5.61824941635132</t>
   </si>
   <si>
     <t xml:space="preserve">5.56826496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52191591262817</t>
+    <t xml:space="preserve">5.52191638946533</t>
   </si>
   <si>
     <t xml:space="preserve">5.48011112213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41013288497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33833694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3774151802063</t>
+    <t xml:space="preserve">5.41013240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33833646774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37741565704346</t>
   </si>
   <si>
     <t xml:space="preserve">5.34651613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37468910217285</t>
+    <t xml:space="preserve">5.37468957901001</t>
   </si>
   <si>
     <t xml:space="preserve">5.38468599319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32652282714844</t>
+    <t xml:space="preserve">5.32652235031128</t>
   </si>
   <si>
     <t xml:space="preserve">5.36469221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41376733779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3919563293457</t>
+    <t xml:space="preserve">5.41376781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39195680618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.41467666625977</t>
@@ -5609,10 +5609,10 @@
     <t xml:space="preserve">5.31925201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35469532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48738098144531</t>
+    <t xml:space="preserve">5.35469579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48738145828247</t>
   </si>
   <si>
     <t xml:space="preserve">5.54463577270508</t>
@@ -5621,7 +5621,7 @@
     <t xml:space="preserve">5.57917070388794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57099151611328</t>
+    <t xml:space="preserve">5.57099199295044</t>
   </si>
   <si>
     <t xml:space="preserve">5.59462070465088</t>
@@ -5633,7 +5633,7 @@
     <t xml:space="preserve">5.64278745651245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5700831413269</t>
+    <t xml:space="preserve">5.57008266448975</t>
   </si>
   <si>
     <t xml:space="preserve">5.57190036773682</t>
@@ -5645,7 +5645,7 @@
     <t xml:space="preserve">5.54645395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51646280288696</t>
+    <t xml:space="preserve">5.51646327972412</t>
   </si>
   <si>
     <t xml:space="preserve">5.52646017074585</t>
@@ -5657,7 +5657,7 @@
     <t xml:space="preserve">5.52918672561646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60552644729614</t>
+    <t xml:space="preserve">5.6055269241333</t>
   </si>
   <si>
     <t xml:space="preserve">5.56099462509155</t>
@@ -5666,19 +5666,19 @@
     <t xml:space="preserve">5.44194078445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44375801086426</t>
+    <t xml:space="preserve">5.44375848770142</t>
   </si>
   <si>
     <t xml:space="preserve">5.49465179443359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36832761764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36105728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29380464553833</t>
+    <t xml:space="preserve">5.36832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36105680465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29380512237549</t>
   </si>
   <si>
     <t xml:space="preserve">5.17929553985596</t>
@@ -5687,13 +5687,13 @@
     <t xml:space="preserve">5.18656539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33742761611938</t>
+    <t xml:space="preserve">5.33742809295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.31470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26563262939453</t>
+    <t xml:space="preserve">5.26563215255737</t>
   </si>
   <si>
     <t xml:space="preserve">5.25836133956909</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">5.33651924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.411949634552</t>
+    <t xml:space="preserve">5.41195011138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.49737787246704</t>
@@ -5726,25 +5726,25 @@
     <t xml:space="preserve">5.67277812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68004894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74820852279663</t>
+    <t xml:space="preserve">5.68004846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74820899963379</t>
   </si>
   <si>
     <t xml:space="preserve">5.80182886123657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85817432403564</t>
+    <t xml:space="preserve">5.8581748008728</t>
   </si>
   <si>
     <t xml:space="preserve">5.91452074050903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13899660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13626956939697</t>
+    <t xml:space="preserve">6.13899612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13627004623413</t>
   </si>
   <si>
     <t xml:space="preserve">6.10173559188843</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">6.14444923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12082004547119</t>
+    <t xml:space="preserve">6.12082052230835</t>
   </si>
   <si>
     <t xml:space="preserve">6.06538248062134</t>
@@ -5777,10 +5777,10 @@
     <t xml:space="preserve">6.0535683631897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05265951156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97086668014526</t>
+    <t xml:space="preserve">6.05265998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97086715698242</t>
   </si>
   <si>
     <t xml:space="preserve">6.01630687713623</t>
@@ -5795,13 +5795,13 @@
     <t xml:space="preserve">6.12172937393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19170761108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17807483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09809970855713</t>
+    <t xml:space="preserve">6.19170713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17807531356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09810018539429</t>
   </si>
   <si>
     <t xml:space="preserve">6.06992721557617</t>
@@ -5810,7 +5810,7 @@
     <t xml:space="preserve">5.96904945373535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03539180755615</t>
+    <t xml:space="preserve">6.03539228439331</t>
   </si>
   <si>
     <t xml:space="preserve">5.95632600784302</t>
@@ -5834,13 +5834,13 @@
     <t xml:space="preserve">5.87907743453979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94542026519775</t>
+    <t xml:space="preserve">5.9454197883606</t>
   </si>
   <si>
     <t xml:space="preserve">5.97813749313354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95087337493896</t>
+    <t xml:space="preserve">5.95087289810181</t>
   </si>
   <si>
     <t xml:space="preserve">5.90452432632446</t>
@@ -5852,22 +5852,22 @@
     <t xml:space="preserve">6.00449275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98449897766113</t>
+    <t xml:space="preserve">5.98449850082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.02812194824219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04266262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09446430206299</t>
+    <t xml:space="preserve">6.04266309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09446477890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.11809349060059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1698956489563</t>
+    <t xml:space="preserve">6.16989612579346</t>
   </si>
   <si>
     <t xml:space="preserve">6.25714159011841</t>
@@ -5876,7 +5876,7 @@
     <t xml:space="preserve">6.17171335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1262731552124</t>
+    <t xml:space="preserve">6.12627363204956</t>
   </si>
   <si>
     <t xml:space="preserve">6.15081119537354</t>
@@ -6813,6 +6813,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.9379997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95600032806396</t>
   </si>
 </sst>
 </file>
@@ -72385,7 +72388,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6912037037</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>22453349</v>
@@ -72406,6 +72409,32 @@
         <v>2266</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6935416667</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>16149815</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>8.98799991607666</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>8.93000030517578</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>8.94499969482422</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>8.95600032806396</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>2267</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="2269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="2270">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958226203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22277045249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23223900794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448588371277</t>
+    <t xml:space="preserve">2.27958250045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22277069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23223924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448564529419</t>
   </si>
   <si>
     <t xml:space="preserve">2.21685266494751</t>
@@ -62,49 +62,49 @@
     <t xml:space="preserve">2.20146584510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23460698127747</t>
+    <t xml:space="preserve">2.23460626602173</t>
   </si>
   <si>
     <t xml:space="preserve">2.21211814880371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17187666893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281798362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767335891724</t>
+    <t xml:space="preserve">2.17187643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13281774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767383575439</t>
   </si>
   <si>
     <t xml:space="preserve">2.09257578849792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16004037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20620036125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19436454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513747215271</t>
+    <t xml:space="preserve">2.16004061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20620059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19436478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513723373413</t>
   </si>
   <si>
     <t xml:space="preserve">2.25236034393311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987198829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081377983093</t>
+    <t xml:space="preserve">2.17305946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395396232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081425666809</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702105522156</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">2.09849405288696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07008838653564</t>
+    <t xml:space="preserve">2.07008790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.06772089004517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0866584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09376001358032</t>
+    <t xml:space="preserve">2.08665871620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0937602519989</t>
   </si>
   <si>
     <t xml:space="preserve">2.16477465629578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1505720615387</t>
+    <t xml:space="preserve">2.15057158470154</t>
   </si>
   <si>
     <t xml:space="preserve">2.156489610672</t>
@@ -143,274 +143,274 @@
     <t xml:space="preserve">2.15293908119202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0949432849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18016171455383</t>
+    <t xml:space="preserve">2.09494280815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18016123771667</t>
   </si>
   <si>
     <t xml:space="preserve">2.19199728965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791507720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24170827865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25354337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31508946418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30798888206482</t>
+    <t xml:space="preserve">2.21330213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791555404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16714215278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542695999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24170804023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25354361534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31509017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30798840522766</t>
   </si>
   <si>
     <t xml:space="preserve">2.30207061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30562090873718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32574248313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31745719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982398033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153893470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088710784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3139066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059714317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36716771125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30680513381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496836662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27366471290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595816612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22632122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23579001426697</t>
+    <t xml:space="preserve">2.30562114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32574200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3174569606781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982445716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31153869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088663101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31390643119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35059690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36716794967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.306804895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496908187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2736644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595864295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22632145881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23579025268555</t>
   </si>
   <si>
     <t xml:space="preserve">2.21921968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26182913780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129745483398</t>
+    <t xml:space="preserve">2.26182866096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129721641541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29615235328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3423125743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34112906455994</t>
+    <t xml:space="preserve">2.2961528301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35769891738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34112882614136</t>
   </si>
   <si>
     <t xml:space="preserve">2.3292932510376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30917191505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941411018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071847915649</t>
+    <t xml:space="preserve">2.30917167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941363334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071824073792</t>
   </si>
   <si>
     <t xml:space="preserve">2.37663626670837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33757781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35296440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33166003227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36125016212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33994555473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385866165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41096019744873</t>
+    <t xml:space="preserve">2.3375780582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35296487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33165979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36124968528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33994483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095995903015</t>
   </si>
   <si>
     <t xml:space="preserve">2.42989778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42516350746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43699932098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38965582847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794087409973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37781977653503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463182449341</t>
+    <t xml:space="preserve">2.42516303062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43699908256531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38965606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794111251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37782001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463158607483</t>
   </si>
   <si>
     <t xml:space="preserve">2.44173336029053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43936634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3565149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3186411857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2783989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37900328636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43817067146301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44433403015137</t>
+    <t xml:space="preserve">2.43936681747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651469230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31864047050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27839875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37900304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43817019462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44433379173279</t>
   </si>
   <si>
     <t xml:space="preserve">2.40735411643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46652126312256</t>
+    <t xml:space="preserve">2.46652102470398</t>
   </si>
   <si>
     <t xml:space="preserve">2.21875977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21013116836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627799034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365648269653</t>
+    <t xml:space="preserve">2.21013164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627751350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365672111511</t>
   </si>
   <si>
     <t xml:space="preserve">2.45296216011047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45049643516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45419478416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3925633430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37653803825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4221465587616</t>
+    <t xml:space="preserve">2.45049715042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45419430732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39256286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37653827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42214608192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.43940329551697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45912575721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46035814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282362937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467990398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48008060455322</t>
+    <t xml:space="preserve">2.45912528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4603579044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44679856300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48008036613464</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254537582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47638249397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47268462181091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53801465034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5256884098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240684509277</t>
+    <t xml:space="preserve">2.47638273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47268438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53801488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52568769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240708351135</t>
   </si>
   <si>
     <t xml:space="preserve">2.48131275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49117398262024</t>
+    <t xml:space="preserve">2.49117422103882</t>
   </si>
   <si>
     <t xml:space="preserve">2.52322292327881</t>
@@ -419,100 +419,100 @@
     <t xml:space="preserve">2.5108962059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350046157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49856972694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53308415412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52938652038574</t>
+    <t xml:space="preserve">2.50350022315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49857020378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53308439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52938628196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.47021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42461156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707633972168</t>
+    <t xml:space="preserve">2.42461133003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.39749312400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40242409706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42830944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42954206466675</t>
+    <t xml:space="preserve">2.402423620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42830896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42954182624817</t>
   </si>
   <si>
     <t xml:space="preserve">2.4357054233551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45172929763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41351747512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43200731277466</t>
+    <t xml:space="preserve">2.45172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41351723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43200755119324</t>
   </si>
   <si>
     <t xml:space="preserve">2.48747587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48994135856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541063308716</t>
+    <t xml:space="preserve">2.48994159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761464118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541039466858</t>
   </si>
   <si>
     <t xml:space="preserve">2.5306191444397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4961051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44556617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105198860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41475033760071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39132976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41968107223511</t>
+    <t xml:space="preserve">2.49610495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44556665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41474986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3913300037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41968083381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.40981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44803142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41721510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42091345787048</t>
+    <t xml:space="preserve">2.44803094863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41721558570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4209132194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.44926428794861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41228461265564</t>
+    <t xml:space="preserve">2.41228532791138</t>
   </si>
   <si>
     <t xml:space="preserve">2.3728404045105</t>
@@ -521,205 +521,205 @@
     <t xml:space="preserve">2.35928153991699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32476663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051392555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33832621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31983661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36421155929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35435032844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43693780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858769416809</t>
+    <t xml:space="preserve">2.32476735115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051344871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3383264541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31983685493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36421203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35435080528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4369375705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858697891235</t>
   </si>
   <si>
     <t xml:space="preserve">2.4307746887207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41598296165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37037515640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36297917366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35311770439148</t>
+    <t xml:space="preserve">2.41598272323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37037491798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36297941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35311841964722</t>
   </si>
   <si>
     <t xml:space="preserve">2.36667728424072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.327232837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24711036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.243412733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22369027137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24957609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28285717964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22862100601196</t>
+    <t xml:space="preserve">2.38393378257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32723212242126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24711108207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24341297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22369050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957585334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2828574180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22862076759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.24834322929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31860375404358</t>
+    <t xml:space="preserve">2.31860423088074</t>
   </si>
   <si>
     <t xml:space="preserve">2.3075098991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29764890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30257940292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586096763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35065269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33339595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51952457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336169242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47884774208069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49980282783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53924751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56513285636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54910898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266784667969</t>
+    <t xml:space="preserve">2.29764938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30257964134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35065245628357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3333957195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51952481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336216926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47884750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49980306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53924679756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5651330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910826683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266713142395</t>
   </si>
   <si>
     <t xml:space="preserve">2.58115720748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60211253166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57252883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57622647285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55896949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047989845276</t>
+    <t xml:space="preserve">2.60211229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57252860069275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57622623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55896973609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048013687134</t>
   </si>
   <si>
     <t xml:space="preserve">2.54664349555969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56636548042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55403923988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650448799133</t>
+    <t xml:space="preserve">2.56636571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55403900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55650424957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.55157351493835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57299399375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56795454025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52763319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50873231887817</t>
+    <t xml:space="preserve">2.57299447059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56795430183411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52763295173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50873208045959</t>
   </si>
   <si>
     <t xml:space="preserve">2.47849178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4255702495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43439030647278</t>
+    <t xml:space="preserve">2.42557001113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43438982963562</t>
   </si>
   <si>
     <t xml:space="preserve">2.43565034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44825029373169</t>
+    <t xml:space="preserve">2.44825077056885</t>
   </si>
   <si>
     <t xml:space="preserve">2.46715116500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41927003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069027900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54401350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55031394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023337364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53267312049866</t>
+    <t xml:space="preserve">2.41926980018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5440137386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55031323432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023289680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5326726436615</t>
   </si>
   <si>
     <t xml:space="preserve">2.49361228942871</t>
@@ -737,28 +737,28 @@
     <t xml:space="preserve">2.5263729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50369238853455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52007293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283331871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57803416252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59945511817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60323548316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6082751750946</t>
+    <t xml:space="preserve">2.50369215011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5200731754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283403396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57803463935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59945487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60323524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60827469825745</t>
   </si>
   <si>
     <t xml:space="preserve">2.62717580795288</t>
@@ -767,31 +767,31 @@
     <t xml:space="preserve">2.63851618766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63347601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63473582267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961603164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67757749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65237665176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63977646827698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6586766242981</t>
+    <t xml:space="preserve">2.63347554206848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63473606109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67757678031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6523768901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6397762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65867686271667</t>
   </si>
   <si>
     <t xml:space="preserve">2.71033811569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70151805877686</t>
+    <t xml:space="preserve">2.70151829719543</t>
   </si>
   <si>
     <t xml:space="preserve">2.71537852287292</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">2.7342791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74183940887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75191903114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7808997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77963995933533</t>
+    <t xml:space="preserve">2.74183893203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75191974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78090023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77964019775391</t>
   </si>
   <si>
     <t xml:space="preserve">2.7746000289917</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">2.76199984550476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77208018302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309945106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75948023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75821971893311</t>
+    <t xml:space="preserve">2.7720799446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75947976112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75821948051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.72671890258789</t>
@@ -836,124 +836,124 @@
     <t xml:space="preserve">2.67253732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907807350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80484104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79097986221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77081990242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939966201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78720021247864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650205612183</t>
+    <t xml:space="preserve">2.70907831192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80484056472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79098033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77712035179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77081942558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939894676208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7872006893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350113868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650300979614</t>
   </si>
   <si>
     <t xml:space="preserve">2.88422298431396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87792348861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86658310890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87918329238892</t>
+    <t xml:space="preserve">2.87792277336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8665828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8791835308075</t>
   </si>
   <si>
     <t xml:space="preserve">2.87414288520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87666296958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94974517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91572403907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9220244884491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9799861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526689529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518679618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02912759780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96108508110046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97872614860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99762678146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01274704933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990561485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156758308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11354994773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08582925796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05180811882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05558800697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810904502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440877914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968996047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10724997520447</t>
+    <t xml:space="preserve">2.87666273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88044285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94974493980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92202496528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100474357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998642921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526737213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98628616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00518727302551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.029128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96108555793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97872638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99762654304504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148772239685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11354970932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08582901954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05180788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05558824539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810832977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968972206116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10724949836731</t>
   </si>
   <si>
     <t xml:space="preserve">3.08204936981201</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">3.10347008705139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1185896396637</t>
+    <t xml:space="preserve">3.11858987808228</t>
   </si>
   <si>
     <t xml:space="preserve">3.02408766746521</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">3.04928803443909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98754668235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95730566978455</t>
+    <t xml:space="preserve">2.98754644393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95730495452881</t>
   </si>
   <si>
     <t xml:space="preserve">2.99888706207275</t>
@@ -986,55 +986,55 @@
     <t xml:space="preserve">2.98880624771118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95478534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9736852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282691001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06944942474365</t>
+    <t xml:space="preserve">2.95478630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97368597984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02282786369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778721809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06944847106934</t>
   </si>
   <si>
     <t xml:space="preserve">3.1324508190155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13119006156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10094928741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489032745361</t>
+    <t xml:space="preserve">3.13118958473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12489008903503</t>
   </si>
   <si>
     <t xml:space="preserve">3.12867045402527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0933895111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906027793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.079270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1177773475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831448554993</t>
+    <t xml:space="preserve">3.09338927268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07927060127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.08953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09595608711243</t>
+    <t xml:space="preserve">3.09595584869385</t>
   </si>
   <si>
     <t xml:space="preserve">3.13703036308289</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">3.13189601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17040371894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19864130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735813140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1922242641449</t>
+    <t xml:space="preserve">3.17040324211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19864201545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735765457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532797813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19222354888916</t>
   </si>
   <si>
     <t xml:space="preserve">3.1601345539093</t>
@@ -1064,232 +1064,232 @@
     <t xml:space="preserve">3.22816371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25062537193298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383496284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2345814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19607424736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26025247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987862586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26346135139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29876017570496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950572967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28271484375</t>
+    <t xml:space="preserve">3.2506263256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23458123207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19607400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26025176048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26346206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29875922203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28271508216858</t>
   </si>
   <si>
     <t xml:space="preserve">3.3019688129425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33084917068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122230529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614632606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27629709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30517840385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28592371940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28913283348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27308797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24099922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18708968162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23778986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31480431556702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801295280457</t>
+    <t xml:space="preserve">3.3308482170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122206687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614656448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405733108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159543991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27629685401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30517721176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28592395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28913307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2730884552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099898338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18708944320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23779034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25704336166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31480383872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801223754883</t>
   </si>
   <si>
     <t xml:space="preserve">3.32763910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3083860874176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32442998886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.350102186203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39502668380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39181733131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4142804145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748929023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45599555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44316053390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44957828521729</t>
+    <t xml:space="preserve">3.30838656425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32443070411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35010170936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39502716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181756973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41428017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4559965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44316029548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44957780838013</t>
   </si>
   <si>
     <t xml:space="preserve">3.45920515060425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46241426467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4399516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42390727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38540005683899</t>
+    <t xml:space="preserve">3.4624137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42390704154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38539958000183</t>
   </si>
   <si>
     <t xml:space="preserve">3.3725643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37898230552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39823579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689354896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331082344055</t>
+    <t xml:space="preserve">3.37898182868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689283370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331058502197</t>
   </si>
   <si>
     <t xml:space="preserve">3.40786266326904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43674206733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883106231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51375699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092077255249</t>
+    <t xml:space="preserve">3.43674254417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883177757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.513756275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092101097107</t>
   </si>
   <si>
     <t xml:space="preserve">3.44636988639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51054739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54584574699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5618908405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114314079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166799545288</t>
+    <t xml:space="preserve">3.51054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5458459854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56189012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114409446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53621912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166751861572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50412964820862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36293816566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2923412322998</t>
+    <t xml:space="preserve">3.41107130050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36293768882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29234147071838</t>
   </si>
   <si>
     <t xml:space="preserve">3.42711639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40144419670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44611430168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4297513961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047813415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37738823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35382485389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31717109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34466147422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31586265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310067176819</t>
+    <t xml:space="preserve">3.40144443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4461145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42975068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047861099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37738871574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35382580757141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31717133522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34466195106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31586241722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25302672386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310091018677</t>
   </si>
   <si>
     <t xml:space="preserve">3.12146639823914</t>
@@ -1298,142 +1298,142 @@
     <t xml:space="preserve">3.19019222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09070372581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06844973564148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0461950302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12866592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13652062416077</t>
+    <t xml:space="preserve">3.09070348739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310418128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06844902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04619479179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.128666639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13652038574219</t>
   </si>
   <si>
     <t xml:space="preserve">3.18102836608887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12735652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212061882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630324363708</t>
+    <t xml:space="preserve">3.12735605239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212109565735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630300521851</t>
   </si>
   <si>
     <t xml:space="preserve">3.16466522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15877461433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16597461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801074981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688470840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07695865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09528541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12670207023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16793823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1653196811676</t>
+    <t xml:space="preserve">3.15877437591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16597414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801146507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11688446998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04815864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07695841789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09528493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12670302391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1679379940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16531991958618</t>
   </si>
   <si>
     <t xml:space="preserve">3.1633563041687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1875741481781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17448377609253</t>
+    <t xml:space="preserve">3.18757367134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17448329925537</t>
   </si>
   <si>
     <t xml:space="preserve">3.19673752784729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22684574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150114059448</t>
+    <t xml:space="preserve">3.22684550285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1915009021759</t>
   </si>
   <si>
     <t xml:space="preserve">3.13913869857788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17513799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259291648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25629997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24320888519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24844551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30539011955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277180671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3224081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324458122253</t>
+    <t xml:space="preserve">3.17513751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979268074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25630044937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24320936203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24844527244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30538964271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30277156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764339447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324362754822</t>
   </si>
   <si>
     <t xml:space="preserve">3.34597039222717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34727931022644</t>
+    <t xml:space="preserve">3.34727954864502</t>
   </si>
   <si>
     <t xml:space="preserve">3.40095162391663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39833402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38393378257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40487957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39309692382812</t>
+    <t xml:space="preserve">3.39833331108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38393354415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40487909317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39309787750244</t>
   </si>
   <si>
     <t xml:space="preserve">3.44284200668335</t>
@@ -1442,40 +1442,40 @@
     <t xml:space="preserve">3.43629693984985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44807839393616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49520468711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4821138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52531337738037</t>
+    <t xml:space="preserve">3.44807767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49520516395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48211312294006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52531313896179</t>
   </si>
   <si>
     <t xml:space="preserve">3.52662229537964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43891477584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3210985660553</t>
+    <t xml:space="preserve">3.43891453742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109832763672</t>
   </si>
   <si>
     <t xml:space="preserve">3.31848049163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34335231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36298894882202</t>
+    <t xml:space="preserve">3.3433530330658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3629891872406</t>
   </si>
   <si>
     <t xml:space="preserve">3.23797345161438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26153612136841</t>
+    <t xml:space="preserve">3.26153635978699</t>
   </si>
   <si>
     <t xml:space="preserve">3.20590090751648</t>
@@ -1487,85 +1487,85 @@
     <t xml:space="preserve">3.19542860984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19215631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037462234497</t>
+    <t xml:space="preserve">3.19215536117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037414550781</t>
   </si>
   <si>
     <t xml:space="preserve">3.10772109031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08415770530701</t>
+    <t xml:space="preserve">3.08415746688843</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888681411743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11033940315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07826662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855818748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1332483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564902305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386780738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692248344421</t>
+    <t xml:space="preserve">3.11033892631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07826733589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.098557472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13324809074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564854621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386733055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692296028137</t>
   </si>
   <si>
     <t xml:space="preserve">3.11557579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12932109832764</t>
+    <t xml:space="preserve">3.12932062149048</t>
   </si>
   <si>
     <t xml:space="preserve">3.18953776359558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18888378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401028633118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204714775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15746521949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0848126411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10641169548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06452202796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12342953681946</t>
+    <t xml:space="preserve">3.18888354301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401052474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1574649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10641241073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06452226638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808493614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12342929840088</t>
   </si>
   <si>
     <t xml:space="preserve">3.10313940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11361193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510277748108</t>
+    <t xml:space="preserve">3.11361145973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510301589966</t>
   </si>
   <si>
     <t xml:space="preserve">3.15550184249878</t>
@@ -1574,103 +1574,103 @@
     <t xml:space="preserve">3.14437460899353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710185050964</t>
+    <t xml:space="preserve">3.17710137367249</t>
   </si>
   <si>
     <t xml:space="preserve">3.1973922252655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186546325684</t>
+    <t xml:space="preserve">3.17644715309143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186522483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.1489565372467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18364691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1941192150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113729476929</t>
+    <t xml:space="preserve">3.18364667892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17252016067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411897659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113705635071</t>
   </si>
   <si>
     <t xml:space="preserve">3.17952394485474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15530872344971</t>
+    <t xml:space="preserve">3.15530848503113</t>
   </si>
   <si>
     <t xml:space="preserve">3.13647532463074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14656472206116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338014602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20844626426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08401036262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347350120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.044997215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08468270301819</t>
+    <t xml:space="preserve">3.14656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17212462425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338038444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20844674110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08400964736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347302436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432463645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04499769210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08468294143677</t>
   </si>
   <si>
     <t xml:space="preserve">3.0833375453949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06921243667603</t>
+    <t xml:space="preserve">3.06921195983887</t>
   </si>
   <si>
     <t xml:space="preserve">3.00598502159119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99051475524902</t>
+    <t xml:space="preserve">2.99051427841187</t>
   </si>
   <si>
     <t xml:space="preserve">3.01203894615173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98042511940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638964653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96629977226257</t>
+    <t xml:space="preserve">2.9804253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638916969299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96629953384399</t>
   </si>
   <si>
     <t xml:space="preserve">2.9979133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9851336479187</t>
+    <t xml:space="preserve">2.98513340950012</t>
   </si>
   <si>
     <t xml:space="preserve">2.95082926750183</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">2.95150208473206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94006681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89836382865906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540555953979</t>
+    <t xml:space="preserve">2.92997765541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94006729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89836454391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540508270264</t>
   </si>
   <si>
     <t xml:space="preserve">2.85397028923035</t>
@@ -1700,46 +1700,46 @@
     <t xml:space="preserve">2.88625717163086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94477581977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091818809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719470024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584978103638</t>
+    <t xml:space="preserve">2.88558411598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94477534294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584906578064</t>
   </si>
   <si>
     <t xml:space="preserve">3.03894400596619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06652164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05979585647583</t>
+    <t xml:space="preserve">3.06652188301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05979537963867</t>
   </si>
   <si>
     <t xml:space="preserve">3.03625345230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05912303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0739209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09342694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1014986038208</t>
+    <t xml:space="preserve">3.05912280082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1162965297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07392072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09342670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10149788856506</t>
   </si>
   <si>
     <t xml:space="preserve">3.08064675331116</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">2.94746613502502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562695503235</t>
+    <t xml:space="preserve">2.96562743186951</t>
   </si>
   <si>
     <t xml:space="preserve">3.04096150398254</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">2.94343018531799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92325139045715</t>
+    <t xml:space="preserve">2.92325162887573</t>
   </si>
   <si>
     <t xml:space="preserve">2.88423895835876</t>
@@ -1778,31 +1778,31 @@
     <t xml:space="preserve">2.99589562416077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96898984909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93468618392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9844605922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96697211265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612097740173</t>
+    <t xml:space="preserve">2.96899056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93468642234802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97975182533264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98446011543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96697235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612073898315</t>
   </si>
   <si>
     <t xml:space="preserve">2.95957326889038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94544816017151</t>
+    <t xml:space="preserve">2.91517996788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94544839859009</t>
   </si>
   <si>
     <t xml:space="preserve">2.96428179740906</t>
@@ -1811,70 +1811,70 @@
     <t xml:space="preserve">2.97168111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00665760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01540160179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280068397522</t>
+    <t xml:space="preserve">3.00665712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01540112495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02280116081238</t>
   </si>
   <si>
     <t xml:space="preserve">2.99455046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02683663368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06853938102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.133784532547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13243865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1647253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19835758209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20441031455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21517276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037531852722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22189927101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23804235458374</t>
+    <t xml:space="preserve">3.02683639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0685396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13378500938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13243985176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16472578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19835734367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20441102981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21517395973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037508010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22189950942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23804211616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.22728037834167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24880409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19297623634338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19364905357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961358070374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23333406448364</t>
+    <t xml:space="preserve">3.24880456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19364881515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2333345413208</t>
   </si>
   <si>
     <t xml:space="preserve">3.3167405128479</t>
@@ -1886,46 +1886,46 @@
     <t xml:space="preserve">3.37525939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37256860733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122321128845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655752182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48826146125793</t>
+    <t xml:space="preserve">3.37256836891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48826098442078</t>
   </si>
   <si>
     <t xml:space="preserve">3.39543795585632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39274716377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099785804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808266639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673655509949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153519630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47346305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53130960464478</t>
+    <t xml:space="preserve">3.39274740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965246200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099833488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46673703193665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47346329689026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53130912780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.49767732620239</t>
@@ -1934,82 +1934,82 @@
     <t xml:space="preserve">3.50440359115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51113033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50978446006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458357810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032179832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5827579498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.574467420578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683327674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690285682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56755828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62144541740417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61591744422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63802480697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57170343399048</t>
+    <t xml:space="preserve">3.51112985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50978517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458238601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032251358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446694374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57861185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58690166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56755876541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6214451789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6159188747406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63802552223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57170295715332</t>
   </si>
   <si>
     <t xml:space="preserve">3.58137536048889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54545164108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472615242004</t>
+    <t xml:space="preserve">3.54545068740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472567558289</t>
   </si>
   <si>
     <t xml:space="preserve">3.55097842216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59104704856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071921348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61729884147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282633781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61039066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61453628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6242082118988</t>
+    <t xml:space="preserve">3.59104776382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60348296165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729979515076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282681465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61039137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61453604698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62420797348022</t>
   </si>
   <si>
     <t xml:space="preserve">3.64631509780884</t>
@@ -2018,58 +2018,58 @@
     <t xml:space="preserve">3.66980457305908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6615138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533135414124</t>
+    <t xml:space="preserve">3.66151452064514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533087730408</t>
   </si>
   <si>
     <t xml:space="preserve">3.67118644714355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66427755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085789680481</t>
+    <t xml:space="preserve">3.66427779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085885047913</t>
   </si>
   <si>
     <t xml:space="preserve">3.72921776771545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80106639862061</t>
+    <t xml:space="preserve">3.80106616020203</t>
   </si>
   <si>
     <t xml:space="preserve">3.78863072395325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77205085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79830265045166</t>
+    <t xml:space="preserve">3.77205038070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79830288887024</t>
   </si>
   <si>
     <t xml:space="preserve">3.79001307487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79139471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895903587341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350159645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.830082654953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495281219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225935935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258647918701</t>
+    <t xml:space="preserve">3.79139423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350183486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495352745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225888252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258695602417</t>
   </si>
   <si>
     <t xml:space="preserve">3.93923711776733</t>
@@ -2078,145 +2078,145 @@
     <t xml:space="preserve">3.94752717018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92818403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90883946418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94338202476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93440055847168</t>
+    <t xml:space="preserve">3.92818260192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94061851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90884041786194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091108322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9433810710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93440103530884</t>
   </si>
   <si>
     <t xml:space="preserve">3.93370962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92127442359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91022038459778</t>
+    <t xml:space="preserve">3.92127466201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022109985352</t>
   </si>
   <si>
     <t xml:space="preserve">3.89847636222839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87567806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564303398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419253349304</t>
+    <t xml:space="preserve">3.87567925453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564351081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379559516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81419205665588</t>
   </si>
   <si>
     <t xml:space="preserve">3.81695628166199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81281042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80244851112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82593727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840678215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83629941940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182667732239</t>
+    <t xml:space="preserve">3.81281065940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80244755744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82593679428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840797424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83630037307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288000106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531615257263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182643890381</t>
   </si>
   <si>
     <t xml:space="preserve">3.87015175819397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85218954086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83491826057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452084541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85149788856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85080766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186075210571</t>
+    <t xml:space="preserve">3.8521888256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8349187374115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452013015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8514986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85080718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186194419861</t>
   </si>
   <si>
     <t xml:space="preserve">3.88880443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93094658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98068761825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92403793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99934077262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906316757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84804439544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407343864441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108598709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06980800628662</t>
+    <t xml:space="preserve">3.9309458732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98068785667419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99934101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8390634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84804463386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407296180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581650733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108503341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06980752944946</t>
   </si>
   <si>
     <t xml:space="preserve">4.02628374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06911659240723</t>
+    <t xml:space="preserve">4.04010105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06911706924438</t>
   </si>
   <si>
     <t xml:space="preserve">4.13889312744141</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">4.1934700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20037937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30884265899658</t>
+    <t xml:space="preserve">4.20037889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30884313583374</t>
   </si>
   <si>
     <t xml:space="preserve">4.26255464553833</t>
@@ -2237,28 +2237,28 @@
     <t xml:space="preserve">4.27637243270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30538845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3005518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20314168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24182891845703</t>
+    <t xml:space="preserve">4.3053879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30055141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2031421661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24182939529419</t>
   </si>
   <si>
     <t xml:space="preserve">4.23215818405151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32473182678223</t>
+    <t xml:space="preserve">4.32473230361938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42697763442993</t>
@@ -2270,43 +2270,43 @@
     <t xml:space="preserve">4.42145109176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4283595085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42766857147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43941259384155</t>
+    <t xml:space="preserve">4.42835998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42766904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43941402435303</t>
   </si>
   <si>
     <t xml:space="preserve">4.49744510650635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45668363571167</t>
+    <t xml:space="preserve">4.45668458938599</t>
   </si>
   <si>
     <t xml:space="preserve">4.48500967025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49951791763306</t>
+    <t xml:space="preserve">4.4995174407959</t>
   </si>
   <si>
     <t xml:space="preserve">4.5312967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34407615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43239831924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43310546875</t>
+    <t xml:space="preserve">4.34407520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43310594558716</t>
   </si>
   <si>
     <t xml:space="preserve">4.47267436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41402816772461</t>
+    <t xml:space="preserve">4.41402864456177</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
@@ -2315,94 +2315,94 @@
     <t xml:space="preserve">4.41332101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35891485214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38011121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40908193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940502166748</t>
+    <t xml:space="preserve">4.35891389846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3801121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40908145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940454483032</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33418369293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33842325210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26493835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28472328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29461526870728</t>
+    <t xml:space="preserve">4.33418416976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33842277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28472375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29461479187012</t>
   </si>
   <si>
     <t xml:space="preserve">4.2458610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44087696075439</t>
+    <t xml:space="preserve">4.44087743759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.49316549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4062557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46419525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44017124176025</t>
+    <t xml:space="preserve">4.40625524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44017171859741</t>
   </si>
   <si>
     <t xml:space="preserve">4.39706945419312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59208679199219</t>
+    <t xml:space="preserve">4.59208726882935</t>
   </si>
   <si>
     <t xml:space="preserve">4.59349966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6860613822937</t>
+    <t xml:space="preserve">4.68606185913086</t>
   </si>
   <si>
     <t xml:space="preserve">4.6592116355896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71997880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72068500518799</t>
+    <t xml:space="preserve">4.71997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72068548202515</t>
   </si>
   <si>
     <t xml:space="preserve">4.7609601020813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70937967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758321762085</t>
+    <t xml:space="preserve">4.70938014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758417129517</t>
   </si>
   <si>
     <t xml:space="preserve">4.62458992004395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58572769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55181121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263746261597</t>
+    <t xml:space="preserve">4.58572721481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55181169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263889312744</t>
   </si>
   <si>
     <t xml:space="preserve">4.65779876708984</t>
@@ -2411,49 +2411,49 @@
     <t xml:space="preserve">4.58007478713989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480499267578</t>
+    <t xml:space="preserve">4.60480451583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.69878101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67404937744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71361875534058</t>
+    <t xml:space="preserve">4.67405080795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64649391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71362018585205</t>
   </si>
   <si>
     <t xml:space="preserve">4.78215789794922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75530767440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82737874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7948751449585</t>
+    <t xml:space="preserve">4.75530815124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82737827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79487657546997</t>
   </si>
   <si>
     <t xml:space="preserve">4.84080410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81678104400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71220684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69100856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77226638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83656406402588</t>
+    <t xml:space="preserve">4.81678056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71220588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6910080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77226543426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83656454086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.78498363494873</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">4.81536722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78145122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78993034362793</t>
+    <t xml:space="preserve">4.78145027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78992986679077</t>
   </si>
   <si>
     <t xml:space="preserve">4.83161926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80830049514771</t>
+    <t xml:space="preserve">4.80830097198486</t>
   </si>
   <si>
     <t xml:space="preserve">4.78357076644897</t>
@@ -2483,85 +2483,85 @@
     <t xml:space="preserve">4.82455348968506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84221792221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86129522323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84998941421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85564279556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87754583358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90369033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89733076095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249206542969</t>
+    <t xml:space="preserve">4.7659068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84221696853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86129570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84998989105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8556432723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87754726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90368986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89733123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92347478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249254226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.87472009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77085256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85140323638916</t>
+    <t xml:space="preserve">4.77085208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85140371322632</t>
   </si>
   <si>
     <t xml:space="preserve">4.84716367721558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93407344818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662456512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8577618598938</t>
+    <t xml:space="preserve">4.93407297134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662408828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85776233673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.84857654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87401342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82596635818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7871036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76943922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83303260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85493659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84433698654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66698455810547</t>
+    <t xml:space="preserve">4.87401294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82596588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759477615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78710412979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83303213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85493564605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84433746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66698551177979</t>
   </si>
   <si>
     <t xml:space="preserve">4.71785879135132</t>
@@ -2570,37 +2570,37 @@
     <t xml:space="preserve">4.75036191940308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75601387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83727169036865</t>
+    <t xml:space="preserve">4.75601434707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83727121353149</t>
   </si>
   <si>
     <t xml:space="preserve">4.89309167861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9531512260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93336725234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94679260253906</t>
+    <t xml:space="preserve">4.95315074920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93336629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94679164886475</t>
   </si>
   <si>
     <t xml:space="preserve">5.09164094924927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06973743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04359292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99695920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09588050842285</t>
+    <t xml:space="preserve">5.06973886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04359340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99695873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09588098526001</t>
   </si>
   <si>
     <t xml:space="preserve">5.09517431259155</t>
@@ -2609,55 +2609,55 @@
     <t xml:space="preserve">5.10577297210693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10859966278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13686227798462</t>
+    <t xml:space="preserve">5.1085991859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13686323165894</t>
   </si>
   <si>
     <t xml:space="preserve">5.16159296035767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24073076248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22871828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2435564994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37780714035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45835828781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50453615188599</t>
+    <t xml:space="preserve">5.24072980880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22871923446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355745315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3778076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45835781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50453567504883</t>
   </si>
   <si>
     <t xml:space="preserve">5.49082660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44464874267578</t>
+    <t xml:space="preserve">5.44464921951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.49804210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64162635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69934892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77871704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83571767807007</t>
+    <t xml:space="preserve">5.64162588119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53700494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69934797286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77871656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83571720123291</t>
   </si>
   <si>
     <t xml:space="preserve">5.66760158538818</t>
@@ -2672,61 +2672,61 @@
     <t xml:space="preserve">5.82272911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602115631104</t>
+    <t xml:space="preserve">5.86602163314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.89993333816528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91652822494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91147756576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86746454238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92157936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97208595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05650424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18060731887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08464384078979</t>
+    <t xml:space="preserve">5.91652870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91147804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86746406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9215784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97208642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05650520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18060779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08464431762695</t>
   </si>
   <si>
     <t xml:space="preserve">6.09258127212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79386901855469</t>
+    <t xml:space="preserve">5.79386854171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.63152456283569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73975372314453</t>
+    <t xml:space="preserve">5.73975324630737</t>
   </si>
   <si>
     <t xml:space="preserve">5.71161460876465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46629571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51247215270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6228666305542</t>
+    <t xml:space="preserve">5.46629524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51247262954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62286615371704</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538879394531</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">5.69357633590698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1271767616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712244033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70436239242554</t>
+    <t xml:space="preserve">5.12717723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70436143875122</t>
   </si>
   <si>
     <t xml:space="preserve">3.7707040309906</t>
@@ -2753,94 +2753,94 @@
     <t xml:space="preserve">4.05426502227783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95830273628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12714004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2497992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20650720596313</t>
+    <t xml:space="preserve">3.95830202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1271390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24979877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20650768280029</t>
   </si>
   <si>
     <t xml:space="preserve">4.24907732009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30896425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55356216430664</t>
+    <t xml:space="preserve">4.30896472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55356168746948</t>
   </si>
   <si>
     <t xml:space="preserve">4.54562568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53047323226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44100475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60767698287964</t>
+    <t xml:space="preserve">4.53047370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44100427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">4.57376527786255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37823152542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378877639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37895250320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43018054962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59974002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53480195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65601921081543</t>
+    <t xml:space="preserve">4.37823104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37895202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59974050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53480339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65601873397827</t>
   </si>
   <si>
     <t xml:space="preserve">4.65169048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47852373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50882720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47996664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46770048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33277463912964</t>
+    <t xml:space="preserve">4.47852325439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50882768630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47996616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46770095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">4.31834411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2757740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25701475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37967395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43739652633667</t>
+    <t xml:space="preserve">4.27577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25701427459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37967491149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43739604949951</t>
   </si>
   <si>
     <t xml:space="preserve">4.52397966384888</t>
@@ -2852,52 +2852,52 @@
     <t xml:space="preserve">4.33421754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39266109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37750959396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46481513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47347354888916</t>
+    <t xml:space="preserve">4.39266061782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37750911712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46481370925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47347259521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.38688945770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35081243515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24547004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672159194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30319166183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35586404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5109920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56727170944214</t>
+    <t xml:space="preserve">4.35081338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24547052383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30319213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35586309432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51099157333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56727123260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.62499332427979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69714593887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198221206665</t>
+    <t xml:space="preserve">4.69714641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147514343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198268890381</t>
   </si>
   <si>
     <t xml:space="preserve">4.90061712265015</t>
@@ -2906,130 +2906,130 @@
     <t xml:space="preserve">4.97926378250122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0492525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1870641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41434574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40063571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46773767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46701669692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176340103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28663492202759</t>
+    <t xml:space="preserve">5.04925107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18706369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41434526443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40063524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46773815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46701622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28663444519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.29962205886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31188726425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361110687256</t>
+    <t xml:space="preserve">5.31188821792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45907926559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41506671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361158370972</t>
   </si>
   <si>
     <t xml:space="preserve">5.63585376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50092840194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5290675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51175117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57308053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53989124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55720710754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73398113250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68131065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71017169952393</t>
+    <t xml:space="preserve">5.50092887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5117506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57308101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55720806121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73398208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68131017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71017122268677</t>
   </si>
   <si>
     <t xml:space="preserve">5.75418472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83427429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78232479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89416027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95476913452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08031368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12669515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13258647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03246259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98828887939453</t>
+    <t xml:space="preserve">5.83427476882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86024856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78232431411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89416122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9547700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08031511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12669563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13258600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03246212005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98828983306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.84841060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83147811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81601858139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87123346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69601583480835</t>
+    <t xml:space="preserve">5.83147764205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8712329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69601631164551</t>
   </si>
   <si>
     <t xml:space="preserve">5.69012689590454</t>
@@ -3038,31 +3038,31 @@
     <t xml:space="preserve">5.78362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7931957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76669120788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69086265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75343990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79025077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97062063217163</t>
+    <t xml:space="preserve">5.79319524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7666916847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69086313247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75344085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79025030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97062015533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.89552783966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80497407913208</t>
+    <t xml:space="preserve">5.8049750328064</t>
   </si>
   <si>
     <t xml:space="preserve">5.74828624725342</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">5.70926809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69159841537476</t>
+    <t xml:space="preserve">5.69159936904907</t>
   </si>
   <si>
     <t xml:space="preserve">5.79098701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74534177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460422515869</t>
+    <t xml:space="preserve">5.7453408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460470199585</t>
   </si>
   <si>
     <t xml:space="preserve">5.58705806732178</t>
@@ -3098,52 +3098,52 @@
     <t xml:space="preserve">5.52448034286499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45675039291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59000301361084</t>
+    <t xml:space="preserve">5.6304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45674991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000205993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.50165843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63270330429077</t>
+    <t xml:space="preserve">5.63270282745361</t>
   </si>
   <si>
     <t xml:space="preserve">5.5981011390686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.639328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5664439201355</t>
+    <t xml:space="preserve">5.63932847976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56644487380981</t>
   </si>
   <si>
     <t xml:space="preserve">5.61650562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57675075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263980865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3441104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208736419678</t>
+    <t xml:space="preserve">5.5767502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319129943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34411001205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38975429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208688735962</t>
   </si>
   <si>
     <t xml:space="preserve">5.42582893371582</t>
@@ -3152,31 +3152,31 @@
     <t xml:space="preserve">5.40006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48325300216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52153587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46116733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49797630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4434986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42141246795654</t>
+    <t xml:space="preserve">5.48325347900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52153635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46116781234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4979772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44349813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42141199111938</t>
   </si>
   <si>
     <t xml:space="preserve">5.59221124649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55613708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5392050743103</t>
+    <t xml:space="preserve">5.5561375617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53920459747314</t>
   </si>
   <si>
     <t xml:space="preserve">5.6592059135437</t>
@@ -3185,31 +3185,31 @@
     <t xml:space="preserve">5.67761135101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49429607391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54141283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58190393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53257846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472452163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57233381271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44423389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11662292480469</t>
+    <t xml:space="preserve">5.49429559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5414137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49871397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58190441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472547531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57233333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4442343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11662340164185</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705184936523</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">5.03122329711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31318998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42435646057129</t>
+    <t xml:space="preserve">5.14312696456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31318950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42435693740845</t>
   </si>
   <si>
     <t xml:space="preserve">5.60325479507446</t>
@@ -3236,46 +3236,46 @@
     <t xml:space="preserve">5.92423963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04571390151978</t>
+    <t xml:space="preserve">6.04571437835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.94853401184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90436267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95515918731689</t>
+    <t xml:space="preserve">5.90436315536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95516014099121</t>
   </si>
   <si>
     <t xml:space="preserve">5.97209310531616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97945547103882</t>
+    <t xml:space="preserve">5.9794545173645</t>
   </si>
   <si>
     <t xml:space="preserve">6.01037549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737243652344</t>
+    <t xml:space="preserve">6.0611743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19737195968628</t>
   </si>
   <si>
     <t xml:space="preserve">6.24817037582397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23565483093262</t>
+    <t xml:space="preserve">6.23565530776978</t>
   </si>
   <si>
     <t xml:space="preserve">6.25921249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16203355789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522315979004</t>
+    <t xml:space="preserve">6.162034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522411346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.09724760055542</t>
@@ -3287,70 +3287,70 @@
     <t xml:space="preserve">6.04129695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02289152145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00743103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97798347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04424142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9257116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92276763916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00890302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01700210571289</t>
+    <t xml:space="preserve">6.0228910446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00743055343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97798252105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92571210861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.922767162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00890350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01700162887573</t>
   </si>
   <si>
     <t xml:space="preserve">5.94190883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08914995193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14362812042236</t>
+    <t xml:space="preserve">6.0891489982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14362859725952</t>
   </si>
   <si>
     <t xml:space="preserve">6.09283065795898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18043899536133</t>
+    <t xml:space="preserve">6.22608327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18043947219849</t>
   </si>
   <si>
     <t xml:space="preserve">6.57357215881348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46166944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019876480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48081111907959</t>
+    <t xml:space="preserve">6.46167039871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58756017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48081064224243</t>
   </si>
   <si>
     <t xml:space="preserve">6.57062816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50289678573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52203750610352</t>
+    <t xml:space="preserve">6.50289630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52203798294067</t>
   </si>
   <si>
     <t xml:space="preserve">6.44768571853638</t>
@@ -3359,46 +3359,46 @@
     <t xml:space="preserve">6.43942356109619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44242715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26743602752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25992488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30874300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18932723999023</t>
+    <t xml:space="preserve">6.44242811203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3530535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26743507385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3087420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18932771682739</t>
   </si>
   <si>
     <t xml:space="preserve">6.30949306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15177440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17430543899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15853404998779</t>
+    <t xml:space="preserve">6.15177536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17430591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15853452682495</t>
   </si>
   <si>
     <t xml:space="preserve">6.42290115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42590475082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34404134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38384580612183</t>
+    <t xml:space="preserve">6.42590427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3440408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38384675979614</t>
   </si>
   <si>
     <t xml:space="preserve">6.22162246704102</t>
@@ -3407,97 +3407,97 @@
     <t xml:space="preserve">6.24715709686279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35530662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35981416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23589181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15552997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0661563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105262756348</t>
+    <t xml:space="preserve">6.35530614852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35981273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2358922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15553092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06615591049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105215072632</t>
   </si>
   <si>
     <t xml:space="preserve">5.94824314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88816022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89116382598877</t>
+    <t xml:space="preserve">5.88815927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89116334915161</t>
   </si>
   <si>
     <t xml:space="preserve">5.96852111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85962057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72743701934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8904128074646</t>
+    <t xml:space="preserve">5.85962009429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7274374961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89041328430176</t>
   </si>
   <si>
     <t xml:space="preserve">5.91294431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07141304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1697998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25316524505615</t>
+    <t xml:space="preserve">6.07141351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16979932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25316572189331</t>
   </si>
   <si>
     <t xml:space="preserve">6.19984197616577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14426469802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18707418441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12999439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05639219284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23814487457275</t>
+    <t xml:space="preserve">6.14426422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18707466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12999486923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05639266967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2381443977356</t>
   </si>
   <si>
     <t xml:space="preserve">6.25166320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32826948165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34028577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32902050018311</t>
+    <t xml:space="preserve">6.32826900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32902002334595</t>
   </si>
   <si>
     <t xml:space="preserve">6.38910341262817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33352756500244</t>
+    <t xml:space="preserve">6.33352613449097</t>
   </si>
   <si>
     <t xml:space="preserve">6.37858915328979</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">6.44843626022339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49725294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45444488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44392967224121</t>
+    <t xml:space="preserve">6.49725389480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44393014907837</t>
   </si>
   <si>
     <t xml:space="preserve">6.47472286224365</t>
@@ -3530,46 +3530,46 @@
     <t xml:space="preserve">6.44468212127686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50326299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50551509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42515420913696</t>
+    <t xml:space="preserve">6.50326156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50551462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4251537322998</t>
   </si>
   <si>
     <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54757356643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5603404045105</t>
+    <t xml:space="preserve">6.54757452011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034231185913</t>
   </si>
   <si>
     <t xml:space="preserve">6.48899269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34479284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26217794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20885372161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27569675445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16304016113281</t>
+    <t xml:space="preserve">6.34479188919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26217842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20885515213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27569627761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16304111480713</t>
   </si>
   <si>
     <t xml:space="preserve">6.22537660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20960521697998</t>
+    <t xml:space="preserve">6.20960426330566</t>
   </si>
   <si>
     <t xml:space="preserve">6.214111328125</t>
@@ -3581,22 +3581,22 @@
     <t xml:space="preserve">6.07742166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16153860092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12623977661133</t>
+    <t xml:space="preserve">6.16153907775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">6.10445976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98279047012329</t>
+    <t xml:space="preserve">5.98279094696045</t>
   </si>
   <si>
     <t xml:space="preserve">6.06390333175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14952182769775</t>
+    <t xml:space="preserve">6.1495213508606</t>
   </si>
   <si>
     <t xml:space="preserve">6.12774229049683</t>
@@ -3617,64 +3617,64 @@
     <t xml:space="preserve">5.994056224823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92721366882324</t>
+    <t xml:space="preserve">5.92721271514893</t>
   </si>
   <si>
     <t xml:space="preserve">5.95650482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01057910919189</t>
+    <t xml:space="preserve">6.01057958602905</t>
   </si>
   <si>
     <t xml:space="preserve">6.01733922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01808881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97903537750244</t>
+    <t xml:space="preserve">6.01808929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">6.02484893798828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08493185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06840944290161</t>
+    <t xml:space="preserve">6.08493280410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06840896606445</t>
   </si>
   <si>
     <t xml:space="preserve">6.16829776763916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06765842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04888296127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09845066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08943891525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98654556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03386163711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01508569717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98879861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03686618804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88215065002441</t>
+    <t xml:space="preserve">6.0676589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04888200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09845113754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08943843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98654651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03386116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01508617401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98879909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03686571121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88215160369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.89491939544678</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">5.93772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401453018188</t>
+    <t xml:space="preserve">5.96401500701904</t>
   </si>
   <si>
     <t xml:space="preserve">5.92045450210571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.951247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05489110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05188703536987</t>
+    <t xml:space="preserve">5.95124673843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05489158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05188655853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.02635145187378</t>
@@ -3707,49 +3707,49 @@
     <t xml:space="preserve">5.95725584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0158371925354</t>
+    <t xml:space="preserve">6.01583671569824</t>
   </si>
   <si>
     <t xml:space="preserve">5.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8513560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00277042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1157546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18723487854004</t>
+    <t xml:space="preserve">5.85135555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.002769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11575412750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1872353553772</t>
   </si>
   <si>
     <t xml:space="preserve">6.21106147766113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11959648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19107866287231</t>
+    <t xml:space="preserve">6.11959743499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.191077709198</t>
   </si>
   <si>
     <t xml:space="preserve">6.16033363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97971296310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94820022583008</t>
+    <t xml:space="preserve">5.97971248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.91361284255981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92053031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95819091796875</t>
+    <t xml:space="preserve">5.92053079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95819139480591</t>
   </si>
   <si>
     <t xml:space="preserve">5.96357154846191</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">5.98586130142212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02044916152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02890348434448</t>
+    <t xml:space="preserve">6.02044820785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02890253067017</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348991394043</t>
@@ -3773,52 +3773,52 @@
     <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97740602493286</t>
+    <t xml:space="preserve">5.97740697860718</t>
   </si>
   <si>
     <t xml:space="preserve">6.03735733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08885431289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01967906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96510887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90131521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90208339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95511674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93129062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99815893173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.935133934021</t>
+    <t xml:space="preserve">6.08885335922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14957332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0196795463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96510982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9013147354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90208387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95511722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93129110336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99815797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93513345718384</t>
   </si>
   <si>
     <t xml:space="preserve">5.92975378036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83367919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77833890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78756189346313</t>
+    <t xml:space="preserve">5.83367872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78756332397461</t>
   </si>
   <si>
     <t xml:space="preserve">5.66842937469482</t>
@@ -3827,22 +3827,22 @@
     <t xml:space="preserve">5.7637357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71454572677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39941835403442</t>
+    <t xml:space="preserve">5.71454524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39941883087158</t>
   </si>
   <si>
     <t xml:space="preserve">5.38097286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34869194030762</t>
+    <t xml:space="preserve">5.34869146347046</t>
   </si>
   <si>
     <t xml:space="preserve">5.25722789764404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30257511138916</t>
+    <t xml:space="preserve">5.30257558822632</t>
   </si>
   <si>
     <t xml:space="preserve">5.33408784866333</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">5.39403867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33946752548218</t>
+    <t xml:space="preserve">5.33946895599365</t>
   </si>
   <si>
     <t xml:space="preserve">5.25492238998413</t>
@@ -3866,22 +3866,22 @@
     <t xml:space="preserve">5.11196231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17191314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17883110046387</t>
+    <t xml:space="preserve">5.17191362380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17883062362671</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3056492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31794738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18651676177979</t>
+    <t xml:space="preserve">5.30565023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31794786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1865177154541</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958353042603</t>
@@ -3893,52 +3893,52 @@
     <t xml:space="preserve">5.30795574188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4424614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54160976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51317167282104</t>
+    <t xml:space="preserve">5.44246053695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54161024093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51317119598389</t>
   </si>
   <si>
     <t xml:space="preserve">5.47781658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42708921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54622173309326</t>
+    <t xml:space="preserve">5.42708873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5462212562561</t>
   </si>
   <si>
     <t xml:space="preserve">5.58772611618042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5615930557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925508499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5577507019043</t>
+    <t xml:space="preserve">5.56159400939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55775022506714</t>
   </si>
   <si>
     <t xml:space="preserve">5.57696580886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57389116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60617256164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53008079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45245265960693</t>
+    <t xml:space="preserve">5.57389163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60617303848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5300817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45245218276978</t>
   </si>
   <si>
     <t xml:space="preserve">5.50318002700806</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">5.49549436569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44707202911377</t>
+    <t xml:space="preserve">5.44707250595093</t>
   </si>
   <si>
     <t xml:space="preserve">5.4324688911438</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">5.34177398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34331130981445</t>
+    <t xml:space="preserve">5.34331178665161</t>
   </si>
   <si>
     <t xml:space="preserve">5.30872392654419</t>
@@ -3971,16 +3971,16 @@
     <t xml:space="preserve">5.41479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49472522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2387809753418</t>
+    <t xml:space="preserve">5.49472618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23878145217896</t>
   </si>
   <si>
     <t xml:space="preserve">5.21802949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15500402450562</t>
+    <t xml:space="preserve">5.15500450134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.19189691543579</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">5.06507730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01588773727417</t>
+    <t xml:space="preserve">5.01588726043701</t>
   </si>
   <si>
     <t xml:space="preserve">5.16730165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039253234863</t>
+    <t xml:space="preserve">5.23493814468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039348602295</t>
   </si>
   <si>
     <t xml:space="preserve">5.1511607170105</t>
@@ -4010,34 +4010,34 @@
     <t xml:space="preserve">5.07583808898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0927472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14731788635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10965585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18497848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11349964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25338506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28489828109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31564140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32486486434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40787315368652</t>
+    <t xml:space="preserve">5.09274768829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1473183631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18497896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1134991645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25338459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2848973274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31564235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32486438751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40787363052368</t>
   </si>
   <si>
     <t xml:space="preserve">5.38789033889771</t>
@@ -4046,25 +4046,25 @@
     <t xml:space="preserve">5.4155592918396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51240348815918</t>
+    <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
     <t xml:space="preserve">5.47243547439575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34100532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31026124954224</t>
+    <t xml:space="preserve">5.34100484848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31026077270508</t>
   </si>
   <si>
     <t xml:space="preserve">5.32640171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32717084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32025337219238</t>
+    <t xml:space="preserve">5.32717132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32025241851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.35022830963135</t>
@@ -4076,43 +4076,43 @@
     <t xml:space="preserve">5.27490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38250970840454</t>
+    <t xml:space="preserve">5.38250923156738</t>
   </si>
   <si>
     <t xml:space="preserve">5.3071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26766967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26845979690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41546440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33642959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35935020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41704607009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41309356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35776948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24712038040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08272838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00369358062744</t>
+    <t xml:space="preserve">5.26766920089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41546535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33643007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35934972763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41309309005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35776901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24712085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08272790908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
     <t xml:space="preserve">5.11908435821533</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">5.08351898193359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05348491668701</t>
+    <t xml:space="preserve">5.05348587036133</t>
   </si>
   <si>
     <t xml:space="preserve">4.99499988555908</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">5.08114767074585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14516639709473</t>
+    <t xml:space="preserve">5.14516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">5.12303590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08588886260986</t>
+    <t xml:space="preserve">5.08588981628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.97603130340576</t>
@@ -4148,43 +4148,43 @@
     <t xml:space="preserve">4.99025774002075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89383459091187</t>
+    <t xml:space="preserve">4.89383506774902</t>
   </si>
   <si>
     <t xml:space="preserve">5.17598915100098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21550607681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87960863113403</t>
+    <t xml:space="preserve">5.21550703048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87960815429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.87644720077515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7065224647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48127365112305</t>
+    <t xml:space="preserve">4.70652198791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48127412796021</t>
   </si>
   <si>
     <t xml:space="preserve">4.39512538909912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52237176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77291202545166</t>
+    <t xml:space="preserve">4.52237129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7729115486145</t>
   </si>
   <si>
     <t xml:space="preserve">4.53580713272095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52711391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59903526306152</t>
+    <t xml:space="preserve">4.52711343765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59903478622437</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456800460815</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">4.60298681259155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52079105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55240488052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60219669342041</t>
+    <t xml:space="preserve">4.52079057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55240535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60219717025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.51209688186646</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">4.56030797958374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64566564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80294513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81875133514404</t>
+    <t xml:space="preserve">4.64566516876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80294561386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">4.79583168029785</t>
@@ -4226,46 +4226,46 @@
     <t xml:space="preserve">4.82902669906616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92544889450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90648126602173</t>
+    <t xml:space="preserve">4.92544794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90648078918457</t>
   </si>
   <si>
     <t xml:space="preserve">4.87486696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98709583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.968918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93809461593628</t>
+    <t xml:space="preserve">4.98709630966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96891784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.89857721328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90173864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88514184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87249517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7523627281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81559085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79978322982788</t>
+    <t xml:space="preserve">4.90173816680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88514137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87249565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75236320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82349443435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79978370666504</t>
   </si>
   <si>
     <t xml:space="preserve">4.91596460342407</t>
@@ -4274,34 +4274,34 @@
     <t xml:space="preserve">4.91438388824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87881898880005</t>
+    <t xml:space="preserve">4.87881755828857</t>
   </si>
   <si>
     <t xml:space="preserve">4.93888473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89541482925415</t>
+    <t xml:space="preserve">4.89541530609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.78555727005005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74841070175171</t>
+    <t xml:space="preserve">4.74841117858887</t>
   </si>
   <si>
     <t xml:space="preserve">4.64171361923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61721277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7262806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61405229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69229650497437</t>
+    <t xml:space="preserve">4.61721324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72628116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6140513420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69229602813721</t>
   </si>
   <si>
     <t xml:space="preserve">4.73181343078613</t>
@@ -4310,22 +4310,22 @@
     <t xml:space="preserve">4.74999189376831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69308614730835</t>
+    <t xml:space="preserve">4.69308710098267</t>
   </si>
   <si>
     <t xml:space="preserve">4.69150543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83930110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84720468521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84641408920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88751220703125</t>
+    <t xml:space="preserve">4.83930158615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84720420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84641456604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88751268386841</t>
   </si>
   <si>
     <t xml:space="preserve">4.88909292221069</t>
@@ -4337,52 +4337,52 @@
     <t xml:space="preserve">4.77686357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68202114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7057318687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66700506210327</t>
+    <t xml:space="preserve">4.6820216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70573282241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66700553894043</t>
   </si>
   <si>
     <t xml:space="preserve">4.76500797271729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73260450363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62037515640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52790451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33189821243286</t>
+    <t xml:space="preserve">4.73260354995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62037467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52790355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33189725875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.25839471817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21492624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39117431640625</t>
+    <t xml:space="preserve">4.21492576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39117336273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.26787948608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30107402801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33822059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31925249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22915267944336</t>
+    <t xml:space="preserve">4.30107355117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33822011947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31925201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22915172576904</t>
   </si>
   <si>
     <t xml:space="preserve">4.2852668762207</t>
@@ -4391,34 +4391,34 @@
     <t xml:space="preserve">4.35718870162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2749924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32794570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26946020126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12561655044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01259708404541</t>
+    <t xml:space="preserve">4.27499198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32794523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1256160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19911956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17382764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01259756088257</t>
   </si>
   <si>
     <t xml:space="preserve">4.09084129333496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15960121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15090799331665</t>
+    <t xml:space="preserve">4.15960216522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15090751647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.14300441741943</t>
@@ -4427,19 +4427,19 @@
     <t xml:space="preserve">4.0924220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05211400985718</t>
+    <t xml:space="preserve">4.05211448669434</t>
   </si>
   <si>
     <t xml:space="preserve">3.82133293151855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.951740026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03307485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606672286987</t>
+    <t xml:space="preserve">3.95173978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0330753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606624603271</t>
   </si>
   <si>
     <t xml:space="preserve">3.95831227302551</t>
@@ -4448,10 +4448,10 @@
     <t xml:space="preserve">3.90080332756042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88108468055725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90244579315186</t>
+    <t xml:space="preserve">3.88108515739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90244555473328</t>
   </si>
   <si>
     <t xml:space="preserve">3.89053320884705</t>
@@ -4463,16 +4463,16 @@
     <t xml:space="preserve">3.93818426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06922483444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99610495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00514221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0363621711731</t>
+    <t xml:space="preserve">4.06922435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9961051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0051417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03636169433594</t>
   </si>
   <si>
     <t xml:space="preserve">4.06758117675781</t>
@@ -4481,22 +4481,22 @@
     <t xml:space="preserve">4.13412809371948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11441135406494</t>
+    <t xml:space="preserve">4.11441040039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10783720016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13659334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19163799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18753051757812</t>
+    <t xml:space="preserve">4.10783767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13659286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19163751602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18753004074097</t>
   </si>
   <si>
     <t xml:space="preserve">4.18342256546021</t>
@@ -4505,16 +4505,16 @@
     <t xml:space="preserve">4.11030244827271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05443572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05854463577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06265211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06347322463989</t>
+    <t xml:space="preserve">4.05443620681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05854368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06265163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06347417831421</t>
   </si>
   <si>
     <t xml:space="preserve">3.97022533416748</t>
@@ -4526,19 +4526,19 @@
     <t xml:space="preserve">3.95461511611938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85767030715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81412768363953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90614295005798</t>
+    <t xml:space="preserve">3.857670545578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81412744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90614318847656</t>
   </si>
   <si>
     <t xml:space="preserve">3.86136746406555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84288215637207</t>
+    <t xml:space="preserve">3.84288167953491</t>
   </si>
   <si>
     <t xml:space="preserve">3.90162467956543</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">3.94845390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98871040344238</t>
+    <t xml:space="preserve">3.98871064186096</t>
   </si>
   <si>
     <t xml:space="preserve">4.10085439682007</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">4.02321672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04170179367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073881149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97679758071899</t>
+    <t xml:space="preserve">4.0417013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97679781913757</t>
   </si>
   <si>
     <t xml:space="preserve">3.98419213294983</t>
@@ -4577,28 +4577,28 @@
     <t xml:space="preserve">3.97186803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81535959243774</t>
+    <t xml:space="preserve">3.81535983085632</t>
   </si>
   <si>
     <t xml:space="preserve">3.73607873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54835057258606</t>
+    <t xml:space="preserve">3.53438401222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54835033416748</t>
   </si>
   <si>
     <t xml:space="preserve">3.49001932144165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47030138969421</t>
+    <t xml:space="preserve">3.47030115127563</t>
   </si>
   <si>
     <t xml:space="preserve">3.57957005500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.667067527771</t>
+    <t xml:space="preserve">3.66706728935242</t>
   </si>
   <si>
     <t xml:space="preserve">3.55040407180786</t>
@@ -4622,34 +4622,34 @@
     <t xml:space="preserve">3.34542322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37910771369934</t>
+    <t xml:space="preserve">3.37910747528076</t>
   </si>
   <si>
     <t xml:space="preserve">3.46290731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49823474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51918458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48426795005798</t>
+    <t xml:space="preserve">3.49823451042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51918482780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48426818847656</t>
   </si>
   <si>
     <t xml:space="preserve">3.44606518745422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52740073204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59764432907104</t>
+    <t xml:space="preserve">3.52740025520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59764456748962</t>
   </si>
   <si>
     <t xml:space="preserve">3.60257387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71512866020203</t>
+    <t xml:space="preserve">3.71512842178345</t>
   </si>
   <si>
     <t xml:space="preserve">3.67405080795288</t>
@@ -4661,49 +4661,49 @@
     <t xml:space="preserve">3.72950649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77304935455322</t>
+    <t xml:space="preserve">3.77304911613464</t>
   </si>
   <si>
     <t xml:space="preserve">3.7578501701355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84452557563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89217615127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9591338634491</t>
+    <t xml:space="preserve">3.84452533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89217638969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037939071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95913362503052</t>
   </si>
   <si>
     <t xml:space="preserve">4.11605405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14727306365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19821071624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22203588485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23682498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17767095565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15959692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2335376739502</t>
+    <t xml:space="preserve">4.14727258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274188995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1982102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22203636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23682451248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17767143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15959739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23353815078735</t>
   </si>
   <si>
     <t xml:space="preserve">4.23518133163452</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19492387771606</t>
+    <t xml:space="preserve">4.19492435455322</t>
   </si>
   <si>
     <t xml:space="preserve">4.21792793273926</t>
@@ -4724,19 +4724,19 @@
     <t xml:space="preserve">4.32719659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33623361587524</t>
+    <t xml:space="preserve">4.33623313903809</t>
   </si>
   <si>
     <t xml:space="preserve">4.27708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29186916351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2507905960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29022645950317</t>
+    <t xml:space="preserve">4.29186868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25079107284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29022598266602</t>
   </si>
   <si>
     <t xml:space="preserve">4.2705078125</t>
@@ -4745,28 +4745,28 @@
     <t xml:space="preserve">4.31158685684204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31487274169922</t>
+    <t xml:space="preserve">4.31487226486206</t>
   </si>
   <si>
     <t xml:space="preserve">4.1530237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14891719818115</t>
+    <t xml:space="preserve">4.14891672134399</t>
   </si>
   <si>
     <t xml:space="preserve">4.14563035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14645099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21464204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16863346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19081592559814</t>
+    <t xml:space="preserve">4.14645147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21464157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16863393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1908164024353</t>
   </si>
   <si>
     <t xml:space="preserve">4.17192077636719</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">4.62542581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68868637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70593929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7716646194458</t>
+    <t xml:space="preserve">4.68868589401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70593881607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77166414260864</t>
   </si>
   <si>
     <t xml:space="preserve">4.73222970962524</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">4.73551559448242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64760780334473</t>
+    <t xml:space="preserve">4.64760875701904</t>
   </si>
   <si>
     <t xml:space="preserve">4.6418571472168</t>
@@ -4829,40 +4829,40 @@
     <t xml:space="preserve">4.6810359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66570472717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66996335983276</t>
+    <t xml:space="preserve">4.66570520401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66996288299561</t>
   </si>
   <si>
     <t xml:space="preserve">4.67166709899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6273775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5916051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58394002914429</t>
+    <t xml:space="preserve">4.62737798690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59160566329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58393955230713</t>
   </si>
   <si>
     <t xml:space="preserve">4.56690549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58138561248779</t>
+    <t xml:space="preserve">4.58138513565063</t>
   </si>
   <si>
     <t xml:space="preserve">4.56435060501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55327844619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54816865921021</t>
+    <t xml:space="preserve">4.55327892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54816818237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.60863971710205</t>
@@ -4874,25 +4874,25 @@
     <t xml:space="preserve">4.58223676681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5881986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57712650299072</t>
+    <t xml:space="preserve">4.58819913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57712697982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.55924034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55668497085571</t>
+    <t xml:space="preserve">4.55668544769287</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687549591064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48003101348877</t>
+    <t xml:space="preserve">4.46214437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48003149032593</t>
   </si>
   <si>
     <t xml:space="preserve">4.45788621902466</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">4.51920938491821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52857875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42892742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48428916931152</t>
+    <t xml:space="preserve">4.52857828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42892789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48428964614868</t>
   </si>
   <si>
     <t xml:space="preserve">4.5149507522583</t>
@@ -4922,22 +4922,22 @@
     <t xml:space="preserve">4.53113412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53028202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53624439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4519248008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5686092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46810626983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51069259643555</t>
+    <t xml:space="preserve">4.53028154373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53624391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45192384719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56860971450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46810674667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51069211959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.50302743911743</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">4.65378141403198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69125652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77813148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79261112213135</t>
+    <t xml:space="preserve">4.69125604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77813196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79261064529419</t>
   </si>
   <si>
     <t xml:space="preserve">4.77131843566895</t>
@@ -4979,10 +4979,10 @@
     <t xml:space="preserve">4.82242107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98169183731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02853631973267</t>
+    <t xml:space="preserve">4.98169231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02853584289551</t>
   </si>
   <si>
     <t xml:space="preserve">5.10348749160767</t>
@@ -5003,43 +5003,43 @@
     <t xml:space="preserve">4.94762325286865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97402715682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05153274536133</t>
+    <t xml:space="preserve">4.97402667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05153322219849</t>
   </si>
   <si>
     <t xml:space="preserve">5.13414859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15799760818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25083446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27979326248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19376993179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19462108612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18440008163452</t>
+    <t xml:space="preserve">5.15799713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2508339881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27979278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19376945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19462156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18440055847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.2482795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2116551399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2056941986084</t>
+    <t xml:space="preserve">5.21165561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20569324493408</t>
   </si>
   <si>
     <t xml:space="preserve">5.1895112991333</t>
@@ -5048,10 +5048,10 @@
     <t xml:space="preserve">5.14777660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15970087051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12563180923462</t>
+    <t xml:space="preserve">5.15970134735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12563228607178</t>
   </si>
   <si>
     <t xml:space="preserve">5.12733554840088</t>
@@ -5063,28 +5063,28 @@
     <t xml:space="preserve">5.02598142623901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11796617507935</t>
+    <t xml:space="preserve">5.1179666519165</t>
   </si>
   <si>
     <t xml:space="preserve">5.14351797103882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13670444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080491065979</t>
+    <t xml:space="preserve">5.1367039680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08049154281616</t>
   </si>
   <si>
     <t xml:space="preserve">5.00809526443481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07112169265747</t>
+    <t xml:space="preserve">5.07112216949463</t>
   </si>
   <si>
     <t xml:space="preserve">5.07367706298828</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12052202224731</t>
+    <t xml:space="preserve">5.12052249908447</t>
   </si>
   <si>
     <t xml:space="preserve">4.98935747146606</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">5.07452917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14947986602783</t>
+    <t xml:space="preserve">5.14948034286499</t>
   </si>
   <si>
     <t xml:space="preserve">5.10774612426758</t>
@@ -5108,31 +5108,31 @@
     <t xml:space="preserve">5.17247676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20484161376953</t>
+    <t xml:space="preserve">5.20484209060669</t>
   </si>
   <si>
     <t xml:space="preserve">5.16992139816284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20228624343872</t>
+    <t xml:space="preserve">5.20228672027588</t>
   </si>
   <si>
     <t xml:space="preserve">5.19632434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15884923934937</t>
+    <t xml:space="preserve">5.15884971618652</t>
   </si>
   <si>
     <t xml:space="preserve">5.17843866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2269868850708</t>
+    <t xml:space="preserve">5.22698640823364</t>
   </si>
   <si>
     <t xml:space="preserve">5.23635482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25338983535767</t>
+    <t xml:space="preserve">5.25339031219482</t>
   </si>
   <si>
     <t xml:space="preserve">5.31471300125122</t>
@@ -5141,28 +5141,28 @@
     <t xml:space="preserve">5.39903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14266633987427</t>
+    <t xml:space="preserve">5.28916120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14266586303711</t>
   </si>
   <si>
     <t xml:space="preserve">5.1929178237915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1750316619873</t>
+    <t xml:space="preserve">5.17503213882446</t>
   </si>
   <si>
     <t xml:space="preserve">5.21250677108765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30619525909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39136743545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31300926208496</t>
+    <t xml:space="preserve">5.3061957359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39136791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31300973892212</t>
   </si>
   <si>
     <t xml:space="preserve">5.34622669219971</t>
@@ -5171,10 +5171,10 @@
     <t xml:space="preserve">5.34452342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3607063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39647722244263</t>
+    <t xml:space="preserve">5.36070585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39647769927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.44836759567261</t>
@@ -5183,13 +5183,13 @@
     <t xml:space="preserve">5.45012617111206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47035360336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55038690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51872539520264</t>
+    <t xml:space="preserve">5.4703540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55038642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51872587203979</t>
   </si>
   <si>
     <t xml:space="preserve">5.5160870552063</t>
@@ -5216,19 +5216,19 @@
     <t xml:space="preserve">5.28302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36129951477051</t>
+    <t xml:space="preserve">5.36129903793335</t>
   </si>
   <si>
     <t xml:space="preserve">5.32436084747314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23553371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17484951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21002864837646</t>
+    <t xml:space="preserve">5.23553419113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17484998703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21002817153931</t>
   </si>
   <si>
     <t xml:space="preserve">5.2671947479248</t>
@@ -5243,10 +5243,10 @@
     <t xml:space="preserve">5.37273263931274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39120101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45892095565796</t>
+    <t xml:space="preserve">5.39120149612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4589204788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.43957233428955</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">5.41406774520874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40791177749634</t>
+    <t xml:space="preserve">5.40791130065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.39383983612061</t>
@@ -5264,19 +5264,19 @@
     <t xml:space="preserve">5.36745548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46068048477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44484949111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45188522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38768291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56006097793579</t>
+    <t xml:space="preserve">5.46068000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44484901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45188474655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38768339157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56006145477295</t>
   </si>
   <si>
     <t xml:space="preserve">5.52752017974854</t>
@@ -5285,16 +5285,16 @@
     <t xml:space="preserve">5.48442602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4747519493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35338401794434</t>
+    <t xml:space="preserve">5.47475147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35338354110718</t>
   </si>
   <si>
     <t xml:space="preserve">5.31644582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25488185882568</t>
+    <t xml:space="preserve">5.25488233566284</t>
   </si>
   <si>
     <t xml:space="preserve">5.23113632202148</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">5.14582681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09042024612427</t>
+    <t xml:space="preserve">5.09041976928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.11856317520142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97872638702393</t>
+    <t xml:space="preserve">4.97872591018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.85208129882812</t>
@@ -5318,7 +5318,7 @@
     <t xml:space="preserve">4.88726043701172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88462209701538</t>
+    <t xml:space="preserve">4.88462162017822</t>
   </si>
   <si>
     <t xml:space="preserve">4.92595720291138</t>
@@ -5330,10 +5330,10 @@
     <t xml:space="preserve">5.02270030975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08426332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06051731109619</t>
+    <t xml:space="preserve">5.08426380157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06051778793335</t>
   </si>
   <si>
     <t xml:space="preserve">5.03325366973877</t>
@@ -5345,16 +5345,16 @@
     <t xml:space="preserve">5.04996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96641302108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00511074066162</t>
+    <t xml:space="preserve">5.01390504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99719476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96641254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00511026382446</t>
   </si>
   <si>
     <t xml:space="preserve">5.07722759246826</t>
@@ -5363,13 +5363,13 @@
     <t xml:space="preserve">5.05875825881958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08250379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06139659881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17660856246948</t>
+    <t xml:space="preserve">5.08250427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06139707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17660903930664</t>
   </si>
   <si>
     <t xml:space="preserve">5.26631546020508</t>
@@ -5378,19 +5378,19 @@
     <t xml:space="preserve">5.30589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37712955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41758489608765</t>
+    <t xml:space="preserve">5.37713003158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4175853729248</t>
   </si>
   <si>
     <t xml:space="preserve">5.40527248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38152742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35426330566406</t>
+    <t xml:space="preserve">5.38152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3542628288269</t>
   </si>
   <si>
     <t xml:space="preserve">5.39032220840454</t>
@@ -5405,16 +5405,16 @@
     <t xml:space="preserve">5.54247140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63305807113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70781326293945</t>
+    <t xml:space="preserve">5.63305854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70781278610229</t>
   </si>
   <si>
     <t xml:space="preserve">5.6427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62074518203735</t>
+    <t xml:space="preserve">5.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">5.61282968521118</t>
@@ -5426,10 +5426,10 @@
     <t xml:space="preserve">5.65680360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66559791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65768337249756</t>
+    <t xml:space="preserve">5.66559839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6576828956604</t>
   </si>
   <si>
     <t xml:space="preserve">5.70429515838623</t>
@@ -5444,7 +5444,7 @@
     <t xml:space="preserve">5.760582447052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75882291793823</t>
+    <t xml:space="preserve">5.75882339477539</t>
   </si>
   <si>
     <t xml:space="preserve">5.75354623794556</t>
@@ -5453,28 +5453,28 @@
     <t xml:space="preserve">5.77465391159058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73155927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.815110206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91185283660889</t>
+    <t xml:space="preserve">5.73155975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81510972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91185188293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.86611938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85996294021606</t>
+    <t xml:space="preserve">5.85996341705322</t>
   </si>
   <si>
     <t xml:space="preserve">5.89250373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86436080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86963748931885</t>
+    <t xml:space="preserve">5.86436033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86963701248169</t>
   </si>
   <si>
     <t xml:space="preserve">5.90921401977539</t>
@@ -5486,19 +5486,19 @@
     <t xml:space="preserve">5.90041923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91888856887817</t>
+    <t xml:space="preserve">5.91888809204102</t>
   </si>
   <si>
     <t xml:space="preserve">5.82742214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91361141204834</t>
+    <t xml:space="preserve">5.91361093521118</t>
   </si>
   <si>
     <t xml:space="preserve">5.88458824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89162445068359</t>
+    <t xml:space="preserve">5.89162397384644</t>
   </si>
   <si>
     <t xml:space="preserve">5.92504453659058</t>
@@ -5513,13 +5513,13 @@
     <t xml:space="preserve">5.98660802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93647766113281</t>
+    <t xml:space="preserve">5.93647718429565</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8239049911499</t>
+    <t xml:space="preserve">5.82390451431274</t>
   </si>
   <si>
     <t xml:space="preserve">5.85908365249634</t>
@@ -6819,6 +6819,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.08199977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00500011444092</t>
   </si>
 </sst>
 </file>
@@ -72469,7 +72472,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6932638889</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>19357508</v>
@@ -72490,6 +72493,32 @@
         <v>2268</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6927430556</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>20482894</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>8.97900009155273</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>9.0310001373291</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>9.00500011444092</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>2269</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="2270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2271">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697352409363</t>
+    <t xml:space="preserve">2.23697328567505</t>
   </si>
   <si>
     <t xml:space="preserve">ENEL.MI</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">2.23223924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21448564529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21685266494751</t>
+    <t xml:space="preserve">2.21448493003845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21685242652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.20146584510803</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">2.23460626602173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21211814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17187643051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767383575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09257578849792</t>
+    <t xml:space="preserve">2.21211791038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1718761920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13281846046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09257650375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.16004061698914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20620059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19436478614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22513723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22395396232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19081425666809</t>
+    <t xml:space="preserve">2.20620036125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19436430931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22513794898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25236010551453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987222671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22395372390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19081354141235</t>
   </si>
   <si>
     <t xml:space="preserve">2.14702105522156</t>
@@ -116,52 +116,52 @@
     <t xml:space="preserve">2.07008790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06772089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08665871620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01090908050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0937602519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16477465629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15057158470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.156489610672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228677749634</t>
+    <t xml:space="preserve">2.06772065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0866584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01090884208679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09375977516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1647744178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15057182312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15648984909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228653907776</t>
   </si>
   <si>
     <t xml:space="preserve">2.15293908119202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09494280815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18016123771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19199728965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21330213546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19791555404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16714215278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542695999146</t>
+    <t xml:space="preserve">2.09494376182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18016171455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19199705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21330165863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19791507720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16714191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542719841003</t>
   </si>
   <si>
     <t xml:space="preserve">2.24170804023743</t>
@@ -170,52 +170,52 @@
     <t xml:space="preserve">2.25354361534119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31509017944336</t>
+    <t xml:space="preserve">2.3150897026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.30798840522766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30207061767578</t>
+    <t xml:space="preserve">2.30207085609436</t>
   </si>
   <si>
     <t xml:space="preserve">2.30562114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32574200630188</t>
+    <t xml:space="preserve">2.32574248313904</t>
   </si>
   <si>
     <t xml:space="preserve">2.3174569606781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088663101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31390643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36716794967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.306804895401</t>
+    <t xml:space="preserve">2.31982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31153893470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3139066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35059714317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36716771125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30680465698242</t>
   </si>
   <si>
     <t xml:space="preserve">2.29496908187866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2736644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738410949707</t>
+    <t xml:space="preserve">2.27366495132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738387107849</t>
   </si>
   <si>
     <t xml:space="preserve">2.16595864295959</t>
@@ -224,175 +224,175 @@
     <t xml:space="preserve">2.22632145881653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23579025268555</t>
+    <t xml:space="preserve">2.23578953742981</t>
   </si>
   <si>
     <t xml:space="preserve">2.21921968460083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26182866096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129721641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32337522506714</t>
+    <t xml:space="preserve">2.26182818412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129769325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32337498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.2961528301239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35769891738892</t>
+    <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
     <t xml:space="preserve">2.39912462234497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231281280518</t>
+    <t xml:space="preserve">2.34231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.34112882614136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3292932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30917167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941363334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071824073792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37663626670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3375780582428</t>
+    <t xml:space="preserve">2.32929301261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3091721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941411018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071847915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37663698196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757877349854</t>
   </si>
   <si>
     <t xml:space="preserve">2.35296487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33165979385376</t>
+    <t xml:space="preserve">2.33166027069092</t>
   </si>
   <si>
     <t xml:space="preserve">2.36124968528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33994483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40385818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095995903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42989778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42516303062439</t>
+    <t xml:space="preserve">2.3399453163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40385890007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41096019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42989754676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42516326904297</t>
   </si>
   <si>
     <t xml:space="preserve">2.43699908256531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38965606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794111251831</t>
+    <t xml:space="preserve">2.38965582847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794087409973</t>
   </si>
   <si>
     <t xml:space="preserve">2.37782001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43463158607483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44173336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43936681747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651469230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31864047050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27839875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37900304794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43817019462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44433379173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40735411643982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46652102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21875977516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627751350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365672111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45296216011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049715042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45419430732727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39256286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37653827667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42214608192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43940329551697</t>
+    <t xml:space="preserve">2.43463206291199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44173359870911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43936657905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651564598083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31864094734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2783989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37900376319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43817043304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44433355331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4073543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46652126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21875953674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21013140678406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365648269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45296192169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049691200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45419502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39256238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37653803825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42214632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43940305709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.45912528038025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4603579044342</t>
+    <t xml:space="preserve">2.46035814285278</t>
   </si>
   <si>
     <t xml:space="preserve">2.46282339096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44679856300354</t>
+    <t xml:space="preserve">2.44679927825928</t>
   </si>
   <si>
     <t xml:space="preserve">2.48008036613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48254537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47638273239136</t>
+    <t xml:space="preserve">2.48254561424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47638249397278</t>
   </si>
   <si>
     <t xml:space="preserve">2.47268438339233</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">2.53801488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52568769454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49240708351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48131275177002</t>
+    <t xml:space="preserve">2.52568817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49240732192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48131322860718</t>
   </si>
   <si>
     <t xml:space="preserve">2.49117422103882</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">2.5108962059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350022315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49857020378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53308439254761</t>
+    <t xml:space="preserve">2.50350069999695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49856996536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53308415412903</t>
   </si>
   <si>
     <t xml:space="preserve">2.52938628196716</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">2.47021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42461133003235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707657814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39749312400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.402423620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42830896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42954182624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4357054233551</t>
+    <t xml:space="preserve">2.42461156845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39749360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42830920219421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42954206466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43570518493652</t>
   </si>
   <si>
     <t xml:space="preserve">2.45172953605652</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">2.41351723670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43200755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48747587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48994159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761464118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541039466858</t>
+    <t xml:space="preserve">2.43200707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48747658729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48994135856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541063308716</t>
   </si>
   <si>
     <t xml:space="preserve">2.5306191444397</t>
@@ -485,127 +485,127 @@
     <t xml:space="preserve">2.44556665420532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41474986076355</t>
+    <t xml:space="preserve">2.41105151176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41475009918213</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913300037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41968083381653</t>
+    <t xml:space="preserve">2.41968107223511</t>
   </si>
   <si>
     <t xml:space="preserve">2.40981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44803094863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41721558570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4209132194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926428794861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41228532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3728404045105</t>
+    <t xml:space="preserve">2.4480311870575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4172158241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42091345787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41228485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37284016609192</t>
   </si>
   <si>
     <t xml:space="preserve">2.35928153991699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32476735115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36051344871521</t>
+    <t xml:space="preserve">2.32476687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
     <t xml:space="preserve">2.3383264541626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31983685493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36421203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35435080528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40858697891235</t>
+    <t xml:space="preserve">2.31983637809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36421179771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35435056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43693804740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40858721733093</t>
   </si>
   <si>
     <t xml:space="preserve">2.4307746887207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41598272323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37037491798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36297941207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35311841964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36667728424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38393378257751</t>
+    <t xml:space="preserve">2.41598296165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37037467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36297965049744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35311818122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36667680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38393425941467</t>
   </si>
   <si>
     <t xml:space="preserve">2.32723212242126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24711108207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24341297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22369050979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24957585334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25080871582031</t>
+    <t xml:space="preserve">2.24711060523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.243412733078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24957633018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25080847740173</t>
   </si>
   <si>
     <t xml:space="preserve">2.2828574180603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22862076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24834322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860423088074</t>
+    <t xml:space="preserve">2.22862148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2483434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860375404358</t>
   </si>
   <si>
     <t xml:space="preserve">2.3075098991394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29764938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30257964134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33586120605469</t>
+    <t xml:space="preserve">2.29764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.302579164505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33586096763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.35065245628357</t>
@@ -614,37 +614,37 @@
     <t xml:space="preserve">2.3333957195282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51952481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51336216926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47884750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49980306625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53924679756165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5651330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54910826683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56266713142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58115720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60211229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56883120536804</t>
+    <t xml:space="preserve">2.51952505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51336240768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47884774208069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4998025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5392472743988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56513285636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54910850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56266736984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58115696907043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60211205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56883096694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.57252860069275</t>
@@ -653,37 +653,37 @@
     <t xml:space="preserve">2.57622623443604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55896973609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54048013687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54664349555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56636571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55403900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55650424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55157351493835</t>
+    <t xml:space="preserve">2.55896997451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54048037528992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54664373397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56636548042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55403876304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55650401115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55157375335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.57299447059631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56795430183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52763295173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50873208045959</t>
+    <t xml:space="preserve">2.56795454025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52763271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50873279571533</t>
   </si>
   <si>
     <t xml:space="preserve">2.47849178314209</t>
@@ -692,283 +692,283 @@
     <t xml:space="preserve">2.42557001113892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43438982963562</t>
+    <t xml:space="preserve">2.43439054489136</t>
   </si>
   <si>
     <t xml:space="preserve">2.43565034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46715116500854</t>
+    <t xml:space="preserve">2.44825100898743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46715092658997</t>
   </si>
   <si>
     <t xml:space="preserve">2.41926980018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5440137386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55031323432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023289680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5326726436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49361228942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53141307830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54527354240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52133297920227</t>
+    <t xml:space="preserve">2.44069075584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54401397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55031371116638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53267312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49361205101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53141331672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5452733039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52133274078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.5263729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50369215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200731754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55787372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55283403396606</t>
+    <t xml:space="preserve">2.50369238853455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52007246017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55787396430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55283379554749</t>
   </si>
   <si>
     <t xml:space="preserve">2.57803463935852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59945487976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60323524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60827469825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62717580795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63851618766785</t>
+    <t xml:space="preserve">2.5994553565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60323572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6082751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62717604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63851594924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.63347554206848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63473606109619</t>
+    <t xml:space="preserve">2.63473653793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67757678031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6523768901825</t>
+    <t xml:space="preserve">2.67757701873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65237617492676</t>
   </si>
   <si>
     <t xml:space="preserve">2.6397762298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65867686271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71033811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70151829719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71537852287292</t>
+    <t xml:space="preserve">2.6586766242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71033883094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70151805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71537828445435</t>
   </si>
   <si>
     <t xml:space="preserve">2.7342791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74183893203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75191974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78090023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77964019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7746000289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76199984550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7720799446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74309921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75947976112366</t>
+    <t xml:space="preserve">2.74183917045593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75191926956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78090047836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77963995933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77459979057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7619993686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77208018302917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74309968948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7594792842865</t>
   </si>
   <si>
     <t xml:space="preserve">2.75821948051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67253732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907831192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80484056472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79098033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77712035179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77081942558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939894676208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7872006893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79350113868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85650300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88422298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87792277336121</t>
+    <t xml:space="preserve">2.72671866416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67253756523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907855033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80484104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79098057746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7771201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77081990242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939942359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78719997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79350066184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85650253295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8842236995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87792348861694</t>
   </si>
   <si>
     <t xml:space="preserve">2.8665828704834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8791835308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87414288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87666273117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88044285774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94974493980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92202496528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95100474357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97998642921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98628616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00518727302551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.029128074646</t>
+    <t xml:space="preserve">2.87918329238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87414264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87666296958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94974517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92202472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95100569725037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97998595237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01526713371277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9862859249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00518679618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02912783622742</t>
   </si>
   <si>
     <t xml:space="preserve">2.96108555793762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97872638702393</t>
+    <t xml:space="preserve">2.97872686386108</t>
   </si>
   <si>
     <t xml:space="preserve">2.99762654304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01274728775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96990585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01148772239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02156734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11354970932007</t>
+    <t xml:space="preserve">3.01274633407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96990609169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01148748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02156639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11354994773865</t>
   </si>
   <si>
     <t xml:space="preserve">3.08582901954651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05180788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05558824539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05810832977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09968972206116</t>
+    <t xml:space="preserve">3.05180835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05558800697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05810856819153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440854072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09968948364258</t>
   </si>
   <si>
     <t xml:space="preserve">3.10724949836731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08204936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13749027252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10347008705139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11858987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02408766746521</t>
+    <t xml:space="preserve">3.08204889297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13749003410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10347032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11859011650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02408742904663</t>
   </si>
   <si>
     <t xml:space="preserve">3.04928803443909</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">2.95730495452881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99888706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880624771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95478630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97368597984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02282786369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01778721809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06944847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1324508190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13118958473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10094952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12489008903503</t>
+    <t xml:space="preserve">2.99888682365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95478534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9736852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01778674125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06944894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13245034217834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13119029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10094928741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12488985061646</t>
   </si>
   <si>
     <t xml:space="preserve">3.12867045402527</t>
@@ -1019,115 +1019,115 @@
     <t xml:space="preserve">3.09338927268982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11906051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07927060127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11777687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13831400871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09595584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13703036308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13189601898193</t>
+    <t xml:space="preserve">3.119060754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11777710914612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13831424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08953905105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09595656394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13703107833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13189625740051</t>
   </si>
   <si>
     <t xml:space="preserve">3.17040324211121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19864201545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19735765457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21532797813416</t>
+    <t xml:space="preserve">3.19864177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19735789299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21532821655273</t>
   </si>
   <si>
     <t xml:space="preserve">3.19222354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1601345539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22816371917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2506263256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25383472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23458123207092</t>
+    <t xml:space="preserve">3.16013431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22816324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25062537193298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25383496284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23458194732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.19607400894165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26025176048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26987886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26346206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29875922203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27950620651245</t>
+    <t xml:space="preserve">3.26025295257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26987934112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26346135139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27950596809387</t>
   </si>
   <si>
     <t xml:space="preserve">3.28271508216858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3019688129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3308482170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32122206687927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36614656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33405733108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31159543991089</t>
+    <t xml:space="preserve">3.30196857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33084797859192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32122182846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36614680290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33405804634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31159520149231</t>
   </si>
   <si>
     <t xml:space="preserve">3.27629685401917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30517721176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28592395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28913307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2730884552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24099898338318</t>
+    <t xml:space="preserve">3.3051769733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28592371940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28913235664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27308821678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24099946022034</t>
   </si>
   <si>
     <t xml:space="preserve">3.18708944320679</t>
@@ -1136,115 +1136,115 @@
     <t xml:space="preserve">3.23779034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25704336166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31480383872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31801223754883</t>
+    <t xml:space="preserve">3.2570436000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31480431556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31801295280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.32763910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30838656425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32443070411682</t>
+    <t xml:space="preserve">3.30838632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3244309425354</t>
   </si>
   <si>
     <t xml:space="preserve">3.35010170936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39502716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39181756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41428017616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41748857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4559965133667</t>
+    <t xml:space="preserve">3.39502787590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39181804656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41428089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41748929023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45599627494812</t>
   </si>
   <si>
     <t xml:space="preserve">3.44316029548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44957780838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45920515060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43995213508606</t>
+    <t xml:space="preserve">3.44957876205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45920562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46241402626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43995141983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.42390704154968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38539958000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3725643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37898182868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34689283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35331058502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40786266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43674254417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46883177757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.513756275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50092101097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44636988639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51054763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5458459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56189012527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58114409446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53621912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48166751861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50412964820862</t>
+    <t xml:space="preserve">3.38539981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256550788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37898230552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34689331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35331010818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40786242485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43674278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46883249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51375651359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44636964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51054716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54584574699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56188988685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58114314079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53621983528137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48166799545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5041298866272</t>
   </si>
   <si>
     <t xml:space="preserve">3.41107130050659</t>
@@ -1253,145 +1253,145 @@
     <t xml:space="preserve">3.36293768882751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29234147071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42711639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4461145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42975068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39047861099243</t>
+    <t xml:space="preserve">3.29234170913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42711663246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40144467353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44611477851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4297513961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">3.37738871574402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35382580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31717133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34466195106506</t>
+    <t xml:space="preserve">3.35382533073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31717157363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34466147422791</t>
   </si>
   <si>
     <t xml:space="preserve">3.31586241722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25302672386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21310091018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12146639823914</t>
+    <t xml:space="preserve">3.25302720069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21310019493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12146663665771</t>
   </si>
   <si>
     <t xml:space="preserve">3.19019222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09070348739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03310418128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06844902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04619479179382</t>
+    <t xml:space="preserve">3.09070372581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03310370445251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0684494972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04619550704956</t>
   </si>
   <si>
     <t xml:space="preserve">3.128666639328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13652038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735605239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12212109565735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07630300521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16466522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15877437591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16597414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801146507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11688446998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04815864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07695841789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09528493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12670302391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1679379940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16531991958618</t>
+    <t xml:space="preserve">3.13652062416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18102884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735748291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12212085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07630348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16466569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15877461433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16597437858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801122665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11688470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0481584072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0769579410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09528517723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12670207023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16793823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1653196811676</t>
   </si>
   <si>
     <t xml:space="preserve">3.1633563041687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18757367134094</t>
+    <t xml:space="preserve">3.18757390975952</t>
   </si>
   <si>
     <t xml:space="preserve">3.17448329925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19673752784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22684550285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1915009021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13913869857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17513751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13259315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13979268074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25630044937134</t>
+    <t xml:space="preserve">3.19673705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22684574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150137901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13913798332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.175137758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13259339332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13979363441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25629997253418</t>
   </si>
   <si>
     <t xml:space="preserve">3.24320936203003</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">3.24844527244568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30538964271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30277156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32764339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32240772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31324362754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34597039222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34727954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40095162391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39833331108093</t>
+    <t xml:space="preserve">3.30539035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3027720451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32764410972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32240796089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31324458122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34597086906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34728002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40095186233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39833378791809</t>
   </si>
   <si>
     <t xml:space="preserve">3.38393354415894</t>
@@ -1433,208 +1433,208 @@
     <t xml:space="preserve">3.40487909317017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39309787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44284200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43629693984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44807767868042</t>
+    <t xml:space="preserve">3.3930971622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44284224510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43629622459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44807863235474</t>
   </si>
   <si>
     <t xml:space="preserve">3.49520516395569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48211312294006</t>
+    <t xml:space="preserve">3.4821138381958</t>
   </si>
   <si>
     <t xml:space="preserve">3.52531313896179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52662229537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43891453742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32109832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3433530330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3629891872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23797345161438</t>
+    <t xml:space="preserve">3.52662205696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43891477584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32109880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31848096847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34335327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36298966407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23797273635864</t>
   </si>
   <si>
     <t xml:space="preserve">3.26153635978699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20590090751648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19542860984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19215536117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10772109031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08415746688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888681411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11033892631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07826733589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.098557472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13324809074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07564854621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06386733055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00692296028137</t>
+    <t xml:space="preserve">3.2059006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20655560493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19542837142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19215559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10772061347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08415794372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888657569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11033916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0782675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855818748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13324761390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07564878463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06386780738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00692248344421</t>
   </si>
   <si>
     <t xml:space="preserve">3.11557579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12932062149048</t>
+    <t xml:space="preserve">3.12932085990906</t>
   </si>
   <si>
     <t xml:space="preserve">3.18953776359558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401052474976</t>
+    <t xml:space="preserve">3.18888306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401076316833</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204738616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1574649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08481216430664</t>
+    <t xml:space="preserve">3.15746545791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08481192588806</t>
   </si>
   <si>
     <t xml:space="preserve">3.10641241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06452226638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08808493614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12342929840088</t>
+    <t xml:space="preserve">3.06452178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08808517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12342977523804</t>
   </si>
   <si>
     <t xml:space="preserve">3.10313940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11361145973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10510301589966</t>
+    <t xml:space="preserve">3.11361193656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10510277748108</t>
   </si>
   <si>
     <t xml:space="preserve">3.15550184249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437460899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710137367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1973922252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17644715309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17186522483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1489565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18364667892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17252016067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19411897659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21048331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20917415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21113705635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17952394485474</t>
+    <t xml:space="preserve">3.14437437057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19739246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17186498641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14895606040955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18364691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17251992225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19411945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21048307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20917367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21113729476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17952346801758</t>
   </si>
   <si>
     <t xml:space="preserve">3.15530848503113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13647532463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14656448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17212462425232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16338038444519</t>
+    <t xml:space="preserve">3.13647508621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14656496047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17212510108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16338062286377</t>
   </si>
   <si>
     <t xml:space="preserve">3.20844674110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08400964736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02347302436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04432463645935</t>
+    <t xml:space="preserve">3.08401036262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02347326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04432487487793</t>
   </si>
   <si>
     <t xml:space="preserve">3.04499769210815</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">3.08468294143677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0833375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06921195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00598502159119</t>
+    <t xml:space="preserve">3.08333706855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06921243667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00598454475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.99051427841187</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">3.01203894615173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9804253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97638916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96629953384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9979133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98513340950012</t>
+    <t xml:space="preserve">2.98042559623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97638940811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96629977226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99791359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9851336479187</t>
   </si>
   <si>
     <t xml:space="preserve">2.95082926750183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96293640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95150208473206</t>
+    <t xml:space="preserve">2.96293663978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95150184631348</t>
   </si>
   <si>
     <t xml:space="preserve">2.92997765541077</t>
@@ -1688,58 +1688,58 @@
     <t xml:space="preserve">2.94006729125977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89836454391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86540508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85397028923035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88625717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88558411598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94477534294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96091842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06719398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06584906578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03894400596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06652188301086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05979537963867</t>
+    <t xml:space="preserve">2.89836430549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86540555953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8539707660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8862566947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88558435440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94477558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96091866493225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06719422340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06584930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03894352912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06652140617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05979514122009</t>
   </si>
   <si>
     <t xml:space="preserve">3.03625345230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05912280082703</t>
+    <t xml:space="preserve">3.05912303924561</t>
   </si>
   <si>
     <t xml:space="preserve">3.1162965297699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07392072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09342670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10149788856506</t>
+    <t xml:space="preserve">3.07392048835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09342646598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10149812698364</t>
   </si>
   <si>
     <t xml:space="preserve">3.08064675331116</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">2.96764469146729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94746613502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562743186951</t>
+    <t xml:space="preserve">2.9474663734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562671661377</t>
   </si>
   <si>
     <t xml:space="preserve">3.04096150398254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9999315738678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97504377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94410300254822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94343018531799</t>
+    <t xml:space="preserve">2.99993109703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97504353523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94410276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94343066215515</t>
   </si>
   <si>
     <t xml:space="preserve">2.92325162887573</t>
@@ -1781,409 +1781,409 @@
     <t xml:space="preserve">2.96899056434631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93468642234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97975182533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98446011543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96697235107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94612073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95957326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91517996788025</t>
+    <t xml:space="preserve">2.93468594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97975254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9844605922699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9669725894928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94612097740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95957398414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91518020629883</t>
   </si>
   <si>
     <t xml:space="preserve">2.94544839859009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96428179740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97168111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00665712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01540112495422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02280116081238</t>
+    <t xml:space="preserve">2.96428155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97168064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00665760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01540160179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0228009223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.99455046653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02683639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0685396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09275412559509</t>
+    <t xml:space="preserve">3.02683663368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06853914260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09275436401367</t>
   </si>
   <si>
     <t xml:space="preserve">3.13378500938416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13243985176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16472578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19835734367371</t>
+    <t xml:space="preserve">3.13243913650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16472554206848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19835710525513</t>
   </si>
   <si>
     <t xml:space="preserve">3.20441102981567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21517395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20037508010864</t>
+    <t xml:space="preserve">3.21517324447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20037531852722</t>
   </si>
   <si>
     <t xml:space="preserve">3.22189950942993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23804211616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22728037834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24880456924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1929759979248</t>
+    <t xml:space="preserve">3.2380428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22727942466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24880480766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19297623634338</t>
   </si>
   <si>
     <t xml:space="preserve">3.19364881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2333345413208</t>
+    <t xml:space="preserve">3.18961310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23333430290222</t>
   </si>
   <si>
     <t xml:space="preserve">3.3167405128479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37660455703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37525939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37256836891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37122344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44655823707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46270084381104</t>
+    <t xml:space="preserve">3.37660384178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3752589225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37256789207458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37122368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44655776023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46270108222961</t>
   </si>
   <si>
     <t xml:space="preserve">3.48826098442078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39543795585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39274740219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41965246200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42099833488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46673703193665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48153495788574</t>
+    <t xml:space="preserve">3.39543843269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.392746925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41965222358704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42099809646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46808218955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46673679351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48153424263</t>
   </si>
   <si>
     <t xml:space="preserve">3.47346329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53130912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49767732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50440359115601</t>
+    <t xml:space="preserve">3.5313093662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49767756462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50440406799316</t>
   </si>
   <si>
     <t xml:space="preserve">3.51112985610962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50978517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52458238601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57032251358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57446694374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54683351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57861185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58690166473389</t>
+    <t xml:space="preserve">3.50978493690491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52458310127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57032179832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58275723457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57446718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54683208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5786120891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5869026184082</t>
   </si>
   <si>
     <t xml:space="preserve">3.56755876541138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6214451789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6159188747406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63802552223206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57170295715332</t>
+    <t xml:space="preserve">3.62144470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61591839790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63802576065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57170343399048</t>
   </si>
   <si>
     <t xml:space="preserve">3.58137536048889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54545068740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52472567558289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55097842216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59104776382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60348296165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60071849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61729979515076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62282681465149</t>
+    <t xml:space="preserve">3.54545164108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52472591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55097794532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5910472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60348272323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60071921348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61729955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62282705307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.61039137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61453604698181</t>
+    <t xml:space="preserve">3.61453628540039</t>
   </si>
   <si>
     <t xml:space="preserve">3.62420797348022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64631509780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66980457305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66151452064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67533087730408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67118644714355</t>
+    <t xml:space="preserve">3.646315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66980385780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6615149974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67533135414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67118668556213</t>
   </si>
   <si>
     <t xml:space="preserve">3.66427779197693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68085885047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72921776771545</t>
+    <t xml:space="preserve">3.68085813522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72921800613403</t>
   </si>
   <si>
     <t xml:space="preserve">3.80106616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78863072395325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77205038070679</t>
+    <t xml:space="preserve">3.78863191604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77205061912537</t>
   </si>
   <si>
     <t xml:space="preserve">3.79830288887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79001307487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79139423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77895927429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81350183486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495352745056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89225888252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88258695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93923711776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94752717018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92818260192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94061851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90884041786194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91091108322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9433810710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93440103530884</t>
+    <t xml:space="preserve">3.79001259803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79139471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77895832061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81350111961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89225912094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88258719444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93923687934875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94752812385559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92818331718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90883946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91091084480286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94338297843933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93440079689026</t>
   </si>
   <si>
     <t xml:space="preserve">3.93370962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92127466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91022109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89847636222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87567925453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85564351081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78379559516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81419205665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81695628166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81281065940857</t>
+    <t xml:space="preserve">3.9212749004364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91022038459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89847707748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85564374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78379535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8141930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81695604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81281042098999</t>
   </si>
   <si>
     <t xml:space="preserve">3.80244755744934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82593679428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85840797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83630037307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89571237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85288000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86531615257263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84182643890381</t>
+    <t xml:space="preserve">3.82593727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85840725898743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83629965782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89571261405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85288047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86531543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84182691574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.87015175819397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8521888256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8349187374115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80452013015747</t>
+    <t xml:space="preserve">3.85218954086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83491778373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.8514986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85080718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86186194419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88880443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9309458732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98690462112427</t>
+    <t xml:space="preserve">3.85080766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86186075210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88880467414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93094635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98690485954285</t>
   </si>
   <si>
     <t xml:space="preserve">3.98068785667419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92403841018677</t>
+    <t xml:space="preserve">3.92403769493103</t>
   </si>
   <si>
     <t xml:space="preserve">3.99934101104736</t>
@@ -2192,61 +2192,61 @@
     <t xml:space="preserve">3.8390634059906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84804463386536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87844181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94407296180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95581650733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01108503341675</t>
+    <t xml:space="preserve">3.84804368019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87844109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94407224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95581746101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01108551025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.06980752944946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02628374099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010105133057</t>
+    <t xml:space="preserve">4.02628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010057449341</t>
   </si>
   <si>
     <t xml:space="preserve">4.06911706924438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13889312744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1934700012207</t>
+    <t xml:space="preserve">4.13889265060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19347047805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.20037889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30884313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26255464553833</t>
+    <t xml:space="preserve">4.30884218215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26255559921265</t>
   </si>
   <si>
     <t xml:space="preserve">4.27637243270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3053879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28397274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19692468643188</t>
+    <t xml:space="preserve">4.30538845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3005518913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28397178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19692373275757</t>
   </si>
   <si>
     <t xml:space="preserve">4.2031421661377</t>
@@ -2255,58 +2255,58 @@
     <t xml:space="preserve">4.24182939529419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23215818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32473230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42697763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4539213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42145109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42835998535156</t>
+    <t xml:space="preserve">4.2321572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32473278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45392084121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42145156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4283595085144</t>
   </si>
   <si>
     <t xml:space="preserve">4.42766904830933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43941402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49744510650635</t>
+    <t xml:space="preserve">4.43941259384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49744558334351</t>
   </si>
   <si>
     <t xml:space="preserve">4.45668458938599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48500967025757</t>
+    <t xml:space="preserve">4.48501014709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.4995174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5312967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34407520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43310594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47267436981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41402864456177</t>
+    <t xml:space="preserve">4.53129577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34407567977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4323992729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43310499191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4726734161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41402769088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.38788414001465</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">4.41332101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35891389846802</t>
+    <t xml:space="preserve">4.35891485214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.3801121711731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37940454483032</t>
+    <t xml:space="preserve">4.40908098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37940549850464</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33418416976929</t>
+    <t xml:space="preserve">4.33418369293213</t>
   </si>
   <si>
     <t xml:space="preserve">4.33842277526855</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">4.26493883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28472375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29461479187012</t>
+    <t xml:space="preserve">4.28472232818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29461526870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.2458610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44087743759155</t>
+    <t xml:space="preserve">4.44087791442871</t>
   </si>
   <si>
     <t xml:space="preserve">4.49316549301147</t>
@@ -2357,91 +2357,91 @@
     <t xml:space="preserve">4.40625524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44017171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39706945419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59208726882935</t>
+    <t xml:space="preserve">4.46419525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44017124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39706897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5920877456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.59349966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68606185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6592116355896</t>
+    <t xml:space="preserve">4.68606233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65921211242676</t>
   </si>
   <si>
     <t xml:space="preserve">4.71997833251953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72068548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7609601020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70938014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67758417129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62458992004395</t>
+    <t xml:space="preserve">4.72068500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76096057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70937919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67758321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62458944320679</t>
   </si>
   <si>
     <t xml:space="preserve">4.58572721481323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55181169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67263889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65779876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58007478713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69878101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67405080795288</t>
+    <t xml:space="preserve">4.55181121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67263793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65780019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58007526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69878149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67405033111572</t>
   </si>
   <si>
     <t xml:space="preserve">4.64649391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71362018585205</t>
+    <t xml:space="preserve">4.71361875534058</t>
   </si>
   <si>
     <t xml:space="preserve">4.78215789794922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75530815124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82737827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79487657546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81678056716919</t>
+    <t xml:space="preserve">4.75530672073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82737922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79487609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84080457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81678009033203</t>
   </si>
   <si>
     <t xml:space="preserve">4.71220588684082</t>
@@ -2453,70 +2453,70 @@
     <t xml:space="preserve">4.77226543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83656454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78498363494873</t>
+    <t xml:space="preserve">4.8365650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78498411178589</t>
   </si>
   <si>
     <t xml:space="preserve">4.81536722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78145027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80476903915405</t>
+    <t xml:space="preserve">4.78145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80476856231689</t>
   </si>
   <si>
     <t xml:space="preserve">4.78992986679077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83161926269531</t>
+    <t xml:space="preserve">4.831618309021</t>
   </si>
   <si>
     <t xml:space="preserve">4.80830097198486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78357076644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82455348968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7659068107605</t>
+    <t xml:space="preserve">4.78357124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8245530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">4.84221696853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86129570007324</t>
+    <t xml:space="preserve">4.8612961769104</t>
   </si>
   <si>
     <t xml:space="preserve">4.84998989105225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8556432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87754726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90368986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89733123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92347478866577</t>
+    <t xml:space="preserve">4.85564231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8775463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90369033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89733219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92347431182861</t>
   </si>
   <si>
     <t xml:space="preserve">4.88249254226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87472009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77085208892822</t>
+    <t xml:space="preserve">4.87471961975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77085256576538</t>
   </si>
   <si>
     <t xml:space="preserve">4.85140371322632</t>
@@ -2525,79 +2525,79 @@
     <t xml:space="preserve">4.84716367721558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93407297134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89662408828735</t>
+    <t xml:space="preserve">4.93407249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89662456512451</t>
   </si>
   <si>
     <t xml:space="preserve">4.85776233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84857654571533</t>
+    <t xml:space="preserve">4.84857606887817</t>
   </si>
   <si>
     <t xml:space="preserve">4.87401294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82596588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80759477615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78710412979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76943969726562</t>
+    <t xml:space="preserve">4.82596635818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80759429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78710460662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76943922042847</t>
   </si>
   <si>
     <t xml:space="preserve">4.83303213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85493564605713</t>
+    <t xml:space="preserve">4.85493612289429</t>
   </si>
   <si>
     <t xml:space="preserve">4.84433746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66698551177979</t>
+    <t xml:space="preserve">4.66698408126831</t>
   </si>
   <si>
     <t xml:space="preserve">4.71785879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75036191940308</t>
+    <t xml:space="preserve">4.75036144256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.75601434707642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83727121353149</t>
+    <t xml:space="preserve">4.83727169036865</t>
   </si>
   <si>
     <t xml:space="preserve">4.89309167861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95315074920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93336629867554</t>
+    <t xml:space="preserve">4.95315170288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9333667755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.94679164886475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09164094924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04359340667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99695873260498</t>
+    <t xml:space="preserve">5.09164047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06973791122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0435938835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9969596862793</t>
   </si>
   <si>
     <t xml:space="preserve">5.09588098526001</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">5.09517431259155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10577297210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1085991859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13686323165894</t>
+    <t xml:space="preserve">5.10577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10859870910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13686370849609</t>
   </si>
   <si>
     <t xml:space="preserve">5.16159296035767</t>
@@ -2621,16 +2621,16 @@
     <t xml:space="preserve">5.24072980880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22871923446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24355745315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45835781097412</t>
+    <t xml:space="preserve">5.22871875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37780809402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45835876464844</t>
   </si>
   <si>
     <t xml:space="preserve">5.50453567504883</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">5.49804210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64162588119507</t>
+    <t xml:space="preserve">5.64162540435791</t>
   </si>
   <si>
     <t xml:space="preserve">5.53700494766235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69934797286987</t>
+    <t xml:space="preserve">5.69934892654419</t>
   </si>
   <si>
     <t xml:space="preserve">5.77871656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83571720123291</t>
+    <t xml:space="preserve">5.83571767807007</t>
   </si>
   <si>
     <t xml:space="preserve">5.66760158538818</t>
@@ -2666,25 +2666,25 @@
     <t xml:space="preserve">5.74769067764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77222299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82272911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89993333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91652870178223</t>
+    <t xml:space="preserve">5.77222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82272958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89993381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91652774810791</t>
   </si>
   <si>
     <t xml:space="preserve">5.91147804260254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86746406555176</t>
+    <t xml:space="preserve">5.86746454238892</t>
   </si>
   <si>
     <t xml:space="preserve">5.9215784072876</t>
@@ -2693,70 +2693,70 @@
     <t xml:space="preserve">5.97208642959595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05650520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10917568206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18060779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08464431762695</t>
+    <t xml:space="preserve">6.05650472640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10917663574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18060731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08464479446411</t>
   </si>
   <si>
     <t xml:space="preserve">6.09258127212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79386854171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63152456283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71161460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46629524230957</t>
+    <t xml:space="preserve">5.79386901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63152551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71161508560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46629571914673</t>
   </si>
   <si>
     <t xml:space="preserve">5.51247262954712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62286615371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87684535980225</t>
+    <t xml:space="preserve">5.6228666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87684488296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.69357633590698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12717723846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83712291717529</t>
+    <t xml:space="preserve">5.1271767616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83712244033813</t>
   </si>
   <si>
     <t xml:space="preserve">4.70436143875122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7707040309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05426502227783</t>
+    <t xml:space="preserve">3.77070426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05426549911499</t>
   </si>
   <si>
     <t xml:space="preserve">3.95830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1271390914917</t>
+    <t xml:space="preserve">4.12713861465454</t>
   </si>
   <si>
     <t xml:space="preserve">4.24979877471924</t>
@@ -2765,25 +2765,25 @@
     <t xml:space="preserve">4.20650768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24907732009888</t>
+    <t xml:space="preserve">4.24907827377319</t>
   </si>
   <si>
     <t xml:space="preserve">4.30896472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55356168746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54562568664551</t>
+    <t xml:space="preserve">4.55356216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54562520980835</t>
   </si>
   <si>
     <t xml:space="preserve">4.53047370910645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44100427627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60767650604248</t>
+    <t xml:space="preserve">4.44100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6076774597168</t>
   </si>
   <si>
     <t xml:space="preserve">4.57376527786255</t>
@@ -2792,43 +2792,43 @@
     <t xml:space="preserve">4.37823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43378829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37895202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4301815032959</t>
+    <t xml:space="preserve">4.43378877639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3789529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43018054962158</t>
   </si>
   <si>
     <t xml:space="preserve">4.59974050521851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53480339050293</t>
+    <t xml:space="preserve">4.53480291366577</t>
   </si>
   <si>
     <t xml:space="preserve">4.65601873397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65169048309326</t>
+    <t xml:space="preserve">4.6516900062561</t>
   </si>
   <si>
     <t xml:space="preserve">4.47852325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50882768630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47996616363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46770095825195</t>
+    <t xml:space="preserve">4.50882816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47996664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46770048141479</t>
   </si>
   <si>
     <t xml:space="preserve">4.3327751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31834411621094</t>
+    <t xml:space="preserve">4.3183445930481</t>
   </si>
   <si>
     <t xml:space="preserve">4.27577495574951</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">4.25701427459717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37967491149902</t>
+    <t xml:space="preserve">4.37967395782471</t>
   </si>
   <si>
     <t xml:space="preserve">4.43739604949951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52397966384888</t>
+    <t xml:space="preserve">4.52398014068604</t>
   </si>
   <si>
     <t xml:space="preserve">4.4994478225708</t>
@@ -2852,124 +2852,124 @@
     <t xml:space="preserve">4.33421754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39266061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37750911712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46481370925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47347259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38688945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35081338882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24547052383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15672254562378</t>
+    <t xml:space="preserve">4.39266204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37751007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46481466293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47347211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38688993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3508129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24546909332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15672206878662</t>
   </si>
   <si>
     <t xml:space="preserve">4.30319213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35586309432983</t>
+    <t xml:space="preserve">4.35586357116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.51099157333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56727123260498</t>
+    <t xml:space="preserve">4.56727027893066</t>
   </si>
   <si>
     <t xml:space="preserve">4.62499332427979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69714641571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70147514343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75198268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90061712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97926378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04925107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18706369400024</t>
+    <t xml:space="preserve">4.69714689254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70147562026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75198221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90061664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97926473617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0492525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1870641708374</t>
   </si>
   <si>
     <t xml:space="preserve">5.41434526443481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40063524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46773815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46701622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44176292419434</t>
+    <t xml:space="preserve">5.40063667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46773862838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46701717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44176340103149</t>
   </si>
   <si>
     <t xml:space="preserve">5.42011737823486</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28663444519043</t>
+    <t xml:space="preserve">5.28663492202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.29962205886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31188821792603</t>
+    <t xml:space="preserve">5.31188774108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.45907926559448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41506671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39197778701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48361158370972</t>
+    <t xml:space="preserve">5.41506576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39197731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48361206054688</t>
   </si>
   <si>
     <t xml:space="preserve">5.63585376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50092887878418</t>
+    <t xml:space="preserve">5.50092792510986</t>
   </si>
   <si>
     <t xml:space="preserve">5.52906799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5117506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57308101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53989028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55720806121826</t>
+    <t xml:space="preserve">5.51175165176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57308149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5398907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5572075843811</t>
   </si>
   <si>
     <t xml:space="preserve">5.73398208618164</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">5.68131017684937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71017122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75418472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83427476882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72604513168335</t>
+    <t xml:space="preserve">5.71017169952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75418424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83427429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72604465484619</t>
   </si>
   <si>
     <t xml:space="preserve">5.86024856567383</t>
@@ -3002,25 +3002,25 @@
     <t xml:space="preserve">5.9547700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08031511306763</t>
+    <t xml:space="preserve">6.08031558990479</t>
   </si>
   <si>
     <t xml:space="preserve">6.12669563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13258600234985</t>
+    <t xml:space="preserve">6.1325855255127</t>
   </si>
   <si>
     <t xml:space="preserve">6.03246212005615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98828983306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84841060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83147764205933</t>
+    <t xml:space="preserve">5.98828935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84841012954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83147811889648</t>
   </si>
   <si>
     <t xml:space="preserve">5.81601762771606</t>
@@ -3032,133 +3032,133 @@
     <t xml:space="preserve">5.69601631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69012689590454</t>
+    <t xml:space="preserve">5.69012641906738</t>
   </si>
   <si>
     <t xml:space="preserve">5.78362464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79319524765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7666916847229</t>
+    <t xml:space="preserve">5.79319477081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76669311523438</t>
   </si>
   <si>
     <t xml:space="preserve">5.69086313247681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75344085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79025030136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86313438415527</t>
+    <t xml:space="preserve">5.75344038009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86313581466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.97062015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89552783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8049750328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74828624725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73356246948242</t>
+    <t xml:space="preserve">5.89552736282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80497455596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74828720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73356294631958</t>
   </si>
   <si>
     <t xml:space="preserve">5.70926809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69159936904907</t>
+    <t xml:space="preserve">5.69159841537476</t>
   </si>
   <si>
     <t xml:space="preserve">5.79098701477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7453408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60767126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62460470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58705806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52448034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58043241500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45674991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59000205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50165843963623</t>
+    <t xml:space="preserve">5.74534225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74092483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60767221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62460422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58705902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52448081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63049411773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58043193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4567494392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50165748596191</t>
   </si>
   <si>
     <t xml:space="preserve">5.63270282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5981011390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63932847976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56644487380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61650562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5767502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43319129943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34411001205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38975429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49208688735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42582893371582</t>
+    <t xml:space="preserve">5.59810066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63932752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5664439201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61650609970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57675075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43319177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46263980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38975524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49208736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42582941055298</t>
   </si>
   <si>
     <t xml:space="preserve">5.40006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48325347900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52153635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46116781234741</t>
+    <t xml:space="preserve">5.48325252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52153539657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4611668586731</t>
   </si>
   <si>
     <t xml:space="preserve">5.4979772567749</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">5.59221124649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5561375617981</t>
+    <t xml:space="preserve">5.55613660812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.53920459747314</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">5.6592059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67761135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49429559707642</t>
+    <t xml:space="preserve">5.67761039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49429607391357</t>
   </si>
   <si>
     <t xml:space="preserve">5.5414137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49871397018433</t>
+    <t xml:space="preserve">5.49871301651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.58190441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53257894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48472547531128</t>
+    <t xml:space="preserve">5.53257942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48472499847412</t>
   </si>
   <si>
     <t xml:space="preserve">5.57233333587646</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">5.4442343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11662340164185</t>
+    <t xml:space="preserve">5.11662244796753</t>
   </si>
   <si>
     <t xml:space="preserve">5.10705184936523</t>
@@ -3218,31 +3218,31 @@
     <t xml:space="preserve">5.03122329711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312696456909</t>
+    <t xml:space="preserve">5.14312648773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.31318950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42435693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60325479507446</t>
+    <t xml:space="preserve">5.42435646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60325527191162</t>
   </si>
   <si>
     <t xml:space="preserve">5.92718410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92423963546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04571437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94853401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90436315536499</t>
+    <t xml:space="preserve">5.92424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04571390151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94853448867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90436267852783</t>
   </si>
   <si>
     <t xml:space="preserve">5.95516014099121</t>
@@ -3251,43 +3251,43 @@
     <t xml:space="preserve">5.97209310531616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9794545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01037549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0611743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19737195968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24817037582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23565530776978</t>
+    <t xml:space="preserve">5.97945499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01037502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06117343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1973729133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24816989898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23565435409546</t>
   </si>
   <si>
     <t xml:space="preserve">6.25921249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.162034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522411346436</t>
+    <t xml:space="preserve">6.16203355789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1252236366272</t>
   </si>
   <si>
     <t xml:space="preserve">6.09724760055542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04129695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0228910446167</t>
+    <t xml:space="preserve">6.04350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04129648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02289056777954</t>
   </si>
   <si>
     <t xml:space="preserve">6.00743055343628</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">6.00890350341797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01700162887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94190883636475</t>
+    <t xml:space="preserve">6.01700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9419093132019</t>
   </si>
   <si>
     <t xml:space="preserve">6.0891489982605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14362859725952</t>
+    <t xml:space="preserve">6.14362907409668</t>
   </si>
   <si>
     <t xml:space="preserve">6.09283065795898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22608327865601</t>
+    <t xml:space="preserve">6.22608375549316</t>
   </si>
   <si>
     <t xml:space="preserve">6.18043947219849</t>
@@ -3332,28 +3332,28 @@
     <t xml:space="preserve">6.57357215881348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46167039871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58019733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58756017684937</t>
+    <t xml:space="preserve">6.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58019781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58755970001221</t>
   </si>
   <si>
     <t xml:space="preserve">6.48081064224243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57062816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50289630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52203798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44768571853638</t>
+    <t xml:space="preserve">6.57062721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50289726257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52203845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44768524169922</t>
   </si>
   <si>
     <t xml:space="preserve">6.43942356109619</t>
@@ -3368,73 +3368,73 @@
     <t xml:space="preserve">6.26743507385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.259925365448</t>
+    <t xml:space="preserve">6.25992488861084</t>
   </si>
   <si>
     <t xml:space="preserve">6.3087420463562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18932771682739</t>
+    <t xml:space="preserve">6.18932723999023</t>
   </si>
   <si>
     <t xml:space="preserve">6.30949306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15177536010742</t>
+    <t xml:space="preserve">6.15177440643311</t>
   </si>
   <si>
     <t xml:space="preserve">6.17430591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15853452682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42290115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42590427398682</t>
+    <t xml:space="preserve">6.15853404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42290067672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42590475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.3440408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38384675979614</t>
+    <t xml:space="preserve">6.38384580612183</t>
   </si>
   <si>
     <t xml:space="preserve">6.22162246704102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24715709686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35530614852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35981273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35756015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2358922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15553092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06615591049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99105215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94824314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88815927505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89116334915161</t>
+    <t xml:space="preserve">6.24715757369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35530662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35981369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35756063461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23589181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15552997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06615686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99105167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94824361801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88815975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89116382598877</t>
   </si>
   <si>
     <t xml:space="preserve">5.96852111816406</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">5.85962009429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7274374961853</t>
+    <t xml:space="preserve">5.72743701934814</t>
   </si>
   <si>
     <t xml:space="preserve">5.89041328430176</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">5.91294431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07141351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08568382263184</t>
+    <t xml:space="preserve">6.07141256332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08568286895752</t>
   </si>
   <si>
     <t xml:space="preserve">6.16979932785034</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">6.25316572189331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19984197616577</t>
+    <t xml:space="preserve">6.19984149932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.14426422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18707466125488</t>
+    <t xml:space="preserve">6.18707418441772</t>
   </si>
   <si>
     <t xml:space="preserve">6.12999486923218</t>
@@ -3479,22 +3479,22 @@
     <t xml:space="preserve">6.05639266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2381443977356</t>
+    <t xml:space="preserve">6.23814487457275</t>
   </si>
   <si>
     <t xml:space="preserve">6.25166320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32826900482178</t>
+    <t xml:space="preserve">6.32826948165894</t>
   </si>
   <si>
     <t xml:space="preserve">6.34028625488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32902002334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38910341262817</t>
+    <t xml:space="preserve">6.32902050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38910436630249</t>
   </si>
   <si>
     <t xml:space="preserve">6.33352613449097</t>
@@ -3506,67 +3506,67 @@
     <t xml:space="preserve">6.33502912521362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42440223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44843626022339</t>
+    <t xml:space="preserve">6.42440271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44843673706055</t>
   </si>
   <si>
     <t xml:space="preserve">6.49725389480591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44393014907837</t>
+    <t xml:space="preserve">6.45444345474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44392967224121</t>
   </si>
   <si>
     <t xml:space="preserve">6.47472286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39060544967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44468212127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50326156616211</t>
+    <t xml:space="preserve">6.39060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44468116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50326299667358</t>
   </si>
   <si>
     <t xml:space="preserve">6.50551462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4251537322998</t>
+    <t xml:space="preserve">6.42515325546265</t>
   </si>
   <si>
     <t xml:space="preserve">6.37408351898193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54757452011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56034231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34479188919067</t>
+    <t xml:space="preserve">6.54757404327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56034135818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4889931678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34479236602783</t>
   </si>
   <si>
     <t xml:space="preserve">6.26217842102051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20885515213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27569627761841</t>
+    <t xml:space="preserve">6.20885467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27569675445557</t>
   </si>
   <si>
     <t xml:space="preserve">6.16304111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22537660598755</t>
+    <t xml:space="preserve">6.22537612915039</t>
   </si>
   <si>
     <t xml:space="preserve">6.20960426330566</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">6.16153907775879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12623882293701</t>
+    <t xml:space="preserve">6.12623929977417</t>
   </si>
   <si>
     <t xml:space="preserve">6.10445976257324</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">6.06390333175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1495213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12774229049683</t>
+    <t xml:space="preserve">6.14952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12774181365967</t>
   </si>
   <si>
     <t xml:space="preserve">6.13374948501587</t>
@@ -3611,31 +3611,31 @@
     <t xml:space="preserve">6.11572456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05038404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.994056224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92721271514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95650482177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01057958602905</t>
+    <t xml:space="preserve">6.05038452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99405670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92721366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95650434494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01057910919189</t>
   </si>
   <si>
     <t xml:space="preserve">6.01733922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01808929443359</t>
+    <t xml:space="preserve">6.01808881759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.97903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02484893798828</t>
+    <t xml:space="preserve">6.02484941482544</t>
   </si>
   <si>
     <t xml:space="preserve">6.08493280410767</t>
@@ -3644,16 +3644,16 @@
     <t xml:space="preserve">6.06840896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16829776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0676589012146</t>
+    <t xml:space="preserve">6.16829824447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06765842437744</t>
   </si>
   <si>
     <t xml:space="preserve">6.04888200759888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09845113754272</t>
+    <t xml:space="preserve">6.09845066070557</t>
   </si>
   <si>
     <t xml:space="preserve">6.08943843841553</t>
@@ -3662,79 +3662,79 @@
     <t xml:space="preserve">5.98654651641846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03386116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01508617401123</t>
+    <t xml:space="preserve">6.03386068344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01508569717407</t>
   </si>
   <si>
     <t xml:space="preserve">5.98879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03686571121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88215160369873</t>
+    <t xml:space="preserve">6.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88215112686157</t>
   </si>
   <si>
     <t xml:space="preserve">5.89491939544678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8964204788208</t>
+    <t xml:space="preserve">5.89642143249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.93772888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96401500701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92045450210571</t>
+    <t xml:space="preserve">5.96401453018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92045402526855</t>
   </si>
   <si>
     <t xml:space="preserve">5.95124673843384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489158630371</t>
+    <t xml:space="preserve">6.05489110946655</t>
   </si>
   <si>
     <t xml:space="preserve">6.05188655853271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02635145187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95725584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01583671569824</t>
+    <t xml:space="preserve">6.02635097503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95725536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01583623886108</t>
   </si>
   <si>
     <t xml:space="preserve">5.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85135555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.002769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11575412750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1872353553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21106147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11959743499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.191077709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16033363342285</t>
+    <t xml:space="preserve">5.8513560295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00277090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1157546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18723487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21106195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11959791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19107723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16033411026001</t>
   </si>
   <si>
     <t xml:space="preserve">5.97971248626709</t>
@@ -3752,19 +3752,19 @@
     <t xml:space="preserve">5.95819139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99354696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98586130142212</t>
+    <t xml:space="preserve">5.96357202529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9935474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98586177825928</t>
   </si>
   <si>
     <t xml:space="preserve">6.02044820785522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02890253067017</t>
+    <t xml:space="preserve">6.02890300750732</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348991394043</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">6.03120899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97740697860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03735733032227</t>
+    <t xml:space="preserve">5.97740602493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03735780715942</t>
   </si>
   <si>
     <t xml:space="preserve">6.08885335922241</t>
@@ -3788,49 +3788,49 @@
     <t xml:space="preserve">6.0196795463562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96510982513428</t>
+    <t xml:space="preserve">5.96510934829712</t>
   </si>
   <si>
     <t xml:space="preserve">5.9013147354126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90208387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95511722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93129110336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99815797805786</t>
+    <t xml:space="preserve">5.90208435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95511770248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93129062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99815893173218</t>
   </si>
   <si>
     <t xml:space="preserve">5.93513345718384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92975378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83367872238159</t>
+    <t xml:space="preserve">5.92975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83367824554443</t>
   </si>
   <si>
     <t xml:space="preserve">5.77833938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78756332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7637357711792</t>
+    <t xml:space="preserve">5.78756237030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66842985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76373529434204</t>
   </si>
   <si>
     <t xml:space="preserve">5.71454524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39941883087158</t>
+    <t xml:space="preserve">5.39941930770874</t>
   </si>
   <si>
     <t xml:space="preserve">5.38097286224365</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">5.30257558822632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33408784866333</t>
+    <t xml:space="preserve">5.33408832550049</t>
   </si>
   <si>
     <t xml:space="preserve">5.44092321395874</t>
@@ -3854,34 +3854,34 @@
     <t xml:space="preserve">5.39403867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33946895599365</t>
+    <t xml:space="preserve">5.33946847915649</t>
   </si>
   <si>
     <t xml:space="preserve">5.25492238998413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22110414505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11196231842041</t>
+    <t xml:space="preserve">5.22110366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11196279525757</t>
   </si>
   <si>
     <t xml:space="preserve">5.17191362380981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17883062362671</t>
+    <t xml:space="preserve">5.17883110046387</t>
   </si>
   <si>
     <t xml:space="preserve">5.17114496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30565023422241</t>
+    <t xml:space="preserve">5.30564975738525</t>
   </si>
   <si>
     <t xml:space="preserve">5.31794786453247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1865177154541</t>
+    <t xml:space="preserve">5.18651723861694</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958353042603</t>
@@ -3890,25 +3890,25 @@
     <t xml:space="preserve">5.24954175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30795574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44246053695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54161024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51317119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47781658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42708873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49165105819702</t>
+    <t xml:space="preserve">5.30795621871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44246101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54160976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51317167282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47781705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42708826065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">5.5462212562561</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">5.56159400939941</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59925556182861</t>
+    <t xml:space="preserve">5.59925508499146</t>
   </si>
   <si>
     <t xml:space="preserve">5.55775022506714</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">5.60617303848267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5300817489624</t>
+    <t xml:space="preserve">5.53008127212524</t>
   </si>
   <si>
     <t xml:space="preserve">5.45245218276978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50318002700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45629549026489</t>
+    <t xml:space="preserve">5.5031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45629501342773</t>
   </si>
   <si>
     <t xml:space="preserve">5.49549436569214</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">5.44707250595093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4324688911438</t>
+    <t xml:space="preserve">5.43246841430664</t>
   </si>
   <si>
     <t xml:space="preserve">5.41248512268066</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">5.30872392654419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41479110717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49472618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23878145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21802949905396</t>
+    <t xml:space="preserve">5.41479063034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49472570419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21802997589111</t>
   </si>
   <si>
     <t xml:space="preserve">5.15500450134277</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">5.19189691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06507730484009</t>
+    <t xml:space="preserve">5.0650782585144</t>
   </si>
   <si>
     <t xml:space="preserve">5.01588726043701</t>
@@ -3998,19 +3998,19 @@
     <t xml:space="preserve">5.23493814468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039348602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1511607170105</t>
+    <t xml:space="preserve">5.15039253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15116119384766</t>
   </si>
   <si>
     <t xml:space="preserve">5.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07583808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09274768829346</t>
+    <t xml:space="preserve">5.0758376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0927472114563</t>
   </si>
   <si>
     <t xml:space="preserve">5.1473183631897</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">5.18497896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1134991645813</t>
+    <t xml:space="preserve">5.11349964141846</t>
   </si>
   <si>
     <t xml:space="preserve">5.25338459014893</t>
@@ -4031,28 +4031,28 @@
     <t xml:space="preserve">5.2848973274231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31564235687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32486438751221</t>
+    <t xml:space="preserve">5.31564140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32486486434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.40787363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38789033889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4155592918396</t>
+    <t xml:space="preserve">5.38788986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41555976867676</t>
   </si>
   <si>
     <t xml:space="preserve">5.51240301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47243547439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34100484848022</t>
+    <t xml:space="preserve">5.47243595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34100437164307</t>
   </si>
   <si>
     <t xml:space="preserve">5.31026077270508</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">5.32025241851807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35022830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23186445236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27490615844727</t>
+    <t xml:space="preserve">5.35022783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2318639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27490568161011</t>
   </si>
   <si>
     <t xml:space="preserve">5.38250923156738</t>
@@ -4085,19 +4085,19 @@
     <t xml:space="preserve">5.26766920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41546535491943</t>
+    <t xml:space="preserve">5.26845979690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41546487808228</t>
   </si>
   <si>
     <t xml:space="preserve">5.33643007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35934972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41704559326172</t>
+    <t xml:space="preserve">5.35935020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41704511642456</t>
   </si>
   <si>
     <t xml:space="preserve">5.41309309005737</t>
@@ -4106,22 +4106,22 @@
     <t xml:space="preserve">5.35776901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24712085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08272790908813</t>
+    <t xml:space="preserve">5.24712038040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08272838592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.00369310379028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11908435821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08351898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05348587036133</t>
+    <t xml:space="preserve">5.11908483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08351850509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05348539352417</t>
   </si>
   <si>
     <t xml:space="preserve">4.99499988555908</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">5.14516592025757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12303590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08588981628418</t>
+    <t xml:space="preserve">5.12303638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08588886260986</t>
   </si>
   <si>
     <t xml:space="preserve">4.97603130340576</t>
@@ -4145,19 +4145,19 @@
     <t xml:space="preserve">5.01396751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99025774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89383506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17598915100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21550703048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87960815429688</t>
+    <t xml:space="preserve">4.99025821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89383459091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17598867416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2155065536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87960863113403</t>
   </si>
   <si>
     <t xml:space="preserve">4.87644720077515</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">4.70652198791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48127412796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39512538909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52237129211426</t>
+    <t xml:space="preserve">4.48127365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52237176895142</t>
   </si>
   <si>
     <t xml:space="preserve">4.7729115486145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53580713272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52711343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59903478622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60456800460815</t>
+    <t xml:space="preserve">4.53580760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5271143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59903526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.604567527771</t>
   </si>
   <si>
     <t xml:space="preserve">4.60298681259155</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">4.51209688186646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56030797958374</t>
+    <t xml:space="preserve">4.5603084564209</t>
   </si>
   <si>
     <t xml:space="preserve">4.64566516876221</t>
@@ -4214,40 +4214,40 @@
     <t xml:space="preserve">4.80294561386108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8187518119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82428455352783</t>
+    <t xml:space="preserve">4.81875228881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79583215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82428407669067</t>
   </si>
   <si>
     <t xml:space="preserve">4.82902669906616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92544794082642</t>
+    <t xml:space="preserve">4.92544841766357</t>
   </si>
   <si>
     <t xml:space="preserve">4.90648078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87486696243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98709630966187</t>
+    <t xml:space="preserve">4.87486743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98709583282471</t>
   </si>
   <si>
     <t xml:space="preserve">4.96891784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89857721328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90173816680908</t>
+    <t xml:space="preserve">4.93809413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8985767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90173864364624</t>
   </si>
   <si>
     <t xml:space="preserve">4.88514137268066</t>
@@ -4256,19 +4256,19 @@
     <t xml:space="preserve">4.87249565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75236320495605</t>
+    <t xml:space="preserve">4.75236225128174</t>
   </si>
   <si>
     <t xml:space="preserve">4.82349443435669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81558990478516</t>
+    <t xml:space="preserve">4.81559038162231</t>
   </si>
   <si>
     <t xml:space="preserve">4.79978370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91596460342407</t>
+    <t xml:space="preserve">4.91596412658691</t>
   </si>
   <si>
     <t xml:space="preserve">4.91438388824463</t>
@@ -4286,16 +4286,16 @@
     <t xml:space="preserve">4.78555727005005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74841117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64171361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61721324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72628116607666</t>
+    <t xml:space="preserve">4.74841070175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64171409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61721277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7262806892395</t>
   </si>
   <si>
     <t xml:space="preserve">4.6140513420105</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">4.69308710098267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69150543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83930158615112</t>
+    <t xml:space="preserve">4.69150590896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83930110931396</t>
   </si>
   <si>
     <t xml:space="preserve">4.84720420837402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84641456604004</t>
+    <t xml:space="preserve">4.84641408920288</t>
   </si>
   <si>
     <t xml:space="preserve">4.88751268386841</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">4.70573282241821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66700553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76500797271729</t>
+    <t xml:space="preserve">4.66700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76500844955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.73260354995728</t>
@@ -4355,13 +4355,13 @@
     <t xml:space="preserve">4.62037467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52790355682373</t>
+    <t xml:space="preserve">4.52790403366089</t>
   </si>
   <si>
     <t xml:space="preserve">4.33189725875854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25839471817017</t>
+    <t xml:space="preserve">4.25839424133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.21492576599121</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">4.31925201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22915172576904</t>
+    <t xml:space="preserve">4.2291522026062</t>
   </si>
   <si>
     <t xml:space="preserve">4.2852668762207</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">4.35718870162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27499198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32794523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26945972442627</t>
+    <t xml:space="preserve">4.2749924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32794570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26945924758911</t>
   </si>
   <si>
     <t xml:space="preserve">4.1256160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19911956787109</t>
+    <t xml:space="preserve">4.19911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">4.17382764816284</t>
@@ -4427,19 +4427,19 @@
     <t xml:space="preserve">4.0924220085144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05211448669434</t>
+    <t xml:space="preserve">4.05211400985718</t>
   </si>
   <si>
     <t xml:space="preserve">3.82133293151855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95173978805542</t>
+    <t xml:space="preserve">3.95174026489258</t>
   </si>
   <si>
     <t xml:space="preserve">4.0330753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606624603271</t>
+    <t xml:space="preserve">4.08606576919556</t>
   </si>
   <si>
     <t xml:space="preserve">3.95831227302551</t>
@@ -4448,25 +4448,25 @@
     <t xml:space="preserve">3.90080332756042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88108515739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90244555473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89053320884705</t>
+    <t xml:space="preserve">3.88108563423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90244603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89053273200989</t>
   </si>
   <si>
     <t xml:space="preserve">3.88683652877808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93818426132202</t>
+    <t xml:space="preserve">3.93818473815918</t>
   </si>
   <si>
     <t xml:space="preserve">4.06922435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9961051940918</t>
+    <t xml:space="preserve">3.99610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.0051417350769</t>
@@ -4475,43 +4475,43 @@
     <t xml:space="preserve">4.03636169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06758117675781</t>
+    <t xml:space="preserve">4.06758165359497</t>
   </si>
   <si>
     <t xml:space="preserve">4.13412809371948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11441040039062</t>
+    <t xml:space="preserve">4.11440992355347</t>
   </si>
   <si>
     <t xml:space="preserve">4.09756851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10783767700195</t>
+    <t xml:space="preserve">4.10783815383911</t>
   </si>
   <si>
     <t xml:space="preserve">4.13659286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19163751602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18753004074097</t>
+    <t xml:space="preserve">4.19163799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18752956390381</t>
   </si>
   <si>
     <t xml:space="preserve">4.18342256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11030244827271</t>
+    <t xml:space="preserve">4.11030197143555</t>
   </si>
   <si>
     <t xml:space="preserve">4.05443620681763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05854368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06265163421631</t>
+    <t xml:space="preserve">4.05854320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06265211105347</t>
   </si>
   <si>
     <t xml:space="preserve">4.06347417831421</t>
@@ -4523,13 +4523,13 @@
     <t xml:space="preserve">3.94640040397644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95461511611938</t>
+    <t xml:space="preserve">3.95461559295654</t>
   </si>
   <si>
     <t xml:space="preserve">3.857670545578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81412744522095</t>
+    <t xml:space="preserve">3.81412720680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.90614318847656</t>
@@ -4553,13 +4553,13 @@
     <t xml:space="preserve">4.10085439682007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06593799591064</t>
+    <t xml:space="preserve">4.06593751907349</t>
   </si>
   <si>
     <t xml:space="preserve">4.04211235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02321672439575</t>
+    <t xml:space="preserve">4.02321624755859</t>
   </si>
   <si>
     <t xml:space="preserve">4.0417013168335</t>
@@ -4568,13 +4568,13 @@
     <t xml:space="preserve">4.05073833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97679781913757</t>
+    <t xml:space="preserve">3.97679829597473</t>
   </si>
   <si>
     <t xml:space="preserve">3.98419213294983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97186803817749</t>
+    <t xml:space="preserve">3.97186851501465</t>
   </si>
   <si>
     <t xml:space="preserve">3.81535983085632</t>
@@ -4592,28 +4592,28 @@
     <t xml:space="preserve">3.49001932144165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47030115127563</t>
+    <t xml:space="preserve">3.47030162811279</t>
   </si>
   <si>
     <t xml:space="preserve">3.57957005500793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66706728935242</t>
+    <t xml:space="preserve">3.66706705093384</t>
   </si>
   <si>
     <t xml:space="preserve">3.55040407180786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42593693733215</t>
+    <t xml:space="preserve">3.42593669891357</t>
   </si>
   <si>
     <t xml:space="preserve">3.38609099388123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44154644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34870958328247</t>
+    <t xml:space="preserve">3.44154691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">3.28873491287231</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">3.46290731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49823451042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51918482780457</t>
+    <t xml:space="preserve">3.49823474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51918530464172</t>
   </si>
   <si>
     <t xml:space="preserve">3.48426818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44606518745422</t>
+    <t xml:space="preserve">3.44606494903564</t>
   </si>
   <si>
     <t xml:space="preserve">3.52740025520325</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">3.59764456748962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60257387161255</t>
+    <t xml:space="preserve">3.60257411003113</t>
   </si>
   <si>
     <t xml:space="preserve">3.71512842178345</t>
@@ -4655,25 +4655,25 @@
     <t xml:space="preserve">3.67405080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71266436576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72950649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77304911613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7578501701355</t>
+    <t xml:space="preserve">3.71266388893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72950601577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7730495929718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75784969329834</t>
   </si>
   <si>
     <t xml:space="preserve">3.84452533721924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89217638969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93037939071655</t>
+    <t xml:space="preserve">3.89217686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93037986755371</t>
   </si>
   <si>
     <t xml:space="preserve">3.95913362503052</t>
@@ -4682,16 +4682,16 @@
     <t xml:space="preserve">4.11605405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14727258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17274188995361</t>
+    <t xml:space="preserve">4.14727306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17274141311646</t>
   </si>
   <si>
     <t xml:space="preserve">4.1982102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22203636169434</t>
+    <t xml:space="preserve">4.22203588485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.23682451248169</t>
@@ -4712,13 +4712,13 @@
     <t xml:space="preserve">4.16534805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19492435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21792793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31322956085205</t>
+    <t xml:space="preserve">4.19492387771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2179274559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31322908401489</t>
   </si>
   <si>
     <t xml:space="preserve">4.32719659805298</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">4.2705078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31158685684204</t>
+    <t xml:space="preserve">4.3115873336792</t>
   </si>
   <si>
     <t xml:space="preserve">4.31487226486206</t>
@@ -4751,13 +4751,13 @@
     <t xml:space="preserve">4.1530237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14891672134399</t>
+    <t xml:space="preserve">4.14891624450684</t>
   </si>
   <si>
     <t xml:space="preserve">4.14563035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14645147323608</t>
+    <t xml:space="preserve">4.14645195007324</t>
   </si>
   <si>
     <t xml:space="preserve">4.21464157104492</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">4.17192077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14809465408325</t>
+    <t xml:space="preserve">4.14809417724609</t>
   </si>
   <si>
     <t xml:space="preserve">4.13248491287231</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">4.50794124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50054740905762</t>
+    <t xml:space="preserve">4.50054693222046</t>
   </si>
   <si>
     <t xml:space="preserve">4.6016001701355</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">4.59995651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54819774627686</t>
+    <t xml:space="preserve">4.54819822311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.62542581558228</t>
@@ -6822,6 +6822,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.00500011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73200035095215</t>
   </si>
 </sst>
 </file>
@@ -72498,7 +72501,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6927430556</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>20482894</v>
@@ -72519,6 +72522,32 @@
         <v>2269</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6918518519</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>24135087</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>8.94600009918213</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>8.73200035095215</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>8.94600009918213</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>8.73200035095215</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENEL.MI.xlsx
+++ b/data/ENEL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="2272">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,40 +44,40 @@
     <t xml:space="preserve">ENEL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27958250045776</t>
+    <t xml:space="preserve">2.27958273887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.22277069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23223924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21448493003845</t>
+    <t xml:space="preserve">2.23223876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21448516845703</t>
   </si>
   <si>
     <t xml:space="preserve">2.21685242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20146584510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23460626602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21211791038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1718761920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13281846046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15767335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09257650375366</t>
+    <t xml:space="preserve">2.20146608352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23460602760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21211814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17187666893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1328182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15767359733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09257626533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.16004061698914</t>
@@ -89,67 +89,67 @@
     <t xml:space="preserve">2.19436430931091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22513794898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25236010551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987222671509</t>
+    <t xml:space="preserve">2.22513747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25235939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17306017875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987198829651</t>
   </si>
   <si>
     <t xml:space="preserve">2.22395372390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19081354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14702105522156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09849405288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07008790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06772065162659</t>
+    <t xml:space="preserve">2.19081377983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14702153205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09849429130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07008814811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06772112846375</t>
   </si>
   <si>
     <t xml:space="preserve">2.0866584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01090884208679</t>
+    <t xml:space="preserve">2.01090836524963</t>
   </si>
   <si>
     <t xml:space="preserve">2.09375977516174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1647744178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15057182312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15648984909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14228653907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15293908119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09494376182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18016171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19199705123901</t>
+    <t xml:space="preserve">2.16477465629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15057158470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.156489610672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14228630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15293860435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0949432849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18016147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19199776649475</t>
   </si>
   <si>
     <t xml:space="preserve">2.21330165863037</t>
@@ -158,121 +158,121 @@
     <t xml:space="preserve">2.19791507720947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16714191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17542719841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24170804023743</t>
+    <t xml:space="preserve">2.1671416759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17542743682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24170780181885</t>
   </si>
   <si>
     <t xml:space="preserve">2.25354361534119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3150897026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30798840522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30207085609436</t>
+    <t xml:space="preserve">2.31508994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30798864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30207061767578</t>
   </si>
   <si>
     <t xml:space="preserve">2.30562114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32574248313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3174569606781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31153893470764</t>
+    <t xml:space="preserve">2.32574224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31982445716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31153917312622</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088710784912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3139066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35059714317322</t>
+    <t xml:space="preserve">2.31390619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35059809684753</t>
   </si>
   <si>
     <t xml:space="preserve">2.36716771125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30680465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29496908187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27366495132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20738387107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16595864295959</t>
+    <t xml:space="preserve">2.306804895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29496932029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27366471290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20738363265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16595816612244</t>
   </si>
   <si>
     <t xml:space="preserve">2.22632145881653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23578953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21921968460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26182818412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27129769325256</t>
+    <t xml:space="preserve">2.23578977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21921992301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26182866096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27129721641541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32337498664856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2961528301239</t>
+    <t xml:space="preserve">2.29615259170532</t>
   </si>
   <si>
     <t xml:space="preserve">2.3576991558075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39912462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231233596802</t>
+    <t xml:space="preserve">2.39912438392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231209754944</t>
   </si>
   <si>
     <t xml:space="preserve">2.34112882614136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32929301261902</t>
+    <t xml:space="preserve">2.3292932510376</t>
   </si>
   <si>
     <t xml:space="preserve">2.3091721534729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34941411018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37071847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37663698196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33757877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35296487808228</t>
+    <t xml:space="preserve">2.34941434860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37071871757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37663602828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33757781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3529646396637</t>
   </si>
   <si>
     <t xml:space="preserve">2.33166027069092</t>
@@ -281,37 +281,37 @@
     <t xml:space="preserve">2.36124968528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3399453163147</t>
+    <t xml:space="preserve">2.33994555473328</t>
   </si>
   <si>
     <t xml:space="preserve">2.40385890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42989754676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42516326904297</t>
+    <t xml:space="preserve">2.41096043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42989778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42516350746155</t>
   </si>
   <si>
     <t xml:space="preserve">2.43699908256531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38965582847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39794087409973</t>
+    <t xml:space="preserve">2.38965606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39794063568115</t>
   </si>
   <si>
     <t xml:space="preserve">2.37782001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43463206291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44173359870911</t>
+    <t xml:space="preserve">2.43463182449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44173336029053</t>
   </si>
   <si>
     <t xml:space="preserve">2.43936657905579</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">2.35651564598083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31864094734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2783989906311</t>
+    <t xml:space="preserve">2.31864070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27839922904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.37900376319885</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.43817043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44433355331421</t>
+    <t xml:space="preserve">2.44433379173279</t>
   </si>
   <si>
     <t xml:space="preserve">2.4073543548584</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.46652126312256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21875953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21013140678406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30627703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40365648269653</t>
+    <t xml:space="preserve">2.21876001358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21013116836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30627727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40365672111511</t>
   </si>
   <si>
     <t xml:space="preserve">2.45296192169189</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">2.39256238937378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37653803825378</t>
+    <t xml:space="preserve">2.37653851509094</t>
   </si>
   <si>
     <t xml:space="preserve">2.42214632034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43940305709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45912528038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46035814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46282339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44679927825928</t>
+    <t xml:space="preserve">2.43940281867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45912551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4603579044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46282362937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44679951667786</t>
   </si>
   <si>
     <t xml:space="preserve">2.48008036613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48254561424255</t>
+    <t xml:space="preserve">2.4825451374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.47638249397278</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">2.47268438339233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53801488876343</t>
+    <t xml:space="preserve">2.53801441192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.52568817138672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49240732192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48131322860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49117422103882</t>
+    <t xml:space="preserve">2.49240708351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4813129901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49117398262024</t>
   </si>
   <si>
     <t xml:space="preserve">2.52322292327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5108962059021</t>
+    <t xml:space="preserve">2.51089668273926</t>
   </si>
   <si>
     <t xml:space="preserve">2.50350069999695</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">2.49856996536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53308415412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52938628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47021913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42461156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42707681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39749360084534</t>
+    <t xml:space="preserve">2.53308463096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52938604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47021889686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42461085319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42707705497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39749336242676</t>
   </si>
   <si>
     <t xml:space="preserve">2.40242385864258</t>
@@ -449,88 +449,88 @@
     <t xml:space="preserve">2.42830920219421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42954206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43570518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45172953605652</t>
+    <t xml:space="preserve">2.42954182624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43570494651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45172929763794</t>
   </si>
   <si>
     <t xml:space="preserve">2.41351723670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43200707435608</t>
+    <t xml:space="preserve">2.43200755119324</t>
   </si>
   <si>
     <t xml:space="preserve">2.48747658729553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48994135856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54541063308716</t>
+    <t xml:space="preserve">2.48994183540344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54541015625</t>
   </si>
   <si>
     <t xml:space="preserve">2.5306191444397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49610495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44556665420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41105151176453</t>
+    <t xml:space="preserve">2.49610471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44556641578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41105222702026</t>
   </si>
   <si>
     <t xml:space="preserve">2.41475009918213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3913300037384</t>
+    <t xml:space="preserve">2.39132976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.41968107223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4480311870575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4172158241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42091345787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44926452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41228485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37284016609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35928153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32476687431335</t>
+    <t xml:space="preserve">2.40981936454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44803214073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41721558570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4209132194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44926404953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41228532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35928106307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32476711273193</t>
   </si>
   <si>
     <t xml:space="preserve">2.36051392555237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3383264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31983637809753</t>
+    <t xml:space="preserve">2.33832621574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31983685493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36421179771423</t>
@@ -539,28 +539,28 @@
     <t xml:space="preserve">2.35435056686401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43693804740906</t>
+    <t xml:space="preserve">2.43693828582764</t>
   </si>
   <si>
     <t xml:space="preserve">2.40858721733093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4307746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41598296165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37037467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36297965049744</t>
+    <t xml:space="preserve">2.43